--- a/nm-reference/citations.xlsx
+++ b/nm-reference/citations.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +48,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -31106,6 +31109,9 @@
           <t>10.21097/ksw.2026.5.21.2.105</t>
         </is>
       </c>
+      <c r="G542" s="1" t="n">
+        <v>46204</v>
+      </c>
       <c r="H542" t="inlineStr">
         <is>
           <t>본 연구의 목적은 키워드 네트워크 분석과 토픽모델링을 활용하여 청년 1인가구를 주제로 한 국내 학술 연구의 동향을 체계적으로 분석하는 것이다. 이를 위해 NetMiner 4.5.1의 확장 프로그램인 Biblio Data Collector(이하 BDC)를 통해 수집한 논문 95편을 대상으로 키워드 빈도분석, 동시출현 빈도분석, 중심성 분석, 토픽모델링을 수행하였다. 연구의 결과 첫째, 빈도분석에서는 우울, 주거환경, 소득, 공유주택, 외로움 순으로 높은 빈도를 보였다. 둘째, 동시출현 빈도분석에서는 라이프스타일-삶의 만족도이 가장 높은 동시출현 빈도를 보였다. 셋째, 중심성 분석에서는 우울과 주거환경이 연결·근접·매개중심성 모두에서 1, 2위를 차지하여 연구 네트워크의 핵심 허브 역할을 담당하고 있음이 확인되었다. 넷째, 토픽모델링 분석에서는 정신건강과 심리적 특성, 일상생활과 사회적 지지, 사회적 고립과 심리적 위기, 외로움과 사회적 자원 부족, 코로나19 전후 생활 변화와 건강, 대안적 주거 환경과 주거 만족의 6개 토픽이 도출되었다. 본 연구의 결과는 청년 1인가구 후속 연구를 위한 기초자료를 제공하고, 청년 1인가구를 위한 정책 마련에 기여할 것으로 보인다.</t>
@@ -31155,6 +31161,9 @@
       <c r="E543" t="n">
         <v>2026</v>
       </c>
+      <c r="G543" s="1" t="n">
+        <v>46204</v>
+      </c>
       <c r="H543" t="inlineStr">
         <is>
           <t>본 연구는 최근 10년간 국내 아동 구강건강 관련 연구를 대상으로 텍스트 네트워크 분석을 수행하여 주요 연구 주제와 지식 구조를 규명하고자 하였다. 연구대상은 학술연구정보서비스에서 아동과 구강을 검색어로 하여 최근 10년, KCI 등재, 한국어, 원문 제공 조건을 충족하는 44편의 논문이다. 수집된 논문의 키워드를 정제한 후 NetMiner 4 프로그램을 활용하여 키워드 빈도분석, 연결중심성 분석, 네트워크 군집분석을 수행하였다. 연구결과, 키워드 빈도분석에서는 아동, 구강건강이 가장 높은 빈도로 나타났고, 구강건강조사, 치아우식증, 칫솔질, 구강운동기능 등이 주요 키워드로 확인되었다. 연결중심성 분석에서는 아동, 구강건강, 치아우식증, 구강건강행동, 부모가 핵심 노드로 나타나 아동 구강건강 연구가 질병, 행동, 보호자 요인을 중심으로 전개되고 있음을 확인하였다. 군집분석 결과, 연구 주제는 치아우식증 및 구강질환, 구강건강행동 및 부모 요인, 장애 아동 구강기능·중재, 구강보건교육 예방·관리의 네 가지 영역으로 구조화되었다. 한편 디지털 헬스케어 및 인공지능 관련 키워드는 주요 네트워크에서 명확하게 확인되지 않아 해당 분야 연구가 제한적인 것으로 확인되었다. 본 연구는 국내 아동 구강건강 연구의 지식구조를 체계적으로 제시하고, 분석 결과를 기반으로 인공지능 기반 구강관리 전략의 적용 방향을 제언하였다는 점에 의의가 있다.</t>
@@ -31208,6 +31217,9 @@
         <is>
           <t>10.14333/kjte.2026.42.3.31</t>
         </is>
+      </c>
+      <c r="G544" s="1" t="n">
+        <v>46204</v>
       </c>
       <c r="H544" t="inlineStr">
         <is>
@@ -31299,6 +31311,9 @@
           <t>10.5334/ijic.9045</t>
         </is>
       </c>
+      <c r="G546" s="1" t="n">
+        <v>46198</v>
+      </c>
       <c r="H546" t="inlineStr">
         <is>
           <t>Objectives: Despite the significant advantages of public-private partnerships (PPPs), understanding of the organisational roles that shape partnership functioning within integrated care networks remains limited. This study investigated the structural characteristics of PPPs and identified organisational roles within an integrated care network in a Seoul district, Korea.Methods: Using the 2020 Integrated Care Network Survey, this study analyzed modularity, eigenvector centrality, and brokerage in 82 public and private organisations across five different types: district offices, public health centres, healthcare institutions, social welfare institutions, and community organisations. Results: Our results reveal that integrated care organisations are predominantly divided into two major networks: disability care and elderly care. The highest centrality in the elderly care network is occupied by the dementia relief centre and social welfare institutions, while the disability care network is dominated by public institutions, the Health and Welfare Cooperative, and a social service centre for the disabled. Regarding organisational roles, social welfare institutions function primarily as coordinators, representatives, and gatekeepers, whereas public institutions-including district offices, public health centres, and community service centres-serve as consultants and liaisons. Notably, public institutions assume more prominent roles and private organisations demonstrate less involvement in the disability care network compared to the elderly care network. Conclusion: These findings underscore the importance of defining clear organisational roles and interaction mechanisms between public and private sectors, offering valuable insights for policy design aimed at enhancing coordination, accountability, and sustainability within PPP-based integrated care systems.</t>
@@ -31347,6 +31362,9 @@
       </c>
       <c r="E547" t="n">
         <v>2026</v>
+      </c>
+      <c r="G547" s="1" t="n">
+        <v>46204</v>
       </c>
       <c r="H547" t="inlineStr">
         <is>
@@ -31405,6 +31423,9 @@
           <t>10.22718/kga.2026.10.2.019</t>
         </is>
       </c>
+      <c r="G548" s="1" t="n">
+        <v>46204</v>
+      </c>
       <c r="H548" t="inlineStr">
         <is>
           <t>본 연구는 키워드 네트워크 분석과 토픽모델링을 활용하여 국내 노인 1인가구 관련 연구동향을 분석하는 데 목적이 있다. 이를 위해 국내 KCI 등재(후보) 학술지에 게재된 노인 1인가구 관련 논문 111편을 대상으로 넷마이너(NetMiner 4)를 이용하여 키워드 네트워크 분석과 토픽모델링을 수행하였다. 키워드 네트워크 분석에서는 키워드 빈도분석과 동시출현 분석을 실시하고 연결중심성, 근접중심성, 매개중심성을 산출하여 핵심 개념의 구조를 분석하였다. 분석 결과, 사회적 관계, 우울, 정책, 지원, 삶의 만족 등이 주요 키워드로 나타났다. 토픽모델링 분석에서는 총 4개의 토픽이 도출되었다. 토픽-1은 사회적 지지와 돌봄을 통한 노년기 삶의 질, 토픽-2는 경제 및 주거 조건과 빈곤 문제, 토픽-3은 사회참여와 공동체 활동을 통한 능동적 삶, 토픽-4는 우울과 건강 상태를 중심으로 한 심리·정서적 위기와 관련된 주제로 나타났다. 이러한 결과는 노인 1인가구 연구가 경제적 조건과 사회적 관계를 중심으로 사회참여와 정신건강 등 다양한 주제로 확장되어 왔음을 보여준다. 본 연구는 국내 노인 1인가구 연구의 주요 주제와 지식 구조를 체계적으로 제시하고, 향후 연구 방향을 위한 기초자료를 제공한다는 점에서 의의를 가진다.</t>
@@ -31459,6 +31480,9 @@
           <t>10.22173/ksss.2026.39.specialissue.6</t>
         </is>
       </c>
+      <c r="G549" s="1" t="n">
+        <v>46204</v>
+      </c>
       <c r="H549" t="inlineStr">
         <is>
           <t>본 연구는 학교스포츠클럽 관련 언론 보도의 변화를 텍스트 마이닝 기법을 활용하여 분석하였다. 2007년부터 2023년까지 빅카인즈를 통해 수집된 7,922개의 언론 보도 기사를 바탕으로 27,286개의 키워드를 추출하고, 시기별(1기: 2007- 2011, 2기: 2012-2018, 3기: 2019-2023) 핵심 주제어의 변화를 분석하였다. 넷마이너 4.5 프로그램을 사용하여 TF-IDF 분석, 의미연결망 분석 및 네트워크 시각화 분석을 수행하였다. 이를 통해 도출된 결론은 다음과 같다. TF-IDF 분석에서는 제1기에는 체육, 참여, 지원 등이, 제2기에는 교육, 지역, 종목 등이, 제3기에는 건강, 체력, 코로나 등이 중요한 키워드로 도출되어 시기별 관심 주제의 차이를 확인할 수 있었다. 의미연결망 분석에서는 제1기에는 스포츠, 체육, 학교, 학생, 교육, 운영, 활성, 건강, 참여 순으로 높은 연결 중심성 지수가 나타났다. 제2기에는 스포츠, 학교, 학생, 활동, 대회, 인성, 폭력, 여학생, 시설 등의 순으로 중심성이 높게 나타났다. 제3기에는 스포츠, 체육, 학교, 학생, 건강, 대회, 코로나, 운동, 온라인, 소통 등의 순으로 연결 중심성이 확인되었다. 이를 통해 학교스포츠클럽 관련 언론 보도는 시기별 정책 환경과 사회적 이슈 변화에 따라 핵심 키워드와 연결 구조가 달라졌음을 확인하였다.</t>
@@ -31545,6 +31569,9 @@
         <is>
           <t>10.1136/bmjopen-2025-101505</t>
         </is>
+      </c>
+      <c r="G551" s="1" t="n">
+        <v>46198</v>
       </c>
       <c r="H551" t="inlineStr">
         <is>
@@ -31783,6 +31810,9 @@
       <c r="E555" t="n">
         <v>2026</v>
       </c>
+      <c r="G555" s="1" t="n">
+        <v>46204</v>
+      </c>
       <c r="H555" t="inlineStr">
         <is>
           <t>Purpose : This study aimed to examine research trends and explore the conceptual structure of employment preparation stress among nursing students using text network analysis and topic modeling. Methods : A descriptive study was conducted based on the abstracts of 39 Korean studies published between 2015 and 2024.
@@ -31837,6 +31867,9 @@
         <is>
           <t>10.24881/tjk.2026.17.2.131</t>
         </is>
+      </c>
+      <c r="G556" s="1" t="n">
+        <v>46204</v>
       </c>
       <c r="H556" t="inlineStr">
         <is>
@@ -31895,6 +31928,9 @@
           <t>10.35734/karp.2026.33.2.007</t>
         </is>
       </c>
+      <c r="G557" s="1" t="n">
+        <v>46204</v>
+      </c>
       <c r="H557" t="inlineStr">
         <is>
           <t>본 연구는 키워드 네트워크 분석과 토픽모델링을 활용하여 국내 학술지에 게재된 집단상담 관련 연구동향을 분석하는 데 목적이 있다. 이를 위하여 국내 등재 학술지에 게재된 910편의 논문을 분석하였다. 논문 분석을 위하여 넷마이너(NetMiner) 4.5 프로그램을 활용하여 논문에 잠재된 토픽과 키워드를 도출하였다. 본 연구는 전기(2000년-2010년)와 후기(2011-2022년)로 나누어 토픽모델링을 분석하고 토픽 분류결과 동일하게 나타난 토픽 간 연결중심성과 상위단어들의 동시출현단어들을 분석하였다. 또한 전체 집단상담에 대한 토픽 변화추이를 분석하여 연구 주제가 시간 추이에 따라 어떻게 변화하는지를 살펴보았다. 분석결과, 전기에는 학교생활적응 개입, 정서조절 및 적응 개입, 부적응과 가족 요인 개입, 인터넷중독 개입, 진로 개입, 정신건강 개입 등의 토픽이 도출되었으며, 후기에는 정신건강 개입, 정서조절 및 적응 개입, 진로 개입, 매체중독 개입 등의 토픽이 주요 연구주제로 나타났다. 또한 시기별 토픽 추이 분석 결과, 진로 개입과 정서조절 및 적응 개입은 전 기간에 걸쳐 지속적으로 나타난 주요 연구주제로 확인되었으며, 최근에는 정신건강 및 매체중독 관련 연구의 증가가 확인되었다. 이상의 분석결과와 논의를 바탕으로 향후 집단상담 연구에 대한 시사점을 제시하였다.</t>

--- a/nm-reference/citations.xlsx
+++ b/nm-reference/citations.xlsx
@@ -16,9 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -48,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -504,22 +501,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Parental and child perspectives on healthy lifestyles and artificial intelligence chatbot use among childhood and adolescent cancer survivors: a descriptive comparative study in South Korea</t>
+          <t>키워드 네트워크 분석 및 토픽모델링을 활용한 청년 1인가구 연구동향 분석</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kyung-Ah Kang; Shin-Jeong Kim; In-Hye Song; Heejin Yoon</t>
+          <t>Jeong Moon Kyeong</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Child Health Nursing Research</t>
+          <t>한국웰니스학회지</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Korean Academy of Child Health Nursing</t>
+          <t>한국웰니스학회</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -527,27 +524,27 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10.4094/chnr.2025.046</t>
+          <t>10.21097/ksw.2026.5.21.2.105</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>PURPOSE: This study compared healthy lifestyle (HLS) practices and awareness regarding the use of chatbots (A-uC) for health management between childhood and adolescent cancer survivors (CACSs) and their parents, with the aim of assessing the feasibility of tailored artificial intelligence (AI) chatbot-based interventions for holistic survivorship care. METHODS: A descriptive comparative design was employed involving 80 CACSs and 80 parents (N=160) recruited through the Korean Pediatric Cancer Foundation. HLS practices were assessed using a validated seven-domain instrument encompassing physical activity, nutrition, interpersonal relations, stress management, positive life perspective, health responsibility, and spiritual health. A-uC was evaluated using an extended technology acceptance model-based tool. Responses to the open-ended question addressing unmet HLS practices were analyzed using latent Dirichlet allocation topic modeling. RESULTS: No significant differences were observed between CACSs and parents in overall HLS (CACSs: 3.16±0.80; parents: 3.18±0.36, p=.74). While perceptions across most A-uC domains did not differ significantly, parents demonstrated a significantly higher "intention to use" chatbots for health management than CACSs (p=.03). The mean A-uC scores exceeded 4 (out of 5) in both groups, reflecting positive perceptions of chatbot-based HLS support. Topic modeling identified "exercise," "healthy diet," and "regular lifestyle" as common unmet areas. CONCLUSION: CACSs and their parents share largely concordant views on HLS and A-uC, with a strong interest in chatbot interventions. These findings underscore the potential of tailored AI chatbot programs to address unmet lifestyle needs and promote holistic survivorship care.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>https://openalex.org/W7126273275</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>4</v>
-      </c>
-      <c r="N2" t="n">
-        <v>70.0941</v>
+          <t>본 연구의 목적은 키워드 네트워크 분석과 토픽모델링을 활용하여 청년 1인가구를 주제로 한 국내 학술 연구의 동향을 체계적으로 분석하는 것이다. 이를 위해 NetMiner 4.5.1의 확장 프로그램인 Biblio Data Collector(이하 BDC)를 통해 수집한 논문 95편을 대상으로 키워드 빈도분석, 동시출현 빈도분석, 중심성 분석, 토픽모델링을 수행하였다. 연구의 결과 첫째, 빈도분석에서는 우울, 주거환경, 소득, 공유주택, 외로움 순으로 높은 빈도를 보였다. 둘째, 동시출현 빈도분석에서는 라이프스타일-삶의 만족도이 가장 높은 동시출현 빈도를 보였다. 셋째, 중심성 분석에서는 우울과 주거환경이 연결·근접·매개중심성 모두에서 1, 2위를 차지하여 연구 네트워크의 핵심 허브 역할을 담당하고 있음이 확인되었다. 넷째, 토픽모델링 분석에서는 정신건강과 심리적 특성, 일상생활과 사회적 지지, 사회적 고립과 심리적 위기, 외로움과 사회적 자원 부족, 코로나19 전후 생활 변화와 건강, 대안적 주거 환경과 주거 만족의 6개 토픽이 도출되었다. 본 연구의 결과는 청년 1인가구 후속 연구를 위한 기초자료를 제공하고, 청년 1인가구를 위한 정책 마련에 기여할 것으로 보인다.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ART003340143</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>74.0941</v>
+        <v>0</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -558,50 +555,45 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Therapeutic Insights and Immune Pathway Connections Revealed by Core Symptom Gene Network Analysis in Ankylosing Spondylitis</t>
+          <t>텍스트 네트워크 분석 기반 아동 구강건강 연구동향 분석</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>La Yoon Choi; Mi Hye Kim; D. Y. Kim</t>
+          <t>Kim Seol Hee</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Current Issues in Molecular Biology</t>
+          <t>한국건강사회융합연구</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Caister Academic Press</t>
+          <t>웰다잉융합연구소</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>2026</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>10.3390/cimb48020199</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Ankylosing spondylitis (AS) exhibits marked clinical heterogeneity that is poorly captured by conventional disease-centric analyses, hindering the development of personalized therapies. We propose a symptom-centered network pharmacology framework that directly links individual clinical symptoms to their underlying molecular mechanisms and therapeutic targets. AS- and symptom-associated genes were collected from GeneCards and prioritized using centrality analysis within protein–protein interaction networks. Symptom relevance was validated using patient-derived transcriptomic datasets. Network proximity between symptom modules and FDA-approved drug targets was assessed. A refined gene set, integrating TNF-associated neighbors and highly central nodes, was subjected to pathway enrichment analysis. Disease-centric analysis yielded a restricted 18-gene core enriched mainly in broad immune pathways. In contrast, the symptom-centered network identified 145 genes associated with specific symptoms such as inflammatory back pain and morning stiffness. Key genes, including PTEN, TLR4, JAK2, NRAS, and NR3C1, were significantly upregulated in AS patients. TNF showed local connectivity but limited global proximity, while IL17A- and JAK inhibitor-related targets were absent. A refined 24-gene module revealed enrichment in interleukin- and cytokine-mediated signaling pathways. Symptom-centered network analysis more effectively captures molecular heterogeneity in AS, providing a robust framework for symptom-specific target discovery and personalized therapeutic strategies.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>https://openalex.org/W7128601789</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" t="n">
-        <v>14.1251</v>
+          <t>본 연구는 최근 10년간 국내 아동 구강건강 관련 연구를 대상으로 텍스트 네트워크 분석을 수행하여 주요 연구 주제와 지식 구조를 규명하고자 하였다. 연구대상은 학술연구정보서비스에서 아동과 구강을 검색어로 하여 최근 10년, KCI 등재, 한국어, 원문 제공 조건을 충족하는 44편의 논문이다. 수집된 논문의 키워드를 정제한 후 NetMiner 4 프로그램을 활용하여 키워드 빈도분석, 연결중심성 분석, 네트워크 군집분석을 수행하였다. 연구결과, 키워드 빈도분석에서는 아동, 구강건강이 가장 높은 빈도로 나타났고, 구강건강조사, 치아우식증, 칫솔질, 구강운동기능 등이 주요 키워드로 확인되었다. 연결중심성 분석에서는 아동, 구강건강, 치아우식증, 구강건강행동, 부모가 핵심 노드로 나타나 아동 구강건강 연구가 질병, 행동, 보호자 요인을 중심으로 전개되고 있음을 확인하였다. 군집분석 결과, 연구 주제는 치아우식증 및 구강질환, 구강건강행동 및 부모 요인, 장애 아동 구강기능·중재, 구강보건교육 예방·관리의 네 가지 영역으로 구조화되었다. 한편 디지털 헬스케어 및 인공지능 관련 키워드는 주요 네트워크에서 명확하게 확인되지 않아 해당 분야 연구가 제한적인 것으로 확인되었다. 본 연구는 국내 아동 구강건강 연구의 지식구조를 체계적으로 제시하고, 분석 결과를 기반으로 인공지능 기반 구강관리 전략의 적용 방향을 제언하였다는 점에 의의가 있다.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ART003339594</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>15.1251</v>
+        <v>0</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -612,43 +604,49 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A Keyword Network Analysis of Treands in Research on Early Childhood Education Teachers After the Implementation of Play-Based Early Childhood Education Curriculum</t>
+          <t>텍스트마이닝을 활용한 교육실습 경험의 구조 분석: 관계, 수업, 성찰을 중심으로</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ji-su An; Ki-won Nam</t>
+          <t>Lee, Jin-Yung; Son, Eun-Young</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Korea open association for early childhood education</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+          <t>교원교육</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>교육연구원</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2026</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10.20437/koaece31-1-06</t>
+          <t>10.14333/kjte.2026.42.3.31</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>본 연구는 키워드 네트워크 분석을 활용하여 놀이중심 영유아교육과정 실행 이후 영유아교사 관련 연구 동향을 살펴보는 데 목적이 있다. 이를 위해 RISS에서 2019 개정 누리과정 및 제4차 표준보육과정이 실행된 2020년부터 2024년 하반기까지 ‘유치원/어린이집/유아/영아/보육교사’ 키워드로 검색된 1,663편의 총 233개의 키워드를 NetMiner 4.0 프로그램을 사용하여 키워드 네트워크 분석을 실시하였다. 연구 결과, 상위 출현 빈도 키워드는 ‘교사-영유아상호작용’, ‘직무만족’, ‘교사효능감’ 순으로 나타났다. 다음으로 네트워크 중심성 분석 결과, 연결중심성과 근접중심성의 상위 키워드는 ‘교사효능감’, ‘직무만족’, ‘교사-영유아상호작용’로 나타났으며, 매개중심성은 ‘직무스트레스’로 나타났다. 이러한 결과는 교육과정의 변화에 따라 영유아교사 관련 연구는 교육과정 실천역량 기반으로 활발하게 이루어졌으며, 이를 지원하기 위해서는 그 매개가 되는 교사의 정서적 지원을 돕는 정책적 접근이 필수적임을 시사한다. 또한 유보통합이 추진되는 현시점에서 영유아교사를 위한 실질적인 제도 및 정책적 지원방안 모색의 근거를 제공할 것으로 기대된다.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>W7144151918</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
+          <t>연구목적: 본 연구는 중등예비 교사들의 교육실습 성찰 에세이를 텍스트마이닝 기법으로 분석하여 예비 교사의 경험과 정서, 그리고 의미구조를 체계적으로 도출하고자 하였다.
+연구방법: 이를 위해 2022년부터 2025년까지 중학교와 고등학교에서 교육실습에 참여한 예비 교사 180명의 성찰 에세이를 수집하고, NetMiner 4.5를 활용하여 키워드 네트워크 분석과 토픽모델링을 수행하였으며, RStudio 4.4.3을 활용하여 토픽모델링 결과를 보완⋅검증하였다.
+연구결과: 분석결과, ‘경험’을 중심으로 교육실습과 관련된 ‘불안, 참관, 교과’ 등의 키워드가 도출되었고, 실습과정에서 경험하는 ‘관계, 지도, 계획, 노력’ 등의 핵심 키워드가 도출되었다. PFnet 분석에서는 ‘경험’, ‘불안’, ‘참관’, ‘관계’, ‘고민’이 중심 개념으로 나타났다. 연결중심성과 근접중심성 분석 결과, ‘경험’을 중심으로 다양한 활동과 상호작용이 이루어지며 긍정적 정서와 성장 가능성, 그리고 인식의 변화가 나타났다. 토픽모델링 분석을 통해 교육실습 경험은 수업참여 및 학습 경험, 교직경험과 진로 인식, 상담 및 관계 형성의 어려움, 학급 운영과 수업 불안의 네 가지 주제로 나타났다.
+결론: 본 연구는 예비 교사의 교육실습 경험을 데이터 기반으로 분석하여 그 의미 구조를 체계적으로 탐색하고, 교육과정 개선과 현장 연계 강화, 상담적 지원을 위한 기초자료를 제공하였다는 점에 의의가 있다.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ART003340926</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
@@ -663,17 +661,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Analysis of elder abuse-related news articles using BIGKinds and topic modeling</t>
+          <t>Typology of Public-Private Partnerships in Integrated Care: Evidence from a Municipality in Seoul, Korea</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Youngji Kim</t>
+          <t>Il-Ho Kim; Cheong-Seok Kim; Bon Kim; Dong Hee Joo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>The Journal of Korean Academic Society of Nursing Education</t>
+          <t>International Journal of Integrated Care</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Ubiquity Press</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -681,17 +684,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10.5977/jkasne.2026.32.2.208</t>
+          <t>10.5334/ijic.9045</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Purpose: This study analyzed the dominant themes and media frames in Korean newspaper coverage of elder abuse to examine how such representations shape social discourse, with implications for nursing practice, education, and policy.Methods: A total of 812 articles published between January 2021 and December 2025 were collected from 12 national daily newspapers using the BIGKinds. Keyword trends, semantic networks, and related-word analyses were conducted, and latent Dirichlet allocation topic modeling was applied to identify latent thematic structures.Results: Six major topics were identified: (1) violence in long-term care facilities; (2) abuse reporting and protective agency responses; (3) prevention and human rights protection; (4) criminal investigations based on video evidence; (5) operational and management issues in long-term care facilities; and (6) crimes targeting older adults. News coverage peaked in 2021~2022 during the COVID-19 pandemic and concentrated on “Elder Abuse Prevention Day” in June. Reporting remained reactive and event-driven, with limited attention being paid to structural causes and preventive approaches.Conclusion: Korean elder abuse coverage prioritizes punitive, post-incident responses over prevention, reducing complex social issues to individual deviance. A shift toward structural and preventive media framing is needed, along with integrated protection systems. Nurses, as frontline professionals in early detection and advocacy, should be supported through nursing education focused on abuse recognition, simulation-based training, and multidisciplinary collaboration.</t>
+          <t>Objectives: Despite the significant advantages of public-private partnerships (PPPs), understanding of the organisational roles that shape partnership functioning within integrated care networks remains limited. This study investigated the structural characteristics of PPPs and identified organisational roles within an integrated care network in a Seoul district, Korea.Methods: Using the 2020 Integrated Care Network Survey, this study analyzed modularity, eigenvector centrality, and brokerage in 82 public and private organisations across five different types: district offices, public health centres, healthcare institutions, social welfare institutions, and community organisations. Results: Our results reveal that integrated care organisations are predominantly divided into two major networks: disability care and elderly care. The highest centrality in the elderly care network is occupied by the dementia relief centre and social welfare institutions, while the disability care network is dominated by public institutions, the Health and Welfare Cooperative, and a social service centre for the disabled. Regarding organisational roles, social welfare institutions function primarily as coordinators, representatives, and gatekeepers, whereas public institutions-including district offices, public health centres, and community service centres-serve as consultants and liaisons. Notably, public institutions assume more prominent roles and private organisations demonstrate less involvement in the disability care network compared to the elderly care network. Conclusion: These findings underscore the importance of defining clear organisational roles and interaction mechanisms between public and private sectors, offering valuable insights for policy design aimed at enhancing coordination, accountability, and sustainability within PPP-based integrated care systems.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://openalex.org/W7163060697</t>
+          <t>https://openalex.org/W7131795813</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -712,41 +715,44 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Comparing Seafood Purchasing Behavior Across Online and Offline Channels</t>
+          <t>국내 비약물 중재 연구의 핵심어 네트워크 구조 분석: 경도인지장애와 치매 대상 연구의 주제 차이를 중심으로</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sora Kim; 김지웅</t>
+          <t>Park, Chi-Soo; Yoo, Doo-Han</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Journal of Channel and Retailing</t>
+          <t>대한보조공학기술학회지</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>대한보조공학기술학회</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>2026</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>10.17657/jcr.2026.4.30.1</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>수산물 구매 경로는 온라인 쇼핑의 확산과 소비자의 식생활 변화로 다변화되고 있다. 수산물은 품목별로 신선도, 가공도, 가격대, 계절성 등 속성이 다양하여 유통채널 간 구매 구조가 크게 다를 수 있다. 따라서 온라인과 오프라인 각 유통채널만의 차별화와 경쟁우위를 확보하고 유지하기 위해 유통채널별 구매 연구는 필수적이다. 본 연구는 카드 결제 데이터를 활용해 온라인과 오프라인 유통채널 간 수산물 구매 구조를 비교하여 채널별 구매 특성 및 패턴, 연관 구조, 기여도를 파악하고자 하였다. 2022년 1월부터 2023년 5월까지의 카드 결제 데이터를 활용하여 30개 주요 수산물의 주차 단위 거래를 분석하였다. 분석 결과, 온라인과 오프라인 채널의 구매 특성은 다르며, 동일 수산물이라도 채널에 따라 구매 금액의 평균 수준과 변동 패턴이 구조적으로 상이함을 확인하였다. 오프라인 채널은 일상 소비 품목의 구매가 연속적이었으며, 고가 수산물의 주기적 거래가 결합된 안정적 구조를 보였다. 반면 온라인은 일부 품목에서 특정 시점에 고액 거래가 집중되는 비연속적 구조로 나타났다. 또한 채널별 수산물 연관 구조와 핵심 수산물 포트폴리오가 다르게 형성되어 있는 것으로 나타났다. 오프라인 채널에서는 오징어와 멸치가, 온라인 채널에서는 참치, 연어, 어묵이 다른 품목과의 상관성이 높고 매출 기여도가 높은 수산물로 나타났다. 이때 주꾸미는 오프라인 대비 온라인 강세 품목으로 나타났고, 광어, 전복, 대게는 오프라인 강세 품목으로 확인되었다. 본 연구는 생산자와 유통업자가 품목 특성에 따른 채널 적합성, 오프라인의 연계 진열·번들 전략, 온라인의 신뢰·재구매 기반 전략을 설계하는 데 실질적 근거를 제공한다.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>https://openalex.org/W7161150960</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
+          <t>목적 : 본 연구는 주제어 네트워크 분석을 활용하여 최근 10년간(2015-2025년) 국내에서 수행된 경도인지장애(Mild Cognitive Impairment, MCI) 및 치매 환자를 위한 비약물 중재 연구의 동향을 파악하고 두 집단 간의 차이를 비교하고자 하였다.
+연구방법 : 한국교육학술정보원(RISS)을 통해 수집한 251편(MCI 91편, 치매 160편)의 논문에서 주제어를 추출하였으며, 빈도분석, 연결 중심성 분석, 응집성 분석을 NetMiner 4.0을 활용하여 수행하였다.
+결과 : 빈도분석 결과, MCI 연구에서는 '인지기능', '치매', '인지중재'가, 치매 연구에서는 '인지기능', 'MCI', '우울'이 다빈도 주제어로 나타났다. 연결 중심성 분석에서 MCI는 인지중재(0.575), 우울(0.493), 신체활동(0.452)을 중심으로, 치매는 체계적 문헌고찰(0.454), 인지기능(0.351), 우울(0.339)을 중심으로 연구가 수행되었다. 응집성 분석에서 MCI는 5개, 치매는 7개의 클러스터로 분류되었으며, 디지털 중재와 지역사회 클러스터가 두 집단에서 공통적으로 나타났다. 그러나 MCI에서는 자가 관리 역량 강화를 목적으로 한 디지털 중재가, 치매에서는 부양 부담 경감 및 안전 모니터링 기반 기술이 강조되는 등 적용 목적에서 차이를 보였다.
+결론 : MCI 연구는 예방과 기능 회복에, 치매 연구는 BPSD 관리와 부양자 지원에 초점을 맞추고 있어 두 집단의 병태생리학적 특성을 반영한 차별화된 중재 전략이 필요함을 확인하였다. 향후 연구에서는 두 집단의 특수성을 고려한 맞춤형 중재 개발이 활발히 이루어져야 할 것이다.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ART003331207</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
@@ -761,54 +767,46 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Exploring Career Awareness and Experiences for College Students with Undeclared Majors</t>
+          <t>키워드 네트워크 분석 및 토픽모델링을 활용한 노인 1인가구 관련 연구동향 분석</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hyunjoo Kim; Eunyoung Son; Jinyung Lee</t>
+          <t>YOUNGSIL YUN; Jeong Moon Kyeong</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>The Korea Association of Yeolin Education</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+          <t>한국과 국제사회</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>한국정치사회연구소</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2026</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>10.18230/tjye.2026.34.2.301</t>
+          <t>10.22718/kga.2026.10.2.019</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>This study aims to provide insights into the university system for personalized counseling and career education for students with undeclared majors. To this end, ten students in their second year or higher who had experience selecting their majors and career paths through the undeclared major system were selected. The questionnaire asked about the academic and career experiences that helped them eventually declare their majors. Their responses were analyzed by NetMiner for text analysis and topic modeling analysis. The findings from text analysis are as follows. Personal factors such as self concept, personality, values, and interests were found to play an important role in career and major selection. Also, their motivations to join as undeclared students were found to be connected with department, major, autonomy, and related areas. University selection was found to be connected with name value and influence from their high school counselors. The topic modeling analysis revealed 5 topics: course selection and requirements, considering faculty and academic interests, department selection and student concerns, engaging in career exploration and self-understanding, and major courses and graduation preparation. Based on the questionnaire responses, personalized counseling, tailored programs, and institutional support for students in the undeclared major program were discussed.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>W7154391189</t>
+          <t>본 연구는 키워드 네트워크 분석과 토픽모델링을 활용하여 국내 노인 1인가구 관련 연구동향을 분석하는 데 목적이 있다. 이를 위해 국내 KCI 등재(후보) 학술지에 게재된 노인 1인가구 관련 논문 111편을 대상으로 넷마이너(NetMiner 4)를 이용하여 키워드 네트워크 분석과 토픽모델링을 수행하였다. 키워드 네트워크 분석에서는 키워드 빈도분석과 동시출현 분석을 실시하고 연결중심성, 근접중심성, 매개중심성을 산출하여 핵심 개념의 구조를 분석하였다. 분석 결과, 사회적 관계, 우울, 정책, 지원, 삶의 만족 등이 주요 키워드로 나타났다. 토픽모델링 분석에서는 총 4개의 토픽이 도출되었다. 토픽-1은 사회적 지지와 돌봄을 통한 노년기 삶의 질, 토픽-2는 경제 및 주거 조건과 빈곤 문제, 토픽-3은 사회참여와 공동체 활동을 통한 능동적 삶, 토픽-4는 우울과 건강 상태를 중심으로 한 심리·정서적 위기와 관련된 주제로 나타났다. 이러한 결과는 노인 1인가구 연구가 경제적 조건과 사회적 관계를 중심으로 사회참여와 정신건강 등 다양한 주제로 확장되어 왔음을 보여준다. 본 연구는 국내 노인 1인가구 연구의 주요 주제와 지식 구조를 체계적으로 제시하고, 향후 연구 방향을 위한 기초자료를 제공한다는 점에서 의의를 가진다.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>ART003325319</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+          <t>ART003332640</t>
+        </is>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
@@ -823,28 +821,616 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>e스포츠에 대한 학교체육 운영 주체의 인식</t>
+          <t>학교스포츠클럽에 대한 언론보도 변화 분석 - 텍스트마이닝을 활용한 빅데이터 분석을 중심으로 -</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cho, Sang Wan; Yeom, Hyo Eun; Hwang, Sung-Ha</t>
+          <t>MINSU JE; Kim In Hyung</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>한국체육교육학회지</t>
+          <t>한국스포츠사회학회지</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>한국체육교육학회</t>
+          <t>한국스포츠사회학회</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>2026</v>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>10.22173/ksss.2026.39.specialissue.6</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
+        <is>
+          <t>본 연구는 학교스포츠클럽 관련 언론 보도의 변화를 텍스트 마이닝 기법을 활용하여 분석하였다. 2007년부터 2023년까지 빅카인즈를 통해 수집된 7,922개의 언론 보도 기사를 바탕으로 27,286개의 키워드를 추출하고, 시기별(1기: 2007- 2011, 2기: 2012-2018, 3기: 2019-2023) 핵심 주제어의 변화를 분석하였다. 넷마이너 4.5 프로그램을 사용하여 TF-IDF 분석, 의미연결망 분석 및 네트워크 시각화 분석을 수행하였다. 이를 통해 도출된 결론은 다음과 같다. TF-IDF 분석에서는 제1기에는 체육, 참여, 지원 등이, 제2기에는 교육, 지역, 종목 등이, 제3기에는 건강, 체력, 코로나 등이 중요한 키워드로 도출되어 시기별 관심 주제의 차이를 확인할 수 있었다. 의미연결망 분석에서는 제1기에는 스포츠, 체육, 학교, 학생, 교육, 운영, 활성, 건강, 참여 순으로 높은 연결 중심성 지수가 나타났다. 제2기에는 스포츠, 학교, 학생, 활동, 대회, 인성, 폭력, 여학생, 시설 등의 순으로 중심성이 높게 나타났다. 제3기에는 스포츠, 체육, 학교, 학생, 건강, 대회, 코로나, 운동, 온라인, 소통 등의 순으로 연결 중심성이 확인되었다. 이를 통해 학교스포츠클럽 관련 언론 보도는 시기별 정책 환경과 사회적 이슈 변화에 따라 핵심 키워드와 연결 구조가 달라졌음을 확인하였다.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ART003326639</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>What do patients value? A retrospective study of compliment letters from a single institution</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Y.-J. Kwon; Myeong Namgung; Mi Kyung Kim; Jae Chol Choi; Daun Jeong; Chan Woong Kim</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BMJ Open</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>BMJ</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>10.1136/bmjopen-2025-101505</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>OBJECTIVES: This study aimed to analyse patient-initiated compliment letters from a single institution, identify the key elements that patients value and offer actionable insights to enhance patient-centred care. DESIGN: A retrospective, single-institution study using the Healthcare Complaints Analysis Tool (HCAT), text network analysis and latent Dirichlet allocation (LDA) topic modelling on patient compliment letters to pinpoint key valued care elements. SETTING: A newly established general hospital in Gwangmyeong, South Korea, opened on 22 March 2022. PARTICIPANTS: A total of 1213 compliment letters were collected through the hospital's feedback system, which accepted both online and on-site submissions between 25 March 2022 and 28 June 2024. Letters lacking substantive descriptive content and those containing purely administrative requests were excluded. PRIMARY AND SECONDARY OUTCOME MEASURES: The HCAT was adapted to categorise positive statements into clinical, management and relationship domains, along with six stages of care. Inter-rater reliability was evaluated using Gwet's AC1 statistic. A text network analysis, applying a term frequency-inverse document frequency approach, was conducted to identify prominent keywords. Subsequently, LDA was performed to extract thematic topics. RESULTS: Most compliments concerned the 'relationship' domain (62%), particularly during the care in the ward stage (56%). Keyword analysis indicated that the most frequently mentioned terms were 'gratitude', 'kindness', 'nurse', 'doctor' and 'heart/mind', underscoring patients' high valuation of positive interactions, professional competence and compassionate communication with medical staff. Topic modelling identified three primary topics, namely, 'appreciation of nursing care' (39%), 'professionalism in surgery and treatment' (35%) and 'effective communication during consultations' (26%). CONCLUSIONS: Positive relationships with medical staff, particularly kindness, professionalism and effective communication, influence patient satisfaction. Patient compliment letters serve as important indicators of exceptional care and can inform quality improvement initiatives. Healthcare institutions should leverage these insights to enhance patient-centred services by strengthening patient-provider relationships and promoting a culture of excellence.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>https://openalex.org/W7135066543</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>간호대학생의 취업준비 스트레스 연구동향과 개념구조: 텍스트 네트워크 분석을 중심으로</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Yu, Ga Eul; park sook kyoung</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>한국간호연구학회지</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>한국간호연구학회</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Purpose : This study aimed to examine research trends and explore the conceptual structure of employment preparation stress among nursing students using text network analysis and topic modeling. Methods : A descriptive study was conducted based on the abstracts of 39 Korean studies published between 2015 and 2024.
+Text data were preprocessed through Korean morphological analysis, and keyword co-occurrence matrices were constructed at the document level. Frequency, centrality, and network visualization analyses were performed using NetMiner, and LDA(Latent Dirichlet Allocation) topic modeling was conducted to identify major thematic patterns in the literature. Results : The most frequent keywords were ‘employment preparation stress’, ‘career decision-making self-efficacy’, ‘clinical practice’, ‘career preparation behavior’, and ‘self-efficacy’. Topic modeling identified five topic clusters: psychological stress, career-related cognition and behavior, clinical practice and educational environment, coping and psychological resources, and personal characteristics and emotional responses. Conclusion : Research on employment preparation stress among nursing students has evolved around interconnected psychological, career-related, educational, and personal dimensions. These findings suggest the need for integrated educational strategies that promote career preparation, clinical adaptation, effective coping, and the development of psychological resilience and personal competencies among nursing students.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ART003352583</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>대학부 태권도 선수의 랭킹제도 인식 구조 : 키워드 네트워크 분석을 중심으로</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ha-Young, SHIN; Jiwun Yoon; Jae-Hyeon</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>국기원 태권도연구</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>국기원</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>10.24881/tjk.2026.17.2.131</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>목적  이 연구의 목적은 2024년부터 도입된 국내 랭킹제도에 대한 대학부 태권도 겨루기 선수의 인식을 확인하는 것에 있다. 나아가 선수들이 인식하는 랭킹제도 관련 개념 간 관계를 구조적으로 제시하여 제도 운영 이해를 위한 기초 자료를 제공하고자 한다.
+방법  이 목적을 달성하기 위해 2024년도 국가대표 최종선발전에 출전한 선수 및 국가대표 선수 선발 최종전에 진출하였거나 입상한 대학부 선수 10명을 대상으로 초점집단면접(Focus Group Interview)을 실시하였다. 이후 NetMiner 4.0을 활용하여 연결중심성을 지표로 분석하였다.
+결과  첫째, 선수들은 랭킹제도의 운영 원칙과 점수 산출 방식 등 제도의 기본 구조에 대해 비교적 명확하게 인식하고 있었다. 둘째, 랭킹 점수 획득을 위한 반복적인 대회 출전 구조는 선수들에게 신체적·심리적 부담과 연관된 인식으로 나타났으며, 이는 제도 선호도 및 평가와 연결되어 인식되고 있었다. 셋째, 공지 및 정보 전달 체계와 관련된 절차적 요소 역시 제도 신뢰와 연관된 인식 요소로 확인되었다.
+결론  대학부 태권도 선수들의 랭킹제도 인식은 제도의 구조적 이해와 실제 운영 경험이 함께 반영된 형태로 나타났다. 이러한 연구 결과는 향후 랭킹제도 운영과 관련된 논의를 위한 기초 자료로 활용될 수 있을 것이다.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ART003350083</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>토픽모델링을 통한 집단상담 연구동향 분석</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Son, Hye-Seon; Cheon, Seong-Moon</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>재활심리연구</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>한국재활심리학회</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>10.35734/karp.2026.33.2.007</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>본 연구는 키워드 네트워크 분석과 토픽모델링을 활용하여 국내 학술지에 게재된 집단상담 관련 연구동향을 분석하는 데 목적이 있다. 이를 위하여 국내 등재 학술지에 게재된 910편의 논문을 분석하였다. 논문 분석을 위하여 넷마이너(NetMiner) 4.5 프로그램을 활용하여 논문에 잠재된 토픽과 키워드를 도출하였다. 본 연구는 전기(2000년-2010년)와 후기(2011-2022년)로 나누어 토픽모델링을 분석하고 토픽 분류결과 동일하게 나타난 토픽 간 연결중심성과 상위단어들의 동시출현단어들을 분석하였다. 또한 전체 집단상담에 대한 토픽 변화추이를 분석하여 연구 주제가 시간 추이에 따라 어떻게 변화하는지를 살펴보았다. 분석결과, 전기에는 학교생활적응 개입, 정서조절 및 적응 개입, 부적응과 가족 요인 개입, 인터넷중독 개입, 진로 개입, 정신건강 개입 등의 토픽이 도출되었으며, 후기에는 정신건강 개입, 정서조절 및 적응 개입, 진로 개입, 매체중독 개입 등의 토픽이 주요 연구주제로 나타났다. 또한 시기별 토픽 추이 분석 결과, 진로 개입과 정서조절 및 적응 개입은 전 기간에 걸쳐 지속적으로 나타난 주요 연구주제로 확인되었으며, 최근에는 정신건강 및 매체중독 관련 연구의 증가가 확인되었다. 이상의 분석결과와 논의를 바탕으로 향후 집단상담 연구에 대한 시사점을 제시하였다.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ART003350468</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Parental and child perspectives on healthy lifestyles and artificial intelligence chatbot use among childhood and adolescent cancer survivors: a descriptive comparative study in South Korea</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kyung-Ah Kang; Shin-Jeong Kim; In-Hye Song; Heejin Yoon</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Child Health Nursing Research</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Korean Academy of Child Health Nursing</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>10.4094/chnr.2025.046</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>PURPOSE: This study compared healthy lifestyle (HLS) practices and awareness regarding the use of chatbots (A-uC) for health management between childhood and adolescent cancer survivors (CACSs) and their parents, with the aim of assessing the feasibility of tailored artificial intelligence (AI) chatbot-based interventions for holistic survivorship care. METHODS: A descriptive comparative design was employed involving 80 CACSs and 80 parents (N=160) recruited through the Korean Pediatric Cancer Foundation. HLS practices were assessed using a validated seven-domain instrument encompassing physical activity, nutrition, interpersonal relations, stress management, positive life perspective, health responsibility, and spiritual health. A-uC was evaluated using an extended technology acceptance model-based tool. Responses to the open-ended question addressing unmet HLS practices were analyzed using latent Dirichlet allocation topic modeling. RESULTS: No significant differences were observed between CACSs and parents in overall HLS (CACSs: 3.16±0.80; parents: 3.18±0.36, p=.74). While perceptions across most A-uC domains did not differ significantly, parents demonstrated a significantly higher "intention to use" chatbots for health management than CACSs (p=.03). The mean A-uC scores exceeded 4 (out of 5) in both groups, reflecting positive perceptions of chatbot-based HLS support. Topic modeling identified "exercise," "healthy diet," and "regular lifestyle" as common unmet areas. CONCLUSION: CACSs and their parents share largely concordant views on HLS and A-uC, with a strong interest in chatbot interventions. These findings underscore the potential of tailored AI chatbot programs to address unmet lifestyle needs and promote holistic survivorship care.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>https://openalex.org/W7126273275</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>4</v>
+      </c>
+      <c r="N13" t="n">
+        <v>70.0941</v>
+      </c>
+      <c r="O13" t="n">
+        <v>74.0941</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Therapeutic Insights and Immune Pathway Connections Revealed by Core Symptom Gene Network Analysis in Ankylosing Spondylitis</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>La Yoon Choi; Mi Hye Kim; D. Y. Kim</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Current Issues in Molecular Biology</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Caister Academic Press</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>10.3390/cimb48020199</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Ankylosing spondylitis (AS) exhibits marked clinical heterogeneity that is poorly captured by conventional disease-centric analyses, hindering the development of personalized therapies. We propose a symptom-centered network pharmacology framework that directly links individual clinical symptoms to their underlying molecular mechanisms and therapeutic targets. AS- and symptom-associated genes were collected from GeneCards and prioritized using centrality analysis within protein–protein interaction networks. Symptom relevance was validated using patient-derived transcriptomic datasets. Network proximity between symptom modules and FDA-approved drug targets was assessed. A refined gene set, integrating TNF-associated neighbors and highly central nodes, was subjected to pathway enrichment analysis. Disease-centric analysis yielded a restricted 18-gene core enriched mainly in broad immune pathways. In contrast, the symptom-centered network identified 145 genes associated with specific symptoms such as inflammatory back pain and morning stiffness. Key genes, including PTEN, TLR4, JAK2, NRAS, and NR3C1, were significantly upregulated in AS patients. TNF showed local connectivity but limited global proximity, while IL17A- and JAK inhibitor-related targets were absent. A refined 24-gene module revealed enrichment in interleukin- and cytokine-mediated signaling pathways. Symptom-centered network analysis more effectively captures molecular heterogeneity in AS, providing a robust framework for symptom-specific target discovery and personalized therapeutic strategies.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>https://openalex.org/W7128601789</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>14.1251</v>
+      </c>
+      <c r="O14" t="n">
+        <v>15.1251</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A Keyword Network Analysis of Treands in Research on Early Childhood Education Teachers After the Implementation of Play-Based Early Childhood Education Curriculum</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ji-su An; Ki-won Nam</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Korea open association for early childhood education</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>10.20437/koaece31-1-06</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>본 연구는 키워드 네트워크 분석을 활용하여 놀이중심 영유아교육과정 실행 이후 영유아교사 관련 연구 동향을 살펴보는 데 목적이 있다. 이를 위해 RISS에서 2019 개정 누리과정 및 제4차 표준보육과정이 실행된 2020년부터 2024년 하반기까지 ‘유치원/어린이집/유아/영아/보육교사’ 키워드로 검색된 1,663편의 총 233개의 키워드를 NetMiner 4.0 프로그램을 사용하여 키워드 네트워크 분석을 실시하였다. 연구 결과, 상위 출현 빈도 키워드는 ‘교사-영유아상호작용’, ‘직무만족’, ‘교사효능감’ 순으로 나타났다. 다음으로 네트워크 중심성 분석 결과, 연결중심성과 근접중심성의 상위 키워드는 ‘교사효능감’, ‘직무만족’, ‘교사-영유아상호작용’로 나타났으며, 매개중심성은 ‘직무스트레스’로 나타났다. 이러한 결과는 교육과정의 변화에 따라 영유아교사 관련 연구는 교육과정 실천역량 기반으로 활발하게 이루어졌으며, 이를 지원하기 위해서는 그 매개가 되는 교사의 정서적 지원을 돕는 정책적 접근이 필수적임을 시사한다. 또한 유보통합이 추진되는 현시점에서 영유아교사를 위한 실질적인 제도 및 정책적 지원방안 모색의 근거를 제공할 것으로 기대된다.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>W7144151918</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Analysis of elder abuse-related news articles using BIGKinds and topic modeling</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Youngji Kim</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>The Journal of Korean Academic Society of Nursing Education</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>10.5977/jkasne.2026.32.2.208</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Purpose: This study analyzed the dominant themes and media frames in Korean newspaper coverage of elder abuse to examine how such representations shape social discourse, with implications for nursing practice, education, and policy.Methods: A total of 812 articles published between January 2021 and December 2025 were collected from 12 national daily newspapers using the BIGKinds. Keyword trends, semantic networks, and related-word analyses were conducted, and latent Dirichlet allocation topic modeling was applied to identify latent thematic structures.Results: Six major topics were identified: (1) violence in long-term care facilities; (2) abuse reporting and protective agency responses; (3) prevention and human rights protection; (4) criminal investigations based on video evidence; (5) operational and management issues in long-term care facilities; and (6) crimes targeting older adults. News coverage peaked in 2021~2022 during the COVID-19 pandemic and concentrated on “Elder Abuse Prevention Day” in June. Reporting remained reactive and event-driven, with limited attention being paid to structural causes and preventive approaches.Conclusion: Korean elder abuse coverage prioritizes punitive, post-incident responses over prevention, reducing complex social issues to individual deviance. A shift toward structural and preventive media framing is needed, along with integrated protection systems. Nurses, as frontline professionals in early detection and advocacy, should be supported through nursing education focused on abuse recognition, simulation-based training, and multidisciplinary collaboration.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>https://openalex.org/W7163060697</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Comparing Seafood Purchasing Behavior Across Online and Offline Channels</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Sora Kim; 김지웅</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Journal of Channel and Retailing</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>10.17657/jcr.2026.4.30.1</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>수산물 구매 경로는 온라인 쇼핑의 확산과 소비자의 식생활 변화로 다변화되고 있다. 수산물은 품목별로 신선도, 가공도, 가격대, 계절성 등 속성이 다양하여 유통채널 간 구매 구조가 크게 다를 수 있다. 따라서 온라인과 오프라인 각 유통채널만의 차별화와 경쟁우위를 확보하고 유지하기 위해 유통채널별 구매 연구는 필수적이다. 본 연구는 카드 결제 데이터를 활용해 온라인과 오프라인 유통채널 간 수산물 구매 구조를 비교하여 채널별 구매 특성 및 패턴, 연관 구조, 기여도를 파악하고자 하였다. 2022년 1월부터 2023년 5월까지의 카드 결제 데이터를 활용하여 30개 주요 수산물의 주차 단위 거래를 분석하였다. 분석 결과, 온라인과 오프라인 채널의 구매 특성은 다르며, 동일 수산물이라도 채널에 따라 구매 금액의 평균 수준과 변동 패턴이 구조적으로 상이함을 확인하였다. 오프라인 채널은 일상 소비 품목의 구매가 연속적이었으며, 고가 수산물의 주기적 거래가 결합된 안정적 구조를 보였다. 반면 온라인은 일부 품목에서 특정 시점에 고액 거래가 집중되는 비연속적 구조로 나타났다. 또한 채널별 수산물 연관 구조와 핵심 수산물 포트폴리오가 다르게 형성되어 있는 것으로 나타났다. 오프라인 채널에서는 오징어와 멸치가, 온라인 채널에서는 참치, 연어, 어묵이 다른 품목과의 상관성이 높고 매출 기여도가 높은 수산물로 나타났다. 이때 주꾸미는 오프라인 대비 온라인 강세 품목으로 나타났고, 광어, 전복, 대게는 오프라인 강세 품목으로 확인되었다. 본 연구는 생산자와 유통업자가 품목 특성에 따른 채널 적합성, 오프라인의 연계 진열·번들 전략, 온라인의 신뢰·재구매 기반 전략을 설계하는 데 실질적 근거를 제공한다.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>https://openalex.org/W7161150960</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Exploring Career Awareness and Experiences for College Students with Undeclared Majors</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Hyunjoo Kim; Eunyoung Son; Jinyung Lee</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>The Korea Association of Yeolin Education</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>10.18230/tjye.2026.34.2.301</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>This study aims to provide insights into the university system for personalized counseling and career education for students with undeclared majors. To this end, ten students in their second year or higher who had experience selecting their majors and career paths through the undeclared major system were selected. The questionnaire asked about the academic and career experiences that helped them eventually declare their majors. Their responses were analyzed by NetMiner for text analysis and topic modeling analysis. The findings from text analysis are as follows. Personal factors such as self concept, personality, values, and interests were found to play an important role in career and major selection. Also, their motivations to join as undeclared students were found to be connected with department, major, autonomy, and related areas. University selection was found to be connected with name value and influence from their high school counselors. The topic modeling analysis revealed 5 topics: course selection and requirements, considering faculty and academic interests, department selection and student concerns, engaging in career exploration and self-understanding, and major courses and graduation preparation. Based on the questionnaire responses, personalized counseling, tailored programs, and institutional support for students in the undeclared major program were discussed.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>W7154391189</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ART003325319</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>e스포츠에 대한 학교체육 운영 주체의 인식</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Cho, Sang Wan; Yeom, Hyo Eun; Hwang, Sung-Ha</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>한국체육교육학회지</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>한국체육교육학회</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t>목적: 이 연구의 목적은 학교체육 운영 주체가 인식하는 e스포츠의 의미 구조를 탐색하고, 학교체육 맥락에서 e스포츠의 교육적 수용 가능성을 분석하는 데 있다.
 방법: 학교체육 운영 주체인 ‘학생’과 ‘교사’ 총 788명을 대상으로 온라인 기반 개방형 설문을 실시하여 자료를 수집하였다. 수집된 텍스트 자료는 Textom을 활용하여 표준화 및 정제 과정을 거친 후 키워드 빈도 및TF-IDF 분석을 실시하였다. 키워드 간 의미 구조를 확인하기 위해 공출현 행렬을 구성하고 연결중심성 지수를 산출하였으며, NetMiner 5.0 프로그램을 활용하여 의미연결망을 분석하였다.
@@ -852,271 +1438,271 @@
 결론: e스포츠의 교육적 활용은 활동 자체의 특성보다 교육 환경, 운영 체계, 지도 주체와 같은 제도적 조건에 의해 좌우된다. 따라서 e스포츠의 학교체육 수용은 교육적 의미를 어떻게 구조화하고 운영하는가에 따라그 가치가 달라진다. 이는 디지털 전환 시대 학교체육의 포용적 확장을 위한 실천적 기반을 제공할 수 있다.</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>ART003333283</t>
         </is>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Keyword Network Analysis of Non-Pharmacological Intervention Research in South Korea : Comparing Mild Cognitive Impairment and Dementia Studies</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Chi-Soo Park; Doo‐Han Yoo</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>The Journal of Korean Society of Assistive Technology</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E20" t="n">
         <v>2026</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>10.55091/ksat.2026.18.1.29</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>목적 : 본 연구는 주제어 네트워크 분석을 활용하여 최근 10년간(2015-2025년) 국내에서 수행된 경도인지장애(Mild Cognitive Impairment, MCI) 및 치매 환자를 위한 비약물 중재 연구의 동향을 파악하고 두 집단 간의 차이를 비교하고 자 하였다. 연구방법 : 한국교육학술정보원(RISS)을 통해 수집한 251편(MCI 91편, 치매 160편)의 논문에서 주제어를 추출하였으며, 빈도분석, 연결 중심성 분석, 응집성 분석을 NetMiner 4.0을 활용하여 수행하였다. 결과 : 빈도분석 결과, MCI 연구에서는 '인지기능', '치매', '인지중재'가, 치매 연구에서는 '인지기능', 'MCI', '우울'이 다빈 도 주제어로 나타났다. 연결 중심성 분석에서 MCI는 인지중재(0.575), 우울(0.493), 신체활동(0.452)을 중심으로, 치매 는 체계적 문헌고찰(0.454), 인지기능(0.351), 우울(0.339)을 중심으로 연구가 수행되었다. 응집성 분석에서 MCI는 5개, 치매는 7개의 클러스터로 분류되었으며, 디지털 중재와 지역사회 클러스터가 두 집단에서 공통적으로 나타났다. 그러나 MCI에서는 자가 관리 역량 강화를 목적으로 한 디지털 중재가, 치매에서는 부양 부담 경감 및 안전 모니터링 기반 기술 이 강조되는 등 적용 목적에서 차이를 보였다. 결론 : MCI 연구는 예방과 기능 회복에, 치매 연구는 BPSD 관리와 부양자 지원에 초점을 맞추고 있어 두 집단의 병태생 리학적 특성을 반영한 차별화된 중재 전략이 필요함을 확인하였다. 향후 연구에서는 두 집단의 특수성을 고려한 맞춤형 중재 개발이 활발히 이루어져야 할 것이다.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>https://openalex.org/W7160891106</t>
         </is>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Keyword Network Analysis on Discussions of International Students in RISE Project</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Sunhee Kwon</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Asia-pacific Journal of Convergent Research Interchange</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E21" t="n">
         <v>2026</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>10.47116/apjcri.2026.01.49</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>This study reviewed the characteristics and main aspects of discussions on International Students in the RISE (Regional Innovation System for Education) project through keyword network analysis.The results of keyword network analysis and ego network analysis of about 7,600 web documents collected in 2025 showed that recruitment, global, university, region, education, support, international, student, university president, employment, and expansion were the main keywords.The ego network analysis results showed that in the recruitment ego network, the education, global, training, and expansion nodes exerted strong influence.It was also shown that, in the global ego network, reinforcement and recruitment nodes occupied important positions.In contrast, in the international ego network, exchange and culture nodes occupied important positions, suggesting that policies related to international students were expanding into dimensions of social integration, such as culture and exchange.The results of the employment/entrepreneurship ego network analysis indicated that local employment and the settlement of international students were key issues, and the Ministry of Education/City Hall ego network clearly identified the central government and local institutions as key actors in international student policies.The results of this study suggest that, regarding international students, the RISE project aims to serve as an innovative project that combines local higher education with internationalization strategies.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>https://openalex.org/W7126165482</t>
         </is>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>An Analysis of Interviews between Nurse Educators and Newly Graduated Nurses Regarding Adaptation to Clinical Nursing Practice: Text Network Analysis and Topic Modeling</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Hyowon Jo; Hyunjung Ko; Seulki Jeong; Minyoung Park; Seul Lee; Seok Hee Jeong</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Journal of Korean Academy of Nursing Administration</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>10.11111/jkana.2025.0059</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Purpose: This study identified themes associated with the clinical adaptation of newly graduated nurses. Methods: We collected 522 interview journals from newly graduated nurses and nurse educators at a tertiary hospital between January 2021 and December 2023. After excluding incomplete data, 407 “promoting enjoyment” entries and 426 “presenting challenges” entries were analyzed using network analysis and topic modeling in NetMiner 4.5.1. Results: Topic modeling identified four themes in each category. For promoting enjoyment, the themes were: “Upon completing my designated responsibilities, I depart from the workplace,” “On my days off, I enjoy indulging in my favorite activities,” “Being recognized by my colleagues makes me feel like I’m contributing my part to the team,” and “The condition of my patient has improved.” For presenting challenges, the themes were: “The numerous responsibilities I must handle make it difficult to complete everything within the designated time frame,” “I struggle with both my tasks and relationships with colleagues,” “I’m anxious about caring for patients on my own,” and “Irregular shift patterns and occupational distress significantly impair my sleep quality.” Conclusion: Educational methodologies need to be developed to facilitate the clinical adaptation of newly graduated nurses. These findings can inform the Ministry of Health and Welfare’s nurse educator policy and future nursing workforce strategies.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>W7143431381</t>
         </is>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="inlineStr">
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Mapping the Landscape of Medical AI Research in Korea Using Topic Modeling</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>HeeJang Yun; Y. Lee</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Multidisciplinary Digital Publishing Institute</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E23" t="n">
         <v>2026</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>10.3390/healthcare14040549</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Background/Objectives: This study analyzed ten years of domestic research on medical artificial intelligence (AI) from 2015 to 2024 using topic modeling and keyword network analysis. Chronological comparison showed that the research emphasis evolved through three stages—Introduction (2015–2018), Expansion (2019–2022), and Post-ChatGPT (2023–2024)—reflecting the growing incorporation of AI into clinical and service domains. Methods: We collected a curated set of 686 papers from the Korea Citation Index (KCI). After preprocessing—stopword removal, synonym unification, and lemmatization—7489 unique terms were extracted for the analysis. Results: Topic modeling identified three dominant themes: Diagnostic Imaging and Algorithm Validation, Healthcare Service and System Integration, and Patient-Centered Prediction and Disease Modeling. Keyword network analysis further revealed a structural shift from algorithm-oriented studies to system-level and patient-focused applications. Conclusions: These findings indicate that Korean medical AI research is maturing toward a more interpretable, integrated, and human-centered paradigm, underscoring the need for explainable AI (XAI), multidisciplinary collaboration, and governance frameworks for safe and ethical deployment.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>https://openalex.org/W7131085989</t>
         </is>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>증상-유전자 네트워크 분석을 활용한 파킨슨병의 한의학적  적용 가능성 탐색</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>YeRim Kang; GeunBi Lee; Ji Won Ha; La Yoon Choi; Gi-Sang Bae; Mi Hye Kim; Dae Yong Kim</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>대한한의학회지</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>대한한의학회</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>10.13048/jkm.26005</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Objectives: Parkinson’s disease (PD) is a multifactorial neurodegenerative disorder characterized by both motor and non-motor symptoms. While pharmacological and surgical treatments primarily target symptom alleviation, they often fall short in addressing disease progression or the complexity of symptoms. This study aimed to identify key genes associated with diverse PD symptoms through network centrality analysis and investigate their relevance to herbal medicines used in Korean Medicine (KM), thereby exploring the scientific basis for KM interventions in PD.
 Methods: PD-related symptoms and associated genes were collected via GeneCards, and a two-mode network was constructed. Centrality measures (degree, betweenness, closeness, eigenvector) were calculated using NetMiner software to identify key genes. These core genes were then matched with herbal medicines listed in Korean clinical practice guidelines for PD. Enrichment analyses were performed using DAVID to evaluate the biological functions and pathways linked to gene-herb associations.
@@ -1124,490 +1710,490 @@
 Conclusions:  This study presents a systems biology approach integrating symptom-gene networks with traditional herbal prescriptions, offering a novel framework for personalized KM strategies in PD management. The findings support the potential of selected herbs as multi-target modulators and warrant further experimental validation.</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>ART003307116</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="inlineStr">
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>New Trends in the Use of Artificial Intelligence and Natural Language Processing for Occupational Risks Prevention</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Natalia Orviz-Martínez; Efrén Pérez-Santín; José Ignacio López Sánchez</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Safety</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Multidisciplinary Digital Publishing Institute</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="E25" t="n">
         <v>2026</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>10.3390/safety12010007</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>In an increasingly technologized and automated world, workplace safety and health remain a major global challenge. After decades of regulatory frameworks and substantial technical and organizational advances, the expanding interaction between humans and machines and the growing complexity of work systems are gaining importance. In parallel, the digitalization of Industry 4.0/5.0 is generating unprecedented volumes of safety-relevant data and new opportunities to move from reactive analysis to proactive, data-driven prevention. This review maps how artificial intelligence (AI), with a specific focus on natural language processing (NLP) and large language models (LLMs), is being applied to occupational risk prevention across sectors. A structured search of the Web of Science Core Collection (2013–October 2025), combined OSH-related terms with AI, NLP and LLM terms. After screening and full-text assessment, 123 studies were discussed. Early work relied on text mining and traditional machine learning to classify accident types and causes, extract risk factors and support incident analysis from free-text narratives. More recent contributions use deep learning to predict injury severity, potential serious injuries and fatalities (PSIF) and field risk control program (FRCP) levels and to fuse textual data with process, environmental and sensor information in multi-source risk models. The latest wave of studies deploys LLMs, retrieval-augmented generation and vision–language architectures to generate task-specific safety guidance, support accident investigation, map occupations and job tasks and monitor personal protective equipment (PPE) compliance. Together, these developments show that AI-, NLP- and LLM-based systems can exploit unstructured OSH information to provide more granular, timely and predictive safety insights. However, the field is still constrained by data quality and bias, limited external validation, opacity, hallucinations and emerging regulatory and ethical requirements. In conclusion, this review positions AI and LLMs as tools to support human decision-making in OSH and outlines a research agenda centered on high-quality datasets and rigorous evaluation of fairness, robustness, explainability and governance.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>https://openalex.org/W7119472048</t>
         </is>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="inlineStr">
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="inlineStr">
         <is>
           <t>언급</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>키워드 빈도분석과 LDA 토픽 모델링을 활용한 『육아지원연구 』 연구동향 분석: 2005-2025</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Ahn Hye Jung; Park, Jinyoung; Ryu, Joo Yeon</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>육아지원연구</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>한국육아지원학회</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>10.16978/ecec.2026.21.1.004</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>본 연구는 텍스트 마이닝 기법을 활용하여 육아지원연구의 연구동향과 주제 구조 변화를 분석하였다. 분석대상은 2005년부터 2025년까지 게재된 논문 485편의 초록이며, 게재 편수 및 인용지수 추이를고려해 형성기(2005?2011), 성장기(2012?2017), 성숙기(2018?2025)로 구분하였다. NetMiner 4.5 프로그램을 활용해 전처리 후 키워드 빈도분석과 LDA 기반 토픽 모델링을 실시하였다. 분석결과, 상위 키워드는 ‘유아’, ‘교육’, ‘교사’, ‘놀이’로 나타났으며, 형성기에는 발달?창의 관련 키워드가, 성장기에는 정서?행동 관련 키워드, 성숙기에는 놀이?지원 관련 키워드가 두드러지게 나타났다. 토픽 모델링에서는5개 토픽이 도출되었으며, 형성기에는 토픽 간 비중이 비교적 균형적으로 나타난 반면, 성장기에는 ‘유아, 교사, 어머니의 사회?정서 역량’토픽의 비중이 확대되었고, 성숙기에는 ‘놀이와 영유아교육과정 운영’및 ‘부모의 자녀 양육지원’토픽이 증가하였다. 본 연구를 통해 육아지원연구가 정책?제도 환경과긴밀히 연계되는 동시에 현장 실천적 성격을 지니고 있음을 확인하였다. 이러한 결과를 바탕으로 향후연구주제와 학술지의 발전 방향을 모색하였다.</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>ART003321746</t>
         </is>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Research Trends and Knowledge Structure of Children’s Oral Health: A Text Network Analysis</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Seol-Hee Kim</t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="E27" t="n">
         <v>2026</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>10.64763/kc.2026.5.1.38</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>This study aimed to identify major research topics and the knowledge structure of oral health studies on Korean children over the past 10 years using text network analysis. A total of 44 articles were retrieved from the Research Information Sharing Service (RISS) using the keywords “children” and “oral.” Eligible studies were published within the last 10 years in KCI-indexed or candidate journals, written in Korean, and available in full text. Refined keywords were analyzed using NetMiner for frequency, degree centrality, and network clustering. The results of the keyword frequency analysis showed that children and oral health were the most frequently occurring keywords, followed by oral health survey, dental caries, toothbrushing, and oral motor function. Degree centrality analysis revealed that children, oral health, dental caries, oral health behavior, and parents were the core nodes, indicating that research on children's oral health has been primarily centered on disease, behavior, and caregiver-related factors. Cluster analysis identified four main research domains: dental caries and oral diseases, oral health behaviors and parental factors, children with disabilities and oral function interventions, and oral health education and preventive management. However, keywords related to digital healthcare and artificial intelligence were not prominent in the main network, suggesting that research in these areas remains limited. This study is significant in that it systematically presents the knowledge structure of children's oral health research in Korea and proposes future directions for the application of artificial intelligence-based oral health management strategies based on the findings.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>https://openalex.org/W7163039799</t>
         </is>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Research Trends in Studies on Midlife Depression: Keyword Network Analysis and Topic Modeling Approach</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Moonkyeong Jeong</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Korean Journal of Security Convergence Management</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>10.24826/kscs.15.3.8</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>연구목적 본 연구는 키워드 네트워크 분석과 토픽모델링을 활용하여 국내 학술지에 게재된 중년기 우울 연구동향을 분석하는데 목적이 있다. 연구방법 이를 위하여 국내 등재(후보) 학술지에 게재된 222편의 논문을 분석하였다. 논문 분석은 넷마이너(NetMiner) 4.5.1 프로그램을 활용한 키워드 네트워크 분석과 토픽모델링을 통해 수행하였다. 프로그램을 활용하여 저자키워드를 도출하고 이를 토대로 빈도분석, 동시출현 빈도분석, 중심성 분석, 토픽모델링 분석 등을 실시하였다. 결과 연구의 결과는 다음과 같다. 첫째, 스트레스, 불안, 프로그램, 자아존중감, 매개효과가 우울과 관련하여 빈도가 높은 키워드로 나타났다. 둘째, 상담-정신문제, 스트레스-영성, 건강-스트레스, 사회적 지지-스트레스 등이 동시출현 빈도가 높은 키워드로 확인되었다. 셋째, 중년기 우울 토픽은 총 5개의 토픽으로 도출하였다. 결론 본 연구의 결과는 향후 중년기 우울 연구를 위한 기초자료를 제공하고, 중년기 우울에 필요한 방안 마련에 기여할 것으로 보인다.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>W7155160336</t>
         </is>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>키워드 네트워크 분석 및 토픽 모델링을 활용한  거부민감성 연구 동향 분석:  2015년∼2025년을 중심으로</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>권현정; LEE Jeeyon</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>교육문화연구</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>교육연구소</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>10.24159/joec.2026.32.1.241</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>본 연구는 2015년부터 2025년까지 발표된 국내 거부민감성 연구를 대상으로 코로나19 팬데믹 이전(2015∼2019)과이후(2020∼2025)의 지식구조가 어떻게 구조적으로 전환되었는지 규명하는 데 목적이 있다. 이를 위해 KCI 등재학술지에 발표된 거부민감성 연구 295편에서 최종 1,706개의 키워드를 추출하였으며, Excel 2019와 NetMiner4.5을활용하여 중심성분석을 포함한 키워드 네트워크 분석과 토픽 모델링을 실시하였다. 주요 분석 결과는 전기(2015∼2019)와후기(2020∼2025)로 나누어 시기별 연구의 특징과 두 시기의 변화를 비교 분석하였다 주요 결과는 다음과 같다. 첫째, 키워드 네트워크 분석 결과, 전기는 대학생, 우울, 경험회피, 공격성, 부모, 사회, 관계문제, 청소년, 불안, 사회불안순으로 나타났으며, 후기는 대학생, 관계문제, 조절, 경험회피, 수치심, 우울, 공격성, 부모, 사회불안, 자기침묵 순으로나타났다. 이들 키워드는 시기별로 약간의 순위 변동은 있었으나, 모든 시기에서 중심성이 높은 핵심 키워드였다.
 둘째, 각 시기별 토픽의 변화 양상을 알아보기 위해 토픽 모델링을 실시하였다. 각 시기별 토픽 주제는 전기에는심리적 부적응, 수치심, 사회불안, 성인애착, 정서조절 실패, 후기에는 경험회피, 단절, 정신화, 내면화된 수치심, 마음챙김으로 나타났다. 각 시기별로 응집도가 높은 5가지 토픽으로 선정하여 토픽별 주제에 따라 토픽명을 설정하고 두시기를 비교 설명하였다. 이 연구는 이상의 분석 결과와 논의를 바탕으로 향후 거부민감성이 높은 사람들에 관한연구에 주는 시사점을 기술하였다.</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>ART003310562</t>
         </is>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>LDA토픽모델링을 적용한 성인발레 콘텐츠 동향분석: 2018~2025 유튜브 데이터를 중심으로</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>염지현; Lee Hae Jun</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>한국무용학회지</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>한국무용학회</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>10.26743/kaod.2026.25.4.006</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>본 연구는 2018년부터 2025년(총 8년) 유튜브에서 ‘성인발레’ 담론의 구조와 시계열 변화를 정량적으로 규명하기 위해 연도별 상위 100개 동영상을 대상으로 잠재 디리클레 분포(LDA)기반 토픽모델링을 수행하였다.
 NetMiner v4를 활용하여 전처리 후 의미론적 일관성(u_mass)과 Spearman’s 상관분석을 통해 시계열 변화를검증하였다. 그 결과, ① 학습·성과(연습·기술 습득·성취), ② 발레복·장비·소비문화(레오타드·용품·추천), ③ 신체효과·건강(체형교정·다이어트), ④ 일상화·콘텐츠 확산(브이로그·챌린지·팁)으로 나타났다. 이 중 Topic 2에서만시간이 지남에 따라 유의하게 증가하는 정(+)의 상관(ρ=0.347, p=0.042)을 보여 소비·장비 중심 담론의 비중이 증가했음을 확인하였다. 따라서 성인발레 담론이 기능적 학습에서 소비·추천 정보를 중심으로 중심성을 높이는 방향으로 재편되고 있으며, 교육·기관·유튜브 창작자는 정보의 표준화와 협찬 및 표시의 투명성 확보를 통해 정보 신뢰성에 기반한 학습문화를 만들어야 할 것이다.</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>ART003303420</t>
         </is>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>키워드 네트워크 분석을 통한 정보 취약 계층의 디지털 리터러시 연구 동향</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Kim Kangmin; Kim, Sooyoung</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>창의정보문화연구</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>한국창의정보문화학회</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>10.32823/jcic.12.1.202602.21</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>본 연구는 정보 취약 계층인 노인, 장애인, 다문화 집단의 디지털 리터러시 연구 동향을 빈도 및 키워드 네트워크 분석을 통해 살펴보았다. 한국학술지용인색인(KCI)과 학술연구정보서비스(RISS)에서 검색된 논문 105편을 대상으로 집단별, 시기별 키워드 네트워크 분석을 실시하였다. 이를 위해 수집된 연구 목록의 키워드 교정, 표준화, 불용어 제거를 통해 데이터를 정제하고 SPSS 21.0과 NetMiner 4.3.2를 사용하여 분석했다. 분석 결과, 모든 집단에서 디지털 리터러시가 가장 핵심적인 키워드였으며, 주제적 초점은 집단별로 달랐다. 노인의 경우 ‘사회활동’ 및 ‘삶의 만족도’, 장애인의 경우 ‘사회자본’ 및 ‘자기효능감’, 그리고 다문화 집단의 경우 ‘한국어교육’, ‘디지털윤리’가 주요 연구 주제로 나타났다. 이를 통해 정보 취약 계층별 디지털 리터러시를 강화할 수 있는 개입 전략을 모색할 수 있는 토대를 마련하였다.</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>ART003310166</t>
         </is>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Text Mining of Port Loading and Unloading Safety Accidents</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Minh-Hoan Pham; Sung-Sam Hong; Hwayoung Kim</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Journal of Next-generation Convergence Information Services Technology</t>
         </is>
       </c>
-      <c r="E21" t="n">
+      <c r="E32" t="n">
         <v>2026</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>10.29056/jncist.2026.02.10</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>Port loading and unloading operations constitute one of the most safety-critical components of maritime logistics, involving complex interactions among workers, heavy equipment, vessels, and cyber-physical infrastructures.Despite the high frequency and severity of accidents, existing research has predominantly focused on statistical records or mechanical failure analyses, leaving the socio-technical dimensions reflected in public media discourse largely unexamined.This study applies an integrated text mining and keyword network analysis framework to systematically analyze Korean news media coverage of port loading and unloading accidents from 2015 to 2025.A total of 189 manually verified articles were processed through noun-based keyword extraction, TF-IDF weighting, Latent Dirichlet Allocation (LDA), and centrality-based network modeling.The results reveal three dominant thematic clusters: (1) Safety Inspection and Incident Response, (2) Maritime Infrastructure and Operations, and (3) Occupational Hazards in Cargo Handling.High-frequency terms such as worker, inspection, container, and accident site indicate that media narratives emphasize human vulnerability, regulatory oversight, and operational risk concentration.Centrality analysis further identifies pier, container, and accident site as critical structural hubs bridging distinct discourse domains, suggesting that public perception of port safety is shaped by interconnected concerns spanning human factors, equipment reliability, and infrastructural constraints.The findings highlight systemic risk patterns not captured in conventional statistical datasets and provide actionable insights for improving safety management, inspection protocols, and risk communication strategies.This study demonstrates the value of text-driven analytical approaches in understanding emerging risk themes and complements traditional accident analysis frameworks by revealing the narrative logic embedded in public discourse.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>https://openalex.org/W7131617440</t>
         </is>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Text Network Analysis of Global Literature on Self-Management of Low Back Pain</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Jinkyung Park; Wonjung Noh; Kyounghae Kim</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Pain Management Nursing</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Elsevier BV</t>
         </is>
       </c>
-      <c r="E22" t="n">
+      <c r="E33" t="n">
         <v>2026</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>10.1016/j.pmn.2026.04.013</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>Purpose: To identify the knowledge structure of low back pain (LBP) self-management literature by developing schematic diagrams of keyword relationships from a macro perspective, while examining research topics and trends across time and income.
 Design: A quantitative content analysis.
@@ -1617,285 +2203,285 @@
 Clinical implications: Nurses play a leading role in educating patients with LBP on self-management, particularly in hospital settings, focusing on processes that support their return to work and daily activities. Therefore, nurses are well-positioned to advance evidence-based nursing practices, ensuring high-quality, patient-centered care in clinical settings.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>https://openalex.org/W7162462111</t>
         </is>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>키워드 네트워크 분석과 토픽 모델링을 활용한청소년 우울 관련 연구 동향 분석</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Hee-Soon Shin; Jeong Moon Kyeong</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>사회과학리뷰</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>K교육연구학회</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>10.48033/jss.11.1.6</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>본 연구는 키워드 네트워크 분석과 토픽 모델링을 활용하여 국내 학술지에 게재된 청소년 우울 관련 연구 동향을 분석하는 데 목적이 있다. 이를 위하여 국내 등재(후보) 학술지에 게재된 664편의 논문을 분석하였다. 논문 분석을 위해 넷마이너(NetMiner) 4 프로그램을 활용하여 키워드 네트워크 분석과 토픽 모델링을 수행하였다. 키워드 네트워크 분석을 통해 키워드 빈도분석, 동시 출현 빈도 분석과 함께 연결 중심성, 근접 중심성, 매개 중심성 등의 중심성 분석을 실시하였고, 토픽 모델링 분석을 통해 논문에 잠재된 토픽과 키워드를 도출하였다. 분석 결과, 키워드 네트워크 분석의 키워드 빈도 분석에서는 자살, 자아존중감, 사회적 지지, 과보호, 스마트폰 과의존 등이 주요 키워드로 나타났다. 토픽 모델링 분석에서는 토픽-1(스트레스 및 미디어 의존), 토픽-2(폭력 및 사회 부적응), 토픽-3(정서 및 심리적 자원), 토픽-4(부모 양육태도와 사회적 관계) 등 총 4개의 토픽이 등장하였다. 본 연구의 결과는 향후 청소년 우울 연구의 방향을 제시하고, 관련 정책 수립을 위한 기초 자료를 제공하는 데 기여할 것으로 기대된다.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>W7134824911</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>ART003310230</t>
         </is>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>‘존엄사’에서 ‘연명의료결정’으로  - 국내 언론 담론의 10년간 변화에 대한 토픽모델링 연구 -</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Yun Hee Jang; Kwak Eun Mi</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>안전문화연구</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>사단법인 한국안전문화학회</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>10.52902/kjsc.2026.52.405</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>본 연구의 목적은 2015년부터 2024년까지 지난 10년간 국내 언론에서 ‘존엄사’ 담론이 ‘연명의료결정’이라는 제도적 용어로 전환되는 과정을 실증적으로 규명하는 것이다. 이를 통해 연명의료결정과 관련된 사회적 인식, 윤리·정책적 논의, 그리고 언론 프레이밍의 변화를 심층적으로 추적하고자 하였다. 연구 방법으로는 국내 9개 주요 언론사의 뉴스 기사 4,484건을 수집하여 잠재 디리클레 할당(LDA) 토픽모델링 기법을 적용하였다. 데이터 분석의 정확성을 높이기 위해 NetMiner 4.5.1.e를 활용하여 불용어 제거, 유의어 통합, 표제어 추출 등 체계적인 텍스트 전처리 과정을 수행하였다. 분석 기간은 연명의료결정법 제정 및 확산기(2015?2019), 코로나19 팬데믹기(2020?2022), 포스트 코로나기(2023?2024)로 구분하여 시기별 담론 구조의 동태적 변화를 분석하였다. 분석 결과, 연명의료결정 담론은 ‘정책 및 공공 담론’, ‘삶과 죽음에 대한 가치 인식’, ‘의료 현장의 연명의료 실천’이라는 세 가지 핵심 주제로 구성됨을 확인하였다. 특히 법 제정기에는 가치와 실천에 대한 논의가 주를 이루었으나, 팬데믹 시기에는 정책 담론의 비중이 급증하였고, 이후 다시 가치와 실천에 대한 관심이 회복되는 순환적 변화를 보였다. 더 나아가 포스트 코로나 시기에는 기존의 연명의료 중단 논의를 넘어 ‘조력존엄사’와 같은 새로운 담론이 부상하며 논의의 지평이 확장되는 양상도 관찰되었다. 이러한 결과는 연명의료결정 담론이 법·제도적 변화와 사회적 재난 등 외부 환경에 민감하게 반응하며 역동적으로 진화하는 사회적 구성물임을 시사하며, 향후 관련 정책 수립 및 사회적 소통에 기여할 수 있는 근거를 제시한다.</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>ART003318422</t>
         </is>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>뇌졸중 환자 보행 분석의 생체역학적 연구 동향: 텍스트 마이닝 기반의 체계적 고찰</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Sung Il Lee; Joo Seok Hyeon; Kim soo kyung; Soo Yeon Park; KiHoon Han</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>생명과학회지</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>한국생명과학회</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>10.5352/JLS.2026.36.2.179</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>본 연구는 텍스트 마이닝(text mining) 기법을 활용하여 2015년부터 2025년까지 발표된 국내외 뇌졸중 환자의 보행 및 낙상 관련 학술 문헌 12,066건을 분석하고 연구 동향을 객관적으로 규명하였다. 수집된 문헌 데이터는 NetMiner를 통한 텍스트 전처리를 거쳐 키워드 빈도 분석(TF), 가중치 분석(TF-IDF), LDA 기반 토픽 모델링 및 시기별 분석에 활용되었다. 분석 결과, 국내 연구는 ‘balance’, ‘training’, ‘berg balance scale’ 등을 핵심 키워드로 하여 표준화된 지표를 기반으로 한 재활 프로그램의 임상적 유효성 검증에 주력해 온 것으로 확인되었다. 반면 국외 연구는 ‘knee’, ‘ankle’, ‘propulsion’, ‘kinematic’ 등 하지 관절의 운동역학적 지표와 개별 환자의 생체역학적 기전을 정밀하게 규명하는 데 비중을 두는 차별성을 보였다. 시기별 동향에서는 국내외 연구 모두 초기 점수 기반의 단순 평가에서 점차 체계적인 중재 프로그램 도입과 세부적인 운동 제어 기전 및 족저굴곡 분석 등 미시적 영역으로 연구 초점이 심화되는 양상이 관찰되었다. 이러한 결과를 종합할 때, 국내 연구는 실용적인 재활 성과 도출에는 기여하고 있으나 향후에는 관절 모멘트 및 지면 반발력 등 정밀 지표를 결합하여 보행 장애의 근본 원인을 규명하는 기전 중심의 교량 연구(bridge research)로의 확장이 필수적이다. 본 연구는 뇌졸중 환자를 위한 최적의 맞춤형 재활 전략 수립에 필요한 학문적 토대를 제공한다는 점에서 중요한 의의를 지닌다.</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>ART003304277</t>
         </is>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>국가재난시 전시산업의 협력적 거버넌스 구축에 관한 사회연결망 분석 연구</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>정혜인; KIM BONG-SEOK</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>경상논총</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>한독경상학회</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>본 연구는 국가재난시 전시산업의 협력적 거버넌스 구축을 위한 협력과정별 사회연결망 분석을 통해 각 이해관계자의 네트워크를 구조를 파악하여 현 위치를 알아보고 시사점을 도출하는 데 목적을 두었다. 본 연구에서는 먼저 국가재난의 정의, 전시산업의 특성과 개념을 바탕으로 전시산업의 이해관계자에 대해 정리하였다. 또한, Ansell &amp; Gash 협력적 거버넌스 모형의 선행연구와 협력과정별 이론적 고찰을 바탕으로 국가재난시 전시산업의 현안에 대하여 정리하여, 협력적 거버넌스 구축에 관한 필요성을 제시하였다. 본 연구의 연구문제는 국가재난시 전시산업의 협력적 거버넌스 구축을 위한 협력과정별(면대면대화, 신뢰구축, 이해공유, 협력과정에 대한 참여) 전시산업의 이해관계자 네트워크가 어떻게 형성되는지에 알아보기 위함이다.
 본 연구를 위해 선행연구를 통해 각 협력과정별 2~3개의 설문문항과 총 9개의 문항으로 구성된 설문지를 만들었으며, 40명의 전시산업관련 전문가에게 익명으로 설문조사를 실시하였다. 유효표본 34부를 NetMiner 4.0 프로그램을 이용하여 사회연결망분석을 하였다. 연구결과, 국가재난시 전시산업의 컨트럴타워의 부재는 여러 협력과정을 구축하는 데 어려움이 많다는 점을 알 수 있었다. 또한 산업통상부를 비롯하여 전시산업진흥회가 주축이 되어 각 4대 전시관련 협단체와 전시사업자들 간 협력적 거버넌스 구축을 해야 한다는 점을 도출할 수 있었다.
 종합적으로, 국가재난시 전시산업의 협력적 거버넌스 구축을 위한 협력과정은 수평적인 네트워크를 구축해야하며, 수평적인 관리조직으로서 기능 및 역할이 강화될 필요가 있다.  추후 국가재난 등 전시산업에 위기가 재 발생하였을 때, 이해관계자들의 결속력을 증가할 수 있는 컨트롤타워 등이 마련되어야 할 것이다.</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>ART003327683</t>
         </is>
       </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>보건의료정보관리사 실습 경험 대학생의 실습 역량 인식과 요구에 관한 의미 연결망 분석</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Lee Hye Seung; Park Hyun Rin</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>인문사회과학연구</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>국제인문사회연구학회</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>보건의료정보관리사 실습 경험 대학생의 실습 역량 인식과요구에 관한 의미 연결망 분석
 이 혜 승ㆍ박 현 린
@@ -1906,1072 +2492,466 @@
 핵심어: 보건의료정보관리사, 역량 인식, 실습, 의미연결망 분석, 넷마이너</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>ART003329762</t>
         </is>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>초등학교 식물의 뿌리, 줄기, 잎에서 교사의 지도 개념과 학생의 획득 개념 네트워크</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>JINJOO KWAK; Kim, Youngshin; Yoo Dayeon</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>초등과학교육</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>한국초등과학교육학회</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>본 연구의 목적은 초등학교 과학 ‘식물의 구조와 기능’ 단원을 대상으로 교사의 지도 개념과 학생의 획득 개념을 개념 네트워크 분석을 통해 비교?분석하는 데 있다. 이를 위해 대구광역시에 소재한 초등학교 6학년 학생57명과 교사 3명을 연구 대상으로 선정하였다. 교사의 지도 개념은 실제 수업을 녹음?전사하여 수집하였고, 학생의 획득 개념은 수업 직후와 수업 4주 후에 실시한 학습 기억 검사지(즉시 기억, 장기 기억)를 통해 수집하였다.
 수집된 자료는 NetMiner 4.0을 활용한 언어 네트워크 분석을 통해 개념 네트워크, 주요 개념 네트워크, 그리고차시 간 및 교사?학생 간 연결 개념 네트워크로 분석하였다. 연구 결과, 교사와 학생은 뿌리, 줄기, 잎, 물, 양분과같은 핵심 개념을 공통적으로 사용하고 있었으나, 개념 네트워크의 구조와 연결 양상에서는 차이를 보였다. 교사는 기능적으로 관련된 개념을 중심으로 비교적 명확한 구조를 형성한 반면, 학생들은 개념 간 기능적 관련성이낮더라도 다양한 개념을 연결하여 네트워크를 구성하는 경향을 보였다. 또한 수업 직후 학생의 개념 네트워크는개념의 나열적 특성이 두드러졌으나, 수업 4주 후에는 후속 학습의 영향으로 개념 간 연결이 확장?재구성되는양상이 나타났다. 특히 아이겐벡터 중심성 분석 결과, 수업 4주 후 학생의 경우 교사 및 수업 직후 학생과는 다른개념이 등장하여 학생의 인지 구조가 시간에 따라 역동적으로 변화함을 확인할 수 있었다. 이러한 결과는 학생의획득 개념이 교사의 지도 개념과 동일한 구조로 형성되지 않으며, 학생의 사전 경험과 후속 학습이 개념 구조형성에 중요한 영향을 미친다는 점을 시사한다. 따라서 효과적인 과학 수업을 위해서는 학생의 개념 네트워크구조를 지속적으로 점검하고, 핵심 개념을 중심으로 개념 간 관계를 명확히 구조화할 수 있는 교수 전략이 필요함을 제안한다.</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>ART003329138</t>
         </is>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>키워드 네트워크 분석 및 토픽모델링을 활용한 중년기 우울 연구동향 분석</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Jeong Moon Kyeong</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>한국융합과학회지</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>한국융합과학회</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>연구목적 본 연구는 키워드 네트워크 분석과 토픽모델링을 활용하여 국내 학술지에 게재된 중년기 우울 연구동향을 분석하는데 목적이 있다. 연구방법 이를 위하여 국내 등재(후보) 학술지에 게재된 222편의 논문을 분석하였다. 논문 분석은 넷마이너(NetMiner) 4.5.1 프로그램을 활용한 키워드 네트워크 분석과 토픽모델링을 통해 수행하였다. 프로그램을 활용하여 저자키워드를 도출하고 이를 토대로 빈도분석, 동시출현 빈도분석, 중심성 분석, 토픽모델링 분석 등을 실시하였다. 결과 연구의 결과는 다음과 같다. 첫째, 스트레스, 불안, 프로그램, 자아존중감, 매개효과가 우울과 관련하여 빈도가 높은 키워드로 나타났다. 둘째, 상담-정신문제, 스트레스-영성, 건강-스트레스, 사회적 지지-스트레스 등이 동시출현 빈도가 높은 키워드로 확인되었다. 셋째, 중년기 우울 토픽은 총 5개의 토픽으로 도출하였다. 결론 본 연구의 결과는 향후 중년기 우울 연구를 위한 기초자료를 제공하고, 중년기 우울에 필요한 방안 마련에 기여할 것으로 보인다.</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>ART003325981</t>
         </is>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>키워드 네트워크 분석을 활용한 영유아교사 관련 연구 동향 분석: 놀이중심 영유아교육과정 실행 이후 연구물을 중심으로</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>An, Ji-su; Nam, Ki-Won</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>열린유아교육연구</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>한국열린유아교육학회</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>본 연구는 키워드 네트워크 분석을 활용하여 놀이중심 영유아교육과정 실행 이후영유아교사 관련 연구 동향을 살펴보는 데 목적이 있다. 이를 위해 RISS에서 2019 개정 누리과정 및 제4차 표준보육과정이 실행된 2020년부터 2024년 하반기까지 ‘유치원/어린이집/유아/영아/보육교사’ 키워드로 검색된 1,663편의 총 233개의 키워드를NetMiner 4.0 프로그램을 사용하여 키워드 네트워크 분석을 실시하였다. 연구 결과, 상위 출현 빈도 키워드는 ‘교사-영유아상호작용’, ‘직무만족’, ‘교사효능감’ 순으로 나타났다. 다음으로 네트워크 중심성 분석 결과, 연결중심성과 근접중심성의 상위 키워드는 ‘교사효능감’, ‘직무만족’, ‘교사-영유아상호작용’로 나타났으며, 매개중심성은 ‘직무스트레스’로 나타났다. 이러한 결과는 교육과정의 변화에 따라 영유아교사 관련 연구는 교육과정 실천역량 기반으로 활발하게 이루어졌으며, 이를 지원하기 위해서는 그매개가 되는 교사의 정서적 지원을 돕는 정책적 접근이 필수적임을 시사한다. 또한유보통합이 추진되는 현시점에서 영유아교사를 위한 실질적인 제도 및 정책적 지원방안 모색의 근거를 제공할 것으로 기대된다.</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>ART003313264</t>
         </is>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>키워드 네트워크를 활용한 뉴로피드백 연구 동향</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Hye-Jeong Lee; Han-Ik Jo</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>한국산학기술학회논문지</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>한국산학기술학회</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>10.5762/KAIS.2026.27.3.672</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>본 연구는 2005년부터 2024년까지 국내 뉴로피드백 연구의 동향을 파악하기 위해 키워드 네트워크 분석을 실시하였다. KCI 등재 학술지 117편에서 356개의 키워드를 추출하여 Excel과 NetMiner 4x64를 활용해 중심성 및 구조적공백 분석을 수행하였다. 분석 결과, 전체 시기에서 뇌파, 주의집중력, 뇌기능이 높은 중심성을 보여 뉴로피드백 연구의핵심축을 형성하고 있음을 확인하였다. 또한 구조적 공백 분석 결과, 주의집중력, 뇌파, 주의력결핍과잉행동장애가 높은값을 보여 다양한 연구 영역을 연결하는 중개자 역할을 수행하는 주요 키워드로 나타났다. 시기별 분석 결과, 1기에는정서, 자가훈련, 만다라, 명상 등 심리·생리적 자기조절 연구가 주를 이루었고, 2기에는 윈도우크기, 채널, 뇌-컴퓨터인터페이스 등 기술적 연구가 두드러졌다. 3기에는 주의력결핍과잉행동장애, 불면증, 융합교육, 공감각학습, 창의력 등 임상 및 교육 융합 연구가 활발하였으며, 4기에는 치매, 틱, 디지털콘텐츠 등 융합기술 중심의 연구로 확대되었다. 본 연구는 국내 뉴로피드백 연구가 EEG 중심의 접근을 넘어 다양한 신경영상 기술과의 융합 및 국가 차원의 연구 지원이 필요함을 제언하였다.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>W7153999291</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>ART003319763</t>
         </is>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>Exploring research trends in moral resilience using topic modeling</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Eun-jun Park; Eunju Kwak; Seungmi Park</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>The Journal of Korean Academic Society of Nursing Education</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>10.5977/jkasne.2026.32.1.94</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>Purpose: This study aimed to identify research trends in moral resilience in healthcare through text network analysis and topic modeling of abstracts published in domestic and international journals and to propose future research directions.Methods: A quantitative content analysis was conducted on English abstracts of studies related to moral or ethical resilience in healthcare published through May 2025. Sixty-three papers were selected after removing duplicates, and screening was conducted using eight databases: KISS, RISS, DBpia, KCI, CINAHL, Embase, PubMed, and Web of Science. Texts were analyzed using NetMiner 4.5.1 for keyword co-occurrence network construction and Latent Dirichlet Allocation topic modeling. Core keywords were identified using degree and centrality indices, and topics were named through researcher consensus.Results: Research on moral resilience in healthcare began in 2013 and has increased rapidly after 2023, particularly after the coronavirus disease 2019 pandemic. Among 230 extracted keywords, “moral resilience,” “moral distress,” and “care” showed the highest centrality. Five major topics were identified: (1) moral resilience and burnout in practice, (2) moral resilience among nursing students, (3) moral competence and fatigue in practice, (4) moral resilience assessment, and (5) moral injury and secondary traumatic stress among healthcare workers.Conclusion: Moral resilience reflects the ethical strength that enables healthcare professionals to sustain integrity amid moral adversity. Although the number of international studies has increased, domestic research remains limited. Further work should clarify this concept, develop training programs, and explore organizational strategies to strengthen moral resilience.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>W7133355384</t>
         </is>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>Thematic structure of clinically oriented prefrontal function assessment and intervention research: a keyword network analysis</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Jin Seok Oh; Jong-Gab Ho; Jin‐Hyuck Park</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>BMC Psychiatry</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>BioMed Central</t>
         </is>
       </c>
-      <c r="E33" t="n">
+      <c r="E44" t="n">
         <v>2026</v>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>10.1186/s12888-026-08277-6</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>BACKGROUND: The prefrontal cortex (PFC) has been extensively investigated in relation to higher-order cognition, emotional regulation, and behavioural control, particularly within clinically oriented studies addressing psychiatric symptoms, self-regulation, and intervention outcomes. Although a growing body of literature has examined prefrontal function assessment and intervention, the thematic organization and structural interconnections within this clinically focused literature have not been sufficiently clarified. Mapping these conceptual relationships may help identify dominant research concentrations and underrepresented areas within the retrieved literature. METHODS: A total of 1,301 peer-reviewed articles published between January 2014 and December 2024 were retrieved from Web of Science, PubMed, and Embase. After keyword extraction and standardization, the top 52 high-frequency terms were analyzed using NetMiner 4.0. Network indices including density, inclusiveness, and average path length were calculated, together with degree and betweenness centrality. Cohesive subgroup analysis was additionally performed to identify thematic clusters within the keyword network. RESULTS: The keyword network demonstrated a density of 0.408, inclusiveness of 1.0, and an average distance of 1.621, indicating a highly connected structure without isolated nodes. Central hubs included Cognition, Depressive disorders, Randomized controlled trial, Cognitive behavioural therapy, and Psychotherapy, which emerged as the principal structural hubs, suggesting that the retrieved literature was strongly concentrated on standardized cognitive assessment and clinically applied intervention frameworks. Mobile health, E-health intervention, and Chronic illness group also showed substantial structural influence. Cohesive subgroup analysis identified seven differentiated thematic clusters spanning cognitive rehabilitation, emotional regulation, psychotherapy, digital self-management, mindfulness-based executive support, stress resilience, and neurocognitive motivation. CONCLUSIONS: The retrieved literature analyzed in this study exhibited a strongly interconnected thematic structure centered on clinically oriented assessment and intervention domains. Because direct neuroimaging and neurophysiological modalities were comparatively less represented in the retrieved dataset, the present findings should be interpreted as a structural mapping of clinically weighted prefrontal function research rather than a comprehensive representation of the entire methodological landscape. Nevertheless, this network-based analysis provides a systematic overview of current thematic concentrations and offers a useful foundation for future comparative and longitudinal investigations. CLINICAL TRIAL NUMBER: Not applicable.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>https://openalex.org/W7164572335</t>
         </is>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>태권도원 활성화를 위한 사용자 경험 구조 탐색: 텍스트마이닝의 적용</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Kyo-Sik Kim; Park Kyeong Hoon; YunHo KIM</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>운동재활복지</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>한국운동재활복지협회</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>10.66298/kerwa.2026.7.1.137</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>이  연구는  텍스트마이닝  기법을  적용하여  태권도원  방문객  리뷰에  나타난  사용자  경험의  구성   요소와  구조적  특징을  탐색하는  것을  목적으로  하였다. 태권도원  관련  온라인  리뷰를  분석  대상으로   선정하여  총  898개의  리뷰를  수집하였고  TF와  TF-IDF, LDA, NetMiner 4.0을  활용하여  분석하였다.
 연구결과  첫째, TF-IDF 분석결과  ‘최고’가  114.1로  가장  높은  값을  보였고  ‘아이’, ‘공연’, ‘태권도’ 순으로  나타났다. 다음  토픽별  비중을  비교한  결과  토픽  수는  5개로  설정했을  때  일관성지수가   0.483으로   가장   높게   나타났으며   최적   토픽   수는   5개로   설정하였다. 둘째, 토픽별   키워드   연결중심성  산출결과  토픽  1은  모노레일  0.937, 전망대  0.826, 체험  0.569 순으로  나타났고  토픽  2는   태권도  0.449, 시설  0.354. 프로그램  0.263 순으로  나타났다. 토픽  3은  태권도  1.713, 공연  1.369, 아이   0.970 순으로  나타났고  토픽  4는  태권도  0.635, 공연  0.521, 전망대  0.426 순으로  나타났고  토픽  5는   공연  0.534, 모노레일  0.459, 태권도  0.374 순으로  나타났다. 마지막으로  토픽별  핵심  주제어  도출   결과  토픽  1은  전망대, 모노레일, 셔틀버스, 카페  등의  키워드로  관광지  내  이동  및  편의시설로   선정하였고  토픽  2는  프로그램, 세계, 수련  등의  키워드로  글로벌  수련  프로그램  및  환경으로   선정하였다. 토픽   3은   태권도, 공연, 아이   등의   키워드로   태권도   공연   및   체험형   관광으로   선정하였고  토픽  4는  최고, 장소, 시간  등의  키워드로  방문객  경험  및  만족으로  선정하였고  토픽  5는   시범, 경치, 산  등의  키워드로  태권도  시범과  자연환경으로  선정하였다. 이  연구를  통해  태권도원의   구조적  문제를  파악하여  이용자  관점에서  요구되는  개선  방향을  도출함으로서  향후  태권도원  운영   및  활성화  전략  마련에  필요한  기초자료를  제공할  수  있을  것이다.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>W7151814546</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>ART003323168</t>
         </is>
       </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>A Topic Modeling Analysis of South Korea-China Relations under the Yoon Suk-yeol Administration: Evidence from News Big Data (2022~2025)</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>Yang, Zhao; Yu-Bo Zhou</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>The International Journal of Internet, Broadcasting and Communication</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>국제인공지능학회</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>10.7236/IJIBC.2026.18.1.131</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>This study analyzes South Korea?China relations discourse in major Korean news media during the Yoon Sukyeol administration (May 2022?April 2025). Using 1,023 articles on “Korea?China relations” from seven conservative and progressive outlets, it applies NetMiner-based LDA topic modeling, keyword network, and time-series analyses to derive seven core topics. “High-level Visits and Diplomatic Consultations” forms the agenda core, followed by “High-level South Korea?China diplomacy and ROK?US?Japan balancing in the Indo-Pacific context” and “Diplomatic Frictions and Controversies over Ambassadorial Remarks”. In contrast, economic?technological cooperation and socio-cultural exchange remain peripheral and episodic.
 Overall, the findings show that under Yoon, South Korea?China relations were structurally re-centered on diplomacy, security, and politics, and that Korean media coverage fluctuated in line with U.S.?China strategic rivalry and deepening U.S.?ROK?Japan cooperation, highlighting the need to institutionalize high-level communication and pre-emptively manage diplomatic frictions.</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>ART003309917</t>
         </is>
       </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>키워드 네트워크 분석을 통한 국내 미술치료사 연구의 지식구조 탐색</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Lee, Ji Yeon; Shon, Chang Bea</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>미술치료연구</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>한국미술치료학회</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>10.35594/kata.2026.33.2.010</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>미술치료사를 대상으로 한 연구는 꾸준히 증가해 왔으나, 이들 연구의 지식구조를 체계적으로 분석한 연구는부족한 실정이다. 이에 본 연구는 키워드 네트워크 분석을 활용하여 국내 미술치료사 연구의 지식구조를 탐색하는 데 목적이 있다. 분석 대상 논문에서 추출한 키워드를 바탕으로 NetMiner를 활용하여 출현빈도, 동시출현빈도, 중심성, 응집성 분석을 수행하였다. 연구 결과, 미술치료사 연구는 점진적으로 증가하였으며, 내러티브탐구, 경험, 미술작업 등이 높은 출현빈도를 보였다. 동시출현빈도에서는 내러티브탐구-자전적연구, 내러티브탐구-미술작업, 능력-역전이관리, 완화-의료-호스피스 등의 조합이 빈번하게 나타났다. 중심성 분석에서 내러티브탐구가 전반적으로 가장 높은 값을 보였으며, 경험과 미술작업이 이와 긴밀하게 연결되어 네트워크의 중심 구조를 형성하였다. 응집성 분석에서는 의료?완화 실천, 집단 및 직무 맥락, 전문성?윤리 담론, 질적연구 기반 임상?발달탐구의 네 개 하위 집단이 경험과 내러티브탐구를 매개로 상호 연결되는 통합적 구조를 이루고 있었다. 이러한결과를 바탕으로 본 연구의 의의와 제한점에 대하여 논의하였다.</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>ART003324682</t>
-        </is>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Exploring Trends in Research on Athletes’ Mental Health Using Keyword Network Analysis: Based on Web of Science</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Sihong Sui; Ziwei Liang; Wanghui Li; Juzhi Liang; Zhenbo Zhang; Bin Liu</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Asia Pacific Journal of Applied Sport Sciences</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>아시아스포츠융합과학회</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>2026</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>PURPOSE This study examines core keywords in athlete mental health research, explores trends over time, and identifies interactions among sub-fields. METHOD NetMiner was used to analyze keyword co-occurrence networks based on 1,139 journal articles published from 1992 to 2024 and available in the Web of Science. Degree and betweenness centrality were used to track keyword importance and evolution. Cohesive subgroup analysis was applied to identify thematic clusters. RESULT Keywords such as "athlete," "health," "sport," "performance," "stress," "anxiety," and "intervention" remained central over 30 years, highlighting key research focuses. While early studies emphasized performance and injury, recent work has shifted toward mental health support and career development, with terms such as "support," "well-being," and "identity" emerging. Six thematic groups were identified: youth development, health risks, identity and career, rehabilitation, support systems, and physical function. CONCLUSION Keyword network analysis reveals the evolving landscape of research on athletes’ mental health. The field has expanded from performance-focused topics to a broader, interdisciplinary emphasis on psychological support and long-term well-being.</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>ART003335881</t>
-        </is>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>코비6 농구화의 소비자 인식 구조 분석: 텍스트마이닝 기반 의미연결망 및 CONCOR 분석</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Leehyungju</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>융합과 통섭</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>미래융합통섭학회</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>2026</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>연구목적 본 연구는 온라인 텍스트 데이터를 활용하여 코비6 농구화에 대한 소비자 인식 구조를 분석하는 데 목적이 있다. 구체적으로 텍스트마이닝, 의미연결망 분석 및 CONCOR 분석을 통해 코비6 농구화와 관련된 주요 키워드, 의미 관계 및 인식 군집을 살펴보고자 하였다. 연구 방법 본 연구는 2020년 1월 26일부터 2025년 12월 31일까지 네이버 블로그, 네이버 카페, 온라인 커뮤니티, 뉴스 기사에서 코비6 농구화 관련 온라인 텍스트 데이터를 수집하였다. 검색어는 ‘코비6’, ‘코비 농구화’, ‘코비 프로트로’, ‘Kobe 6’, ‘Kobe basketball shoes’ 등을 활용하였다. Textom은 자료 수집, 전처리, 키워드 빈도분석 및 N-gram 분석에 활용하였고, NetMiner는 의미연결망 분석, 연결중심성 분석 및 CONCOR 분석에 활용하였다. 중복 문서, 불용어, 관련성이 낮은 텍스트, 광고성 게시물은 분석에서 제외하였다. 결과 분석 결과, ‘코비’, ‘코비6’, ‘농구화’는 전체 네트워크에서 중심적인 키워드로 나타났다. ‘착화감’, ‘쿠셔닝’, ‘접지력’, ‘디자인’은 제품 성능 인식과 관련된 키워드로 확인되었으며, ‘리셀’, ‘가격’, ‘구매’, ‘출시’는 소비 및 시장 관련 인식을 반영하는 키워드로 나타났다. CONCOR 분석 결과, 코비6 농구화 관련 키워드는 제품 및 소비 관련 인식 군집과 제품 특성 및 성능 인식 군집으로 구분되었다. 결론 본 연구 결과, 코비6 농구화는 기능적 성능, 브랜드 상징성, 선수 이미지, 희소성 및 리셀 시장 가치가 결합된 상징적 스포츠 제품으로 인식되고 있는 것으로 나타났다. 본 연구는 특정 선수의 시그니처 농구화에 대한 온라인 소비자 인식이 제품 성능과 소비·시장 가치의 두 축을 중심으로 구조화되어 있음을 보여준다는 점에서 스포츠용품 소비 연구에 기여한다.</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>ART003345135</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>키워드 네트워크 분석 및 토픽모델링을 활용한 청년 1인가구 연구동향 분석</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Jeong Moon Kyeong</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>한국웰니스학회지</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>한국웰니스학회</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>10.21097/ksw.2026.5.21.2.105</t>
-        </is>
-      </c>
-      <c r="G39" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>본 연구의 목적은 키워드 네트워크 분석과 토픽모델링을 활용하여 청년 1인가구를 주제로 한 국내 학술 연구의 동향을 체계적으로 분석하는 것이다. 이를 위해 NetMiner 4.5.1의 확장 프로그램인 Biblio Data Collector(이하 BDC)를 통해 수집한 논문 95편을 대상으로 키워드 빈도분석, 동시출현 빈도분석, 중심성 분석, 토픽모델링을 수행하였다. 연구의 결과 첫째, 빈도분석에서는 우울, 주거환경, 소득, 공유주택, 외로움 순으로 높은 빈도를 보였다. 둘째, 동시출현 빈도분석에서는 라이프스타일-삶의 만족도이 가장 높은 동시출현 빈도를 보였다. 셋째, 중심성 분석에서는 우울과 주거환경이 연결·근접·매개중심성 모두에서 1, 2위를 차지하여 연구 네트워크의 핵심 허브 역할을 담당하고 있음이 확인되었다. 넷째, 토픽모델링 분석에서는 정신건강과 심리적 특성, 일상생활과 사회적 지지, 사회적 고립과 심리적 위기, 외로움과 사회적 자원 부족, 코로나19 전후 생활 변화와 건강, 대안적 주거 환경과 주거 만족의 6개 토픽이 도출되었다. 본 연구의 결과는 청년 1인가구 후속 연구를 위한 기초자료를 제공하고, 청년 1인가구를 위한 정책 마련에 기여할 것으로 보인다.</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>ART003340143</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>텍스트 네트워크 분석 기반 아동 구강건강 연구동향 분석</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Kim Seol Hee</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>한국건강사회융합연구</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>웰다잉융합연구소</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>2026</v>
-      </c>
-      <c r="G40" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>본 연구는 최근 10년간 국내 아동 구강건강 관련 연구를 대상으로 텍스트 네트워크 분석을 수행하여 주요 연구 주제와 지식 구조를 규명하고자 하였다. 연구대상은 학술연구정보서비스에서 아동과 구강을 검색어로 하여 최근 10년, KCI 등재, 한국어, 원문 제공 조건을 충족하는 44편의 논문이다. 수집된 논문의 키워드를 정제한 후 NetMiner 4 프로그램을 활용하여 키워드 빈도분석, 연결중심성 분석, 네트워크 군집분석을 수행하였다. 연구결과, 키워드 빈도분석에서는 아동, 구강건강이 가장 높은 빈도로 나타났고, 구강건강조사, 치아우식증, 칫솔질, 구강운동기능 등이 주요 키워드로 확인되었다. 연결중심성 분석에서는 아동, 구강건강, 치아우식증, 구강건강행동, 부모가 핵심 노드로 나타나 아동 구강건강 연구가 질병, 행동, 보호자 요인을 중심으로 전개되고 있음을 확인하였다. 군집분석 결과, 연구 주제는 치아우식증 및 구강질환, 구강건강행동 및 부모 요인, 장애 아동 구강기능·중재, 구강보건교육 예방·관리의 네 가지 영역으로 구조화되었다. 한편 디지털 헬스케어 및 인공지능 관련 키워드는 주요 네트워크에서 명확하게 확인되지 않아 해당 분야 연구가 제한적인 것으로 확인되었다. 본 연구는 국내 아동 구강건강 연구의 지식구조를 체계적으로 제시하고, 분석 결과를 기반으로 인공지능 기반 구강관리 전략의 적용 방향을 제언하였다는 점에 의의가 있다.</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>ART003339594</t>
-        </is>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>텍스트마이닝을 활용한 교육실습 경험의 구조 분석: 관계, 수업, 성찰을 중심으로</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Lee, Jin-Yung; Son, Eun-Young</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>교원교육</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>교육연구원</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>10.14333/kjte.2026.42.3.31</t>
-        </is>
-      </c>
-      <c r="G41" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>연구목적: 본 연구는 중등예비 교사들의 교육실습 성찰 에세이를 텍스트마이닝 기법으로 분석하여 예비 교사의 경험과 정서, 그리고 의미구조를 체계적으로 도출하고자 하였다.
-연구방법: 이를 위해 2022년부터 2025년까지 중학교와 고등학교에서 교육실습에 참여한 예비 교사 180명의 성찰 에세이를 수집하고, NetMiner 4.5를 활용하여 키워드 네트워크 분석과 토픽모델링을 수행하였으며, RStudio 4.4.3을 활용하여 토픽모델링 결과를 보완⋅검증하였다.
-연구결과: 분석결과, ‘경험’을 중심으로 교육실습과 관련된 ‘불안, 참관, 교과’ 등의 키워드가 도출되었고, 실습과정에서 경험하는 ‘관계, 지도, 계획, 노력’ 등의 핵심 키워드가 도출되었다. PFnet 분석에서는 ‘경험’, ‘불안’, ‘참관’, ‘관계’, ‘고민’이 중심 개념으로 나타났다. 연결중심성과 근접중심성 분석 결과, ‘경험’을 중심으로 다양한 활동과 상호작용이 이루어지며 긍정적 정서와 성장 가능성, 그리고 인식의 변화가 나타났다. 토픽모델링 분석을 통해 교육실습 경험은 수업참여 및 학습 경험, 교직경험과 진로 인식, 상담 및 관계 형성의 어려움, 학급 운영과 수업 불안의 네 가지 주제로 나타났다.
-결론: 본 연구는 예비 교사의 교육실습 경험을 데이터 기반으로 분석하여 그 의미 구조를 체계적으로 탐색하고, 교육과정 개선과 현장 연계 강화, 상담적 지원을 위한 기초자료를 제공하였다는 점에 의의가 있다.</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>ART003340926</t>
-        </is>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Typology of Public-Private Partnerships in Integrated Care: Evidence from a Municipality in Seoul, Korea</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Il-Ho Kim; Cheong-Seok Kim; Bon Kim; Dong Hee Joo</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>International Journal of Integrated Care</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Ubiquity Press</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>10.5334/ijic.9045</t>
-        </is>
-      </c>
-      <c r="G42" s="1" t="n">
-        <v>46198</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Objectives: Despite the significant advantages of public-private partnerships (PPPs), understanding of the organisational roles that shape partnership functioning within integrated care networks remains limited. This study investigated the structural characteristics of PPPs and identified organisational roles within an integrated care network in a Seoul district, Korea.Methods: Using the 2020 Integrated Care Network Survey, this study analyzed modularity, eigenvector centrality, and brokerage in 82 public and private organisations across five different types: district offices, public health centres, healthcare institutions, social welfare institutions, and community organisations. Results: Our results reveal that integrated care organisations are predominantly divided into two major networks: disability care and elderly care. The highest centrality in the elderly care network is occupied by the dementia relief centre and social welfare institutions, while the disability care network is dominated by public institutions, the Health and Welfare Cooperative, and a social service centre for the disabled. Regarding organisational roles, social welfare institutions function primarily as coordinators, representatives, and gatekeepers, whereas public institutions-including district offices, public health centres, and community service centres-serve as consultants and liaisons. Notably, public institutions assume more prominent roles and private organisations demonstrate less involvement in the disability care network compared to the elderly care network. Conclusion: These findings underscore the importance of defining clear organisational roles and interaction mechanisms between public and private sectors, offering valuable insights for policy design aimed at enhancing coordination, accountability, and sustainability within PPP-based integrated care systems.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>https://openalex.org/W7131795813</t>
-        </is>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>국내 비약물 중재 연구의 핵심어 네트워크 구조 분석: 경도인지장애와 치매 대상 연구의 주제 차이를 중심으로</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Park, Chi-Soo; Yoo, Doo-Han</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>대한보조공학기술학회지</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>대한보조공학기술학회</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>2026</v>
-      </c>
-      <c r="G43" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>목적 : 본 연구는 주제어 네트워크 분석을 활용하여 최근 10년간(2015-2025년) 국내에서 수행된 경도인지장애(Mild Cognitive Impairment, MCI) 및 치매 환자를 위한 비약물 중재 연구의 동향을 파악하고 두 집단 간의 차이를 비교하고자 하였다.
-연구방법 : 한국교육학술정보원(RISS)을 통해 수집한 251편(MCI 91편, 치매 160편)의 논문에서 주제어를 추출하였으며, 빈도분석, 연결 중심성 분석, 응집성 분석을 NetMiner 4.0을 활용하여 수행하였다.
-결과 : 빈도분석 결과, MCI 연구에서는 '인지기능', '치매', '인지중재'가, 치매 연구에서는 '인지기능', 'MCI', '우울'이 다빈도 주제어로 나타났다. 연결 중심성 분석에서 MCI는 인지중재(0.575), 우울(0.493), 신체활동(0.452)을 중심으로, 치매는 체계적 문헌고찰(0.454), 인지기능(0.351), 우울(0.339)을 중심으로 연구가 수행되었다. 응집성 분석에서 MCI는 5개, 치매는 7개의 클러스터로 분류되었으며, 디지털 중재와 지역사회 클러스터가 두 집단에서 공통적으로 나타났다. 그러나 MCI에서는 자가 관리 역량 강화를 목적으로 한 디지털 중재가, 치매에서는 부양 부담 경감 및 안전 모니터링 기반 기술이 강조되는 등 적용 목적에서 차이를 보였다.
-결론 : MCI 연구는 예방과 기능 회복에, 치매 연구는 BPSD 관리와 부양자 지원에 초점을 맞추고 있어 두 집단의 병태생리학적 특성을 반영한 차별화된 중재 전략이 필요함을 확인하였다. 향후 연구에서는 두 집단의 특수성을 고려한 맞춤형 중재 개발이 활발히 이루어져야 할 것이다.</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>ART003331207</t>
-        </is>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>키워드 네트워크 분석 및 토픽모델링을 활용한 노인 1인가구 관련 연구동향 분석</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>YOUNGSIL YUN; Jeong Moon Kyeong</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>한국과 국제사회</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>한국정치사회연구소</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>10.22718/kga.2026.10.2.019</t>
-        </is>
-      </c>
-      <c r="G44" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>본 연구는 키워드 네트워크 분석과 토픽모델링을 활용하여 국내 노인 1인가구 관련 연구동향을 분석하는 데 목적이 있다. 이를 위해 국내 KCI 등재(후보) 학술지에 게재된 노인 1인가구 관련 논문 111편을 대상으로 넷마이너(NetMiner 4)를 이용하여 키워드 네트워크 분석과 토픽모델링을 수행하였다. 키워드 네트워크 분석에서는 키워드 빈도분석과 동시출현 분석을 실시하고 연결중심성, 근접중심성, 매개중심성을 산출하여 핵심 개념의 구조를 분석하였다. 분석 결과, 사회적 관계, 우울, 정책, 지원, 삶의 만족 등이 주요 키워드로 나타났다. 토픽모델링 분석에서는 총 4개의 토픽이 도출되었다. 토픽-1은 사회적 지지와 돌봄을 통한 노년기 삶의 질, 토픽-2는 경제 및 주거 조건과 빈곤 문제, 토픽-3은 사회참여와 공동체 활동을 통한 능동적 삶, 토픽-4는 우울과 건강 상태를 중심으로 한 심리·정서적 위기와 관련된 주제로 나타났다. 이러한 결과는 노인 1인가구 연구가 경제적 조건과 사회적 관계를 중심으로 사회참여와 정신건강 등 다양한 주제로 확장되어 왔음을 보여준다. 본 연구는 국내 노인 1인가구 연구의 주요 주제와 지식 구조를 체계적으로 제시하고, 향후 연구 방향을 위한 기초자료를 제공한다는 점에서 의의를 가진다.</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>ART003332640</t>
-        </is>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>학교스포츠클럽에 대한 언론보도 변화 분석 - 텍스트마이닝을 활용한 빅데이터 분석을 중심으로 -</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>MINSU JE; Kim In Hyung</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>한국스포츠사회학회지</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>한국스포츠사회학회</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>10.22173/ksss.2026.39.specialissue.6</t>
-        </is>
-      </c>
-      <c r="G45" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>본 연구는 학교스포츠클럽 관련 언론 보도의 변화를 텍스트 마이닝 기법을 활용하여 분석하였다. 2007년부터 2023년까지 빅카인즈를 통해 수집된 7,922개의 언론 보도 기사를 바탕으로 27,286개의 키워드를 추출하고, 시기별(1기: 2007- 2011, 2기: 2012-2018, 3기: 2019-2023) 핵심 주제어의 변화를 분석하였다. 넷마이너 4.5 프로그램을 사용하여 TF-IDF 분석, 의미연결망 분석 및 네트워크 시각화 분석을 수행하였다. 이를 통해 도출된 결론은 다음과 같다. TF-IDF 분석에서는 제1기에는 체육, 참여, 지원 등이, 제2기에는 교육, 지역, 종목 등이, 제3기에는 건강, 체력, 코로나 등이 중요한 키워드로 도출되어 시기별 관심 주제의 차이를 확인할 수 있었다. 의미연결망 분석에서는 제1기에는 스포츠, 체육, 학교, 학생, 교육, 운영, 활성, 건강, 참여 순으로 높은 연결 중심성 지수가 나타났다. 제2기에는 스포츠, 학교, 학생, 활동, 대회, 인성, 폭력, 여학생, 시설 등의 순으로 중심성이 높게 나타났다. 제3기에는 스포츠, 체육, 학교, 학생, 건강, 대회, 코로나, 운동, 온라인, 소통 등의 순으로 연결 중심성이 확인되었다. 이를 통해 학교스포츠클럽 관련 언론 보도는 시기별 정책 환경과 사회적 이슈 변화에 따라 핵심 키워드와 연결 구조가 달라졌음을 확인하였다.</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>ART003326639</t>
-        </is>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>What do patients value? A retrospective study of compliment letters from a single institution</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Y.-J. Kwon; Myeong Namgung; Mi Kyung Kim; Jae Chol Choi; Daun Jeong; Chan Woong Kim</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>BMJ Open</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>BMJ</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>10.1136/bmjopen-2025-101505</t>
-        </is>
-      </c>
-      <c r="G46" s="1" t="n">
-        <v>46198</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>OBJECTIVES: This study aimed to analyse patient-initiated compliment letters from a single institution, identify the key elements that patients value and offer actionable insights to enhance patient-centred care. DESIGN: A retrospective, single-institution study using the Healthcare Complaints Analysis Tool (HCAT), text network analysis and latent Dirichlet allocation (LDA) topic modelling on patient compliment letters to pinpoint key valued care elements. SETTING: A newly established general hospital in Gwangmyeong, South Korea, opened on 22 March 2022. PARTICIPANTS: A total of 1213 compliment letters were collected through the hospital's feedback system, which accepted both online and on-site submissions between 25 March 2022 and 28 June 2024. Letters lacking substantive descriptive content and those containing purely administrative requests were excluded. PRIMARY AND SECONDARY OUTCOME MEASURES: The HCAT was adapted to categorise positive statements into clinical, management and relationship domains, along with six stages of care. Inter-rater reliability was evaluated using Gwet's AC1 statistic. A text network analysis, applying a term frequency-inverse document frequency approach, was conducted to identify prominent keywords. Subsequently, LDA was performed to extract thematic topics. RESULTS: Most compliments concerned the 'relationship' domain (62%), particularly during the care in the ward stage (56%). Keyword analysis indicated that the most frequently mentioned terms were 'gratitude', 'kindness', 'nurse', 'doctor' and 'heart/mind', underscoring patients' high valuation of positive interactions, professional competence and compassionate communication with medical staff. Topic modelling identified three primary topics, namely, 'appreciation of nursing care' (39%), 'professionalism in surgery and treatment' (35%) and 'effective communication during consultations' (26%). CONCLUSIONS: Positive relationships with medical staff, particularly kindness, professionalism and effective communication, influence patient satisfaction. Patient compliment letters serve as important indicators of exceptional care and can inform quality improvement initiatives. Healthcare institutions should leverage these insights to enhance patient-centred services by strengthening patient-provider relationships and promoting a culture of excellence.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>https://openalex.org/W7135066543</t>
-        </is>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
         <v>0</v>
       </c>
       <c r="O46" t="n">
@@ -2986,39 +2966,42 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>간호대학생의 취업준비 스트레스 연구동향과 개념구조: 텍스트 네트워크 분석을 중심으로</t>
+          <t>키워드 네트워크 분석을 통한 국내 미술치료사 연구의 지식구조 탐색</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Yu, Ga Eul; park sook kyoung</t>
+          <t>Lee, Ji Yeon; Shon, Chang Bea</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>한국간호연구학회지</t>
+          <t>미술치료연구</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>한국간호연구학회</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>2026</v>
-      </c>
-      <c r="G47" s="1" t="n">
-        <v>46204</v>
+          <t>한국미술치료학회</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>10.35594/kata.2026.33.2.010</t>
+        </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Purpose : This study aimed to examine research trends and explore the conceptual structure of employment preparation stress among nursing students using text network analysis and topic modeling. Methods : A descriptive study was conducted based on the abstracts of 39 Korean studies published between 2015 and 2024.
-Text data were preprocessed through Korean morphological analysis, and keyword co-occurrence matrices were constructed at the document level. Frequency, centrality, and network visualization analyses were performed using NetMiner, and LDA(Latent Dirichlet Allocation) topic modeling was conducted to identify major thematic patterns in the literature. Results : The most frequent keywords were ‘employment preparation stress’, ‘career decision-making self-efficacy’, ‘clinical practice’, ‘career preparation behavior’, and ‘self-efficacy’. Topic modeling identified five topic clusters: psychological stress, career-related cognition and behavior, clinical practice and educational environment, coping and psychological resources, and personal characteristics and emotional responses. Conclusion : Research on employment preparation stress among nursing students has evolved around interconnected psychological, career-related, educational, and personal dimensions. These findings suggest the need for integrated educational strategies that promote career preparation, clinical adaptation, effective coping, and the development of psychological resilience and personal competencies among nursing students.</t>
+          <t>미술치료사를 대상으로 한 연구는 꾸준히 증가해 왔으나, 이들 연구의 지식구조를 체계적으로 분석한 연구는부족한 실정이다. 이에 본 연구는 키워드 네트워크 분석을 활용하여 국내 미술치료사 연구의 지식구조를 탐색하는 데 목적이 있다. 분석 대상 논문에서 추출한 키워드를 바탕으로 NetMiner를 활용하여 출현빈도, 동시출현빈도, 중심성, 응집성 분석을 수행하였다. 연구 결과, 미술치료사 연구는 점진적으로 증가하였으며, 내러티브탐구, 경험, 미술작업 등이 높은 출현빈도를 보였다. 동시출현빈도에서는 내러티브탐구-자전적연구, 내러티브탐구-미술작업, 능력-역전이관리, 완화-의료-호스피스 등의 조합이 빈번하게 나타났다. 중심성 분석에서 내러티브탐구가 전반적으로 가장 높은 값을 보였으며, 경험과 미술작업이 이와 긴밀하게 연결되어 네트워크의 중심 구조를 형성하였다. 응집성 분석에서는 의료?완화 실천, 집단 및 직무 맥락, 전문성?윤리 담론, 질적연구 기반 임상?발달탐구의 네 개 하위 집단이 경험과 내러티브탐구를 매개로 상호 연결되는 통합적 구조를 이루고 있었다. 이러한결과를 바탕으로 본 연구의 의의와 제한점에 대하여 논의하였다.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>ART003352583</t>
+          <t>ART003324682</t>
         </is>
       </c>
       <c r="L47" t="n">
@@ -3039,46 +3022,35 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>대학부 태권도 선수의 랭킹제도 인식 구조 : 키워드 네트워크 분석을 중심으로</t>
+          <t>Exploring Trends in Research on Athletes’ Mental Health Using Keyword Network Analysis: Based on Web of Science</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ha-Young, SHIN; Jiwun Yoon; Jae-Hyeon</t>
+          <t>Sihong Sui; Ziwei Liang; Wanghui Li; Juzhi Liang; Zhenbo Zhang; Bin Liu</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>국기원 태권도연구</t>
+          <t>Asia Pacific Journal of Applied Sport Sciences</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>국기원</t>
+          <t>아시아스포츠융합과학회</t>
         </is>
       </c>
       <c r="E48" t="n">
         <v>2026</v>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>10.24881/tjk.2026.17.2.131</t>
-        </is>
-      </c>
-      <c r="G48" s="1" t="n">
-        <v>46204</v>
-      </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>목적  이 연구의 목적은 2024년부터 도입된 국내 랭킹제도에 대한 대학부 태권도 겨루기 선수의 인식을 확인하는 것에 있다. 나아가 선수들이 인식하는 랭킹제도 관련 개념 간 관계를 구조적으로 제시하여 제도 운영 이해를 위한 기초 자료를 제공하고자 한다.
-방법  이 목적을 달성하기 위해 2024년도 국가대표 최종선발전에 출전한 선수 및 국가대표 선수 선발 최종전에 진출하였거나 입상한 대학부 선수 10명을 대상으로 초점집단면접(Focus Group Interview)을 실시하였다. 이후 NetMiner 4.0을 활용하여 연결중심성을 지표로 분석하였다.
-결과  첫째, 선수들은 랭킹제도의 운영 원칙과 점수 산출 방식 등 제도의 기본 구조에 대해 비교적 명확하게 인식하고 있었다. 둘째, 랭킹 점수 획득을 위한 반복적인 대회 출전 구조는 선수들에게 신체적·심리적 부담과 연관된 인식으로 나타났으며, 이는 제도 선호도 및 평가와 연결되어 인식되고 있었다. 셋째, 공지 및 정보 전달 체계와 관련된 절차적 요소 역시 제도 신뢰와 연관된 인식 요소로 확인되었다.
-결론  대학부 태권도 선수들의 랭킹제도 인식은 제도의 구조적 이해와 실제 운영 경험이 함께 반영된 형태로 나타났다. 이러한 연구 결과는 향후 랭킹제도 운영과 관련된 논의를 위한 기초 자료로 활용될 수 있을 것이다.</t>
+          <t>PURPOSE This study examines core keywords in athlete mental health research, explores trends over time, and identifies interactions among sub-fields. METHOD NetMiner was used to analyze keyword co-occurrence networks based on 1,139 journal articles published from 1992 to 2024 and available in the Web of Science. Degree and betweenness centrality were used to track keyword importance and evolution. Cohesive subgroup analysis was applied to identify thematic clusters. RESULT Keywords such as "athlete," "health," "sport," "performance," "stress," "anxiety," and "intervention" remained central over 30 years, highlighting key research focuses. While early studies emphasized performance and injury, recent work has shifted toward mental health support and career development, with terms such as "support," "well-being," and "identity" emerging. Six thematic groups were identified: youth development, health risks, identity and career, rehabilitation, support systems, and physical function. CONCLUSION Keyword network analysis reveals the evolving landscape of research on athletes’ mental health. The field has expanded from performance-focused topics to a broader, interdisciplinary emphasis on psychological support and long-term well-being.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>ART003350083</t>
+          <t>ART003335881</t>
         </is>
       </c>
       <c r="L48" t="n">
@@ -3099,43 +3071,35 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>토픽모델링을 통한 집단상담 연구동향 분석</t>
+          <t>코비6 농구화의 소비자 인식 구조 분석: 텍스트마이닝 기반 의미연결망 및 CONCOR 분석</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Son, Hye-Seon; Cheon, Seong-Moon</t>
+          <t>Leehyungju</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>재활심리연구</t>
+          <t>융합과 통섭</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>한국재활심리학회</t>
+          <t>미래융합통섭학회</t>
         </is>
       </c>
       <c r="E49" t="n">
         <v>2026</v>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>10.35734/karp.2026.33.2.007</t>
-        </is>
-      </c>
-      <c r="G49" s="1" t="n">
-        <v>46204</v>
-      </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>본 연구는 키워드 네트워크 분석과 토픽모델링을 활용하여 국내 학술지에 게재된 집단상담 관련 연구동향을 분석하는 데 목적이 있다. 이를 위하여 국내 등재 학술지에 게재된 910편의 논문을 분석하였다. 논문 분석을 위하여 넷마이너(NetMiner) 4.5 프로그램을 활용하여 논문에 잠재된 토픽과 키워드를 도출하였다. 본 연구는 전기(2000년-2010년)와 후기(2011-2022년)로 나누어 토픽모델링을 분석하고 토픽 분류결과 동일하게 나타난 토픽 간 연결중심성과 상위단어들의 동시출현단어들을 분석하였다. 또한 전체 집단상담에 대한 토픽 변화추이를 분석하여 연구 주제가 시간 추이에 따라 어떻게 변화하는지를 살펴보았다. 분석결과, 전기에는 학교생활적응 개입, 정서조절 및 적응 개입, 부적응과 가족 요인 개입, 인터넷중독 개입, 진로 개입, 정신건강 개입 등의 토픽이 도출되었으며, 후기에는 정신건강 개입, 정서조절 및 적응 개입, 진로 개입, 매체중독 개입 등의 토픽이 주요 연구주제로 나타났다. 또한 시기별 토픽 추이 분석 결과, 진로 개입과 정서조절 및 적응 개입은 전 기간에 걸쳐 지속적으로 나타난 주요 연구주제로 확인되었으며, 최근에는 정신건강 및 매체중독 관련 연구의 증가가 확인되었다. 이상의 분석결과와 논의를 바탕으로 향후 집단상담 연구에 대한 시사점을 제시하였다.</t>
+          <t>연구목적 본 연구는 온라인 텍스트 데이터를 활용하여 코비6 농구화에 대한 소비자 인식 구조를 분석하는 데 목적이 있다. 구체적으로 텍스트마이닝, 의미연결망 분석 및 CONCOR 분석을 통해 코비6 농구화와 관련된 주요 키워드, 의미 관계 및 인식 군집을 살펴보고자 하였다. 연구 방법 본 연구는 2020년 1월 26일부터 2025년 12월 31일까지 네이버 블로그, 네이버 카페, 온라인 커뮤니티, 뉴스 기사에서 코비6 농구화 관련 온라인 텍스트 데이터를 수집하였다. 검색어는 ‘코비6’, ‘코비 농구화’, ‘코비 프로트로’, ‘Kobe 6’, ‘Kobe basketball shoes’ 등을 활용하였다. Textom은 자료 수집, 전처리, 키워드 빈도분석 및 N-gram 분석에 활용하였고, NetMiner는 의미연결망 분석, 연결중심성 분석 및 CONCOR 분석에 활용하였다. 중복 문서, 불용어, 관련성이 낮은 텍스트, 광고성 게시물은 분석에서 제외하였다. 결과 분석 결과, ‘코비’, ‘코비6’, ‘농구화’는 전체 네트워크에서 중심적인 키워드로 나타났다. ‘착화감’, ‘쿠셔닝’, ‘접지력’, ‘디자인’은 제품 성능 인식과 관련된 키워드로 확인되었으며, ‘리셀’, ‘가격’, ‘구매’, ‘출시’는 소비 및 시장 관련 인식을 반영하는 키워드로 나타났다. CONCOR 분석 결과, 코비6 농구화 관련 키워드는 제품 및 소비 관련 인식 군집과 제품 특성 및 성능 인식 군집으로 구분되었다. 결론 본 연구 결과, 코비6 농구화는 기능적 성능, 브랜드 상징성, 선수 이미지, 희소성 및 리셀 시장 가치가 결합된 상징적 스포츠 제품으로 인식되고 있는 것으로 나타났다. 본 연구는 특정 선수의 시그니처 농구화에 대한 온라인 소비자 인식이 제품 성능과 소비·시장 가치의 두 축을 중심으로 구조화되어 있음을 보여준다는 점에서 스포츠용품 소비 연구에 기여한다.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>ART003350468</t>
+          <t>ART003345135</t>
         </is>
       </c>
       <c r="L49" t="n">

--- a/nm-reference/citations.xlsx
+++ b/nm-reference/citations.xlsx
@@ -522,6 +522,11 @@
       <c r="E2" t="n">
         <v>2026</v>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>10.52902/kjsc.2026.56.35</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>본 연구는 간호대학생의 환자안전역량 관련 연구의 동향과 지식구조를 체계적으로 규명하기 위하여 텍스트 네트워크 분석과 토픽모델링을 적용한 이차자료 분석 연구이다. 기존 연구들이 개별 변수 간 관계나 교육 중재 효과를 중심으로 수행된 것과 달리, 본 연구는 연구 분야 전반의 구조적 특성과 핵심 주제를 통합적으로 파악하고자 하였다. 2015년부터 2025년까지 국내 주요 학술 데이터베이스(RISS, KISS, DBpia, NDSL, KCI)를 통해 검색된 24편의 논문을 대상으로 포함 및 제외 기준을 적용하여 분석하였다. 선정된 논문의 제목, 초록 및 저자 키워드를 수집하여 전처리한 후 NetMiner 4.0을 활용한 키워드 동시출현 네트워크 분석과 잠재 디리클레 할당(LDA) 기반 토픽모델링을 수행하였다. 분석 결과, ‘환자안전역량’을 중심으로 ‘비판적사고’, ‘환자안전관리’, ‘시뮬레이션’, ‘안전간호수행’, ‘환자안전교육’, ‘안전행동’, ‘의사소통’이 핵심적으로 연결된 네트워크 구조가 확인되었다. 또한 토픽모델링을 통해 환자안전교육, 임상추론 및 문제해결, 의사소통 및 팀워크, 환자안전 인식 및 태도, 환자안전행동의 5개 주요 연구 주제가 도출되었다. 이는 간호대학생의 환자안전역량 연구가 인지적 역량과 교육적 경험을 중심으로 구조화되어 있으며, 협력적 실무 역량이 이를 통합하는 핵심 요소임을 시사한다. 본 연구는 환자안전역량 연구의 지식구조를 구조적으로 제시함으로써 향후 연구 방향 설정과 교육전략 수립에 중요한 근거를 제공한다. 또한 비판적사고, 시뮬레이션 기반 학습, 의사소통 및 팀워크를 통합한 교육전략과 함께 교육과 임상 환경을 연계하는 정책적 지원의 필요성을 제시한다.</t>
@@ -543,7 +548,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>검증필요</t>
+          <t>활용</t>
         </is>
       </c>
     </row>
@@ -570,6 +575,11 @@
       </c>
       <c r="E3" t="n">
         <v>2026</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>10.16980/jitc.22.3.202606.519</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -598,7 +608,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>검증필요</t>
+          <t>활용</t>
         </is>
       </c>
     </row>
@@ -626,6 +636,11 @@
       <c r="E4" t="n">
         <v>2026</v>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>10.16881/jss.2026.07.37.3.311</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>본 연구는 키워드 네트워크 분석을 통하여 국내 트라우마 연구의 동향을 살펴보는 데 목적을 두었다. 이를 위해 국내 학술지에 게재된 트라우마 관련 연구논문을 수집하고, 논문에 제시된 키워드를 추출하였다. 자료 수집 및 분석을 위해 NetMiner 4.5 프로그램을 활용하여 키워드 간 공출현 빈도와 네트워크 구조를 분석하였다. 연구결과는 다음과 같다. 첫째, 트라우마 연구에서 빈도 상위 키워드는 외상 후 성장, 질적연구, 외상 후 스트레스장애, 청소년, 트라우마 경험, 치유 등의 순으로 나타났다. 둘째, 연결중심성과 매개중심성이 높은 키워드는 외상 후 성장과 외상 후 스트레스 장애로 나타나 트라우마 연구에서 핵심적인 역할을 하는 개념임을 확인할 수 있었다. 셋째, 외상 후 성장과 외상 후 스트레스 장애를 중심으로 한 에고 네트워크 분석 결과 다양한 치료 접근과 대상 집단이 연결되어 나타나 트라우마 연구가 회복과 개입, 사회적 맥락을 함께 다루고 있음을 확인할 수 있었다. 넷째, Cluster 분석 결과 외상 경험과 증상, 치유와 개입, 사회적 사건과 대상 집단의 세 가지 주제 영역을 중심으로 연구가 이루어지고 있는 것으로 나타났다. 이러한 연구 결과를 바탕으로 트라우마 연구의 주요 지식구조를 파악하고 향후 연구 방향과 상담학적 시사점을 제시하였다.</t>
@@ -647,7 +662,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>검증필요</t>
+          <t>활용</t>
         </is>
       </c>
     </row>
@@ -863,7 +878,7 @@
         <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>11.7155</v>
+        <v>9.1409</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1310,7 +1325,7 @@
         <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>53.1893</v>
+        <v>46.8229</v>
       </c>
       <c r="O16" t="n">
         <v>4</v>
@@ -1364,7 +1379,7 @@
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>18.7673</v>
+        <v>14.5326</v>
       </c>
       <c r="O17" t="n">
         <v>2</v>
@@ -1961,13 +1976,13 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>7.2188</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -3383,7 +3398,7 @@
         <v>2</v>
       </c>
       <c r="N53" t="n">
-        <v>4.1242</v>
+        <v>2.9536</v>
       </c>
       <c r="O53" t="n">
         <v>2</v>
@@ -3482,13 +3497,13 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N55" t="n">
-        <v>0.9712</v>
+        <v>1.6991</v>
       </c>
       <c r="O55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
@@ -4222,7 +4237,7 @@
         <v>1</v>
       </c>
       <c r="N68" t="n">
-        <v>0.6688</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="O68" t="n">
         <v>1</v>
@@ -7911,7 +7926,7 @@
         <v>16</v>
       </c>
       <c r="N131" t="n">
-        <v>7.0897</v>
+        <v>6.368</v>
       </c>
       <c r="O131" t="n">
         <v>16</v>
@@ -7962,7 +7977,7 @@
         <v>4</v>
       </c>
       <c r="N132" t="n">
-        <v>1.9752</v>
+        <v>1.9216</v>
       </c>
       <c r="O132" t="n">
         <v>4</v>
@@ -8072,7 +8087,7 @@
         <v>4</v>
       </c>
       <c r="N134" t="n">
-        <v>1.1151</v>
+        <v>0.9709</v>
       </c>
       <c r="O134" t="n">
         <v>4</v>
@@ -8196,7 +8211,7 @@
         <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>0.6614</v>
+        <v>0.6504</v>
       </c>
       <c r="O136" t="n">
         <v>8</v>
@@ -8263,7 +8278,7 @@
         <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>0.8303</v>
+        <v>0.796</v>
       </c>
       <c r="O137" t="n">
         <v>4</v>
@@ -8829,7 +8844,7 @@
         <v>1</v>
       </c>
       <c r="N147" t="n">
-        <v>0.8238</v>
+        <v>0.7734</v>
       </c>
       <c r="O147" t="n">
         <v>1</v>
@@ -8960,7 +8975,7 @@
         <v>0</v>
       </c>
       <c r="N149" t="n">
-        <v>0.4431</v>
+        <v>0.4056</v>
       </c>
       <c r="O149" t="n">
         <v>2</v>
@@ -9027,7 +9042,7 @@
         <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>0.4431</v>
+        <v>0.4245</v>
       </c>
       <c r="O150" t="n">
         <v>3</v>
@@ -9078,7 +9093,7 @@
         <v>1</v>
       </c>
       <c r="N151" t="n">
-        <v>0.2044</v>
+        <v>0.1527</v>
       </c>
       <c r="O151" t="n">
         <v>1</v>
@@ -12035,13 +12050,13 @@
         </is>
       </c>
       <c r="K204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>0.4056</v>
       </c>
       <c r="O204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P204" t="inlineStr">
         <is>
@@ -12861,7 +12876,7 @@
         <v>0</v>
       </c>
       <c r="N218" t="n">
-        <v>0.7758</v>
+        <v>0.742</v>
       </c>
       <c r="O218" t="n">
         <v>5</v>
@@ -12909,13 +12924,13 @@
         </is>
       </c>
       <c r="K219" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N219" t="n">
-        <v>2.1617</v>
+        <v>3.2467</v>
       </c>
       <c r="O219" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P219" t="inlineStr">
         <is>
@@ -13195,7 +13210,7 @@
         <v>4</v>
       </c>
       <c r="N224" t="n">
-        <v>0.9579</v>
+        <v>0.9455</v>
       </c>
       <c r="O224" t="n">
         <v>4</v>
@@ -13243,13 +13258,13 @@
         </is>
       </c>
       <c r="K225" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N225" t="n">
-        <v>0.7207</v>
+        <v>0.9466</v>
       </c>
       <c r="O225" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P225" t="inlineStr">
         <is>
@@ -13297,7 +13312,7 @@
         <v>1</v>
       </c>
       <c r="N226" t="n">
-        <v>1.9609</v>
+        <v>1.9705</v>
       </c>
       <c r="O226" t="n">
         <v>1</v>
@@ -13658,7 +13673,7 @@
         <v>2</v>
       </c>
       <c r="N232" t="n">
-        <v>0.8791</v>
+        <v>0.8588</v>
       </c>
       <c r="O232" t="n">
         <v>2</v>
@@ -13709,7 +13724,7 @@
         <v>2</v>
       </c>
       <c r="N233" t="n">
-        <v>0.4789</v>
+        <v>0.4728</v>
       </c>
       <c r="O233" t="n">
         <v>2</v>
@@ -13757,13 +13772,13 @@
         </is>
       </c>
       <c r="K234" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N234" t="n">
-        <v>0.4789</v>
+        <v>0.7114</v>
       </c>
       <c r="O234" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P234" t="inlineStr">
         <is>
@@ -14856,7 +14871,7 @@
         <v>1</v>
       </c>
       <c r="N253" t="n">
-        <v>0.3288</v>
+        <v>0.3239</v>
       </c>
       <c r="O253" t="n">
         <v>1</v>
@@ -17104,7 +17119,7 @@
         <v>2</v>
       </c>
       <c r="N292" t="n">
-        <v>0.6283</v>
+        <v>0.6257</v>
       </c>
       <c r="O292" t="n">
         <v>2</v>
@@ -17219,13 +17234,13 @@
         </is>
       </c>
       <c r="K294" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N294" t="n">
-        <v>1.4371</v>
+        <v>1.4293</v>
       </c>
       <c r="O294" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P294" t="inlineStr">
         <is>
@@ -17289,7 +17304,7 @@
         <v>0</v>
       </c>
       <c r="N295" t="n">
-        <v>3.5686</v>
+        <v>3.4879</v>
       </c>
       <c r="O295" t="n">
         <v>45</v>
@@ -17337,13 +17352,13 @@
         </is>
       </c>
       <c r="K296" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N296" t="n">
-        <v>5.1194</v>
+        <v>4.9612</v>
       </c>
       <c r="O296" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P296" t="inlineStr">
         <is>
@@ -17501,7 +17516,7 @@
         <v>15</v>
       </c>
       <c r="N299" t="n">
-        <v>5.282</v>
+        <v>5.2024</v>
       </c>
       <c r="O299" t="n">
         <v>15</v>
@@ -17770,7 +17785,7 @@
         <v>8</v>
       </c>
       <c r="N304" t="n">
-        <v>2.1818</v>
+        <v>2.2603</v>
       </c>
       <c r="O304" t="n">
         <v>8</v>
@@ -17837,7 +17852,7 @@
         <v>0</v>
       </c>
       <c r="N305" t="n">
-        <v>0.9684</v>
+        <v>0.9699</v>
       </c>
       <c r="O305" t="n">
         <v>9</v>
@@ -17895,7 +17910,7 @@
         </is>
       </c>
       <c r="K306" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L306" t="n">
         <v>7</v>
@@ -17907,7 +17922,7 @@
         <v>1.9765</v>
       </c>
       <c r="O306" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P306" t="inlineStr">
         <is>
@@ -18615,13 +18630,13 @@
         </is>
       </c>
       <c r="K318" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N318" t="n">
-        <v>0.9686</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="O318" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P318" t="inlineStr">
         <is>
@@ -19012,7 +19027,7 @@
         <v>4</v>
       </c>
       <c r="N325" t="n">
-        <v>0.7744</v>
+        <v>0.7703</v>
       </c>
       <c r="O325" t="n">
         <v>4</v>
@@ -19063,7 +19078,7 @@
         <v>5</v>
       </c>
       <c r="N326" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="O326" t="n">
         <v>5</v>
@@ -19786,7 +19801,7 @@
         <v>2</v>
       </c>
       <c r="N339" t="n">
-        <v>0.2831</v>
+        <v>0.2835</v>
       </c>
       <c r="O339" t="n">
         <v>2</v>
@@ -19904,7 +19919,7 @@
         <v>2</v>
       </c>
       <c r="N341" t="n">
-        <v>0.0813</v>
+        <v>0.0808</v>
       </c>
       <c r="O341" t="n">
         <v>2</v>
@@ -21507,13 +21522,13 @@
         </is>
       </c>
       <c r="K372" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N372" t="n">
-        <v>13.0126</v>
+        <v>17.688</v>
       </c>
       <c r="O372" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P372" t="inlineStr">
         <is>
@@ -21561,7 +21576,7 @@
         <v>19</v>
       </c>
       <c r="N373" t="n">
-        <v>4.2495</v>
+        <v>4.3259</v>
       </c>
       <c r="O373" t="n">
         <v>19</v>
@@ -22324,7 +22339,7 @@
         <v>7</v>
       </c>
       <c r="N386" t="n">
-        <v>2.0742</v>
+        <v>2.1594</v>
       </c>
       <c r="O386" t="n">
         <v>7</v>
@@ -22442,7 +22457,7 @@
         <v>9</v>
       </c>
       <c r="N388" t="n">
-        <v>0.3798</v>
+        <v>0.3805</v>
       </c>
       <c r="O388" t="n">
         <v>9</v>
@@ -24071,13 +24086,13 @@
         </is>
       </c>
       <c r="K416" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N416" t="n">
-        <v>0.3878</v>
+        <v>0.3789</v>
       </c>
       <c r="O416" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P416" t="inlineStr">
         <is>
@@ -24125,7 +24140,7 @@
         <v>2</v>
       </c>
       <c r="N417" t="n">
-        <v>0.3798</v>
+        <v>0.3789</v>
       </c>
       <c r="O417" t="n">
         <v>2</v>
@@ -25953,7 +25968,7 @@
         <v>17</v>
       </c>
       <c r="N451" t="n">
-        <v>4.3538</v>
+        <v>4.4885</v>
       </c>
       <c r="O451" t="n">
         <v>17</v>
@@ -27541,13 +27556,13 @@
         </is>
       </c>
       <c r="K477" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N477" t="n">
-        <v>0.3538</v>
+        <v>0.3443</v>
       </c>
       <c r="O477" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P477" t="inlineStr">
         <is>
@@ -27595,7 +27610,7 @@
         <v>5</v>
       </c>
       <c r="N478" t="n">
-        <v>1.1189</v>
+        <v>1.1408</v>
       </c>
       <c r="O478" t="n">
         <v>5</v>
@@ -29920,7 +29935,7 @@
         <v>66</v>
       </c>
       <c r="N519" t="n">
-        <v>1.8142</v>
+        <v>1.7677</v>
       </c>
       <c r="O519" t="n">
         <v>66</v>
@@ -30003,13 +30018,13 @@
         </is>
       </c>
       <c r="K520" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N520" t="n">
-        <v>6.2918</v>
+        <v>6.3235</v>
       </c>
       <c r="O520" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P520" t="inlineStr">
         <is>
@@ -30057,7 +30072,7 @@
         <v>17</v>
       </c>
       <c r="N521" t="n">
-        <v>1.723</v>
+        <v>1.6771</v>
       </c>
       <c r="O521" t="n">
         <v>17</v>
@@ -30133,7 +30148,7 @@
         <v>10</v>
       </c>
       <c r="N522" t="n">
-        <v>6.2116</v>
+        <v>6.0624</v>
       </c>
       <c r="O522" t="n">
         <v>10</v>
@@ -30269,7 +30284,7 @@
         <v>3</v>
       </c>
       <c r="N524" t="n">
-        <v>0.217</v>
+        <v>0.2169</v>
       </c>
       <c r="O524" t="n">
         <v>3</v>
@@ -30432,7 +30447,7 @@
         <v>1</v>
       </c>
       <c r="N527" t="n">
-        <v>0.3944</v>
+        <v>0.3962</v>
       </c>
       <c r="O527" t="n">
         <v>1</v>
@@ -30975,7 +30990,7 @@
         <v>331</v>
       </c>
       <c r="N539" t="n">
-        <v>36.6041</v>
+        <v>37.0458</v>
       </c>
       <c r="O539" t="n">
         <v>331</v>
@@ -31123,7 +31138,7 @@
         <v>33</v>
       </c>
       <c r="N542" t="n">
-        <v>3.1998</v>
+        <v>3.1147</v>
       </c>
       <c r="O542" t="n">
         <v>33</v>
@@ -31179,7 +31194,7 @@
         <v>4</v>
       </c>
       <c r="N543" t="n">
-        <v>0.6822</v>
+        <v>0.6844</v>
       </c>
       <c r="O543" t="n">
         <v>4</v>
@@ -31585,7 +31600,7 @@
         <v>80</v>
       </c>
       <c r="N553" t="n">
-        <v>14.4577</v>
+        <v>13.7236</v>
       </c>
       <c r="O553" t="n">
         <v>80</v>
@@ -31641,7 +31656,7 @@
         <v>22</v>
       </c>
       <c r="N554" t="n">
-        <v>0.949</v>
+        <v>0.9577</v>
       </c>
       <c r="O554" t="n">
         <v>22</v>
@@ -31697,7 +31712,7 @@
         <v>9</v>
       </c>
       <c r="N555" t="n">
-        <v>0.7161</v>
+        <v>0.7188</v>
       </c>
       <c r="O555" t="n">
         <v>9</v>
@@ -31753,7 +31768,7 @@
         <v>5</v>
       </c>
       <c r="N556" t="n">
-        <v>2.2427</v>
+        <v>2.246</v>
       </c>
       <c r="O556" t="n">
         <v>5</v>

--- a/nm-reference/citations.xlsx
+++ b/nm-reference/citations.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P565"/>
+  <dimension ref="A1:P623"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3582,6 +3582,11 @@
           <t>10.1186/s12912-025-03625-5</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>포함</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>BACKGROUND: The gap between knowledge and clinical practice causes stress and reality shock, contributing to low job satisfaction and high turnover among new nurses; in 2023, the turnover rate in South Korea reached 52.4%. Korean preceptorship programs are often too brief to adequately support new nurses' adaptation. Clinical nurse educators (CNEs) play a crucial role in addressing these issues by offering knowledge transfer, emotional support, and career guidance. Therefore, strategies to strengthen CNEs' coaching and mentoring skills are essential to support new nurses' stable clinical adaptation. This study analyzed how CNEs mentored new hospital nurses by responding to their post-entry journals. METHODS: This study employed a quantitative content analysis. We used NetMiner 4.5.1 to conduct a text network analysis of 1,742 mentoring journal responses written by four CNEs for 120 new nurses at C University Hospital in South Korea between June 2021 and May 2022. RESULTS: The keyword "attitude" had the highest frequency (726), emphasizing the clinical importance of fostering positive attitudes among new nurses. The keyword network had average centrality measures of degree (.15), closeness (.43), and betweenness (.05). Keywords with high centrality, such as "attitude," "importance," "performance," and "difficulty, highlighted mentoring practices focused on enhancing clinical judgment, nursing performance, and managing workplace challenges. Eigenvector analysis identified three subtopic groups with optimal modularity (.295). Subthemes included: 1) helping new nurses to improve their professional competence, 2) encouraging new nurses struggling to adapt to the field, and 3) empathy for new nurses' burdens and stress. CONCLUSIONS: The findings revealed that the CNEs' mentoring feedback focused on encouraging new nurses to maintain a positive attitude, inspiring their personal and professional growth, and offering empathy and encouragement to help them cope with burdens and stress. Based on these findings, targeted training modules for CNEs and mentoring guidelines should be developed to further support new nurses' adaptation to clinical practice.</t>
@@ -4166,6 +4171,11 @@
           <t>10.1002/brb3.70910</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>포함</t>
+        </is>
+      </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>PURPOSE: This study examined how social network strength (i.e., the intensity and frequency of interactions within one's personal network, assessed using centrality measures such as degree, closeness, betweenness, and eigenvector centrality) affects mental health. METHODS: The study was conducted with 108 first-year university students. Data were collected using a structured questionnaire, and NetMiner 4.0 was employed to analyze degree centrality, closeness centrality, betweenness centrality, and eigenvector centrality as indicators of social network centrality. Additionally, Quadratic Assignment Procedure (QAP) correlation analysis and QAP regression analysis were conducted to assess the relationship between social network strength and mental health. RESULTS: = 0.143, F = 2.423, p &lt; 0.05). These results suggest that building stronger and more integrated social networks may help reduce psychological distress and support mental well-being in late adolescence. CONCLUSION: Stronger social networks in late adolescence are associated with better mental health, highlighting the importance of social connections. While correlational findings suggest general links between centrality and emotional well-being, the regression results underscore specific predictors with practical implications. In-degree, in-closeness, and eigenvector centrality were associated with reduced depressive symptoms, indicating that being well-integrated within a social network may offer protective benefits. In contrast, high out-closeness centrality predicted increased depression, suggesting that the effort required to maintain outward-reaching connections may impose psychological burdens. These findings suggest that targeted interventions should focus on strengthening inward social integration while addressing the stress related to maintaining extensive outward connections, providing direction for more effective youth mental health strategies.</t>
@@ -4217,6 +4227,11 @@
           <t>10.1097/cin.0000000000001347</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>포함</t>
+        </is>
+      </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>PURPOSE: This study utilized text network analysis and topic modeling to examine the research landscape of nurse preceptor training programs and facilitate the adaptation of new nurses in Korea and internationally. METHODS: Abstracts from three Korean and 45 international studies on preceptor nurse training programs were collected. Keywords and meaningful morphemes from the abstracts and main text were analyzed and refined. A co-occurrence matrix of keywords was generated to analyze degree, closeness, and betweenness centrality using NetMiner 4.5.0 software. Topic modeling was used to identify key thematic structures. RESULTS: Among the top 10 ranked keywords, five common terms-"clinical competence," "educator," "nursing practice," "teaching strategy," and "mentoring"-emerged across both frequency and centrality measures. Topic modeling identified four major subtopics: nurse preceptor programs for strengthening partnership skills and professional insights, communication programs to enhance the self-care competence of nurse preceptors, simulation programs to strengthen the expertise of nurse preceptors, and nurse preceptor programs to foster emotional empathy and growth. CONCLUSION: This study improves patient safety and professional competence by promoting optimal clinical decision-making for new nurse preceptees. Future research should develop educational programs that foster mutual empathy and professional growth between nurse preceptors and new nurse preceptees.</t>
@@ -4268,6 +4283,11 @@
           <t>10.1097/cin.0000000000001373</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>포함</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>This study employed text network analysis to examine nurse managers' feedback journals for new nurses, highlighting the critical need for structured support during their transition period. A total of 429 feedback journals were documented by 32 nurse managers for 239 new nurses between September 2019 and March 2021 in South Korea, aiming to identify the challenges faced by new nurses and explore keyword relationships and thematic patterns. The analysis process included 4 stages: data preprocessing, keyword extraction, network and centrality analysis, and subtheme analysis. Using NetMiner 4.5.0, the analysis identified several central keywords in the feedback journals, with "performance" showing the highest centrality values (degree centrality = 0.448, closeness centrality = 0.580, betweenness centrality = 0.117), followed by "experience" and "explanation." Through community detection analysis using the eigenvector method, 3 distinct subthemes emerged from the network structure: "clinical practice fundamentals," "learning and development process," and "support and educational system." The findings of this study provide empirical evidence for developing structured feedback programs and enhancing nurse managers' interviewing competencies. The findings provide empirical evidence regarding linguistic patterns and thematic structures in nurse managers' feedback, suggesting systematic documentation protocols and utilization of these insights to inform structured feedback initiatives, thereby supporting new nurses' development.</t>
@@ -4319,6 +4339,11 @@
           <t>10.1109/ton.2025.3607440</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>포함</t>
+        </is>
+      </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>Network specification, which describes what an existing network is designed for, can help operators better understand and manage their networks, and is a critical pre-condition for network verification and synthesis tools to work. Existing tools for specification mining either cannot scale to large networks, or scale by sacrificing fidelity. Moreover, the specification contains a huge number of low-level intents (e.g., tens of thousands of pairwise reachability), making it hard for operators to read. To this end, this paper presents &lt;italic xmlns:mml="http://www.w3.org/1998/Math/MathML" xmlns:xlink="http://www.w3.org/1999/xlink"&gt;NetMiner&lt;/i&gt;, which can mine specification from network configurations, with high scalability, fidelity, and easier to read. The key idea of &lt;italic xmlns:mml="http://www.w3.org/1998/Math/MathML" xmlns:xlink="http://www.w3.org/1999/xlink"&gt;NetMiner&lt;/i&gt; is to faithfully simulate the network routing and forwarding behaviors with control plane simulators and data plane verifiers, so as to achieve high fidelity. Meanwhile, &lt;italic xmlns:mml="http://www.w3.org/1998/Math/MathML" xmlns:xlink="http://www.w3.org/1999/xlink"&gt;NetMiner&lt;/i&gt; improves the scalability by identifying relevant failure scenarios, and aggregating them to significantly reduce the number of needed simulations. Moreover, &lt;italic xmlns:mml="http://www.w3.org/1998/Math/MathML" xmlns:xlink="http://www.w3.org/1999/xlink"&gt;NetMiner&lt;/i&gt; clusters similar low-level intents into a high-level intent, to make the specification more concise and easier to read. Experiments using real configurations from a large cloud service provider and synthetic configurations show that &lt;italic xmlns:mml="http://www.w3.org/1998/Math/MathML" xmlns:xlink="http://www.w3.org/1999/xlink"&gt;NetMiner&lt;/i&gt; can mine specification &lt;inline-formula xmlns:mml="http://www.w3.org/1998/Math/MathML" xmlns:xlink="http://www.w3.org/1999/xlink"&gt; &lt;tex-math notation="LaTeX"&gt;$10\times $&lt;/tex-math&gt; &lt;/inline-formula&gt; faster, and reduce the number of intents by &lt;inline-formula xmlns:mml="http://www.w3.org/1998/Math/MathML" xmlns:xlink="http://www.w3.org/1999/xlink"&gt; &lt;tex-math notation="LaTeX"&gt;$100\times $&lt;/tex-math&gt; &lt;/inline-formula&gt;, compared to state-of-the-art tools.</t>
@@ -4542,6 +4567,11 @@
       <c r="F74" t="inlineStr">
         <is>
           <t>10.1371/journal.pone.0322956</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>포함</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -7976,6 +8006,9 @@
       <c r="E132" t="n">
         <v>2024</v>
       </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>활용</t>
@@ -8059,6 +8092,11 @@
           <t>10.1186/s12889-024-19023-6</t>
         </is>
       </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>포함</t>
+        </is>
+      </c>
       <c r="H134" t="inlineStr">
         <is>
           <t>BACKGROUND: The COVID-19 pandemic has been the most widespread and threatening health crisis experienced by the Korean society. Faced with an unprecedented threat to survival, society has been gripped by social fear and anger, questioning the culpability of this pandemic. This study explored the correlation between social cognitions and negative emotions and their changes in response to the severe events stemming from the COVID-19 pandemic in South Korea. METHODS: The analysis was based on a cognitive-emotional model that links fear and anger to the social causes that trigger them and used discursive content from comments posted on YouTube's COVID-19-related videos. A total of 182,915 comments from 1,200 videos were collected between January and December 2020. We performed data analyses and visualizations using R, Netminer 4.0, and Gephi software and calculated Pearson's correlation coefficients between emotions. RESULTS: YouTube videos were analyzed for keywords indicating cognitive assessments of major events related to COVID-19 and keywords indicating negative emotions. Eight topics were identified through topic modeling: causes and risks, perceptions of China, media and information, infection prevention rules, economic activity, school and infection, political leaders, and religion, politics, and infection. The correlation coefficient between fear and anger was 0.462 (p &lt; .001), indicating a moderate linear relationship between the two emotions. Fear was the highest from January to March in the first year of the COVID-19 outbreak, while anger occurred before and after the outbreak, with fluctuations in both emotions during this period. CONCLUSIONS: This study confirmed that social cognitions and negative emotions are intertwined in response to major events related to the COVID-19 pandemic, with each emotion varying individually rather than being ambiguously mixed. These findings could aid in developing social cognition-emotion-based public health strategies through education and communication during future pandemic outbreaks.</t>
@@ -8225,6 +8263,11 @@
           <t>10.4040/jkan.24034</t>
         </is>
       </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>포함</t>
+        </is>
+      </c>
       <c r="H137" t="inlineStr">
         <is>
           <t>Purpose: This study aimed to analyze the experiences of new nurses during their first year of hospital employment to gather data for the development of an evidence-based new nurse residency program focused on adaptability. Methods: This study was conducted at a tertiary hospital in Korea between March and August 2021 with 80 new nurses who wrote in critical reflective journals during their first year of work. NetMiner 4.5.0 was used to conduct a text network analysis of the critical reflective journals to uncover core keywords and topics across three periods. Results: In the journals, over time, degree centrality emerged as “study” and “patient understanding” for 1 to 3 months, “insufficient” and “stress” for 4 to 6 months, and “handover” and “preparation” for 7 to 12 months. Major sub-themes at 1 to 3 months were: “rounds,” “intravenous-cannulation,” “medical device,” and “patient understanding”; at 4 to 6 months they were “admission,” “discharge,” “oxygen therapy,” and “disease”; and at 7 to 12 months they were “burden,” “independence,” and “solution.” Conclusion: These results provide valuable insights into the challenges and experiences encountered by new nurses during different stages of their field adaptation process. This information may highlight the best nurse leadership methods for improving institutional education and supporting new nurses’ transitions to the hospital work environment.</t>
@@ -8605,6 +8648,11 @@
           <t>10.3390/healthcare12191914</t>
         </is>
       </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>포함</t>
+        </is>
+      </c>
       <c r="H143" t="inlineStr">
         <is>
           <t>Background/Objectives: This study aimed to identify the main issues related to public patient safety campaigns reflected in Korean online news. This study utilized a text-mining method to identify keywords and topics related to patient safety campaigns. Methods: The data collection period was from 1 January 2022 to 31 December 2023, and 4110 news articles were extracted. Through data preprocessing, 2661 duplicated news and 1213 unrelated news were removed, and 236 news were selected. Using the NetMiner program, keyword co-occurrence frequency calculation, keyword centrality analysis, and topic modeling analysis were performed. Results: The results showed that the most frequently mentioned keywords with high degree centrality, betweenness centrality, and closeness centrality in online news were hospital, medical, medicine, project, and treatment. The topics of online news related to the patient safety campaign were patient-centered care for medical safety, health promotion projects at a regional institution, hand hygiene education to prevent infection, healthcare quality improvement through the Mint Festival, and safe use of medicines. Conclusions: This study analyzed patient safety campaign news topics using text network analysis and topic modeling. It was confirmed that patient safety campaigns are essential for fostering a patient safety culture, improving medical quality, and encouraging patient participation in hospitals. Therefore, to build a safe medical environment, it is necessary to establish an effective patient safety campaign for not only medical staff providing medical care, but also patients and their caregivers, and for this, cooperation and participation from various professional occupations are necessary.</t>
@@ -8613,6 +8661,9 @@
       <c r="K143" t="n">
         <v>2</v>
       </c>
+      <c r="O143" t="n">
+        <v>2</v>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>활용</t>
@@ -8926,6 +8977,11 @@
           <t>10.1177/00469580241271152</t>
         </is>
       </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>포함</t>
+        </is>
+      </c>
       <c r="H149" t="inlineStr">
         <is>
           <t>With the increasing obesity rates, many studies on obesity prevention and management have been implemented. However, few studies focused on obesity in adulthood and different perceptions of obesity between life cycles. Thus, this study aimed to investigate the demand for customized obesity prevention and management (OPM) strategies across adult age groups. Focus group interviews were conducted to gather insights from three age groups: young adults (20-34 years), middle-aged adults (35-49 years), and seniors (50-64 years). A total of 17 participants took part in the study, with 5 participants in Group 1, 6 participants in Group 2, and 6 participants in Group 3. Thematic analysis and the use of NetMiner version 4.4.3 facilitated data categorization and scrutiny. The study employed qualitative methods to explore perceptions of obesity and preferences for personalized OPM strategies among participants. Diverse perspectives on obesity as a health threat were found among the age groups. While all stressed the importance of personalized OPM, preferences for strategies varied. Diet and exercise combination emerged as a common preference. This study highlighted the need for customized OPM approaches aligned with age-specific preferences.</t>
@@ -9598,6 +9654,9 @@
           <t>10.5993/AJHB.48.5.20</t>
         </is>
       </c>
+      <c r="O160" t="n">
+        <v>0</v>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>활용</t>
@@ -9628,6 +9687,9 @@
           <t>10.1016/j.tfp.2024.100646</t>
         </is>
       </c>
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>활용</t>
@@ -9869,6 +9931,11 @@
           <t>10.1108/K-01-2024-0128</t>
         </is>
       </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>포함</t>
+        </is>
+      </c>
       <c r="H166" t="inlineStr">
         <is>
           <t>Purpose In the context of Industry 4.0, intelligent construction technologies (ICT) represented by information technology and networking will undoubtedly provide new impetus to the development of the prefabricated building supply chain (PBSC), but they will also bring various potential risks. So far, there is a large lack of research on the comprehensive consideration of the risks associated with the intelligent transformation of PBSC based on the information sharing perspective, and the critical risks and interactions are still unclear, making it difficult to identify efficient risk mitigation strategies. Therefore, this paper aims to reveal the interactions between stakeholders and clarify the critical risk nodes and interactions in information sharing of PBSC (IS-PBSC), and propose targeted risk mitigation strategies. Design/methodology/approach Firstly, this paper creatively delineates the risks and critical stakeholders of IS-PBSC. Secondly, Data is collected through questionnaires to understand the degree of risks impact. Thirdly, with the help of NetMiner 4 software, social network analysis is conducted and IS-PBSC risk network is established to reveal critical risk nodes and interactions. Finally, further targeted discussion of critical risk nodes, the effectiveness and reasonableness of the risk mitigation strategies are proposed and verified through NetMiner 4 software simulation. Findings The results show that the critical risks cover the entire process of information sharing, with the lack of information management norms and other information assurance-related risks accounting for the largest proportion. In addition, the government dominates in risk control, followed by other stakeholders. The implementation of risk mitigation strategies is effective, with the overall network density reduced by 41.15% and network cohesion reduced by 24%. Research limitations/implications In the context of Industry 4.0, ICT represented by information technology and networking will undoubtedly provide new impetus to the development of the PBSC, but they will also bring various potential risks. So far, there is a large lack of research on the comprehensive consideration of the risks associated with the intelligent transformation of PBSC based on the information sharing perspective, and the critical risks and interactions are still unclear, making it difficult to identify efficient risk mitigation strategies. Originality/value Based on the results of risk network visualization analysis, this paper proposes an ICT-based IS-PBSC mechanism that promotes the development of the integration of ICT and PBSC while safeguarding the benefits of various stakeholders.</t>
@@ -9969,6 +10036,11 @@
       <c r="F168" t="inlineStr">
         <is>
           <t>10.1371/journal.pone.0299782</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>포함</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10916,6 +10988,9 @@
           <t>본 연구는 국내 수퍼비전 연구 동향과 핵심 연계 개념의 확인을 위해 KCI 등재(후보)지에 게재된 142편의 연구를 키워드 네트워크 분석으로 살펴보았다. 2003년 윤리규정 제정, 2018년 ‘수련 감독 및 상담자 교육’항목 신설과 같은 한국상담심리학회의 제도적 변화가 연구 동향에 미치는 영향을 알아보고자, 시기 1(2004-2017)과 시기 2(2018-2023)로 나눠 연구 주제를 분석하였다. 그 결과 시기 1은 거시적인 수퍼비전 목표와 모델을 제안하는 연구가 주를 이뤘다면, 시기 2는 수퍼비전 상호작용에서 일어나는 미세과정에 대한 연구들이 나타났다. 높은 빈도의 키워드로 ‘수퍼비전’, ‘수퍼바이저’, ‘수퍼바이지’, ‘상담’, ‘상담자’가 두 시기 모두에서 나타났으며, 시기 2에서는 ‘윤리’가 등장하였다. 시기와 무관하게 ‘내담자’는 포함되지 않았다. 토픽모델링 분석 결과, 4개 토픽으로 분류되었으며, 시기 2에서 수퍼바이지 특성에 적합한 수퍼비전 모델과 구조에 대한 연구 비율이 감소하였고 상담자의 어려움에 대한 대처 및 전문성 발달 촉진에 대한 연구는 증가하였다. 본 연구 결과는 수퍼비전 연구의 양과 범위가 성장하고 있으며, 수퍼비전 연구와 실무는 서로 밀접하게 상호작용함을 지지한다.</t>
         </is>
       </c>
+      <c r="O184" t="n">
+        <v>0</v>
+      </c>
       <c r="P184" t="inlineStr">
         <is>
           <t>활용</t>
@@ -11252,6 +11327,9 @@
           <t>10.1145/3648470</t>
         </is>
       </c>
+      <c r="O190" t="n">
+        <v>0</v>
+      </c>
       <c r="P190" t="inlineStr">
         <is>
           <t>소개</t>
@@ -11282,6 +11360,9 @@
           <t>10.3390/su16062412</t>
         </is>
       </c>
+      <c r="O191" t="n">
+        <v>0</v>
+      </c>
       <c r="P191" t="inlineStr">
         <is>
           <t>활용</t>
@@ -11571,6 +11652,9 @@
         <is>
           <t>10.3390/app14198909</t>
         </is>
+      </c>
+      <c r="O196" t="n">
+        <v>0</v>
       </c>
       <c r="P196" t="inlineStr">
         <is>
@@ -12596,6 +12680,11 @@
           <t>10.1016/j.ssci.2023.106239</t>
         </is>
       </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>포함</t>
+        </is>
+      </c>
       <c r="H214" t="inlineStr">
         <is>
           <t>Objective: Through a text network analysis, this study examined major issues related to death from overwork reported in Korean media over the past ten years, focusing on essential workers, and examined the implications for Korean society from the perspective of decent work as described by the Sustainable Development Goals (SDGs). Methods: We retrieved 1,340 news articles from 52 media companies by searching for death from overwork as a keyword using the Big Kinds database operated by the Korea Press Foundation. A total of 4,627 nouns were extracted from news articles, and four topics were found by performing topic modeling using the NetMiner 4 program. We also examined the trend of topic ratios by year. Results: Between 2012 and 2015, 22-36 news articles were reported annually, and Topic 2 (recognition of death from overwork of public officials) was the most common. Between 2016 and 2019, 72-162 news articles were reported annually, and Topic 1 (postal workers' extended working hours) was the most common. Between 2020 and 2021, 314-441 news articles were reported annually, and Topic 3 (measures against industrial accidents of courier workers) and Topic 4 (courier sorting and labor union consensus) were the most common. Conclusion: In Korea, postal workers, public officials, and courier workers are vulnerable to death from overwork. This can be resolved by considerably reducing working hours, recognizing industrial accidents, and improving the working environment. From the perspective of the United Nations Development Programme (UNDP) SDGs' decent work concept, to sustain workers' health and well-being, the State and companies should guarantee workers healthy working hours, choice of working hours, guarantee of decent and productive work, and maximum working hours cap system. The labor system and workplace culture should be improved to guarantee workers' health and well-being.</t>
@@ -12604,6 +12693,9 @@
       <c r="K214" t="n">
         <v>7</v>
       </c>
+      <c r="O214" t="n">
+        <v>7</v>
+      </c>
       <c r="P214" t="inlineStr">
         <is>
           <t>활용</t>
@@ -13292,6 +13384,11 @@
           <t>10.4040/jkan.22117</t>
         </is>
       </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>포함</t>
+        </is>
+      </c>
       <c r="H226" t="inlineStr">
         <is>
           <t>PURPOSE: The purpose of this study was to identify the main keywords, network properties, and main topics of news articles related to artificial intelligence technology in the field of nursing. METHODS: After collecting artificial intelligence-and nursing-related news articles published between January 1, 1991, and July 24, 2022, keywords were extracted via preprocessing. A total of 3,267 articles were searched, and 2,996 were used for the final analysis. Text network analysis and topic modeling were performed using NetMiner 4.4. RESULTS: As a result of analyzing the frequency of appearance, the keywords used most frequently were education, medical robot, telecom, dementia, and the older adults living alone. Keyword network analysis revealed the following results: a density of 0.002, an average degree of 8.79, and an average distance of 2.43; the central keywords identified were 'education,' 'medical robot,' and 'fourth industry.' Five topics were derived from news articles related to artificial intelligence and nursing: 'Artificial intelligence nursing research and development in the health and medical field,' 'Education using artificial intelligence for children and youth care,' 'Nursing robot for older adults care,' 'Community care policy and artificial intelligence,' and 'Smart care technology in an aging society.' CONCLUSION: The use of artificial intelligence may be helpful among the local community, older adult, children, and adolescents. In particular, health management using artificial intelligence is indispensable now that we are facing a super-aging society. In the future, studies on nursing intervention and development of nursing programs using artificial intelligence should be conducted.</t>
@@ -13341,6 +13438,11 @@
       <c r="F227" t="inlineStr">
         <is>
           <t>10.1097/cin.0000000000000993</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>포함</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -13806,6 +13908,11 @@
           <t>10.4040/jkan.23052</t>
         </is>
       </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>포함</t>
+        </is>
+      </c>
       <c r="H235" t="inlineStr">
         <is>
           <t>PURPOSE: This study aimed to identify the main keyword, network structure, and main topics of the national petition related to "nursing" in South Korea. METHODS: Data were gathered from petitions related to the national petition in Korea Blue House related to the topic "nursing" or "nurse" from August 17, 2017, to May 9, 2022. A total of 5,154 petitions were searched, and 995 were selected for the final analysis. Text network analysis and topic modeling were analyzed using the Netminer 4.5.0 program. RESULTS: Regarding network characteristics, a density of 0.03, an average degree of 144.483, and an average distance of 1.943 were found. Compared to results of degree centrality and betweenness centrality, keywords such as "work environment," "nursing university," "license," and "education" appeared typically in the eigenvector centrality analysis. Topic modeling derived four topics: (1) "Improving the working environment and dealing with nursing professionals," (2) "requesting investigation and punishment related to medical accidents," (3) "requiring clear role regulation and legislation of medical and nonmedical professions," and (4) "demanding improvement of healthcare-related systems and services." CONCLUSION: This is the first study to analyze Korea's national petitions in the field of nursing. This study's results confirmed both the internal needs and external demands for nurses in South Korea. Policies and laws that reflect these results should be developed.</t>
@@ -13855,6 +13962,11 @@
       <c r="F236" t="inlineStr">
         <is>
           <t>10.1097/cin.0000000000001040</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>포함</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -15841,6 +15953,9 @@
           <t>10.46254/AU01.20220369</t>
         </is>
       </c>
+      <c r="O270" t="n">
+        <v>0</v>
+      </c>
       <c r="P270" t="inlineStr">
         <is>
           <t>활용</t>
@@ -16669,6 +16784,11 @@
       <c r="F286" t="inlineStr">
         <is>
           <t>10.3390/healthcare11081139</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>포함</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -17319,6 +17439,11 @@
           <t>10.3390/su14094921</t>
         </is>
       </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>포함</t>
+        </is>
+      </c>
       <c r="H296" t="inlineStr">
         <is>
           <t>This exploratory study utilises quantitative analysis to deliver a systematic literature review of published journal papers from 1993 to 2020 with the aim to identify research trends and present a comprehensive overview of research focus conducted in the sustainable packaging domain within the scope of supply chain management. This research is conducted with the data mining software, NetMiner 4, utilising the three analytical tools of statistical analysis, keyword network analysis, and topic analysis. The research also utilises the qualitative method of in-depth interviews in order to investigate current trends and perspectives on the future of sustainable packaging and to validate the analysis results. The research findings reveal that research in the field of ‘sustainable packaging in supply chain management’ field has been extremely limited, and this study acts to address this research gap. The results confirm that the vast majority of research focus has been in the fields of engineering and science. Research on the topic has gained momentum and has significantly increased since 2013 with research trends becoming increasingly diversified and gradually aligned with the concept of circular economy, while the topic of operational management has been highlighted as an area requiring additional attention. The keyword frequency analysis reveals the following highest occurring keywords in TF: life cycle; environmental impact; consumer; transportation; and production. The highest occurring keywords in TF-IDF: production; transportation; consumer; food; and environmental impact. Topic modelling revealed the following six topics: consumer behaviour; environmental pollution; circular economy; waste management; resource conservation; and operational management. This study contributes to understanding past, present, and future research agendas, and can be utilised as foundation for research development, as it provides insight to current research status and trends provided by the keyword network analysis highlighting research focus and trends in ‘sustainable packaging in supply chain management’.</t>
@@ -17375,6 +17500,11 @@
           <t>10.4040/jkan.22002</t>
         </is>
       </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>포함</t>
+        </is>
+      </c>
       <c r="H297" t="inlineStr">
         <is>
           <t>Purpose: The aims of study were to identify the main keywords, the network structure, and the main topics of press articles related to nurses that have appeared in media reports. Methods: Data were media articles related to the topic “nurse” reported in 16 central media within a one-year period spanning July 1, 2019 to June 30, 2020. Data were collected from the Big Kinds database. A total of 7,800 articles were searched, and 1,038 were used for the final analysis. Text network analysis and topic modeling were performed using NetMiner 4.4. Results: The number of media reports related to nurses increased by 3.86 times after the novel coronavirus (COVID-19) outbreak compared to prior. Pre- and post-COVID-19 network characteristics were density 0.002, 0.001; average degree 4.63, 4.92; and average distance 4.25, 4.01, respectively. Four topics were derived before and after the COVID-19 outbreak, respectively. Pre-COVID-19 example topics are “a nurse who committed suicide because she could not withstand the Taewoom at work” and “a nurse as a perpetrator of a newborn abuse case,” while post-COVID-19 examples are “a nurse as a victim of COVID-19,” “a nurse working with the support of the people,” and “a nurse as a top contributor and a warrior to protect from COVID-19.” Conclusion: Topic modeling shows that topics become more positive after the COVID-19 outbreak. Individual nurses and nursing organizations should continuously monitor and conduct further research on nurses’ image.</t>
@@ -17437,6 +17567,11 @@
           <t>10.2196/37622</t>
         </is>
       </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>포함</t>
+        </is>
+      </c>
       <c r="H298" t="inlineStr">
         <is>
           <t>BACKGROUND: As the need for digital health care based on mobile devices is increasing, with the rapid development of digital technologies, especially in the face of the COVID-19 pandemic, gaining a better understanding of the industrial structure is needed to activate the use of digital health care. OBJECTIVE: The aim of this study was to suggest measures to revitalize the digital health care industry by deriving the stakeholders and major issues with respect to the ecosystem of the industry. METHODS: A total of 1822 newspaper articles were collected using Big Kings, a big data system for news, for a limited period from 2016 to August 2021, when the mobile health care project was promoted in Korea centered on public health centers. The R and NetMiner programs were used for network analysis. RESULTS: The Korean government and the Ministry of Health and Welfare showed the highest centrality and appeared as major stakeholders, and their common major issues were "reviewing the introduction of telemedicine," "concerns about bankruptcy of local clinics," and "building an integrated platform for precision medicine." In addition, the major stakeholders of medical institutions and companies were Seoul National University Hospital, Kangbuk Samsung Hospital, Ajou University Hospital, Samsung, and Vuno Inc. CONCLUSIONS: This analysis confirmed that the issues related to digital health care are largely composed of telemedicine, data, and health care business. For digital health care to develop as a national innovative growth engine and to be institutionalized, the development of a digital health care fee model that can improve the regulatory system and the cost-effectiveness of patient care, centering on the Ministry of Health and Welfare as a key stakeholder, is essential.</t>
@@ -17598,6 +17733,11 @@
           <t>10.1016/j.nedt.2022.105674</t>
         </is>
       </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>포함</t>
+        </is>
+      </c>
       <c r="H301" t="inlineStr">
         <is>
           <t>OBJECTIVES: This study aimed to identify the knowledge structure of medication safety nursing education literature by developing schematic diagrams of the relationship between keywords from a macro perspective. This study also identifies the research topics and trends over time. DESIGN: This quantitative content study used text network analysis to explore keywords and research topics using topic modeling within the medication safety nursing education literature. DATA SOURCES: PubMed, EMBASE, and Cochrane databases were used to search for the medication safety nursing education literature published until December 2021. METHODS: Keywords from 2085 articles were examined using text network analysis and topic modeling with NetMiner 4.4.3. RESULTS: The keywords with the most frequency and the highest networking degree in centrality were "patient," "medication," "program," "nurse," and "care." The emerging keywords assessed by time periods were identified; the first phase ("heart failure," "insulin," "chemotherapy," and "infusion"), the second phase ("medication errors," "staff," and "information"), the third phase ("program," "management," and "data"). The results of topic modeling were as follows: safe medication administration, safe medication reconciliation process, medication education for patients, medication errors in nursing practice, and multidisciplinary teamwork for medication safety. CONCLUSION: These findings will help nursing researchers and educators to understand the trends and insights for medication safety education and educate future nurses to provide safer nursing care.</t>
@@ -17865,6 +18005,11 @@
       <c r="F306" t="inlineStr">
         <is>
           <t>10.3390/ijerph19074013</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>포함</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -18613,6 +18758,9 @@
       <c r="K318" t="n">
         <v>6</v>
       </c>
+      <c r="O318" t="n">
+        <v>6</v>
+      </c>
       <c r="P318" t="inlineStr">
         <is>
           <t>활용</t>
@@ -18713,6 +18861,11 @@
       <c r="F320" t="inlineStr">
         <is>
           <t>10.1097/cin.0000000000000971</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>포함</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -19881,6 +20034,11 @@
       <c r="F341" t="inlineStr">
         <is>
           <t>10.1177/00469580221139374</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>포함</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -20690,6 +20848,9 @@
       <c r="K355" t="n">
         <v>6</v>
       </c>
+      <c r="O355" t="n">
+        <v>6</v>
+      </c>
       <c r="P355" t="inlineStr">
         <is>
           <t>활용</t>
@@ -20720,6 +20881,14 @@
           <t>10.1016/j.pedn.2022.08.001</t>
         </is>
       </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>포함</t>
+        </is>
+      </c>
+      <c r="O356" t="n">
+        <v>0</v>
+      </c>
       <c r="P356" t="inlineStr">
         <is>
           <t>활용</t>
@@ -21068,6 +21237,9 @@
         <is>
           <t>10.25219/epoj.v11i1.20143</t>
         </is>
+      </c>
+      <c r="O363" t="n">
+        <v>0</v>
       </c>
       <c r="P363" t="inlineStr">
         <is>
@@ -21423,6 +21595,9 @@
           <t>10.2196/32309</t>
         </is>
       </c>
+      <c r="O370" t="n">
+        <v>0</v>
+      </c>
       <c r="P370" t="inlineStr">
         <is>
           <t>활용</t>
@@ -21629,6 +21804,11 @@
       <c r="F374" t="inlineStr">
         <is>
           <t>10.3390/su13137347</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>포함</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -22510,6 +22690,11 @@
       <c r="F389" t="inlineStr">
         <is>
           <t>10.3390/ijerph18179309</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>포함</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -24607,6 +24792,11 @@
           <t>10.3837/tiis.2021.10.006</t>
         </is>
       </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>포함</t>
+        </is>
+      </c>
       <c r="H425" t="inlineStr">
         <is>
           <t>For accurately analysing and forecasting the social networks of China's political, economic and social power elites, it is necessary to develop a database that collates their information. The development of such a database involves three stages: data definition, data collection and data quality maintenance. The present study recommends distinctive solutions in overcoming the challenges that occur in existing comparable databases. We used organizational and event factors to identify the Chinese power elites to be included in the database, and used their memberships, social relations and interactions in combination with flows data collection methodologies to determine the associations between them. The system can be used to determine the optimal relationship path (i.e., the shortest path) to reach a target elite and to identify of the most important power elite in a social network (e.g., degree, closeness and eigenvector centrality) or a community (e.g., a clique or a cluster). We have used three social network analysis tools (i.e., R, UCINET and NetMiner) in order to find the important nodes in the network. We compared the results of centrality rankings of each tool. We found that all three tools are providing slightly different results of centrality. This is because different tools use different algorithms and even within the same tool there are various libraries which provide the same functionality (i.e., ggraph, igraph and sna in R that provide the different function to calculate centrality). As there are chances that the results may not be the same (i.e. centrality rankings indicating the most important nodes can be varied), we recommend a comparison test using different tools to get accurate results.</t>
@@ -24769,12 +24959,20 @@
           <t>10.4018/IJSI.2021070104</t>
         </is>
       </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>포함</t>
+        </is>
+      </c>
       <c r="H428" t="inlineStr">
         <is>
           <t>Some point out that the influence of YouTube's video recommendation algorithm is causing users to be exposed to only video clips in limited subjects or fields, especially to biased content with opinions that are tilted to one side. However, there is a lack of empirical research on filter bubbles as algorithms in YouTube have not been disclosed. This study indirectly demonstrated the phenomenon of filter bubble on YouTube by extracting comment-based content network between uploaders who posted videos and writers who wrote comments on the video by each subject of the contents. Also, this study analyzed communication patterns between users through social network analysis (SNA). According to the analysis, users' narrow information acquisition and communication phenomenon caused by the filter bubble in YouTube was found.</t>
         </is>
       </c>
       <c r="K428" t="n">
+        <v>1</v>
+      </c>
+      <c r="O428" t="n">
         <v>1</v>
       </c>
       <c r="P428" t="inlineStr">
@@ -25108,6 +25306,9 @@
 본 연구는 지역사회혁신 활성화 주관부서인 행정안전부2)가 주최하는 사회혁신 행사 &lt;사회혁신한마당 SSIN&gt;에 소개된 전국의다양한 사회혁신 프로젝트를 분석하였다. 사회 연결망 분석(Social Network Analysis, SNA)을 활용하여 주요 토픽과 키워드를 도출하고, 이들의 목적에 대한 사회적 동향을 살폈다. 사회혁신 프로젝트의 분야별 특성을 파악하여 지속가능한 사회혁신생태계 조성을 위한 시사점을 제시하고자 한다.</t>
         </is>
       </c>
+      <c r="O434" t="n">
+        <v>0</v>
+      </c>
       <c r="P434" t="inlineStr">
         <is>
           <t>활용</t>
@@ -25350,6 +25551,9 @@
           <t>10.3390/su13105579</t>
         </is>
       </c>
+      <c r="O439" t="n">
+        <v>0</v>
+      </c>
       <c r="P439" t="inlineStr">
         <is>
           <t>활용</t>
@@ -25578,6 +25782,9 @@
         <is>
           <t>10.1108/BEPAM-03-2020-0047</t>
         </is>
+      </c>
+      <c r="O444" t="n">
+        <v>0</v>
       </c>
       <c r="P444" t="inlineStr">
         <is>
@@ -25887,12 +26094,20 @@
           <t>10.1016/j.landurbplan.2020.103934</t>
         </is>
       </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>포함</t>
+        </is>
+      </c>
       <c r="H450" t="inlineStr">
         <is>
           <t>The peri-urban area has undergone tremendous changes in various aspects. Tourism-driven development in this area, echoing the longing of urban residents for recreational and leisure space, provides an alternative to conventional urbanization approaches. Particularly, in view of heightened conflicts and fierce competitions that often occur in the area, developing the knowledge of the co-visitation network, or how different attractions and villages interact with each other from the visitors' perspective, is key to more informed planning strategies. With the rapid development of online social media platforms and mobile devices, researchers can collect massive realtime data on the basis of online user-generated content. While there are already many attempts on its application on tourism design, few studies to date have explored how peri-urban attractions and villages are organized in same trips. In this paper, we design a new methodology on the basis of social media analytics to construct and map a co-visitation network, and apply NetMiner-enabled social network analysis to explain its structure and nodal functions. The usefulness of this methodology is demonstrated through a detailed case study in Shenzhen, China. Research findings reveal types of existing co-visitation patterns, which help planners predict future trends, design new experiences and take specific measures in line with visitor demands.</t>
         </is>
       </c>
       <c r="K450" t="n">
+        <v>37</v>
+      </c>
+      <c r="O450" t="n">
         <v>37</v>
       </c>
       <c r="P450" t="inlineStr">
@@ -26139,12 +26354,20 @@
           <t>10.1016/j.jlp.2020.104122</t>
         </is>
       </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>포함</t>
+        </is>
+      </c>
       <c r="H454" t="inlineStr">
         <is>
           <t>In order to improve the reliability and safety of railway dangerous goods transportation system (RDGTS), and prevent the similar accidents happened again, an easier operated, dynamic, systemic and quantitative approach called expanded Safety Failure Event Network (SFEN) is proposed to analyze the past typical RDGTS accidents. The expanded SFEN focuses on transfer the traditional safety occurrence process into a visible Accident Analysis Network (AAN) platform. To improve the previous SFEN approach, the risk factors categories are expanded including Human actions, Technical failure, Nature of transported goods, Environment factors, Management failure and External factors of the system. An AAN is established by using the risk factors as the nodes and using the interactions among these risk factors as the edges, the RDGTS risk analysis problem is transferred into a quantitative network structure analysis problem from a network perspective. After that, based on the AAN, TouchGraph and NetMiner are applied to calculate and rank the centrality degree of each sub-risk factor (or subheading) in a network. A RDGTS accident happened in 2001 is analyzed, the results show that TouchGraph and NetMiner can present the same interactions and importance of sub-risk factors (or sub-headings) through visible circle images in the platform, NetMiner is more digital because the results can be presented as the centrality degree values. The greatest contributed sub-risk factors are Equipment maintenance failure and Railway inspection agency failure, followed by cargo packaging problems, illegal entrainment problem. Misbehaves of the freight inspector with centrality degree 0.523810 shows that this sub-heading has the greatest contribution to the accident.</t>
         </is>
       </c>
       <c r="K454" t="n">
+        <v>20</v>
+      </c>
+      <c r="O454" t="n">
         <v>20</v>
       </c>
       <c r="P454" t="inlineStr">
@@ -27614,6 +27837,11 @@
           <t>10.1111/jan.14685</t>
         </is>
       </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>포함</t>
+        </is>
+      </c>
       <c r="H478" t="inlineStr">
         <is>
           <t>AIMS: The purpose of this study is to examine the relationship between keywords in existing global health nursing studies during 44 years (1974-2017) and to develop schematic diagrams of the relationship between these keywords from a macro perspective. It is to identify the trend of the literature in global health nursing field. DESIGN: A descriptive bibliometric analysis of publications in global health nursing. METHODS: The keywords from 7,115 articles and literatures were examined using the Text Rank Analyzer via the applied text network analysis with NetMiner 4.0. RESULTS: As for global health nursing, keywords with the most frequent appearance and the highest networking degree in centrality were 'study', 'patient', 'nurse', and 'women'. Six central keywords were also found highly related to other keywords: 'global health nursing', 'study', 'patient', 'care', 'nurse', and 'education'. By measuring the degree of keywords connected to other keywords in centrality, six clusters were established. Then, emerging topics assessed by time periods were identified as follows: the beginning phase ('breastfeeding', 'women', and 'children'), the development phase ('quality', 'life', and 'human immunodeficiency virus'), the maturation phase ('mental health', 'depression', and 'global health'), and the expansion phase ('pregnancy', 'palliative care', and 'infectious disease'). CONCLUSION: The identified trends on this study will help nurse leaders to grasp the trends and insights for global health and to train future nurses to serve clients better in the practice fields. IMPACT: Keywords with the highest appearance and centrality in the network were found in the global health articles. The bibliometric analysis showed various subjects according to the following phases: beginning development maturation and expansion. The awareness of the trend change in the global health helps nursing researchers and educators modify the curriculum of global health nursing and train future nurses to be equipped with the global health competencies.</t>
@@ -27900,12 +28128,20 @@
           <t>10.1177/1420326X17732612</t>
         </is>
       </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>포함</t>
+        </is>
+      </c>
       <c r="H483" t="inlineStr">
         <is>
           <t>This study aimed to investigate the association of spatial configuration with social interaction for elderly. A social housing in Seoul was selected for the case study. Using space syntax and social network analysis, the association was examined statistically. This research employed an integration indicator which is most closely related to space use pattern. Questionnaire and interview surveys were conducted to illustrate the pattern of social network. Using the collected data, NetMiner was utilized to conduct a quantitative analysis. Degree, closeness and betweenness indicators were employed to measure relationships in these networks and between individuals. The characteristics of the association established by the statistical analysis between spatial network of housing estate and social network of elderly were discussed. Our results show that spatial network properties can explain characteristics of social network. The accessibility of residential spaces for elderly individuals in social housing apartment complex has an effect on the strength of the social network with neighbours. Also, analysis of the spatial configuration accessibility for the elderly population with integration values has illustrated that the result was opposite to the general theory that 'the locations with high accessibility could foster more interactions'. Our findings have suggested that we can have a better knowledge to foster more social network among elderly by planning improved spatial network.</t>
         </is>
       </c>
       <c r="K483" t="n">
+        <v>6</v>
+      </c>
+      <c r="O483" t="n">
         <v>6</v>
       </c>
       <c r="P483" t="inlineStr">
@@ -29024,6 +29260,9 @@
         <is>
           <t>10.1016/j.jbi.2020.103516</t>
         </is>
+      </c>
+      <c r="O502" t="n">
+        <v>0</v>
       </c>
       <c r="P502" t="inlineStr">
         <is>
@@ -29776,6 +30015,9 @@
 활성화의 요소가 될 수 있을 것으로 판단됨</t>
         </is>
       </c>
+      <c r="O515" t="n">
+        <v>0</v>
+      </c>
       <c r="P515" t="inlineStr">
         <is>
           <t>활용</t>
@@ -29806,6 +30048,9 @@
           <t>10.3390/su13010005</t>
         </is>
       </c>
+      <c r="O516" t="n">
+        <v>0</v>
+      </c>
       <c r="P516" t="inlineStr">
         <is>
           <t>활용</t>
@@ -29815,17 +30060,22 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Identification of of Knowledge Structure of Pain Management Nursing Research Applying Text Network Analysis</t>
+          <t>19대 국회 체육분야 발의법안 내용분석</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Park, CS; Park, EJ</t>
+          <t>Kim, Hyeon-Hee; Ilgwang Kim</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>JOURNAL OF KOREAN ACADEMY OF NURSING</t>
+          <t>한국체육정책학회지</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>한국체육정책학회</t>
         </is>
       </c>
       <c r="E517" t="n">
@@ -29833,24 +30083,32 @@
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>10.4040/jkan.2019.49.5.538</t>
+          <t>10.52427/kssp.17.4.13</t>
         </is>
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>Purpose: This study aimed to explore and compare the knowledge structure of pain management nursing research, between Korea and other countries, applying a text network analysis. Methods: 321 Korean and 6,685 international study abstracts of pain management, published from 2004 to 2017, were collected. Keywords and meaningful morphemes from the abstracts were analyzed and refined, and their co-occurrence matrix was generated. Two networks of 140 and 424 keywords, respectively, of domestic and international studies were analyzed using NetMiner 4.3 software for degree centrality, closeness centrality, betweenness centrality, and eigenvector community analysis. Results: In both Korean and international studies, the most important, core-keywords were pain, patient, pain management, registered nurses, care, cancer, need, analgesia, assessment and surgery. While some keywords like 'education, knowledge, and patient-controlled analgesia found to be important in Korean studies; treatment hospice palliative care, and children were critical keywords in international studies. Three common sub-topic groups found in Korean and international studies were pain and accompanying symptoms, target groups of pain management, and RNs performance of pain management. It is only in recent years (201617), that keywords such as performance, attitude, depression, and sleep have become more important in Korean studies than, while keywords such as assessment, intervention, analgesia, and chronic pain have become important in international studies. Conclusion: It is suggested that Korean pain-management researchers should expand their concerns to children and adolescents, the elderly, patients with chronic pain, patients in diverse healthcare settings, and patients' use of opioid analgesia. Moreover, researchers need to approach pain-management with a quality of life perspective rather than a mere focus on individual symptoms.</t>
+          <t>The purpose of this study is to examine the characteristics of the lawmakers who proposed the 19th National Assembly Act on Physical Education and the quantitative status of the bill, categorize the bill through its content analysis, and to analyze the relationship between the structure of the bill in the sports field, and the properties of lawmakers and the network index of lawmakers and the bill decision rate. To achieve this goal, the study selected the sports sector bill proposed by the 19th National Assembly and its members as subjects of study, and the period of study is the 19th National Assembly (2012.5.30.-2016.5.29.). The parliamentary information system was used to collect data, and the data analysis was utilized for connection network analysis using frequency analysis, content analysis, and Netminer 4.2. The conclusions are as follows.
+First, the number of lawmakers representing the 19th National Assembly's sports sector bill came to 59, accounting for 19.7 percent of the total lawmakers. First-term lawmakers, lawmakers with sports-related experience, local constituencies, and members of the sports-related standing committee have proposed more bills in the sports sector.
+Second, the 19th National Assembly introduced the largest number of bills in the field of sports ever.
+Third, the contents of the 19th National Assembly's proposed bill on sports can be broadly divided into seven categories, and its ranking was shown in the following categories: 1) sports administration and finance, 2) sports facilities and industries, 3) sports professionals and welfare, 4) international sports, 5) et.al, 6) sports ethics and 7) sports basic rights. The ranking of the bills was shown in the order of 1) sports facilities and industry, 2) et. al, 3) sports administration and finance, 4) international sports, 5) sports basic rights, 6) sports professionals and welfare, 7) sports ethics, indicating that the importance of the proposed bills and the importance of the number of bills passed were different.
+Fourth, the connection of the 19th National Assembly's bill on physical education turned out to be a single, cohesive network.
+In view of the results of this study, a number of people with expertise in physical education need to enter the National Assembly to promote legislation in the field of sports. In addition, bipartisan cooperation among lawmakers and smooth communication with multiple-term lawmakers should continue to take place in order to pass the bill, which includes what is needed for legal and institutional development of the Korean sports sector.</t>
         </is>
       </c>
       <c r="J517" t="inlineStr">
         <is>
-          <t>WOS:000493986000004</t>
-        </is>
-      </c>
-      <c r="K517" t="n">
-        <v>17</v>
+          <t>ART002528394</t>
+        </is>
+      </c>
+      <c r="L517" t="n">
+        <v>1</v>
+      </c>
+      <c r="M517" t="n">
+        <v>0</v>
       </c>
       <c r="O517" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="P517" t="inlineStr">
         <is>
@@ -29861,33 +30119,50 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>연희 종합지원체계 구축 기본 연구보고서</t>
+          <t>PageRank 알고리즘을 활용한 역대 아시안컵 축구 국가별 랭킹산정</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>김정이, 박정민, 박진우 외</t>
+          <t>JINXUANSHANG; Jae-Hyeon Park; Eunhye Jo; Chang-Hwan Choi</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>2019 서울시 연희단 육성지원 사업</t>
+          <t>한국체육측정평가학회지</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>2019 서울시 연희단 육성지원 사업</t>
-        </is>
-      </c>
-      <c r="E518" t="inlineStr">
-        <is>
-          <t>2019</t>
+          <t>한국체육측정평가학회</t>
+        </is>
+      </c>
+      <c r="E518" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>10.21797/ksme.2019.21.1.007</t>
         </is>
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>응답자-연희 단체 소속 2모드 네트워크 분석</t>
-        </is>
+          <t>이 연구는 PageRank 알고리즘을 활용하여 역대 아시안컵 축구 종목의 국가별 랭킹산정을 목적으로 설계되었다. 구체적으로 이 연구는 아시아축구연맹(AFC)에서 주관한 역대 아시안컵 경기결과(1956년부터 2019까지)를 기반으로 국가별 랭킹을 산정하였다. 또한 2000년대 이전과 이후를 구분하여 아시아 지역 축구의 국가별 경기력 수준에 대한 변화를 확인하고자 하였다. 연구목적을 위해 17회 동안 수행된 아시안컵의 경기결과를 수집하였다. 수집된 자료는 전체 24개 국가가 수행한 본선 110개 경기, 220개의 경기결과이다. 자료처리를 위해 MS-Excel, NetMiner와 IBM SPSS 프로그램을 활용하였다. 연구결과는 다음과 같다. 첫째, PageRank 알고리즘을 활용한 역대 아시안컵 축구 강국은 일본으로 나타났다. 2위는 사우디아라비아, 3위는 대한민국 순이다. 둘째, 2000년대 이전의 경우 쿠웨이트, 이란, 일본이 아시아 지역의 축구 강국으로 나타났다. 셋째, 2000년 이후의 아시아 지역 축구 강국은 일본, 카타르, UAE 순으로 나타났다. 이 연구의 결과는 축구종목의 랭킹산정을 위한 새로운 방법론이자 아시아 지역의 축구 경기력 수준을 확인할 수 있는 정보로 활용 가능할 것이다. 특히, PageRank 알고리즘을 활용하여 스포츠 랭킹산정과 관련한 연구에서 기초정보로 다양하게 활용될 수 있을 것이라 판단한다.</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>ART002452388</t>
+        </is>
+      </c>
+      <c r="L518" t="n">
+        <v>8</v>
+      </c>
+      <c r="M518" t="n">
+        <v>0</v>
+      </c>
+      <c r="O518" t="n">
+        <v>8</v>
       </c>
       <c r="P518" t="inlineStr">
         <is>
@@ -29898,42 +30173,45 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>Social network analysis for social risks of construction projects in high-density urban areas in China</t>
+          <t>Research Trends in ‘The Arts in Psychotherapy’ by Using Keyword Network Analysis</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Yuan, JF; Chen, KW; Li, W; Ji, C; Wang, ZR; Skibniewski, MJ</t>
+          <t>Do Hee Kim; Park, Jooryung</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>JOURNAL OF CLEANER PRODUCTION</t>
+          <t>예술심리치료연구</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>한국예술심리치료학회</t>
         </is>
       </c>
       <c r="E519" t="n">
-        <v>2018</v>
-      </c>
-      <c r="F519" t="inlineStr">
-        <is>
-          <t>10.1016/j.jclepro.2018.07.109</t>
-        </is>
+        <v>2019</v>
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>Social impacts have become increasingly important for urban development in China. In addition, unlike general construction projects, construction projects in high-density urban areas have high levels of complexity and uncertainty. Thus, from a network perspective, an improved social risk analysis theory and a method for these projects were generated in this paper. A case study involving 66 cases of social conflicts in construction projects in China was performed, and 16 social risk factors were summarized. Eight stakeholders related to these social risk factors were then identified based on a literature review and the case database. A theoretical model for social risk network analysis considering the interrelationships between stakeholders and risks was developed by using NetMiner, a social network analysis (SNA) tool. A 2-mode network and two 1-mode networks were used to analyze the relationships among the identified 16 social risk factors and 8 stakeholders. In terms of three-level challenges such as complex environments, the unreasonable behavior of individuals or organizations, and diversified interaction between behaviors and environments, the most important social risks of construction projects in high-density urban areas were explored to help the government implement effective social risk management measures. In addition, multiple, complicated relationships among residents, contractors, governmental authorities, and owners represented a major factor leading to social risk; therefore, more attention should be focused on this topic. The proposed social risk analysis method can increase the attention paid by project managers, governmental authorities, and project owners to social risk factors in high-density areas and provide a structured framework to analyze such social risks, as well as put forth possible solutions to reduce the social impacts on construction projects in high-density urban areas. (C) 2018 Elsevier Ltd. All rights reserved.</t>
+          <t>Although literature reviews in the field of arts psychotherapy have previously been conducted, such studies generally only targeted specific topics. Therefore, the aim of this study was to identify research trends in arts psychotherapy through extensive keyword network analysis. To this end, a total of 1,256 articles published in Journal of ‘The Arts in Psychotherapy’ from 1980 to 2017 were analyzed. Keywords were extracted depending on period of decade and the relationship between keywords was visualized using the NetMiner 4.3 program. As a result of this study, trends of appeared keywords and changing patterns of linkages between keywords were structurally examined in a specific decade. Findings indicated that trends were closely related to sociopolitical changes and mental health policy. This study delineates research trends in this field, collating them into a single source. Further, it relates to articles published in the journal over the previous 37 years, providing a detailed description of the most-discussed topics.</t>
         </is>
       </c>
       <c r="J519" t="inlineStr">
         <is>
-          <t>WOS:000442973100082</t>
-        </is>
-      </c>
-      <c r="K519" t="n">
-        <v>141</v>
+          <t>ART002457844</t>
+        </is>
+      </c>
+      <c r="L519" t="n">
+        <v>6</v>
+      </c>
+      <c r="M519" t="n">
+        <v>0</v>
       </c>
       <c r="O519" t="n">
-        <v>141</v>
+        <v>6</v>
       </c>
       <c r="P519" t="inlineStr">
         <is>
@@ -29944,35 +30222,3091 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
+          <t>교육학에서의 전문성 관련 연구 동향 분석</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Oh Ji Hyun; Jung-Yeon, Lim</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>학습자중심교과교육연구</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>학습자중심교과교육학회</t>
+        </is>
+      </c>
+      <c r="E520" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>10.22251/jlcci.2019.19.21.1225</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>본 연구는 인구절벽, 4차 산업혁명 등 급변하는 교육생태계 변화에 맞추어 교육학분야에서의 전문성 관련 연구 동향을 분석하는데 목적이 있다. 이를 위해 최근 10년(2008년~2018년) 동안 KCI 교육학분야 등재지에 “전문성”을 제목에 사용한 국내 학술지 280편의 키워드 1,093개의 네트워크 분석을 실시하였다. 분석은 NetMiner를 사용하였으며, 상위 키워드 빈도분석, 중심성 분석, 커뮤니티 분석을 실시하였다. 연구결과는 다음과 같다. 첫째, 교육학분야의 전문성 관련 연구는 교원, 유아, 교과(수업)관련 학술지에서 전문성 개발방안, 전문성구성요소, 전문성개발 지원환경 등 다양한 영역을 포괄하여 이루어져왔다. 둘째, 교육학 분야 전문성 관련 연구는 교사전문성, 수업전문성을 핵심으로 이를 개발하기 위해 협력, 학습공동체, 실천공동체, 교사연수, 인디스쿨 등이 활용되고 있었다. 셋째, 전문성 연구분야는 전문성평가, 교사의 전문성개발 방안, 교사수업전문성, 전문성 구성요인과 지원방안, 수업현장에서의 전문성개발 등 5개의 영역을 중심으로 이루어지고 있었다. 이러한 결과를 토대로 미래 교육환경 변화에 적극적으로 대응하기 위한 전문성개발 지원 준비가 필요하다는 점을 제안하였다.</t>
+        </is>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>ART002523209</t>
+        </is>
+      </c>
+      <c r="L520" t="n">
+        <v>4</v>
+      </c>
+      <c r="M520" t="n">
+        <v>0</v>
+      </c>
+      <c r="O520" t="n">
+        <v>4</v>
+      </c>
+      <c r="P520" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>국내 영어 교육 분야에서의 비판적 사고 관련 연구 동향</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>방준</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>영어교과교육</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>한국영어교과교육학회</t>
+        </is>
+      </c>
+      <c r="E521" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>10.18649/jkees.2019.18.4.141</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>The purpose of this study was to analyze the trends on critical thinking studies of English education in domestic. For this, 43 papers related to critical thinking of English education for 19 years from 2000 to 2018 were collected from RISS, KISS, DBPIA, NDSL, National Library of Korea, National Assembly Library, National Digital Library. The papers were analyzed according to six standards such as the date of research, publication type, subject, research methodology, research theme and purpose of study. The key-words extracted from the abstract were analyzed by utilizing key-word network analysis methods namely NetMiner. The results showed that the studies on critical thinking of English education have increased steadily centered around university students. In the early 2000’s, studies that focused on ‘critical thinking’ and ‘critical reading’ were developed in various ways such as ‘writing, speaking’ and ‘discussion.’ In the key-word network analysis, ‘critical thinking’ as centered key-word frequency, and key-words ‘critical literacy,’ ‘critical reading,’ ‘critical pedagogy,’ ‘college student’ and ‘writing class’ were the primary key-words. Based on these results, it was suggested that more research on critical thinking of English education reflecting more various age groups and language skills be necessary.</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>ART002526495</t>
+        </is>
+      </c>
+      <c r="L521" t="n">
+        <v>8</v>
+      </c>
+      <c r="M521" t="n">
+        <v>0</v>
+      </c>
+      <c r="O521" t="n">
+        <v>8</v>
+      </c>
+      <c r="P521" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>국내 인지행동치료 연구의 지식구조: 동시출현단어 분석</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Do Hee Kim; Hyeon-Jin Kim; Da-hye An</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>디지털융복합연구</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>한국디지털정책학회</t>
+        </is>
+      </c>
+      <c r="E522" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>10.14400/jdc.2019.17.12.509</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>본 연구는 인지행동치료(Cognitve Behavioral Therapy: CBT)분야 학술지에서 나타난 키워드의 출현패턴을 조사하여 국내 CBT 연구의 지식구조를 규명하는 데에 목적이 있다. 국내·외에서 수행된 CBT 연구를 비교하고자 ‘인지행동치료’에서 출판된 논문 234편(2008-2019)과 ‘Cognitive Therapy and Research’에서 출판된 논문 2,316편(1977-2019)이 수집되었다. 자료는 NetMiner 4.3 프로그램으로 분석되었으며 동시출현단어 분석은 코사인 유사도 행렬을 산출하고, 네트워크를 시각화하는 절차로 수행되었다. 본 연구의 결과로 국내 CBT연구자들의 주요 관심사가 식별되었고, 국내 CBT 지식구조는 9개의 연구영역으로 범주화되었다: ‘척도 타당화’, ‘완벽주의와 속박감’, ‘조현병 환자의 인지, 정서, 관계적 특성’, ‘경계선 성격장애와 우울/양극성 장애 환자의 인지적 특성과 치료’, ‘적응과 심리적 건강’, ‘사회불안장애 환자의 인지적 특성과 치료’, ‘우울의 원인과 공존이환’, ‘수용전념치료’, ‘폭식 장애 환자의 이해와 치료’. 본 연구는 지난 11년 동안 국내 CBT 분야에서 축적된 지식을 점검하였다는 데에 의의가 있으며 국내 CBT 연구의 향후 발전과제로 임상적 실천 표준을 제고하기 위한 연구가 필요하다고 제안한다.</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>ART002533621</t>
+        </is>
+      </c>
+      <c r="L522" t="n">
+        <v>3</v>
+      </c>
+      <c r="M522" t="n">
+        <v>0</v>
+      </c>
+      <c r="O522" t="n">
+        <v>3</v>
+      </c>
+      <c r="P522" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>국내 청소년 배드민턴 단식 개인 및 팀 랭킹 산출: PageRank 알고리즘 적용</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Kyungmin Ra; Lee Mi Sook; Eunhye Jo</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>스포츠사이언스</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>체육과학연구소</t>
+        </is>
+      </c>
+      <c r="E523" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>10.46394/iss.37.1.11</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>이 연구에서는 PageRank 알고리즘을 적용하여 국내 청소년 배드민턴 단식 개인 및 팀의 랭킹을 산출하고 그 유용성을 검토하는 데 목적이 있다. 주요 분석 대상 자료는 대한배드민턴협회(2019) 홈페이지에 공개된 자료로서 2018년도에 실시된 중등부와 고등부의 남ㆍ여 단식경기 결과이다. 수집된 자료는 PageRank 알고리즘을 적용한 랭킹과 승률에 기반한 랭킹(WP_r)을 산출하였으며, 두 랭킹 산출 방법 간의 관련도를 검토하기 위하여 Kendall의 순위상관분석을 적용하였다. 자료 분석을 위해서 MS-Excel, NetMiner 4.0과 IBM SPSS 21.0 프로그램을 사용하였다. 이 연구의 주요결과는 다음과 같다. 첫째, 배드민턴 중등부 남자단식 랭킹, 중등부 여자단식 랭킹, 고등부 남자단식 랭킹, 고등부여자단식 랭킹을 산출한 결과, 상위 15위 결과에서는 PageRank와 승률랭킹 간에는 차이가 있었지만, PageRank와 승률랭킹(WP_r)의 상관도를 검토 한 결과 통계적으로 유의한 것으로 나타났다. 둘째, 배드민턴 중등부 남자단식 팀 랭킹, 중등부 여자단식랭킹, 고등부 남자단식랭킹, 고등부 여자단식랭킹을 산출한 결과, 첫째 결과와 마찬가지로PageRank와 승률랭킹(WP_r)의 상관분석 결과 관계성이 유의하게 높은 것으로 나타났다. 셋째, PageRank와 승률랭킹(WP_r) 간의 결과에서 관계성이 유의한 것으로 확인됨으로써 대한배드민턴협회에서 실시하는 청소년대표 및 국가대표 후보군 선발 시 유용한 객관적인 기초자료 제공이 기대된다.</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>ART002492787</t>
+        </is>
+      </c>
+      <c r="L523" t="n">
+        <v>5</v>
+      </c>
+      <c r="M523" t="n">
+        <v>0</v>
+      </c>
+      <c r="O523" t="n">
+        <v>5</v>
+      </c>
+      <c r="P523" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>국내외 허위정보 연구동향 비교분석</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Heesop Kim; Kang Bora</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>한국문헌정보학회지</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>한국문헌정보학회</t>
+        </is>
+      </c>
+      <c r="E524" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>10.4275/kslis.2019.53.3.291</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>본 연구의 목적은 국내외 허위정보에 관한 연구동향을 비교분석하는 것이다. 이를 위하여 전학문 분야의 학술지를 대상으로 연구기간의 제한이 없이 국내논문 104편과 국외논문 861편에 나타난 저자가 부여한 영문키워드를 수집하였다. 국내논문에서 수집된 283개 영문키워드와 국외논문에서 수집된 3,551개 영문키워드는 NetMiner V.4를 사용하여 키워드 네트워크의 연결중심성과 매개중심성을 분석하였으며, 분석결과는 다음과 같다. 첫째, 연구 주제의 양적 측면에서 국내의 경우는 ‘Freedom of Expression’, ‘Fact Check’, ‘Regulation’, ‘Media Literacy’, ‘Information Literacy’로 순으로, 국외의 경우는 ‘Social Media’, ‘Post Truth’, ‘Propaganda’, ‘Information Literacy’, ‘Journalism’ 순으로 나타났다. 둘째, 연구 주제의 영향력 측면에서 국내의 경우는 ‘Fact Check’, ‘Freedom of Expression’, ‘Hoax’ 순으로, 국외의 경우는 ‘Social Media’, ‘Detection’ 순으로 확인되었다. 마지막으로 연구 주제의 확장성 측면에서 국내의 경우는 ‘Fact Check’, ‘Polarization’, ‘Freedom of Expression’, ‘Commercial’ 순으로 나타났다. 한편, 전체키워드에서 낮은 빈도를 보였던 ‘Commercial’이 ‘Media Literacy’, ‘Freedom of Expression’ 등을 매개하며 상대적으로 매개역할정도가 큰 것으로 확인되었다. 국외의 경우는 ‘Social Media’, ‘Detection’, ‘Machine Learning’이 주요 연결다리로 나타났다.</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>ART002494809</t>
+        </is>
+      </c>
+      <c r="L524" t="n">
+        <v>11</v>
+      </c>
+      <c r="M524" t="n">
+        <v>0</v>
+      </c>
+      <c r="O524" t="n">
+        <v>11</v>
+      </c>
+      <c r="P524" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>금강산관광에 대한 인식 변화 연구: 소셜미디어 빅데이터를 중심으로</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Noh, Hee-Kyung</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>관광경영연구</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>관광경영학회</t>
+        </is>
+      </c>
+      <c r="E525" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>10.18604/tmro.2019.23.43.</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>This study focuses on the fact that most people's perception survey related to Mt. Geumgang tourism is based on a number of positive, neutral, or disagreements. Therefore, this study attempted to confirm various perception changes about Mt. Geumgang tourism. Web crawler collected data related to 'Mt. Geumgang tourism' posted on Naver's blog and cafe. And we used NetMiner program to derive text frequency, weight, and topic modeling. The data collection period was divided into five years before the suspension, five years after the suspension, and up to the latest, based on when the tour was stopped. As a result of analysis, it was recognized as keywords and topics directly related to tourism before the suspension of Mt. Geumgang tourism. This confirms that Mt. Geumgang tourism recognizes not only the tourism aspect but also the various ripple effects. After the suspension of Mt. Geumgang tourism, it was confirmed that the event was recognized as an event, normalization, and dialogue. In addition, economic expectation was recognized most recently, and it was confirmed that it was recognized as a topic such as international politics and political tourism intervention efforts. This study examined the changes in perceptions of Mt. Geumgang tourism by using social media big data, which has been recently used in various fields. It is meaningful to present the basis for drafting a policy that reflects the public's perception of becoming a party to Mt. Geumgang Tourism and Unification Tourism on the Korean Peninsula.</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>ART002510035</t>
+        </is>
+      </c>
+      <c r="L525" t="n">
+        <v>7</v>
+      </c>
+      <c r="M525" t="n">
+        <v>0</v>
+      </c>
+      <c r="O525" t="n">
+        <v>7</v>
+      </c>
+      <c r="P525" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>네트워크 기반 키워드 분석을 활용한 국내 여성 신체활동 연구의 지식구조 탐색</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Chang-Hwan Choi; KIM HYE RYEON</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>한국체육측정평가학회지</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>한국체육측정평가학회</t>
+        </is>
+      </c>
+      <c r="E526" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>10.21797/ksme.2019.21.1.006</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>이 연구는 네트워크 기반 키워드 분석을 활용하여 국내 여성 신체활동을 주제로 수행된 연구들의 지식구조를 탐색하고자 설계되었다. 세부적으로 이 연구는 첫째, 국내 여성 신체활동 연구의 학술지 및 연도별 출판현황에 관한 기초정보를 산출하였으며 둘째, 국내 여성 신체활동 연구에서 사용되는 주요 키워드를 분석하였다. 셋째, 국내 여성 신체활동 연구의 지식구조를 네트워크 기반 키워드 분석을 활용하여 확인하였다. 국내 여성 신체활동 관련 연구를 모집단으로 선정하였으며, 자료정제 과정을 통해 전체 126편의 연구물, 중복포함 854개 키워드, 354개의 개별 키워드를 연구자료로 선정하였다. 자료처리를 위해 기술통계, 네트워크 기반 키워드 분석을 수행하였다. 자료처리는 Netminer 4.0프로그램을 활용하였다. 이 연구의 결과는 다음과 같다. 첫째, 국내 여성 신체활동 관련 연구는 1999년부터 현재까지 지속적으로 증가하고 있다. ‘한국체육과학회지’에 가장 많은 연구물이 출판되고 있으며, 학문분야로서 체육학 분야에서 가장 많은 연구가 이루어지고 있다. 둘째, 국내 여성 신체활동 연구에서 주로 적용되는 상위 5개 키워드는 ‘비만’, ‘노인’, ‘신체’, ‘건강’, ‘운동’ 으로 나타났다. 셋째, 국내 여성 신체활동 연구는 ‘비만’ 키워드를 중심으로 ‘신체 및 운동’, ‘기능 및 연령’, ‘여가 및 사회’, ‘심리’ 연구영역의 지식구조를 형성하고 있음을 나타냈다. 이 연구의 결과는 국내 여성 신체활동 관련 연구동향 및 지식구조에 대한 기초정보로 다양한 학문영역에서 활용될 수 있을 것이다.</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>ART002452387</t>
+        </is>
+      </c>
+      <c r="L526" t="n">
+        <v>20</v>
+      </c>
+      <c r="M526" t="n">
+        <v>0</v>
+      </c>
+      <c r="O526" t="n">
+        <v>20</v>
+      </c>
+      <c r="P526" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>네트워크 분석을 통한 국내 직업교육훈련의 연구동향 분석</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Jung-Yeon, Lim; Youngeun Wee</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>직업과 자격 연구</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>(사)한국직업자격학회</t>
+        </is>
+      </c>
+      <c r="E527" t="n">
+        <v>2019</v>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>본 연구는 국내 직업교육훈련 관련 연구의 특성을 파악하고, 향후 직업교육훈련 연구에 시사점을 도출하는데 목적이 있다. 연구목적을 달성하기 위하여 직업교육훈련과 관련된 국내 연구 중 2003년∼2016년까지 등재학술지에 게재된 논문 1083편의 키워드 3,326개를 분석하였다. 분석은 키워드 네트워크구조 및 중심성분석을 실시하였으며, 연구분야 및 연도별 특징을 심층적으로 분석하였다. 연구결과는 다음과 같다. 첫째, 전체 키워드 분석결과, 직업교육훈련의 대상은 직업계 고등학생 및 대졸청년, 장애인, 중소기업 근로자 등 노동시장 취약계층이 주를 이루어지고 있었으며, 연구내용은 진로, 교육, 취업을 전반적으로 포괄하고 있었다. 둘째, 직업교육훈련 연구는 교육분야 학문을 중심으로 노동, 복지분야와 연결됨으로서 교육과 고용을 통한 복지차원에서의 직업교육훈련의 역할을 강조하고 있었다. 셋째, 직업교육훈련을 바라보는 관점에 따라 진로 혹은 취업, 조직성과 등 연구의 초점에 차이를 보였다. 마지막으로 직업교육훈련 연구는 연도별 주요 직업능력개발 정책과 함께 발전하는 특성을 보였다. 이러한 연구결과를 바탕으로 향후 직업교육훈련에 대한 방향과 시사점을 제시하였다.</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>ART002459708</t>
+        </is>
+      </c>
+      <c r="L527" t="n">
+        <v>10</v>
+      </c>
+      <c r="M527" t="n">
+        <v>0</v>
+      </c>
+      <c r="O527" t="n">
+        <v>10</v>
+      </c>
+      <c r="P527" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>네트워크-메타분석을 활용한 치매환자 대상 신체활동 프로그램의 효과검증</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Jiwun Yoon; Hyo-jun Yun</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>한국체육학회지</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>한국체육학회</t>
+        </is>
+      </c>
+      <c r="E528" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>10.23949/kjpe.2019.03.58.2.517</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>이 연구는 네트워크-메타분석을 활용한 치매환자를 대상으로 신체활동 프로그램의 통합적 효과를 확인하는 것이 목적이다. 이목적을 위하여 Pubmed 등 국제학술지에서 보고된 신체활동 및 치매관련 연구주제를 키워드로 하여 검색하였다. 연구대상으로선정된 18편의 논문에서 치매관련 신체활동 효과를 검증하기 위하여 적용한 6개의 독립변수를 추출하였고, 치매의 개선정도(예: 인지기능의 향상)를 측정하는 MMSE, TCD 등의 변화 값을 종속변수로 선정하였다. 전체 192개의 중재변수들 간 일대일 관계를대상으로 효과크기를 산출하여 네트워크-메타분석에 적용하였다. 각 연구에서 변수 간 관계로부터 산출한 ES를 넷마이너 4.3을이용하여 행렬로 변환시킨 후 네트워크 분석을 수행하였다. 이때, 2-모드 네트워크 분석모형을 적용하여 연결중앙성과 페이지랭크 값을 활용하여 독립변수의 효과순위를 산출하였다. 이 연구의 결론은 다음과 같다. 첫째, 네트워크-메타분석을 활용하여 신체활동 프로그램 효과를 전체적인 관점에서 분석한 결과 치매노인들을 대상으로 MMSE, CDT, TCD 검사를 활용할 때 독립변수의효과를 민감하게 확인할 수 있다. 둘째, 네트워크-메타분석을 활용하여 치매노인들을 대상으로 신체활동 프로그램을 적용한 결과독립변수의 효과는 80-85세 알츠하이머 치매노인을 대상으로, 유산소 및 복합운동프로그램을 적용하여, 표준케어방법으로 1회1-2시간의 활동을 수행하였을 때 가장 효과가 크다. 셋째, 치매검사도구에 따라서 독립변수의 효과크기는 차이가 있다.</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>ART002456826</t>
+        </is>
+      </c>
+      <c r="L528" t="n">
+        <v>3</v>
+      </c>
+      <c r="M528" t="n">
+        <v>0</v>
+      </c>
+      <c r="O528" t="n">
+        <v>3</v>
+      </c>
+      <c r="P528" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>드론 테러에 관한 신문기사 언어 네트워크 분석과 시사점</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Jung, Byung Soo</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>한국융합과학회지</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>한국융합과학회</t>
+        </is>
+      </c>
+      <c r="E529" t="n">
+        <v>2019</v>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>연구목적 : 이 연구의 목적은 드론 테러 관련 신문기사를 대상으로 언어 네트워크 분석을 통해 핵심 이슈를 파악하여 드론 테러의 효율적인 대응을 위한 시사점을 도출하는 것이다. 연구방법 : 이 연구는 드론 테러에 관한 언론보도의 경향 및 특성을 살펴보기 위하여 언어 네트워크 방법론을 활용하였다. 신문기사는 인터넷 검색포털 사이트 ‘Daum’에서 서비스하고 있는 신문기사 상세검색 기능을 활용하여 기사를 검색하였다. 전체 언론사를 대상으로 문재인 정부 출범(2017년 5월 10일) 이후부터 2019년 9월 15일까지의 기간을 설정하고 ‘드론 테러’라는 검색어를 입력하여 신문기사를 수집하였다. 수집된 기사 중에서 중복 기사 및 본 연구에 부합하지 않는 기사는 제외하고 총 116건의 기사를 선별하여 분석에 활용하였다. 언어 네트워크 분석을 실시하기 위해 한국어 텍스트 분석은 KrKwic(Korean Key Words in Context) 프로그램을 이용하였으며, 네트워크 분석 및 시각화는 NetMiner 4 프로그램을 사용하였다. 결론 : 이 연구의 분석결과는 드론 테러에 대한 효율적 대응방안을 모색하는데 있어 몇 가지 시사점을 던져주고 있다. 첫째, 드론 테러의 대응을 위한 가장 강력한 대안으로 안티드론 시스템이 논의되고 있으나 안티드론 시스템은 태생적으로 비용대비 효율이 낮은 문제점이 있으며, 현실적으로 드론에 의해 초래되는 다양한 유형의 위협을 확실하고 정확하게 제거할 수 있는 완벽한 안티드론 기술은 없기 때문에 안티드론 시스템 구축과 더불어 드론 테러를 사전에 예방할 수 있는 대책마련이 요구된다. 둘째, 드론 산업을 성장, 발전시키면서 드론의 부작용을 최소화할 수 있는 실질적이고 현실적인 방안은 안티드론 산업을 미래의 먹거리로 인식을 전환하고 다양한 안티드론 기술을 개발ㆍ적용하는 것이다. 셋째, 외국인 노동자, 국제 결혼, 새터민과 난민의 증가 등으로 인하여 자생 드론 테러의 발생 가능성이 있기 때문에 이에 대한 대비가 필요하다.</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>ART002532137</t>
+        </is>
+      </c>
+      <c r="L529" t="n">
+        <v>10</v>
+      </c>
+      <c r="M529" t="n">
+        <v>0</v>
+      </c>
+      <c r="O529" t="n">
+        <v>10</v>
+      </c>
+      <c r="P529" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>무인항공기 기술진화 탐색 및 유망기술 발굴 연구</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Seong-Hyeon Joo</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>항공우주시스템공학회지</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>항공우주시스템공학회</t>
+        </is>
+      </c>
+      <c r="E530" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>10.20910/jase.2019.13.6.80</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>효과적인 유망기술 발굴을 위해 미래 사회 변화를 전망하고, 미래기술 도출 방법론 및 프로세스 개선 연구가 필요하며, 연구소·기업에서 기술기획에 활용할 기초자료의 필요성이 꾸준히 대두되고 있다. 따라서 본 연구는 국내 무인항공기산업과 같은 신성장동력산업의 국제적 기술 경쟁력 확보와 시장성 확보 및 산업성장이 가능한 미래유망 기술을 도출하는 방법론을 제시하는 것이다. 이에 본 연구는 KrKwic, Excel, NetMiner등의 분석툴을 활용하여 무인항공기산업 분야의 특허데이터를 대상으로 동시출현 단어를 활용한 소셜네트워크분석과 하위그룹분석, 인지지도분석 방법을 제시하였다. 이를 통해, 무인항공기산업 분야의 기술진화를 탐색하고 유망기술을 예측하는 방법을 제시하였다. 그 결과, ‘체계연동/통합 기술’, ‘시험평가/감항인증 기술’, ‘항공전자 기술’, ‘비행제어 기술’, ‘피아식별 기술’, ‘비행통제 시스템 기술’, ‘지원장비 기술’ 등은 향후 유망한 기술로 선정하여 집중 투자할 필요성이 큰 기술이라 볼 수 있었다.</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>ART002540366</t>
+        </is>
+      </c>
+      <c r="L530" t="n">
+        <v>3</v>
+      </c>
+      <c r="M530" t="n">
+        <v>0</v>
+      </c>
+      <c r="O530" t="n">
+        <v>3</v>
+      </c>
+      <c r="P530" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>미디어 담론에 나타난 무용 의미 탐색</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Lee Ye-Seul</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>대한무용학회 논문집</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>대한무용학회</t>
+        </is>
+      </c>
+      <c r="E531" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>10.21317/ksd.77.3.6</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>This study analyzed the words and topics related to dance, focusing on news articles during the media discourse, to explore the meaning of dance recognized by the contemporary public. A total of 34,505 news ar ticles related to 'dance' were collected from Korean Integrated News Database System (KINDS). The collected data went through a data clean ing process. Topic modeling analysis was carried out Latent Dirichlet Allocation(LDA) using to Netminer 4.
+The analysis resulted in five topics. First, the topic of the “Dance Festival” drew attention to the fact that a world-class dance festival that communicates and harmonizes with multicultural families and citizens through dance. Second, the topic of “Television Dance Program” high lighted dance survival, 'Dancing 9,' which focuses on dance. Third, the topic of "Dance Education" showed the therapeutic and educational ef fects of dance and cases of ballet educational institutions worldwide.
+Fourth, the role of dance in Korea becoming the center of Asian culture in the topic of "Universalization of Dance" and Choi Seung-hee, a world-renowned dancer, became an issue. Fifth, in the topic of "Dance Performing Art," works by dance troupes from home and abroad and per formances by world-renowned dance troupes in Korea made headlines.</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>ART002480623</t>
+        </is>
+      </c>
+      <c r="L531" t="n">
+        <v>6</v>
+      </c>
+      <c r="M531" t="n">
+        <v>0</v>
+      </c>
+      <c r="O531" t="n">
+        <v>6</v>
+      </c>
+      <c r="P531" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>미디어 빅데이터를 통한 미디어의 등산 보도 의미연결망 분석</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Kim, Kyung-Sik</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>한국사회체육학회지</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>한국사회체육학회</t>
+        </is>
+      </c>
+      <c r="E532" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>10.51979/kssls.2019.05.76.237</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>Purpose: This study aims to identify the most frequently occurring words, word pairs in the media climbers’ report and the words of high centralities in the semantic network. It also aims to analyze the news frame.
+Method: This study collected data on climbing-related articles reported in national comprehensive daily newspapers and central broadcasting for the past 10 years from January 1, 2009 to December 31, 2018. In order to search for articles related to mountain climbing, the study collected mountain climbing articles for central newspaper and central broadcasting. There were 3,129 articles totaling 32,742 words. This data is composed through Excel and analyzed through the Netminer program. Data were analyzed by frequency analysis, centrality analysis, and cohesion group analysis.
+Results: The results are as follows. First, the frequency of important words was in order of exercise, price, joint, hiking, safety, self, healing, economy, rescuing, climbers, and concurrent word pairs were Korean-hobby, climbing-hiking, and Korean–climbing. Second, the main words showed similar tendencies in the three centralities. Koreans, exercise, spring, fall, etc. were highly central. Third, the climbing network of the media was represented by five subgroups. Subgroup one consisted of altitude sickness and symptom, subgroup two of spring, mountain hiking and hiking, subgroup three of sports, subgroup four of Koreans, and subgroups five of climbers. In this study, we focused on newspaper articles and broadcasting reports, but in the follow-up research, it is necessary to analyze the semantic network of social media such as Twitter, Facebook, YouTube and etc.
+Conclusion: Top words of climbing are similar regardless of centralities. Several particular words and word groups symbolize Korean mountain climbing.</t>
+        </is>
+      </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>ART002471124</t>
+        </is>
+      </c>
+      <c r="L532" t="n">
+        <v>9</v>
+      </c>
+      <c r="M532" t="n">
+        <v>0</v>
+      </c>
+      <c r="O532" t="n">
+        <v>9</v>
+      </c>
+      <c r="P532" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>미용대학 학생의 현장실습이 전공만족, 진로결정자기효능감, 취업행동에 미치는 영향 - 현장실습에 관한 만족과 불만족의 차이를 중심으로 -</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Ran-Sug Seo</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>한국미용학회지</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>한국미용학회</t>
+        </is>
+      </c>
+      <c r="E533" t="n">
+        <v>2019</v>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>The purpose of this study is to clarify the difference between satisfaction and dissatisfaction, career decision - making self - efficacy, and employment behavior in the cosmetology department through fieldwork of university students through social network analysis. The survey was conducted for 20 days from April 1 to 20, 2018 for graduates of the department of beauty. 100 students of university students who were satisfied with on-the-job training, 100 students who were unsatisfied with university students, Respectively. Data were analyzed using SPSS 21.0, AMOS 21.0 and Netminer 4 program. We analyzed the general characteristics of the sample through frequency analysis. The variables were verified through factor analysis. And we analyzed the relationship of variables through network analysis. The results of the study showed that there was a difference between satisfaction and dissatisfaction with major satisfaction, career decision self - efficacy, and social network analysis result of employment behavior according to satisfaction and dissatisfaction of field practice of cosmetology university students. The field practice ultimately has a close relationship with employment behavior and emphasizes the importance of field practice in universities and industry.</t>
+        </is>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>ART002441038</t>
+        </is>
+      </c>
+      <c r="L533" t="n">
+        <v>8</v>
+      </c>
+      <c r="M533" t="n">
+        <v>0</v>
+      </c>
+      <c r="O533" t="n">
+        <v>8</v>
+      </c>
+      <c r="P533" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>빅데이터 분석을 통한 공유문화의 현상 및 시사점 연구 -SNS데이터를 중심으로-</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Meeyoung Hwang</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>한국생활환경학회지</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>한국생활환경학회</t>
+        </is>
+      </c>
+      <c r="E534" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>10.21086/ksles.2019.02.26.1.160</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>Today, the meaning of sharing is recognized as a valuable activity that maximizes economic efficiency through a variety of shared styles, including knowledge and information, as well as physical forms. The purpose of this study is to find out how the concept of sharing, one of the most important cultural phenomena in modern times, is being expressed and constructed in SNS, the plaza of communication among modern people, and to derive suggestions as basic data to help construct spaces supporting shared activities. Also, this study tries to analyze quantitatively the shared phenomenon in social media, its characteristics, and what elements are related to each other.
+Among the SNS data that correspond to the unstructured data of Big Data, this study analyzed the Twitter and blogs in the last 6 months (March to August 2018) using NetMiner4.4, a social network analysis program. As a result, the phenomenon of shared culture on the SNS is mainly focused on the subjects of sharing, the activities for sharing, the feelings of users who are felt by sharing, and the place and space where the shared culture is formed. And a significant amount of results were obtained.</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>ART002446833</t>
+        </is>
+      </c>
+      <c r="L534" t="n">
+        <v>5</v>
+      </c>
+      <c r="M534" t="n">
+        <v>0</v>
+      </c>
+      <c r="O534" t="n">
+        <v>5</v>
+      </c>
+      <c r="P534" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>빅데이터를 활용한 여가트렌드 분석</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>KyungSik Kim; Lee， Yeon-Ju; Han, Seung-Jin; Seungbaek Han</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>한국여가레크리에이션학회지</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>한국여가레크리에이션학회</t>
+        </is>
+      </c>
+      <c r="E535" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>10.26446/kjlrp.2019.3.43.1.25</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>이 연구는 최근 10년 간 여가를 주제로 한 신문 기사를 연구대상으로 선정하고 관련 키워드에 관한 의미연결망 분석을 실시하였다. 즉, 10년이란 기간 동안 신문 미디어를 통해 나타난 여가 관련 키워드의 의미가 형성되는 방식을 연결 키워드 분석을 통해 살펴봄으로써 변화하는 여가 트렌드의 특성을 파악하고자 하였다. 각 키워드의 영향력을 살펴보기 위한 분석방법으로는 활동중심성과 매개중심성 분석, 그리고 하위집단 분석을 실시하였다. 결과는 다음과 같다. 첫째, 최상위 여가 관련 키워드 연결망은 시간의 흐름에 따라 변동하였다. 2008년에는 주말, 경정, 사행성, 헬스 등의 여가 키워드가 상위권에 나타난 반면, 2017년에는 가족, 여행, 관광, 레저, 운동, 쇼핑 등이 상위권에 나타났다. 둘째, 한국사회 여가를 상징하는 연결망에서의 최상위 키워드는 중심성에 관계없이 유사하게 나타났다. 영종도, 서울, 수도권, 아웃도어, 캠핑 등의 키워드는 활동중심성과 매개중심성에 높았다. 동시등장 키워드는 영종도-공항, 하루-5시간, 영종도-물길, 영종도-바다, 영종도-공원, 전시-잠실운동장, 서울-녹지 등의 순으로 많이 출현하였다. 셋째, 최근 10년간 한국사회 여가를 상징하는 키워드 연결망은 총 20개의 크고 작은 하위집단들로 구성되었다. 1군집은 63개(47.0%)의 키워드로 구성된 거대 구성집단이었으며, 다시 1군집은 의미있는 6개의 하위집단으로 묶여졌다.</t>
+        </is>
+      </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>ART002449657</t>
+        </is>
+      </c>
+      <c r="L535" t="n">
+        <v>47</v>
+      </c>
+      <c r="M535" t="n">
+        <v>0</v>
+      </c>
+      <c r="O535" t="n">
+        <v>47</v>
+      </c>
+      <c r="P535" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>빅데이터를 활용한 태권도 연구 의미연결망 분석</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>PARK JONG HWA</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>국기원 태권도연구</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>국기원</t>
+        </is>
+      </c>
+      <c r="E536" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>10.24881/tjk.2019.10.4.301</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>본 연구는 학술연구정보서비스(RISS)를 통해 2009년부터 2018년까지 10년간의 ‘태권도’키워드에서 추출된 논문의 제목 텍스트를 수집하였다. 수집된 논문은 1,824건이었으며, 그 중 중복되거나 동일한 내용의 논문 48건을 제외한 1,776건의 논문이 최종 분석에 사용되었다. 자료처리는빅데이터 분석 및 시각화가 모두 가능한 프로그램 넷마이너 4(NetMiner 4)를 분석도구로 활용하였다. 학술연구정보서비스(RISS)에서 수집된 자료는 엑셀(excel)프로그램에 이용해 다운로드하여 데이터 정제를 실시하였다. 정제 과정을 거친 데이터는 키워드 분석하였으며, 그 중에서도데이터에 포함된 단어들의 빈도를 나타내는 단어 빈도분석을 실시하였다. 빈도분석 결과 텍스트의 단어들의 구조적 관련성을 분석하고 의미를 도출하는 사회연결망 분석을 실시하여 연결 중심성이 높은 단어들을 제시 하였다. 또한 텍스트를 구성하는 단어들 중 유사한 패턴을 형성하는단어들의 의미를 파악하기 위해 군집분석을 실시하였다. 군집분석 결과 G1 태권도 교육 및 효능1, G2 태권도 분석 및 활성화 2, G3 태권도 심리 및 경영 3, G4 태권도 지도자 및 선수 4로총 4개의 그룹으로 분류되었다. 이를 통해 10년간에 태권도분야에 어떠한 연구가 이루어졌는지를 파악할 수 있었으며, 태권도에 다각적인 연구가 이루어졌음을 주지할 수 있었다. 이러한 결과를 통해 향후 10년의 태권도 연구에 연구동향에 관한 기초자료로 제공될 것이며, 나아가 태권도분야에 다각적인 연구방법과 연구대상 등의 연구가 이루어져야 할 것을 기대한다.</t>
+        </is>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>ART002538669</t>
+        </is>
+      </c>
+      <c r="L536" t="n">
+        <v>21</v>
+      </c>
+      <c r="M536" t="n">
+        <v>0</v>
+      </c>
+      <c r="O536" t="n">
+        <v>21</v>
+      </c>
+      <c r="P536" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>사회 네트워크 분석 방법론에 기초한 중국의 여객 철도 네트워크 특성 분석 : 2008년, 2013년, 2018년 운행 데이터를 중심으로</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Pei-Song Zhao; Jin-Hee Lee; Lee, Man-Hyung</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>한국콘텐츠학회 논문지</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>한국콘텐츠학회</t>
+        </is>
+      </c>
+      <c r="E537" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>10.5392/jkca.2019.19.10.685</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>이 연구는 중국의 여객 철도 네트워크의 구조를 분석하여 중국 도시 네트워크의 특성과 변화를 살펴보는 것이 주요 목적이다. 사회 네트워크 분석 도구인 NetMiner4.0을 활용하였으며, 2008년, 2013년, 2018년 각 연도의 전체 중국 여객 열차 운행 O/D데이터를 가공하여 연결중심성, 매개중심성, 근접중심성 분석 및 열차유형에 따른 네트워크 특성 파악을 수행하였다. 또한, 연도별 네트워크의 구조적 특성변화와 네트워크 상위도시를 비교 분석 하였다. 철도 네트워크의 연결중심성은 3개년도 대부분 베이징, 상하이, 광저우, 우한, 시안, 청두, 하얼빈, 선양 지역이 높게 나타났고, 매개중심성 분석을 통해 우루무치, 구이양, 선양, 쿤밍 지역이 개발 잠재력이 내제된 도시로 밝혀졌다. 또한, 근접중심성 분석으로 베이징, 상하이, 광저우 등의 대도시의 철도 접근성이 높음을 확인하였다. 그리고 고속 철도 및 일반철도의 비교 분석을 통해 베이징과 톈진사이의 연계성이 계속 강화되고 있음을 파악할 수 있었다.
+이러한 철도 교통의 발전과 운행에 따라 철도역을 중심으로 인접한 도시와 네트워크를 형성하고 향후 네트워크의 범위가 확대될 것으로 예측된다.</t>
+        </is>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>ART002518597</t>
+        </is>
+      </c>
+      <c r="L537" t="n">
+        <v>5</v>
+      </c>
+      <c r="M537" t="n">
+        <v>0</v>
+      </c>
+      <c r="O537" t="n">
+        <v>5</v>
+      </c>
+      <c r="P537" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>사회연결망 분석을 활용한 경제적 소외계층 비교과 연계 프로그램 연구동향 분석</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>eum yoon jae; Shin Dong Lee</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>학습자중심교과교육연구</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>학습자중심교과교육학회</t>
+        </is>
+      </c>
+      <c r="E538" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>10.22251/jlcci.2019.19.17.1073</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>본 연구는 사회연결망 분석(Social Network Analysis) 중 토픽모델링과 키워드네트워크 분석방법을 활용하여 경제적 소외계층 비교과 연계 프로그램에 대한 선행 연구의 동향을 살펴보는데 그 목적을 두었다. 이를 위해 학술연구정보서비스(RISS), 누리미디어(DBpia), 한국학술정보(KISS)의 데이터베이스 및 Biblio Data Collector를 활용하여 경제적 소외계층 비교과 연계 프로그램 중 학술지에 등재된 114개의 논문을 최종 분석대상으로 선정하였고, 전처리 과정을 통하여 출현빈도 상위 40개의 키워드를 추출하였다. 연구동향을 파악하기 위해 토픽분석, 키워드네트워크 분석이 적용되었는데, 네트워크 분석 도구로는 사회 연결망 분석에서 많이 활용되고 있는 Netminer 4.3 프로그램을 사용하였다. 주요 연구 결과를 간략하게 제시하면 다음과 같다. 첫째, 키워드 출현빈도는 자아존중감, 사회적 기술, 치료 등의 순으로 나타났다. 둘째, LAD모델을 기반으로 한 토픽모델링 분석결과 심리적 어려움, 성장, 정서발달, 복지, 자아개념, 사회성 발달과 관련된 6개의 토픽그룹이 만들어졌으며, 이 중 5개의 토픽그룹이 자아존중감 키워드를 포함하고 있었다. 셋째, 시기별 키워드 등장빈도를 분석하였다. 2001년부터 2006년까지는 가정과 관련된 키워드가 가장 높게 나타났으며, 2007년부터 2012년, 20013년부터 2018년까지는 자아존중감 키워드가 가장 높은 빈도로 분석되었다. 교육학 분야에 새롭게 적용된 사회연결망 분석을 실시한 본 연구의 결과는 앞으로 개발 될 경제적 소외계층 비교과 프로그램이 나아가야 할 방향을 제시하고 발전시키는데 필요한 기초자료와 통찰을 제공할 수 있을 것이다.</t>
+        </is>
+      </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>ART002503441</t>
+        </is>
+      </c>
+      <c r="L538" t="n">
+        <v>6</v>
+      </c>
+      <c r="M538" t="n">
+        <v>0</v>
+      </c>
+      <c r="O538" t="n">
+        <v>6</v>
+      </c>
+      <c r="P538" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>사회체육 연구 주제어 트렌드의 의미연결망 분석</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Kim, Kyung-Sik</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>한국사회체육학회지</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>한국사회체육학회</t>
+        </is>
+      </c>
+      <c r="E539" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>10.51979/kssls.2019.07.77.333</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>Purpose: The purpose of this study is to analyze the changes in the mainstream trends of sport for all research and to identify trends in research of sport for all codnucted up to now. In this study, research pro-b lems were set up as follows: First, what are the trends in the key words of top-level of sport for all? Second, how do trends in the key words of research of sport for all appear? Method: The study searched journal papers for DbPia and Korean academic information (kiss) sites to identify research trends in sport for all. Specifically, Focusnig on three key words sport for all, life physica l education, and life sports, one of these three key words incluedd in the title of the paper were chosen as th e subjects. Data analysis was done using NetMiner program technique. Specifically, frequency analysis was conducted to investigate the change of major key words by year, adn centrality analysis was conducted to clarify the intellectual structure of sport for all research.
+Result: First, there was no significant change in trends at the top. In other words, sport, satisfaction, leisure, program, life, students, school, exercise, health, etc. pairedk ey words in the top were sport-satisfaction, lifesatisfaction, sport-life, leisure-sport, leisure-satisfaction, and so on. Second, the main subjects of sport for a ll research which had been studied from 2000 to 2018 were sport, astisfaction, leisure, life, student, exercise , school, education, job, health, and stress. The main theme of sport for all research which appeared more than 20 times consisted of 1st group based on exercise, 2nd groups based on sport, 3th groups based on student, and 4th groups based on satisfaction.
+Conclusion: For the past two decades, research of sport for all have not changed much, and it was mainly to verify the effect of sports participation in social psychology.</t>
+        </is>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>ART002491568</t>
+        </is>
+      </c>
+      <c r="L539" t="n">
+        <v>5</v>
+      </c>
+      <c r="M539" t="n">
+        <v>0</v>
+      </c>
+      <c r="O539" t="n">
+        <v>5</v>
+      </c>
+      <c r="P539" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>소셜 네트워크 분석을 통한 무형문화유산 공동체 지식연결망 연구 - 정선아리랑을 중심으로 -</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Oh, Jung-Shim</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>헤리티지:역사와 과학</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>국립문화유산연구원</t>
+        </is>
+      </c>
+      <c r="E540" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>10.22755/kjchs.2019.52.3.172</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>본 논문의 목적은 무형문화유산 일반전승자의 역할을 주목하면서, 소셜 네트워크 분석을 활용해 무형문화유산 전승공동체의 연결망과 전승활동에서 발생하는 지식 흐름의 구조적 특징을 분석하는 데 있다. 이러한 연구 목적을 이루기 위해 본 논문에서는 연구 대상을 국가무형문화재 종목들 중에서 일반인의 전승활동이 활발한 ‘아리랑’으로 선정하였다. 아리랑은 오랜 기간 제도권 밖에서 일반대중 활동을 중심으로 자생적으로 전승되었으며, 2015년에 전문전승자 지정 없이 국가무형문화재로 지정된 최초의 사례이다. 현재 아리랑은 약 60여 종, 3,600여 곡에 이르는 것으로 추정된다. 본 논문에서는 이 중에서 전문전승자와 일반전승자의 상호교류가 활발한 향토민요 ‘정선아리랑'을 중심으로 연구하였다.
+소셜 네트워크 분석은 사람과 사람 사이의 관계를 노드(Node)와 링크(Link)로 모델링하여 수치화·통계화·시각화하여 해석하는 방법을 말한다. 이 방법은 전통적으로 사회학에서 사회조직 및 취약계층을 연구하는 데 꾸준히 활용되었다. 최근에는 문헌정보학, 문화콘텐츠학, 경영학 등과 같은 분야에서 연구경향, 시장동향, 조직관리 등을 연구하는 데 이 방법이 활용되고 있다. 이처럼 여러 학문 분야에서 소셜 네트워크 분석을 이용한 연구가 증가하는 추세지만 문화재 분야에서는 관련 연구를 찾아보기가 어렵다.
+소셜 네트워크 분석은 크게 3단계, ‘연결망 모델링’, ‘데이터 수집’, ‘데이터 분석 및 시각화’로 진행된다. 본 논문에서는 첫 번째, 2017년 기준으로 정선아리랑보존회 회원 전체를 조사 대상으로 선정하여 완전한 연결망으로 모델링하였다. 두 번째, 데이터 수집은 보존회 회원 명부를 확보해 2017년 10월 17일 면대면 조사와 2017년 12월 15일 전화 설문조사를 통해 하였다. 세 번째, 데이터 분석은 Netminer 4.0 프로그램을 이용해 중심성 분석, 구조적 등위성 분석, 커뮤니티 분석 등을 주요 지표로 하였다.
+본 논문은 기존에 무형문화유산 계보조사에서 소수 사람들의 구술자료에 의존해 파악하던 방식에서 벗어나 객관적이고 계량적인 방법으로 조사할 수 있는 기반을 제공하였다는 점에서 연구 의의가 있다. 그리고 무형문화유산 전승공동체 구성원들의 관계 및 지식 흐름의 구조를 지식지도(2D Spring Map) 형태로 시각화함으로써 추상적인 내용을 직관적으로 파악할 수 있게 했다는 점에서 의미가 있다.</t>
+        </is>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>ART002506076</t>
+        </is>
+      </c>
+      <c r="L540" t="n">
+        <v>6</v>
+      </c>
+      <c r="M540" t="n">
+        <v>0</v>
+      </c>
+      <c r="O540" t="n">
+        <v>6</v>
+      </c>
+      <c r="P540" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>소셜미디어를 활용한 스포츠관광 인식 분석</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Kim, Kyung-Sik; Seungbaek Han</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>한국여가레크리에이션학회지</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>한국여가레크리에이션학회</t>
+        </is>
+      </c>
+      <c r="E541" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>10.26446/kjlrp.2019.9.43.3.55</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>This study aimed to analyze the public perception of sports tourism in social media through semantic network analysis. To achieve this goal, Instagram, Twitter, and YouTube were selected as research subjects, and semantic network analysis between keywords in sports tourism-related texts was conducted. To this end, a total of 2012 data was collected, and a total of 17,165 keywords were collected from Twitter (409), Instagram (882), and YouTube (15874). We used the NetMiner program for data analysis, and specific analysis methods included Co-Word Analysis, Centrality Analysis, and analysis of Group Cohesiveness. The analyses offered the following results. First, the pairs of words that appeared simultaneously on sports tourism-related social media were 'leisure-sport,' 'diving-Cebu,' 'diving-travel,' 'sports-travel.' and 'instructor-freediving.' Second, the key words that showed 'degree of centrality' and 'betweeness centrality' were "sports", "leisure," "travel," 'diving,' 'free diving,' and 'restaurants.' Third, as a result of the cohesiveness group analysis, it was divided into five groups. The first cohesion group consisted of seven keywords, with 'luxury' as the core keyword, and the second cohesion group consisted of five keywords with 'Yongin' as the core keyword. The third cohesion group consisted of 16 keywords, with the core keyword 'freediving,' and the fourth cohesion group consisted of 18 keywords, with the core keywords' diving' and 'travel.' The fifth and final group is composed of a total of 25 keywords, with ‘leisure’ and ‘sports’ as core keywords.</t>
+        </is>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>ART002504775</t>
+        </is>
+      </c>
+      <c r="L541" t="n">
+        <v>7</v>
+      </c>
+      <c r="M541" t="n">
+        <v>0</v>
+      </c>
+      <c r="O541" t="n">
+        <v>7</v>
+      </c>
+      <c r="P541" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>신체활동을 주제로 한 치매연구 동향 분석: 키워드 네트워크의 활용</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Jiwun Yoon; Hong Sun Song</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>운동과학</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>한국운동생리학회</t>
+        </is>
+      </c>
+      <c r="E542" t="n">
+        <v>2019</v>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>PURPOSE: This study was to identify trends in dementia research based on physical activity using keyword network analysis. METHODS: 2025 keywords were extracted using Python, from 957 papers cited in PubMed over a 6-year span from 2013 to February 2018. Research trends were classified into introduction period (2013-2014), diffusion period (2015-2016), and settlement period (2017-2018) to confirm the temporal change. To identify research trends, frequency analysis, connection centrality analysis, and rate of change analysis were conducted using Excel program and NetMiner 4.3 software program. RESULTS: The results are as follows: First, the most frequently mentioned keywords dementia research based on physical activity were exercise (145), cognition (108), and aging (88). Second, when we look at the words associated with the top 3 keywords classified by the central value of connection, ‘exercise’ is connected to ‘depression’, perception is ‘prevention’, and aging is ‘gait’. Third, in the diffusion period (2015-2016) based on the introduction period (2013-2014), keywords such as ‘stress’, ‘neurodegenerative disease’, ‘obesity’, and ‘memory’ were increased, and ‘walking’, and ‘odds ratio’ keywords were tend to decreased Moreover, the settlement period (20172018), ‘nursing home’ and ‘elderly’ keywords were increased and ‘huntington’ keyword was decreased. CONCLUSIONS: The results of this study can be used to establish a direction for future dementia research based on physical activity.</t>
+        </is>
+      </c>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>ART002445801</t>
+        </is>
+      </c>
+      <c r="L542" t="n">
+        <v>14</v>
+      </c>
+      <c r="M542" t="n">
+        <v>0</v>
+      </c>
+      <c r="O542" t="n">
+        <v>14</v>
+      </c>
+      <c r="P542" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>실과(기술·가정)교육 분야 연구의 공저자 네트워크 분석</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Lee, Yoon-Jung; Eun Jeung Kim; Kim， Ji Sun</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>한국실과교육학회지</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>한국실과교육학회</t>
+        </is>
+      </c>
+      <c r="E543" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>10.24062/kpae.2019.32.1.103</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>이 연구는 실과(기술․가정)교육 분야의 연구자 간 학술 네트워크의 구성을 파악하기 위해 SNA를 활용하여 공저자 네트워크 분석을 수행하였다. 2010년부터 2018년 8월에 발간된 한국실과교육학회지, 한국기술교육학회지, 한국가정과교육학회지를 중심으로 NetMiner 4를 이용하여 공저자 네트워크를 구성하였으며, 그 구조적 속성과 연구자들의 중심성을 파악하여 저자의 학술적 영향력 및 관계를 살펴보았다. 그 결과는 다음과 같다. 첫째, 세 학술지의 공저논문의 비율은 72.5%에서 79.5%로 높은 편이었으며, 그 중 한국기술교육학회지의 공저비율이 가장 높았다. 한국실과교육학회지는 저자수 1명, 한국가정과교육학회지와 한국기술교육학회지는 저자수가 2명이 가장 많았다. 특히 한국기술교육학회지는 8명 이상의 다수 저자가 공저한 논문도 많았다. 학술지 저자의 직업은 한국실과교육학회지와 한국가정과교육학회지의 경우 60%이상이 교수였으나 한국기술교육학회지는 45.5%로 교수 외의 저자가 많음을 알 수 있었다. 한국실과교육학회지는 학생의 비율 낮으며, 한국기술교육학회지는 교사, 연구원, 기타의 비율이 다른 두 학술지에 비하여 현저히 높았다. 둘째, 세 학술지의 공저자 네트워크 분석 결과 네트워크의 밀도와 평균 연결도는 실과교육 분야가 가장 높았고 가정교육 분야가 가장 낮았다. 또한 한국가정과교육학회지의 경우 컴포넌트의 수는 다른 두 학술지의 2배가 넘었으며, 5개 이상의 노드를 가지고 있는 컴포넌트수도 많았고, 평균 거리와 네트워크 지름도 다른 학술지에 비하여 짧은 편이었다. 셋째, 세 학술지의 공저자 네트워크의 연결 중심성, 근접 중심성, 매개 중심성, 아이겐벡터 중심성을 계산하여 각 연구 분야에서 높은 영향력을 가지고 있는 연구자들을 파악하였다. 그 결과 한국기술교육학회지와 한국실과교육학회지의 저자들은 공통저자가 많은 데 비하여, 한국가정과교육학회지의 저자들은 한국실과교육학회지의 저자들과 공통된 경우가 많지 않았다. 또한 실과교육 분야의 저자들 중 영향력이 높은 집단은 대체로 기술교육 분야의 저자들임을 알 수 있었다. 이 연구는 실과(기술․가정)교육이 다양한 학문 공동체로서의 연구자들 간의 상호 교류를 통한 통합적, 융합적 연구가 이루어질 필요가 있음을 보여준다.</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>ART002449202</t>
+        </is>
+      </c>
+      <c r="L543" t="n">
+        <v>8</v>
+      </c>
+      <c r="M543" t="n">
+        <v>0</v>
+      </c>
+      <c r="O543" t="n">
+        <v>8</v>
+      </c>
+      <c r="P543" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>언어 네트워크 분석기법을 활용한 문재인정부의 가치지향과 정책방향 분석: 100대 국정과제를 중심으로</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Lee, In-Won; Lee, Youngmi</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>한국행정논집</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>한국정부학회</t>
+        </is>
+      </c>
+      <c r="E544" t="n">
+        <v>2019</v>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>이 연구는 문재인 정부 국정운영의 로드맵으로 제시된 100대 국정과제 내 세부 487개 실천과제를 언어 네트워크라는 구조적인 관점에서 조망하고 분석함으로써 시사점을 도출하고자 하는 목적을 갖고 수행되었 다. 국정과제는 개별 과제 단위뿐만 아니라 과제 간 연계성을 보다 통합적이고 구조적인 관점에서 파악하고 동시에 관리하려는 노력이 필요하다. 이를 위해서는 국정운영의 전반적인 로드맵인 국정과제에 드러나 개념 들을 관계를 구조적인 관점에서 이해하고 분석하는 노력이 필요하다. 이 연구의 연구대상은 2017년 7월 국 가 비전과 목표 하에 수립된 100대 국정과제에 속하는 487개 실천과제이며, 각 과제의 주제명을 통해 핵심 키워드를 추출한 후 언어네트워크 분석기법을 적용하였고, 핵심키워드들 간의 언어네트워크 분석을 위해 NetMiner 4.0프로그램을 활용하여 중심성 분석, 응집성 분석, 시각화 등을 수행하였다. 분석의 결과 ‘국민 이 주인인 정부’라는 국정목표와 관련해서는 정부시스템의 개선, 행정혁신을 최우선에 두고 있는 것으로 나 타났으며, ‘더불어 잘사는 경제’라는 국정목표와 관련해서는 혁신성장, 각 계층별 좋은 일자리 창출, 공정경 제 등이 핵심에 있는 것으로 나타났다. ‘내 삶을 책임지는 국가’라는 국정목표는 문재인 정부가 추구하고 있 는 적극적 복지정책과 포용국가 전략이 중심축을 이루고 있으며, ‘고르게 발전하는 지역’과 관련해서는 재정 분권, 자치분권, 지역의 자립기반 마련, 협력을 통한 추진 등을 지향하고 있는 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>ART002541563</t>
+        </is>
+      </c>
+      <c r="L544" t="n">
+        <v>10</v>
+      </c>
+      <c r="M544" t="n">
+        <v>0</v>
+      </c>
+      <c r="O544" t="n">
+        <v>10</v>
+      </c>
+      <c r="P544" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>언어네트워크 분석을 활용한 「선교와 신학」의 연구동향 분석</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Kim Hyo Sook</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>선교와신학</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>세계선교연구원</t>
+        </is>
+      </c>
+      <c r="E545" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>10.17778/mat.2019.02.47.189</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>초연결사회에서 다양한 현상들을 네트워크로 정보화하고, 그 속에 내재된 특성들을 과학적으로 분석하려는 노력이 점점 중요해지고 있다. 이 연구는 학술논문의 지식 네트워크 분석에 적합한 언어네트워크 분석을 활용해 「선교와 신학」의 연구 동향을 탐색하고 전망하려는 것이다.
+연구방법은 초록에서 추출한 주제어 간의 동시출현을 기준으로 네트워크를 구성하여 주제어의 기간별 변화 양태를 탐색하고, 의미적 연결망을 분석하는 언어네트워크 분석으로 설계하였다. 이를 위해 분석할 논문을 수집하여 주제어를 추출・정제하고, 동시출현 행렬 및 주제어의 네트워크를 개발한 후 NetMiner 프로그램으로 중심성 및 커뮤니티 분석을 실시하였다.
+연구결과에 따르면, 「선교와 신학」의 핵심 주제어는 선교, 선교신학, 한국교회, 하나님의 선교, 에큐메니칼, 복음, 종교개혁, 문화 순으로, 빈도와 중심성이 모두 높게 나타났다. 기간별 연구 동향은 글로벌한 ‘세계선교’에 대한 연구가 로컬한 ‘한국교회’ 및 ‘지역교회’를 주제어로 한 연구로 이행하고 있고, ‘하나님의 선교’나 ‘통전적 선교’는 ‘선교적 교회’를 구현하는 보다 상황적이며 실천적인 논의로 이행하는 양상을 띠고 있다. 또한 전반기 연구에 비해 후반기 연구는 주제어 간의 연결이 선형적인 형태를 띠므로 선행연구와 후속연구 간의 연결을 강화할 필요가 있음을 제안하였다.
+연구의 한계점이자 제한점은 초록의 주제어를 분석한 것이고, 색인자 효과로 인한 편향의 문제를 배제하지 못했다는 점이다. 그러나 이 연구는 연구주제에 대한 빈도분석을 넘어 의미적 관계를 분석하였으며, 연구주제의 출현과 소멸에 대한 단발적 조사를 넘어 기간별 변화 양태 및 잠재적 연구주제를 논의했다는 점에서 의의가 있다.</t>
+        </is>
+      </c>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>ART002442763</t>
+        </is>
+      </c>
+      <c r="L545" t="n">
+        <v>10</v>
+      </c>
+      <c r="M545" t="n">
+        <v>0</v>
+      </c>
+      <c r="O545" t="n">
+        <v>10</v>
+      </c>
+      <c r="P545" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>온라인지식공동체의 협력유형에 대한 소셜네트워크분석</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Jae Kyung Kim</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>로고스경영연구</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>한국로고스경영학회</t>
+        </is>
+      </c>
+      <c r="E546" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>10.22724/lmr.2019.17.2.81</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>지식공유는 지식관리에서 중요한 연구 분야 중 하나이다. 본 연구는 정보공유에 대한 개인의 행동성향을 순공유자, 상호공유자, 비공유자로 분류함으로써 지식공유에 대한 관점을 넓혔다. 본 연구는 느슨하게 연결된 소셜네트워크로서의 온라인지식공동체에서 회원들 간 자발적 질의응답 형태로 공유되는 지식을 공공재로 보고, 상호주의이론(theory of reciprocity)을 이용하여 온라인지식공동체 회원이 갖는 순공유자, 상호공유자, 비공유자의 세가지 지식공유행태의 존재와 그 구성비율, 그리고 지식공유에 미치는 영향을 연구하였다. 이러한 온라인지식공동체에서의 지식공유 개념은 “주는 것이 받는 것보다 복이 있다 하심을 기억하여야 할지니라” (행 20:25)는 성경 말씀에 부합한다. 온라인지식공동체의 11년간의 질의응답 데이터를 파이썬 웹크롤링방법으로 수집하고, NetMiner4.0을 이용하여 노드 연결관계 분석(degree analysis)을 한 결과, 회원들의 공유행태는 isolate, transmitter, receiver, carrier, ordinary의 행태를 보였으며, 이를 바탕으로 지난 11년간의 순공유자, 상호공유자, 비공유자의 수와 비율, 그리고 전체적인 지식공유와 지식탐색의 변화추이를 분석하였다. 이를 통해, 온라인지식공동체에 존재하는 순공유자, 상호공유자, 비공유자의 분포는 다른 소셜네트워크 특성과 같은 전형적인 멱함수의 분포를 보였으며, 이는 소수의 순공유자 뿐 아니라 대다수를 차지하고 있는 상호공유자들이 매우 중요한 지식공유 역할을 수행하고 있음을 뜻한다.</t>
+        </is>
+      </c>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>ART002485263</t>
+        </is>
+      </c>
+      <c r="L546" t="n">
+        <v>1</v>
+      </c>
+      <c r="M546" t="n">
+        <v>0</v>
+      </c>
+      <c r="O546" t="n">
+        <v>1</v>
+      </c>
+      <c r="P546" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>일개 간호대학생의 시뮬레이션 기반 통합실습 경험 분석: 텍스트 네트워크 분석의 적용</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Mikyung Moon</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>글로벌 건강과 간호</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>간호과학연구소</t>
+        </is>
+      </c>
+      <c r="E547" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>10.35144/ghn.2019.9.1.10</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>Purpose: This study aimed to explore the nursing students’ experiences on a simulation based integrated practicum using a text network analysis. Methods: The data were collected from 103 questionnaires submitted by senior students who took the simulation based integrated nursing practicum course in a college of nursing during spring semester 2018. NetMiner 4.3. was used for the text network analysis. After data cleaning, frequency, degree/betweenness centrality, and subgroup analysis were used for the final analysis. Results: Situation, Patient, Skills, Coping, and Reality were the words with high frequency and centrality in practicum experience among nursing students. Comparing visualized sub-networks groups with course outcomes, ‘the collaboration with health professionals(CO4)’ were not explained by any sub-groups. Embarrassment and Mistake were the high frequency words in the analysis for negative experience. Conclusion: The results identified positive and negative experience, and the unachieved course outcomes from nursing students’ experience of simulation practicum. The results could be used for improving the quality of simulation based integrated nursing practicum.</t>
+        </is>
+      </c>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>ART002436555</t>
+        </is>
+      </c>
+      <c r="L547" t="n">
+        <v>5</v>
+      </c>
+      <c r="M547" t="n">
+        <v>0</v>
+      </c>
+      <c r="O547" t="n">
+        <v>5</v>
+      </c>
+      <c r="P547" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>장서개발관리 분야 최근 연구동향 분석에 대한 연구</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>You Mi Shin; Ok-Nam Park</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>정보관리학회지</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>한국정보관리학회</t>
+        </is>
+      </c>
+      <c r="E548" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>10.3743/kosim.2019.36.2.105</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>본 연구는 장서개발관리 분야의 최근 연구동향을 분석함으로써 핵심 연구주제를 파악하고 학문의 지적구조를 규명하고자 하였다. 2003년부터 2017년까지 15년간 문헌정보학 분야 4개 학회지에 등재된 논문 중 장서개발관리 분야의 키워드를 가진 연구논문을 선정하여 저자키워드를 추출하였다. 추출된 저자키워드를 가지고 NetMiner4 프로그램을 이용하여 키워드 네트워크를 구성한 뒤 빈도분석, 연결중심성 분석, 매개중심성 분석을 수행하였다. 분석은 시간의 흐름에 따른 연구 변화를 살펴보기 위하여 2003년부터 2017년까지 전 구간을 대상으로 한 분석과 5년 단위의 3구간으로 나누어 살펴보았다. 연구결과, ‘오픈액세스’, ‘기관 레포지터리’, ‘학술지’ 등의 장서개발관리 분야의 핵심키워드를 파악하고, ‘대학도서관’ 등의 계속 연구될 분야의 주제어를 파악하였다.</t>
+        </is>
+      </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>ART002480081</t>
+        </is>
+      </c>
+      <c r="L548" t="n">
+        <v>11</v>
+      </c>
+      <c r="M548" t="n">
+        <v>0</v>
+      </c>
+      <c r="O548" t="n">
+        <v>11</v>
+      </c>
+      <c r="P548" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>전자정부법 공동발의에 관한 연결망 분석 : 20대 국회 의안분석을 중심으로</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Lee Hun Hee; Han, Sangik</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>한국컴퓨터정보학회논문지</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>한국컴퓨터정보학회</t>
+        </is>
+      </c>
+      <c r="E549" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>10.9708/jksci.2019.24.06.125</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>This study aimed to investigate the political system related to the Electronic Government Law by analyzing the process of the common initiative of the law. To achieve the goal, this study applied the method of social analysis and sugessted the proper role of the assembly for realizing the electronic government and its control. The data were gathered from the bill information service of the national assembly. Netminer 4.0 was used for refining and analyzing data. The results are as follows. First, by analyzing three centrality(degree, betweenness, and eigenvector) of assembly member, the network effect of the powered party and reelected members were revealed as strong in the network. Second, through the component analysis, 5 sub-network has shown in total. The sub-networks showed two distinctive difference between two big parties. By the difference, members in two parties showed different characteristics in constituting communities and the effect of the powered party revealed as strong and clear. Based on the result, this study demonstrated the necessity of social solidarity rather than solipsism in committing common initiative. And a chronological research is need to anlayze 18th and 19th assembly to verify the effect of the powered party in prospect study.</t>
+        </is>
+      </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>ART002474621</t>
+        </is>
+      </c>
+      <c r="L549" t="n">
+        <v>0</v>
+      </c>
+      <c r="M549" t="n">
+        <v>0</v>
+      </c>
+      <c r="O549" t="n">
+        <v>0</v>
+      </c>
+      <c r="P549" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>정보격차 연구 동향 분석 — 문헌정보학분야와 일반사회과학분야와의 비교 —</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Seongsin Lee; Kang Bora; Sena Lee</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>한국도서관·정보학회지</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>한국도서관·정보학회</t>
+        </is>
+      </c>
+      <c r="E550" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>10.16981/kliss.50.3.201909.139</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>본 연구의 목적은 문헌정보학 분야와 일반 사회과학 분야의 정보격차 연구 동향을 관련 연구논문들의 키워드 네트워크 구축을 통해 비교, 분석하는 것이다. 연구목적 달성을 위해 한국학술지인용색인(KCI)을 통해 2000년도부터 2019년 현재까지의 관련 논문들을 대상으로 저자 키워드를 추출하여 NetMiner4를 활용하여 분석하였다. 분석결과 문헌정보학 분야의 경우 공공도서관의 정보소외 계층을 위한 정보서비스 제공이라는 측면에서 접근한 연구가 대부분이었다. 이에 비해 일반 사회과학 분야의 경우는 정보사회의 특성에 주목한 연구들과 최근의 스마트 환경에서의 정보격차 현상에 주목한 연구들이 많았다. 또한 소외계층 중에서는 노인에 대한 연구가 일반 사회과학 분야에 비해 많지 않았다. 따라서 노인의 정보격차에 대한 연구가 필요하며 공공도서관 중심에서 여러 관종의 도서관들에 대한 관심으로 확장될 필요가 있다. 또한 문헌정보학 분야의 경우 새로운 정보환경에서의 정보격차에 대한 이해를 시도한 연구가 많지 않았다. 따라서 4차산업혁명에 대한 관심이 고조되고 있는 현 상황에서 새로운 스마트환경에서의 정보격차에 대한 관심과 연구가 필요할 것으로 보인다.</t>
+        </is>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>ART002509383</t>
+        </is>
+      </c>
+      <c r="L550" t="n">
+        <v>8</v>
+      </c>
+      <c r="M550" t="n">
+        <v>0</v>
+      </c>
+      <c r="O550" t="n">
+        <v>8</v>
+      </c>
+      <c r="P550" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>제한적 목적지 이미지의 다차원적 접근 모델- 북한관광 빅데이터 사례를 중심으로</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Noh, Hee-Kyung</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>관광연구</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>대한관광경영학회</t>
+        </is>
+      </c>
+      <c r="E551" t="n">
+        <v>2019</v>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>본 연구는 제한적 목적지의 관광이미지를 다차원적으로 이해하고 측정하는 학술적 근거를 마련하는 한편, 북한관광을 사례지역으로 설정하여 접근함에 따라 남북관광과 관련한 관광객의 관광이미지의 차원을 도출하고 이에 근거한 북한관광 및 통일관광의 정책적·제도적 방향에 대한 논리의 근거를 제시하는데 그 목적과 의의가 있다. 
+이를 위해 Java 프로그래밍 언어를 통해 자체 구축한 웹크롤링을 활용하여 2014년 01월 01일부터 2018년 12월 31일로 5년간 국내 대표적인 포털사이트인 네이버와 다음의 블로그와 카페에 게시된 글 중 ‘북한관광’을 검색어로 데이터를 수집하였으며, Netminer4 프로그램을 이용하여 텍스트마이닝 분석을 실시하였다. 분석된 명사 및 형용사형 텍스트를 활용하여 제한적 목적지인 북한관광에 대한 총체적이미지를 형성하는 다양한 차원을 제시하였다.
+이는 이미지의 다차원성에 기인하였으며, 제한적 목적지는 심리적 거리, 구조적 제약 등의 특수성으로 인하여 일반관광목적지 이미지 형성체계와 차이가 존재하므로, 인지적·정서적 차원뿐만 아니라 감성적, 지각적 구조 차원, 동기촉진 이미지 차원으로 접근하는 제한적 목적지 이미지의 다차원적 접근 모델을 제시하였다.</t>
+        </is>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>ART002518393</t>
+        </is>
+      </c>
+      <c r="L551" t="n">
+        <v>3</v>
+      </c>
+      <c r="M551" t="n">
+        <v>0</v>
+      </c>
+      <c r="O551" t="n">
+        <v>3</v>
+      </c>
+      <c r="P551" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>청소년 연구의 동향 : 2010년∼2018년의 ‘청소년학연구’지를 중심으로</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Cin-Jae Chang; Lee Wonjie</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>한국융합학회논문지</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>한국융합학회</t>
+        </is>
+      </c>
+      <c r="E552" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>10.15207/jkcs.2019.10.12.307</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>본 논문은 2010년부터 2018년 동안 청소년학연구 학술지에 게재된 연구 논문의 연구동향을 살펴봄으로써청소년 관련 연구의 지식구조를 파악하고자 하였다. 논문의 초록에서 추출한 키워드를 활용하여 NetMiner 프로그램의 키워드 네트워크 분석(Semantic Network Analysis)의 중심성(Centrality)분석 및 응집성(Cohesion)분석을 사용하였다. 연결 정도 중심성 분석에서 ‘관계’가 가장 중심성이 높게 나타났고, 학교와 청소년이 그 다음으로 높았으며, 부모, 폭력의 순으로 높게 나타났다. 매개 중심성도 ‘관계’가 가장 높게 나타났고, 청소년, 학교, 필요, 교육, 부모, 아동, 학대/정서(같은 수준), 기관, 지역, 휴대폰/예방/복지(같은 수준), 초등, 애착, 자살, 중독, 사회, 폭력, 자녀, 봉사, 지원/정책/재학/교사(같은 수준)의 순으로 높게 나타났다. 응집성 분석 결과, 학교생활과 정책, 중독, 부모 &amp; 또래 관계, 시민 교육 &amp; 복지 지원, 정서와 사고, 대학, 학대 &amp; 자살로 총7개의 하위 주제로 구분되었다.</t>
+        </is>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>ART002533994</t>
+        </is>
+      </c>
+      <c r="L552" t="n">
+        <v>10</v>
+      </c>
+      <c r="M552" t="n">
+        <v>0</v>
+      </c>
+      <c r="O552" t="n">
+        <v>10</v>
+      </c>
+      <c r="P552" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>초등학생 갈등 주제어 네트워크 분석</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Kim, Jeongmi; Parkheejin; Kwon Dongtaik</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>학습자중심교과교육연구</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>학습자중심교과교육학회</t>
+        </is>
+      </c>
+      <c r="E553" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>10.22251/jlcci.2019.19.19.877</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>본 연구의 목적은 초등학생 갈등 연구의 주제어를 분석하여 주요 단어들 간의 의미 관계를 분석하는데 있다. 연구 수행을 위해 학술연구정보서비스(RISS)에서 “초등학생” 과 “갈등”을 차례로 입력하여 검색된 총 1,802 건의 논문들 중 156편을 최종 분석대상으로 선정하였다. 분석대상 논문을 엑셀 프로그램을 이용하여 주제어를 입력하고, KrKwic 프로그램을 이용하여 주제어와 빈도수를 추출했으며, NetMiner 프로그램을 이용하여 주제어 간의 관계를 분석하였다. 학술지 논문 156편에서 추출된 주제어는 총 620개였으며, 정제 작업을 통해 대표 단어를 선정하였다. 빈도수를 분석한 결과 제일 높은 빈도로 분석된 주제어는 20회로 “다문화”이다. 그 다음은 16회로 “또래관계”, “부부갈등” 15회의 순이었다. 3회 이상의 빈도수를 기록한 주제어 56개를 주요 키워드로 선정하고 주요 키워드가 얼마나 많은 연결을 가지고 있는지 연결중심성 분석을 실시하였다. 이 결과를 바탕으로 네트워크 지도를 생성하고 클러스터 분석을 통해 그 의미를 도출하였다.</t>
+        </is>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>ART002514680</t>
+        </is>
+      </c>
+      <c r="L553" t="n">
+        <v>0</v>
+      </c>
+      <c r="M553" t="n">
+        <v>0</v>
+      </c>
+      <c r="O553" t="n">
+        <v>0</v>
+      </c>
+      <c r="P553" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>친환경 공급사슬관리의 체계적 문헌 조사 연구: 계량서지학과 키워드 네트워크를 중심으로</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>EuiBeom Jeong; Jinsoo Park</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>경영학연구</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>한국경영학회</t>
+        </is>
+      </c>
+      <c r="E554" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>10.17287/kmr.2019.48.1.133</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>오늘날 기업의 운영에 있어 친환경 공급사슬관리(Green Supply Chain Management: GSCM)는 시장에서 지속적인경쟁력을 가지기 위한 중요한 사안이다. 이러한 중요성은 다양한 문헌 조사(Literature review) 연구들로 이어져 왔지만, 저자의 주관적인 경향으로 인한 결과와 향후 연구 동향의 계량적인 분석이 한계점으로 남았다. 이에, 본 연구는 학술데이터베이스인 스코퍼스(Scopus)를 이용하여 저널의 영향력 지수(Impact factor)를 기준으로 해외 저명한 저널을 선정하여 2013년부터 2018년까지 게재된 친환경 공급사슬관리 연구논문을 선정하였다. 이를 바탕으로 해당 연구논문의 저자, 소속, 그리고 키워드의 빈도수를 통해 세부 연구주제의 의미 있는 정보를 제공하는 계량서지학적(Bibliometrics) 방법론과 그 연구논문들의 키워드를 바탕으로 친환경 공급사슬관리의 주요 이슈, 토픽 파악에 유용한 키워드 네트워크 분석(Keyword network analysis)을 적용하였다. 아울러, 기존 문헌 조사 연구의 한계점을 극복하기 위해, 신규 키워드에대한 선호도 분석을 실시하여 보다 객관적인 친환경 공급사슬관리의 향후 연구동향을 살펴보고자 하였다. 분석에 있어서는 네트워크 분석 툴인 넷마이너(Netminer)를 사용하였다.</t>
+        </is>
+      </c>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>ART002440757</t>
+        </is>
+      </c>
+      <c r="L554" t="n">
+        <v>3</v>
+      </c>
+      <c r="M554" t="n">
+        <v>0</v>
+      </c>
+      <c r="O554" t="n">
+        <v>3</v>
+      </c>
+      <c r="P554" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>키워드 네트워크 분석을 통한 「교육평가연구」의 최근 연구경향 분석</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Kilseok Yang</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>교육평가연구</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>한국교육평가학회</t>
+        </is>
+      </c>
+      <c r="E555" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>10.31158/jeev.2019.32.4.625</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>본 연구는 키워드 네트워크 분석을 통해 우리나라의 최근 교육평가 분야의 연구 경향성을 밝히는 데 목적을 두고 있다. 이를 위하여 한국교육평가학회에서 발간하는 「교육평가연구」에 2009년(22권 1호)부터 2018년(31권 4호)까지 게재된 총 450편 논문의 키워드 2,043개를 수집하였다. 정제과정을 거쳐 1,295개의 키워드로 정비한 후 NetMiner4.0프로그램을 이용, 키워드의 논문 출현 빈도, 연결중심성, 매개중심성, 네트워크 시각화 등의 분석을 실시하였다. 분석 결과, ‘국가수준 학업성취도 평가’, ‘문항반응이론’, ‘학업성취도’, ‘동등화’, ‘PISA’, ‘차별기능문항’, ‘Rasch 모형’ 등이 교육평가 연구의 중심을 이루고 있음을 확인할 수 있었다. 더불어 문항반응이론의 확장 및 심화, 교육평가 실제(데이터 기반 정책추진, 학업성취도 평가 체제 개선 및 정보 공개, 학생평가의 혁신 등)와 연계된 연구의 활성화라는 시기적 특징도 살펴볼 수 있었다. 끝으로, 교육평가 분야의 학술적 구조를 체계화하고 후속 학문 탐구의 방향을 조망하기 위해 연구 경향성 분석이 전문화, 활성화되어야 함을 제언하였다.</t>
+        </is>
+      </c>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>ART002537208</t>
+        </is>
+      </c>
+      <c r="L555" t="n">
+        <v>18</v>
+      </c>
+      <c r="M555" t="n">
+        <v>0</v>
+      </c>
+      <c r="O555" t="n">
+        <v>18</v>
+      </c>
+      <c r="P555" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>키워드 네트워크 분석을 통한 「패션비즈니스」 연구 동향 -패션마케팅 및 디자인 분야를 중심으로-</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>MiYoung Lee; JungMin Lee</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>패션 비즈니스</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>한국패션비즈니스학회</t>
+        </is>
+      </c>
+      <c r="E556" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>10.12940/jfb.2019.23.3.51</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>The aim of this study is to identify research trends of "Journal of Fashion Business" by analyzing the keyword network of the paper published between 2006 and 2017. The papers selected for analysis in the study were 287 fashion design articles and 281 fashion marketing articles published between February 2006 and December 2017 and titles, volumes, publishing years, authors, keywords, and abstracts of each paper were collected for data analysis. The research was carried out through selection, collection of article data, keyword extraction and coding, keywords refinement, formation of network matrix, and analysis and visualization process. First, based on the title of the paper used in the analysis, the fashion design/aesthetics, marketing/social psychology, clothing materials, clothing composition, and other fields were classified. Research analysis used the Netminer 4 (Ver.4.3.2) program. Results indicated showed that the intellectual structure of the "Fashion Business" research paper showed key word changes over time, and the degree centrality and between centrality of the keywords.</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>ART002488996</t>
+        </is>
+      </c>
+      <c r="L556" t="n">
+        <v>7</v>
+      </c>
+      <c r="M556" t="n">
+        <v>0</v>
+      </c>
+      <c r="O556" t="n">
+        <v>7</v>
+      </c>
+      <c r="P556" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>키워드 네트워크 분석을 활용한 「기독교교육논총」 연구 동향 탐색</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Kim Hyo Sook</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>기독교교육 논총</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>한국기독교교육학회</t>
+        </is>
+      </c>
+      <c r="E557" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>10.17968/jcek.2019..58.005</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>올해는 3.1운동 100주년이자 대한민국임시정부 수립 100주년이 되는 해이다. 민족의 동반자로서 교회의 역할과 기독교교육의 중요성을 기억하는 뜻깊은 해에 기독교교육이 교회중심의 학문으로 고착화되고 있는지를 면밀히 분석하는 것은 매우 중요한 과제다. 따라서 연구의 목적은 기독교교육 연구의 특성과 학문공동체의 지식구조를 확인하기 위해 「기독교교육논총」의 연구 동향을 탐색하는 것이다. 
+연구방법은 「기독교교육논총」에 수록된 학술논문의 주제어 간의 동시출현 행렬을 구성한 후 핵심 주제어의 기간별 변화 양태를 탐색하고, 의미적 연결망을 분석하는 키워드 네트워크 분석으로 설계하였다. 이를 위해 분석할 논문(622편)을 수집하여 주제어를 추출・정제하고, 동시출현 행렬 및 주제어의 네트워크를 개발한 후 NetMiner 프로그램으로 중심성 및 커뮤니티 분석을 실시하였다. 
+분석결과에 따르면, 「기독교교육논총」의 핵심 주제어는 기독교교육, 교회, 교회교육, 교육과정, 어린이, 영성, 기독교학교, 청소년, 영성교육, 여성, 다문화, 신앙, 신앙공동체, 리더십으로 나타났다. 하위주제 집단은 기독교교육, 교회, 교육과정, 어린이, 청소년을 중심으로 한 5개이며, 이 중에서 가장 큰 ‘기독교교육’(G1) 군집은 주로 공공성과 관련된 주제어들이 하나의 지식 네트워크를 형성하는 것으로 나타났다. 또한 기간별 연구 동향을 분석한 결과, 역량, 하나님나라, 신앙공동체, 통일교육, 공동체, 인성교육, 공공성 등이 후반기에 중요도가 높아진 주제어로 밝혀졌다. 기간별 하위주제 집단의 동향은 ‘기독교교육’(G1) 군집이 이론 중심에서 현장 중심으로 이행하는 중이고, ‘교회’(G2) 군집은 다수의 군집에서 하나의 군집으로 수렴되는 양상을 띠며, 공적 신앙과 관련된 ‘영성’(G3) 군집과 교사 및 기독교 대학교육과 관련된 ‘역량’(G4) 군집은 새로운 하위주제군을 형성하고 있는 것으로 나타났다. 이는 기독교교육 연구의 교회 편향성은 점차 해소되고 있고, 기독교교육 학문공동체는 공적 신앙을 실천할 수 있는 연구를 확장해가는 것으로 볼 수 있다.</t>
+        </is>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>ART002479305</t>
+        </is>
+      </c>
+      <c r="L557" t="n">
+        <v>8</v>
+      </c>
+      <c r="M557" t="n">
+        <v>0</v>
+      </c>
+      <c r="O557" t="n">
+        <v>8</v>
+      </c>
+      <c r="P557" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>키워드 네트워크 분석을 활용한 육상경기의 종목별 연구동향</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>YungSun Lee</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>스포츠사이언스</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>체육과학연구소</t>
+        </is>
+      </c>
+      <c r="E558" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>10.46394/iss.37.1.21</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>이 연구는 키워드네트워크 분석을 활용하여 육상경기의 종목별 연구동향을 파악함으로써 육상경기의 발전에 의미있는 자료를 제공하는데 그 목적이 있다. 이 목적을 달성하기 위하여 한국연구재단(KCI: Korea Citation Index)의 학술인용사이트에서 제공하고 있는 논문 318편에 대한 172개의 연구키워드를 활용하였다. Excel 프로그램과 Krkwic 프로그램을 활용하여 자료를 입력하고 정제하는 과정을 거쳤으며 네트워크 분석을 위한 자료 형태로 재구성하였다.
+NetMiner 4.4.1 소프트웨어 프로그램을 활용하여 빈도분석, 연결중앙성분석을 수행하였으며 연구결과는 다음과 같다. 첫째, 육상관련 학술연구에서 빈도가 높게 언급된 키워드는 세계육상선수권(22회)으로 나타났다. 육상관련 학술연구를 수행함에 있어 연구자가 선정한 주요 키워드가 6회 이상 언급된 키워드는 19개이며, 분석(10회), 훈련(11회), 경기력(13회), 단거리(16회), 기록(17회), 속도(19회), 세계육상선수권(22회)등이 주요 핵심 연구키워드임을 확인하였다. 둘째, 전체 육상 종목의 핵심 연구 키워드는 ‘속도’,‘세계육상선수권’,‘기록’, ‘훈련’ 으로 나타났다. 셋째, 육상 세부종목별 핵심 연구키워드는 종목별로 상이한 것으로 나타났다. 구체적으로 단거리 종목에서는 ‘능력’, ‘속도’ 키워드이며, 투척 종목 ‘창던지기’, ‘기록’ 키워드가 핵심 연구키워드이며, 도약 종목에서는 ‘높이뛰기’, ‘남자’ 키워드가 중장거리 종목에서 ‘장거리’, ‘달리기’ ‘심박수’, ‘역치’가 핵심 연구키워드이다. 이 연구의 분석결과는 육상경기의 경기력 향상 방안을 탐색하고 연구주제를 선정하기 위한 기초 정보로 활용 할 수 있다.</t>
+        </is>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>ART002492798</t>
+        </is>
+      </c>
+      <c r="L558" t="n">
+        <v>8</v>
+      </c>
+      <c r="M558" t="n">
+        <v>0</v>
+      </c>
+      <c r="O558" t="n">
+        <v>8</v>
+      </c>
+      <c r="P558" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>키워드 네트워크 분석을 활용한 ‘특수교육연구’ 학술지의 연구 동향</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Yi, Seongyong; Park, So-young</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>특수교육연구</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>국립특수교육원</t>
+        </is>
+      </c>
+      <c r="E559" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>10.34249/jse.2019.26.1.24</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>본 연구의 목적은 키워드 네트워크 분석을 활용해 ‘특수교육연구’ 학술지의 연구 동향을 분석하는 것이다. 이를 위해 본 연구는 국립특수교육원 누리집을 통해 논문자료를 검색하고, 게재논문에서 키워드가 제시되기 시작한 2004년부터 2018년까지 게재된 총 347편의 논문을 최종분석대상으로 선정하였다. 다음 KrKwic, KrTitle 프로그램을 사용해 키워드 추출 및 코딩을 실시하고, 자료를 정제해 핵심 키워드 60개로 1-mode 네트워크 행렬(matrix)을 구축하였다. 연구 동향을 구체적으로 파악하기 위해 빈도분석과 공출현 키워드 네트워크 분석에 기초한 네트워크 구조 특성 분석, 사회적 네트워크 중앙성 분석을 실시하였다. 네트워크 분석 도구는 국내외 키워드 네트워크 분석에서 다수 활용되고 있는 NetMiner 4 프로그램을 적용하였다. 주요 연구 결과는 다음과 같다. 첫째, ‘특수교육연구’ 학술지에 게재된 연구의 주요 키워드는 ‘지적장애’, ‘통합교육’, ‘특수교육’, ‘특수교사’, ‘장애학생’ 등으로 나타났다. 둘째, 연결중심성이 높은 키워드는 ‘통합교육, 인식, 특수교육, 교육과정, 특수교사, 교사’ 등으로 나타났다. 즉, ‘특수교육연구’ 학술지는 지적장애 및 통합교육 주제 관련 연구가 다수 이루어지고 있다는 것을 알 수 있었다. 본 연구의 결과는 ‘특수교육연구’ 학술지의 연구특성을 이해하는 데 유용한 기초 자료와 통찰을 제공할 수 있을 것이다.</t>
+        </is>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>ART002480933</t>
+        </is>
+      </c>
+      <c r="L559" t="n">
+        <v>24</v>
+      </c>
+      <c r="M559" t="n">
+        <v>0</v>
+      </c>
+      <c r="O559" t="n">
+        <v>24</v>
+      </c>
+      <c r="P559" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>텍스트 마이닝 기법을 활용한 국내 가상현실(VR) 연구와 교육적 활용 동향 분석</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Hye-Sun Lee; JUNG YUNHEE; Sang-Youn Kim</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>학습자중심교과교육연구</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>학습자중심교과교육학회</t>
+        </is>
+      </c>
+      <c r="E560" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>10.22251/jlcci.2019.19.18.311</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>4차 산업혁명의 시대적 흐름과 맞물려 최근 다양한 학문영역에서 가상현실(VR) 연구가 활발하게 이루어지고 있다. 이에 본 연구는 텍스트 마이닝 기법을 활용하여 국내 VR 연구의 주제어를 중심으로 국내 연구 전반과 학문영역별, 그리고 교육학의 VR 연구동향을 탐색하고 특히 VR의 교육적 활용 동향을 분석함으로써, 향후 VR의 교육적 활용 및 관련 연구를 위한 기초자료를 마련하는 데 목적이 있다. 이를 위해 1998년부터 2019년 5월까지 한국학술지인용색인(KCI)에 등재된 국내 학술지 및 학술대회 발표논문을 수집하였다. 전처리와 예비 분석을 반복 실시하여 도출된 2,729편의 의 논문에서 5,791개 주제어를 대상으로 R과 NetMiner 프로그램을 이용한 빈도분석으로 연구현황을 확인하고, 연관 규칙 분석과 네트워크 시각화를 통해 주제어 간 관계성을 살펴보았다. 그 결과, 공학, 예술체육학, 복합학, 사회과학, 의약학, 인문학, 자연과학, 농수해양학의 국내 전 학문영역에서 VR 연구가 수행되고 있음을 확인하였다. 특히 국내 VR의 주제어는 유형, 시스템, 사용자, 활용 분야, 기타를 중심으로 범주화되었으며, 이때 각각의 주제어는 VR 또는 AR을 중심으로 연관성을 나타냈다. 또한, 교육학 외에도 다양한 학문 분야에서 VR의 교육적 활용에 관한 관심이 높음을 확인하였다. 본 연구의 결과는 VR의 교육적 활용에 대한 높은 요구와 교육학을 중심으로 한 학제 간 융합연구의 필요성을 실증적으로 확인하였다는 점에서 의의가 있다.</t>
+        </is>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>ART002513031</t>
+        </is>
+      </c>
+      <c r="L560" t="n">
+        <v>30</v>
+      </c>
+      <c r="M560" t="n">
+        <v>0</v>
+      </c>
+      <c r="O560" t="n">
+        <v>30</v>
+      </c>
+      <c r="P560" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>텍스트네트워크분석을 활용한 종양간호학회지 논문의 연구동향 분석</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Miji Kim; Jaehee Jeon; Eunjung Ryu</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Asian Oncology Nursing</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>대한종양간호학회</t>
+        </is>
+      </c>
+      <c r="E561" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>10.5388/aon.2019.19.4.193</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>Purpose: The purpose of this study was to identify the knowledge structure of Asian Oncology Nursing (AON) from 2002 to 2018.
+Methods: Abstracts from 382 studies were reviewed and analyzed using the text network analysis program, NetMiner 4.3. Keywords network trends were compared before and after 2012 when the journal title changed from Journal of Korean Oncology Nursing to Journal of Asian Oncology Nursing. Results: ‘Cancer,’ ‘patient,’ ‘quality of life,’ ‘breast,’ ‘nurse,’ ‘depression,’ ‘health,’ ‘nursing,’ ‘pain,’ ‘family’ were the top 10 most frequent keywords, and ‘cancer,’ ‘patient,’ ‘quality of life,’ ‘health,’ ‘nursing,’ ‘family,’ ‘intervention,’ ‘effect,’ ‘hospital,’ and ‘therapy’ were the dominant keywords that ranked highest in co-appearance frequency. Core keywords changed before and after 2012.
+After 2012, depression, health, symptom and pain were the keywords ranked that replaced nursing, education, family, and intervention from before 2012. Four subtopic groups were identified: 1) cancer treatment, education and information, 2) chemotherapy and psychological adjustment, 3) psychosocial adjustment of cancer survivors, and 4) process of cancer intervention and support. Conclusion: This study provides a general overview of research trends of the Asian Oncology Nursing Society. Findings of this study may guide future research directions in Asian Oncology Nursing research.</t>
+        </is>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>ART002541632</t>
+        </is>
+      </c>
+      <c r="L561" t="n">
+        <v>8</v>
+      </c>
+      <c r="M561" t="n">
+        <v>0</v>
+      </c>
+      <c r="O561" t="n">
+        <v>8</v>
+      </c>
+      <c r="P561" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>텍스트마이닝을 활용한 HPV 백신 접종 관련 연구 동향 분석</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Son Yedong; Hee Sun Kang</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>Child Health Nursing Research</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>한국아동간호학회</t>
+        </is>
+      </c>
+      <c r="E562" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>10.4094/chnr.2019.25.4.458</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>Purpose: The purpose of this study was to identify human papillomavirus (HPV) vaccination research trends by visualizing a keyword network. Methods: Articles about HPV vaccination were retrieved from the PubMed and Web of Science databases. A total of 1,448 articles published in 2006~2016 were selected. Keywords from the abstracts of these articles were extracted using the text mining program WordStat and standardized for analysis. Sixty-four key words out of 287 were finally chosen after pruning. Social network analysis using NetMiner was applied to analyze the whole keyword network and the betweenness centrality of the network. Results: According to the results of the social network analysis, the central keywords with high betweenness centrality included “health education”, “health personnel”, “parents”, “uptake”, “knowledge”, and “health promotion”. Conclusion: To increase the uptake of HPV vaccination, health personnel should provide health education and vaccine promotion for parents and adolescents. Using social media, governmental organizations can offer accurate information that is easily accessible. School-based education will also be helpful.</t>
+        </is>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>ART002519014</t>
+        </is>
+      </c>
+      <c r="L562" t="n">
+        <v>2</v>
+      </c>
+      <c r="M562" t="n">
+        <v>0</v>
+      </c>
+      <c r="O562" t="n">
+        <v>2</v>
+      </c>
+      <c r="P562" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>토픽 모델링을 활용한 도서관, 기록관, 박물관간의 연구 주제 분석</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Heesop Kim; Kang Bora</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>한국도서관·정보학회지</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>한국도서관·정보학회</t>
+        </is>
+      </c>
+      <c r="E563" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>10.16981/kliss.50.4.201912.339</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>본 연구의 목적은 광의의 측면에서 지식정보제공이라는 공동의 임무를 수행하는 도서관, 기록관, 박물관간의 협력 플랫폼 구축에 관한 연구의 동향을 토픽 모델링을 통하여 파악하기 위한 것이다. 연구의 목적을 달성하기 위하여 Scopus로부터 이들 세 기관을 동시에 다루는 논문 637편의 서지정보를 수집하였다. 수집된 서지정보 중에서 초록을 대상으로 NetMiner V.4를 통하여 총 5,218개의 단어를 추출한 후 토픽모델링 분석하였으며, 그 결과는 다음과 같다. 첫째, tf-idf의 가중치에 따른 단어출현 빈도를 분석한 결과 ‘보존(Preservation)’이 가장 높게 나타났으며, 둘째, LDA(Latent Dirichlet Allocation) 알고리즘을 통한 토픽모델링 분석 결과 13개의 주제 영역이 도출되었다. 셋째, 13개의 주제 영역을 네트워크로 표현한 결과 ‘리포지터리 구축(Repository Construction)’을 중심으로 기관간의 협력, 정보자원 보존을 위한 환경 구축, 정부차원에서의 제도와 정책 발굴, 정보자원의 생애주기, 정보자원의 전시, 정보자원의 검색 등이 서로 밀접한 관련성을 가진 것으로 나타났다. 넷째, 13개의 주제 영역의 연도별 동향을 살펴보면, 1998년 이전의 연구는 제도와 정책 발굴, 정보자원의 검색, 정보자원의 생애주기 등과 같이 특정 주제에 한정된 반면, 그 이후의 연구는 보다 다양한 주제를 다룬 것으로 분석되었다.</t>
+        </is>
+      </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>ART002540589</t>
+        </is>
+      </c>
+      <c r="L563" t="n">
+        <v>11</v>
+      </c>
+      <c r="M563" t="n">
+        <v>0</v>
+      </c>
+      <c r="O563" t="n">
+        <v>11</v>
+      </c>
+      <c r="P563" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>패션트렌드 예측색의 색채 특성 및 시즌별 연결구조 도출</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Seo, YeaJi; Young In KIM</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>한국색채학회논문집</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>한국색채학회</t>
+        </is>
+      </c>
+      <c r="E564" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>10.17289/jkscs.33.2.201905.17</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>This study investigated fashion color trends predicted by trend forecasting agencies from the 2009 S/S season to the 2018 F/W season and the structure of color networks. In this study, the fashion trend forecasting companies that were used to build a database were as follows: Intercolor, Promostyl, Première Vision, Pantone, FaDI, Samsung Design Net, and Firstview Korea. The 5,820 forecasted fashion trend colors from the 2009 S/S season to the 2018 F/W season were collected and analyzed in Munsell’s basic 10 hues and PCCS’s 12 tones. To digitize and visually represent the relationships between the forecasted fashion trend colors, network analysis, including frequency analysis, density analysis, degree, and degree centrality, was performed using Netminer 4.0. The conclusions are as follows: First, a comparative analysis of hues was conducted on the forecasted fashion trend colors’ characteristics, which showed that the YR, R, Y, and PB hues were commonly forecasted. Second, the analysis of the seasonal hue usage ratio revealed that b, lt, and p were forecasted mostly during the S/S season, while ltg, g, d, dk, and dkg were commonly forecasted during the F/W season. Third, degree centrality analysis results showed that W was utilized the most in the S/S season and appeared regularly every two or three years. This method was used to quantitatively analyze fashion color trends and identify the relationships between colors. The results are expected to contribute to the development of color patterns required to automatically forecast color trends by utilizing extended color data.</t>
+        </is>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>ART002467176</t>
+        </is>
+      </c>
+      <c r="L564" t="n">
+        <v>5</v>
+      </c>
+      <c r="M564" t="n">
+        <v>0</v>
+      </c>
+      <c r="O564" t="n">
+        <v>5</v>
+      </c>
+      <c r="P564" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>평창동계올림픽에 관한 언론보도의 의미연결망 분석</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Kim, Kyung-Sik</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>한국융합과학회지</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>한국융합과학회</t>
+        </is>
+      </c>
+      <c r="E565" t="n">
+        <v>2019</v>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>연구목적 : 본 연구는 시기별 평창동계올림픽 보도경향을 비교, 분석하고, 동시출현 주제어와 하위집단 분석을 통하여 보도 프레임을 규명하고자 한다. 연구방법 : 본 연구는 평창동계올림픽 개최전(2018. 1. 23 – 2. 8), 개최중(2018. 2. 9 – 2. 25), 개최후(2018. 2. 26 – 3. 14)간 전국종합일간신문에 보도된 평창동계올림픽 관련 신문기사를 연구대상으로 설정하였다. 개최전에는 8,243건, 개최중에는 13,763건, 그리고 개최후에는 3,446건의 기사가 활용되었다. 자료분석은 NetMiner와 UCINET을 프로그램이 활용되었다. 결론 : 첫째, 평창동계올림픽에 관한 시기별 언론보도의 상위권 주제어는 미미하게 변화하였다. 즉, 평창동계올림픽 개최전에는 PyeongChang, Olympic, PyeongChang Winter Olympic, President, South Korea, North Korea 등, 개최중에는 PyeongChang, PyeongChang Winter Olympic, Olympic, President, South Korea, Curling 등, 그리고 개최후에는 PyeongChang, Paralympics, South Korea, Olympic, Young Mi, PyeongChang Winter Olympic 등의 순으로 중요하게 보도되었다. 둘째, 평창동계올림픽에 관한 언론보도에서 중요하게 다룬 동시출현단어쌍은 PyeongChang Winter Olympic-President, North Korea-President, North Korea-Mike Pence, President-Blue House, PyeongChnag-Athlete 등의 순으로 등장하였다. 평창동계올림픽 개최전, 중, 후동안에는 PyeongChang, President, Paralympics, North Korea, Olympic, South Korea, Young Mi 등의 주제어가 중요하게 다뤄졌다. 또한 구조적 등위성에서는 평창동계올림픽, 북한 대표단 개회식 참석, 컬링팀 영미~!와 스피드스케이팅 팀추월 김보름, 노선영 괴롭힘 왕따 공방, 대통령과 김정숙 여사의 올림픽 관전과 한국선수의 응원, 북한, 미국 프레임으로 보도되었다.</t>
+        </is>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>ART002503355</t>
+        </is>
+      </c>
+      <c r="L565" t="n">
+        <v>6</v>
+      </c>
+      <c r="M565" t="n">
+        <v>0</v>
+      </c>
+      <c r="O565" t="n">
+        <v>6</v>
+      </c>
+      <c r="P565" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>학교스포츠클럽 참가 중학생의 인기도 연결망과 학교생활적응의 관계</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Kwon Sun Sin; Kim, Kyung-Sik</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>한국체육학회지</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>한국체육학회</t>
+        </is>
+      </c>
+      <c r="E566" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>10.23949/kjpe.2019.03.58.2.35</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>본 연구의 목적은 학교스포츠클럽에 참가하고 있는 중학생의 인기도 연결망 구조 및 인기도 결정요인을 분석하고 연결망 중앙성과 학교생할적응의 관계를 규명하기 위해 수행되었다. 본 연구에서는 2018년 충청남도 C시에 소재하고 있는 W중학교 학교스포츠클럽에 소속된 학생을 연구대상자로 선정하였다. 표집 된 사례 수는 방송댄스 17명, 플로어볼 15명, 배드민턴 15명, 농구 16 명, 티볼 17명으로 총 80명이다. 본 연구는 실명을 지명하는 설문조사를 실시하였다. 자료처리는 NetMiner를 이용한 인기도 연결망 구조 분석과 SPSS를 활용한 인기도 및 인기도 결정요인과 학교생활적응의 상관관계 분석을 실시하였다. 결론은 다음과 같다. 첫째, 학교스포츠클럽 참가 중학생의 인기도 연결망은 단일 네트워크로 나타났으며, 다수의 학생이 소수의 학생을 지목하는연결망 구조를 보인다. 둘째, 학교스포츠클럽 참가 중학생의 인기도 연결망에서 학생 지명요인은 사회측정적 인기도의 경우 친함, 운동능력, 착해서 그리고 지각된 인기도는 운동능력, 착함, 친함 등의 순이다. 특히, 운동능력은 인기도와 의미 있는 관계가있다. 셋째, 지각된 인기도 연결망은 학교생활적응과 관계가 있다. 즉, 가장 인기 있는 학생 연결망의 활동중앙성이 높을수록 생활적응, 그리고 매개중앙성이 높을수록 교사적응, 수업적응, 친구적응, 생활적응 또한 높다.</t>
+        </is>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>ART002456793</t>
+        </is>
+      </c>
+      <c r="L566" t="n">
+        <v>6</v>
+      </c>
+      <c r="M566" t="n">
+        <v>0</v>
+      </c>
+      <c r="O566" t="n">
+        <v>6</v>
+      </c>
+      <c r="P566" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>텍스트 네트워크 분석을 활용한 고령친화 분야의 연구동향 분석 : 「보건의료산업학회지」 게재논문(2007~2018)을 중심으로</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>고민석</t>
+        </is>
+      </c>
+      <c r="E567" t="n">
+        <v>2019</v>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>Objectives: The purpose of this study was to analyze research trends in age-friendly research and suggest directions for future research. Methods: For this study, 112 articles related to age-friendly research were selected, from 605 published articles in The Korean Journal of Health Service Management (2007-2018). Content analysis and text network analysis were conducted using SPSS 23.0 and NetMiner 4. Results: First, 2 authors (30.4%) and 4 keywords (45.5%) were the most studied. Most of the studies used quantitative research (93.8%). Primary data (61.9%) and SPSS (77.7%) were the most used for analysis. Second, there were seven common keywords in the top 10 in all the centralities. They were Elderly, Geriatric Hospital, Depression, Care Workers, Long-Term Care Facilities, Experience, and Attitude. Conclusions: This study shows the need for diversity of research topics, subjects, research methods, and analytical tools in future age-friendly related studies. In addition, it suggests activating convergence research in this field linked to various industries and services.</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>https://openalex.org/W3084727854</t>
+        </is>
+      </c>
+      <c r="K567" t="n">
+        <v>0</v>
+      </c>
+      <c r="N567" t="n">
+        <v>0</v>
+      </c>
+      <c r="O567" t="n">
+        <v>0</v>
+      </c>
+      <c r="P567" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>A comparison of social network analysis software &amp; application to Nigeria corporate system</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Anthony Ashiedu</t>
+        </is>
+      </c>
+      <c r="E568" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>10.24124/2019/58933</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>Social network analysis (SNA) is a new discipline that examines the social relationship and interaction of entities including individuals, groups or organizations. Special tools are needed to perform SNA and to convey its results numerically and graphically. In this study, we review and compare a range of SNA software functionality which will focus on the directors interlocked systems of the Nigerian corporate network. From the analysis, it is impossible to justify the comparison between the SNA software tools because each tool has its strength and weakness, and their objectives differ, which leads to different functionalities. Our results demonstrate that the Nigerian corporate network is interconnected by a few highly influential elites.</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>https://openalex.org/W4235849778</t>
+        </is>
+      </c>
+      <c r="K568" t="n">
+        <v>0</v>
+      </c>
+      <c r="O568" t="n">
+        <v>0</v>
+      </c>
+      <c r="P568" t="inlineStr">
+        <is>
+          <t>소개</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>A Keyword Network Analysis on Health Disparity in Korea: Focusing on News and its application to Physical Education</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Kim Woo-Kyung</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>Journal of the Korea Society of Computer and Information</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>Korean Society of Computer Information</t>
+        </is>
+      </c>
+      <c r="E569" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>10.9708/jksci.2019.24.03.143</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>(초록 없음)</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>https://openalex.org/W3002504994</t>
+        </is>
+      </c>
+      <c r="K569" t="n">
+        <v>0</v>
+      </c>
+      <c r="N569" t="n">
+        <v>0</v>
+      </c>
+      <c r="O569" t="n">
+        <v>0</v>
+      </c>
+      <c r="P569" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>A Study on the Change of Perception about Mt. Kumgang Tourism : Focused on Social Media Big Data</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>공주대학교 관광경영학과 박사; Heekyung Noh</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Journal of Tourism Management Research</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Conscientia Beam</t>
+        </is>
+      </c>
+      <c r="E570" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>10.18604/tmro.2019.23.5.43</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>This study focuses on the fact that most people's perception survey related to Mt. Geumgang tourism is based on a number of positive, neutral, or disagreements. Therefore, this study attempted to confirm various perception changes about Mt. Geumgang tourism. Web crawler collected data related to 'Mt. Geumgang tourism' posted on Naver's blog and cafe. And we used NetMiner program to derive text frequency, weight, and topic modeling. The data collection period was divided into five years before the suspension, five years after the suspension, and up to the latest, based on when the tour was stopped. As a result of analysis, it was recognized as keywords and topics directly related to tourism before the suspension of Mt. Geumgang tourism. This confirms that Mt. Geumgang tourism recognizes not only the tourism aspect but also the various ripple effects. After the suspension of Mt. Geumgang tourism, it was confirmed that the event was recognized as an event, normalization, and dialogue. In addition, economic expectation was recognized most recently, and it was confirmed that it was recognized as a topic such as international politics and political tourism intervention efforts. This study examined the changes in perceptions of Mt. Geumgang tourism by using social media big data, which has been recently used in various fields. It is meaningful to present the basis for drafting a policy that reflects the public's perception of becoming a party to Mt. Geumgang Tourism and Unification Tourism on the Korean Peninsula.</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>https://openalex.org/W4232666371</t>
+        </is>
+      </c>
+      <c r="K570" t="n">
+        <v>0</v>
+      </c>
+      <c r="N570" t="n">
+        <v>0</v>
+      </c>
+      <c r="O570" t="n">
+        <v>0</v>
+      </c>
+      <c r="P570" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>Research Trend Analysis of Publications in the Journal of Home Economics Education Association Using Network Text Analysis</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Yoon-Jung Lee; Eun Jeung Kim; Ji sun Kim</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>한국가정과교육학회지</t>
+        </is>
+      </c>
+      <c r="E571" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>10.19031/jkheea.2019.12.31.4.1</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>이 연구는 네트워크 텍스트 분석을 이용하여 가정과교육 분야의 연구동향을 분석하였다. 2003년 7월부터 2018년 12월 사이에 한국가정과교육학회지에 게재된 586편의 논문의 주제를 소셜 네트워크 분석프로그램인 Netminer 4의 텍스트분석 도구를 이용하여 주제어들의 출현빈도와 중심성 분석(연결중심성, 근접중심성, 매개중심성), 시기별 LDA 분석 등을 실시하였다. 그 결과는 다음과 같다. 첫째, 전반적으로 출현 빈도가 높은 단어들은 부모, 문화, 단원, 건강, 진로, 소비, 실천성 등이었다. 주제어 네트워크 분석 결과, 연결중심성은 부모, 관리가 가장 높았고, 근접중심성은 부모, 남학생, 매개중심성은 남학생, 단원 등이 가장 높게 나타났다. 둘째, 2003년부터 2018년까지의 연구를 4개 시기로 나누어 중심성 분석을 실시한 결과, 네 시기 모두 교육, 가정, 목적, 수업, 중학교, 학교 등 출현 빈도수가 높은 단어들은 유사하였으나, 시기별로는 제3, 제4시기에는 ‘목적’이라는 단어가, 제4시기에는 ‘과정’ 이라는 단어가 두드러지게 나타났다. 셋째, 시기별 중심성 분석 결과 중심성의 종류와 무관하게 각 시기에 중요한 역할을 하는 단어들은 일정한 것으로 나타났다. 넷째, LDA 분석을 통한 토픽 변화를 분석하였을 때 교육과정, 교과서, 가족건강성, 교수학습, 평가, 식생활, 외모관리, 소비 등은 모든 시기에 지속적으로 등장하였다. 4개 시기의 토픽은 점차 다양화되고, 세분화되며, 심화되는 경향을 보였다. 연구를 통해 교육과정의 변화와 국가정책이 반영되어 새롭게 등장한 토픽인 교사연수와 안전이 주제어로 도출되었으며, 상대적으로 연구의 관심이 낮았던 토픽은 주거임이 드러나 학자들의 관심과 연구 활성화가 요구된다고 할 것이다. 이 연구는 2000년대 이후 한국가정과교육학계에서 이루어진 연구들의 주요 관심사를 파악할 수 있었다는 점과 관심사들의 순위를 제시하였다는 점에서 의미가 있다.The purpose of this study was to analyze the research trend in home economics education using network text analysis method. The 586 research articles published in the Journal of Home Economics Education Association between July, 2003 and December 2018 were examined using Neckinger 4, a social network analysis software. The frequency and centrality measures(degree centrality, closeness centrality, and betweenness centrality) were calculated for the words appeared throughout the whole period, and the centrality analysis and LAD(Latent Dirichlet Allocation) were conducted for the four sub-periods. The results are as follows: first, the most frequently appeared words are parents, culture, unit, health, career, consumption, practicality, etc. The words such as parents and management scored high in degree centrality; parents and male students in closeness centrality; and male students and units in betweenness centrality. Second, when divided into four periods, the words such as education, family, purpose, class, middle school, and school appeared most frequently across the periods; but some words such as ‘purpose’ (in period 3 and 4), or ‘process’ (in period 4) were salient only in certain periods. Third, the words with high centrality were consistent regardless of the types of centrality within each period. Fourth, the topic analysis using LAD showed that curriculum, textbook, family healthiness, teaching-learning, evaluation, dietary life, appearance management, and consumption were the topics consistently appeared across all periods. The topics have become diversified and deepened. New topics such as teacher training and safety appeared in later periods, possibly due to the curriculum and national policy changes, and housing as a less represented topic is suggested as an area that needs further research attention. This study has implication in that it allows researchers to identify the major research interests and the trends in research by researchers in home economic education.</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>https://openalex.org/W3000109586</t>
+        </is>
+      </c>
+      <c r="K571" t="n">
+        <v>3</v>
+      </c>
+      <c r="N571" t="n">
+        <v>0.2125</v>
+      </c>
+      <c r="O571" t="n">
+        <v>3.2125</v>
+      </c>
+      <c r="P571" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>Semantic Network Analysis on Core Values and Policy Orientation: By Focusing on Moon Administration Policy Road-map</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Inwon Lee; Youngmi Lee</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Korean Public Administration Quarterly</t>
+        </is>
+      </c>
+      <c r="E572" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>10.21888/kpaq.2019.12.31.4.643</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>이 연구는 문재인 정부 국정운영의 로드맵으로 제시된 100대 국정과제 내 세부 487개 실천과제를 언어네트워크라는 구조적인 관점에서 조망하고 분석함으로써 시사점을 도출하고자 하는 목적을 갖고 수행되었다. 국정과제는 개별 과제 단위뿐만 아니라 과제 간 연계성을 보다 통합적이고 구조적인 관점에서 파악하고 동시에 관리하려는 노력이 필요하다. 이를 위해서는 국정운영의 전반적인 로드맵인 국정과제에 드러나 개념들을 관계를 구조적인 관점에서 이해하고 분석하는 노력이 필요하다. 이 연구의 연구대상은 2017년 7월 국가 비전과 목표 하에 수립된 100대 국정과제에 속하는 487개 실천과제이며, 각 과제의 주제명을 통해 핵심 키워드를 추출한 후 언어네트워크 분석기법을 적용하였고, 핵심키워드들 간의 언어네트워크 분석을 위해 NetMiner 4.0프로그램을 활용하여 중심성 분석, 응집성 분석, 시각화 등을 수행하였다. 분석의 결과 ‘국민이 주인인 정부’라는 국정목표와 관련해서는 정부시스템의 개선, 행정혁신을 최우선에 두고 있는 것으로 나타났으며, ‘더불어 잘사는 경제’라는 국정목표와 관련해서는 혁신성장, 각 계층별 좋은 일자리 창출, 공정경제 등이 핵심에 있는 것으로 나타났다. ‘내 삶을 책임지는 국가’라는 국정목표는 문재인 정부가 추구하고 있는 적극적 복지정책과 포용국가 전략이 중심축을 이루고 있으며, ‘고르게 발전하는 지역’과 관련해서는 재정분권, 자치분권, 지역의 자립기반 마련, 협력을 통한 추진 등을 지향하고 있는 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>https://openalex.org/W3000149460</t>
+        </is>
+      </c>
+      <c r="K572" t="n">
+        <v>6</v>
+      </c>
+      <c r="N572" t="n">
+        <v>1.7633</v>
+      </c>
+      <c r="O572" t="n">
+        <v>7.7633</v>
+      </c>
+      <c r="P572" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>키워드 네트워크 분석을 통한 ‘The Arts in Psychotherapy’의 연구동향</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Do‐Hee Kim; Jooryung Park</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>예술심리치료연구</t>
+        </is>
+      </c>
+      <c r="E573" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>10.32451/kjoaps.2019.15.1.001</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>Although literature reviews in the field of arts psychotherapy have previously been conducted, such studies generally only targeted specific topics. Therefore, the aim of this study was to identify research trends in arts psychotherapy through extensive keyword network analysis. To this end, a total of 1,256 articles published in Journal of ‘The Arts in Psychotherapy’ from 1980 to 2017 were analyzed. Keywords were extracted depending on period of decade and the relationship between keywords was visualized using the NetMiner 4.3 program. As a result of this study, trends of appeared keywords and changing patterns of linkages between keywords were structurally examined in a specific decade. Findings indicated that trends were closely related to sociopolitical changes and mental health policy. This study delineates research trends in this field, collating them into a single source. Further, it relates to articles published in the journal over the previous 37 years, providing a detailed description of the most-discussed topics.</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>https://openalex.org/W2967825356</t>
+        </is>
+      </c>
+      <c r="K573" t="n">
+        <v>2</v>
+      </c>
+      <c r="N573" t="n">
+        <v>4.6579</v>
+      </c>
+      <c r="O573" t="n">
+        <v>6.6579</v>
+      </c>
+      <c r="P573" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>Trend Analysis of Korean and Chinese Adolescents obesity Using Topic Modeling</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Dong-Jin An; Hyeoi-Jin Kim</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Korean Journal of Sports Science</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>The Korean Society of Sports Science</t>
+        </is>
+      </c>
+      <c r="E574" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>10.35159/kjss.2019.12.28.6.1271</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>The purpose of this study is to conduct a trend study on papers about adolescent obesity in Korea and China through text mining and keyword mining. Using the reptile functionof R language program, the study has Adolescents obesity papers from 2009 to 2019, a total of 83 Korean papers and 55 Chinese papers, and the English abstracts of these papers were used for analysis. The NetMiner 4 program was used for the advance processing of the research data, subject modeling analysis and visualization. The results are as follows. First, in general, the research trends of adolescents obesity papers in Korea and China are generally similar. Second, on the micro level, Korea has a higher proportion in the level of dietary intake, however China has occupied a higher level of weight loss. Third, the overall development trend of the young women</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>https://openalex.org/W2999854423</t>
+        </is>
+      </c>
+      <c r="K574" t="n">
+        <v>0</v>
+      </c>
+      <c r="N574" t="n">
+        <v>0</v>
+      </c>
+      <c r="O574" t="n">
+        <v>0</v>
+      </c>
+      <c r="P574" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>Identification of of Knowledge Structure of Pain Management Nursing Research Applying Text Network Analysis</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Park, CS; Park, EJ</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>JOURNAL OF KOREAN ACADEMY OF NURSING</t>
+        </is>
+      </c>
+      <c r="E575" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>10.4040/jkan.2019.49.5.538</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>포함</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>Purpose: This study aimed to explore and compare the knowledge structure of pain management nursing research, between Korea and other countries, applying a text network analysis. Methods: 321 Korean and 6,685 international study abstracts of pain management, published from 2004 to 2017, were collected. Keywords and meaningful morphemes from the abstracts were analyzed and refined, and their co-occurrence matrix was generated. Two networks of 140 and 424 keywords, respectively, of domestic and international studies were analyzed using NetMiner 4.3 software for degree centrality, closeness centrality, betweenness centrality, and eigenvector community analysis. Results: In both Korean and international studies, the most important, core-keywords were pain, patient, pain management, registered nurses, care, cancer, need, analgesia, assessment and surgery. While some keywords like 'education, knowledge, and patient-controlled analgesia found to be important in Korean studies; treatment hospice palliative care, and children were critical keywords in international studies. Three common sub-topic groups found in Korean and international studies were pain and accompanying symptoms, target groups of pain management, and RNs performance of pain management. It is only in recent years (201617), that keywords such as performance, attitude, depression, and sleep have become more important in Korean studies than, while keywords such as assessment, intervention, analgesia, and chronic pain have become important in international studies. Conclusion: It is suggested that Korean pain-management researchers should expand their concerns to children and adolescents, the elderly, patients with chronic pain, patients in diverse healthcare settings, and patients' use of opioid analgesia. Moreover, researchers need to approach pain-management with a quality of life perspective rather than a mere focus on individual symptoms.</t>
+        </is>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>WOS:000493986000004</t>
+        </is>
+      </c>
+      <c r="K575" t="n">
+        <v>17</v>
+      </c>
+      <c r="O575" t="n">
+        <v>17</v>
+      </c>
+      <c r="P575" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>연희 종합지원체계 구축 기본 연구보고서</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>김정이, 박정민, 박진우 외</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>2019 서울시 연희단 육성지원 사업</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>2019 서울시 연희단 육성지원 사업</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>응답자-연희 단체 소속 2모드 네트워크 분석</t>
+        </is>
+      </c>
+      <c r="O576" t="n">
+        <v>0</v>
+      </c>
+      <c r="P576" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>Social network analysis for social risks of construction projects in high-density urban areas in China</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Yuan, JF; Chen, KW; Li, W; Ji, C; Wang, ZR; Skibniewski, MJ</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>JOURNAL OF CLEANER PRODUCTION</t>
+        </is>
+      </c>
+      <c r="E577" t="n">
+        <v>2018</v>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>10.1016/j.jclepro.2018.07.109</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>포함</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>Social impacts have become increasingly important for urban development in China. In addition, unlike general construction projects, construction projects in high-density urban areas have high levels of complexity and uncertainty. Thus, from a network perspective, an improved social risk analysis theory and a method for these projects were generated in this paper. A case study involving 66 cases of social conflicts in construction projects in China was performed, and 16 social risk factors were summarized. Eight stakeholders related to these social risk factors were then identified based on a literature review and the case database. A theoretical model for social risk network analysis considering the interrelationships between stakeholders and risks was developed by using NetMiner, a social network analysis (SNA) tool. A 2-mode network and two 1-mode networks were used to analyze the relationships among the identified 16 social risk factors and 8 stakeholders. In terms of three-level challenges such as complex environments, the unreasonable behavior of individuals or organizations, and diversified interaction between behaviors and environments, the most important social risks of construction projects in high-density urban areas were explored to help the government implement effective social risk management measures. In addition, multiple, complicated relationships among residents, contractors, governmental authorities, and owners represented a major factor leading to social risk; therefore, more attention should be focused on this topic. The proposed social risk analysis method can increase the attention paid by project managers, governmental authorities, and project owners to social risk factors in high-density areas and provide a structured framework to analyze such social risks, as well as put forth possible solutions to reduce the social impacts on construction projects in high-density urban areas. (C) 2018 Elsevier Ltd. All rights reserved.</t>
+        </is>
+      </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>WOS:000442973100082</t>
+        </is>
+      </c>
+      <c r="K577" t="n">
+        <v>141</v>
+      </c>
+      <c r="O577" t="n">
+        <v>141</v>
+      </c>
+      <c r="P577" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
           <t>Research Trend Visualization by MeSH Terms from PubMed</t>
         </is>
       </c>
-      <c r="B520" t="inlineStr">
+      <c r="B578" t="inlineStr">
         <is>
           <t>Yang, Heyoung, and Hyuck Jai Lee.</t>
         </is>
       </c>
-      <c r="C520" t="inlineStr">
+      <c r="C578" t="inlineStr">
         <is>
           <t>International Journal of Environmental Research and Public Health</t>
         </is>
       </c>
-      <c r="D520" t="inlineStr">
+      <c r="D578" t="inlineStr">
         <is>
           <t>mdpi</t>
         </is>
       </c>
-      <c r="E520" t="inlineStr">
+      <c r="E578" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="F520" t="inlineStr">
+      <c r="F578" t="inlineStr">
         <is>
           <t>10.3390/ijerph15061113</t>
         </is>
       </c>
-      <c r="H520" t="inlineStr">
+      <c r="H578" t="inlineStr">
         <is>
           <t>Motivation: PubMed is a primary source of biomedical information comprising search
 tool function and the biomedical literature from MEDLINE which is the US National Library of
@@ -29995,56 +33329,56 @@
 difﬁculties with search and information analysis.</t>
         </is>
       </c>
-      <c r="I520" t="inlineStr">
+      <c r="I578" t="inlineStr">
         <is>
           <t>W2805947038</t>
         </is>
       </c>
-      <c r="K520" t="n">
+      <c r="K578" t="n">
         <v>66</v>
       </c>
-      <c r="N520" t="n">
+      <c r="N578" t="n">
         <v>1.7677</v>
       </c>
-      <c r="O520" t="n">
+      <c r="O578" t="n">
         <v>66</v>
       </c>
-      <c r="P520" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="521">
-      <c r="A521" t="inlineStr">
+      <c r="P578" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
         <is>
           <t>Mapping the knowledge structure of frailty in journal articles by text network analysis</t>
         </is>
       </c>
-      <c r="B521" t="inlineStr">
+      <c r="B579" t="inlineStr">
         <is>
           <t>Youngji Kim,Soong-nang Jang</t>
         </is>
       </c>
-      <c r="C521" t="inlineStr">
+      <c r="C579" t="inlineStr">
         <is>
           <t>journal articles by text network analysis</t>
         </is>
       </c>
-      <c r="D521" t="inlineStr">
+      <c r="D579" t="inlineStr">
         <is>
           <t>PLOS</t>
         </is>
       </c>
-      <c r="E521" t="n">
+      <c r="E579" t="n">
         <v>2018</v>
       </c>
-      <c r="F521" t="inlineStr">
+      <c r="F579" t="inlineStr">
         <is>
           <t>10.1371/journal.pone.0196104</t>
         </is>
       </c>
-      <c r="H521" t="inlineStr">
+      <c r="H579" t="inlineStr">
         <is>
           <t>Backgrounds
 This study was to understand the trends of frailty research and networking features of key-
@@ -30081,109 +33415,114 @@
 OPEN ACCESS</t>
         </is>
       </c>
-      <c r="I521" t="inlineStr">
+      <c r="I579" t="inlineStr">
         <is>
           <t>W2800679457</t>
         </is>
       </c>
-      <c r="K521" t="n">
+      <c r="K579" t="n">
         <v>59</v>
       </c>
-      <c r="N521" t="n">
+      <c r="N579" t="n">
         <v>6.3235</v>
       </c>
-      <c r="O521" t="n">
+      <c r="O579" t="n">
         <v>59</v>
       </c>
-      <c r="P521" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="522">
-      <c r="A522" t="inlineStr">
+      <c r="P579" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
         <is>
           <t>An analysis of security systems for electronic information for establishing secure internet of things environments: Focusing on research trends in the security field in South Korea</t>
         </is>
       </c>
-      <c r="B522" t="inlineStr">
+      <c r="B580" t="inlineStr">
         <is>
           <t>Seungwan Hong,Sangho Park,Lee Won Park,Minseo Jeon,Hangbae Chang</t>
         </is>
       </c>
-      <c r="C522" t="inlineStr">
+      <c r="C580" t="inlineStr">
         <is>
           <t>Future Generation Computer Systems</t>
         </is>
       </c>
-      <c r="D522" t="inlineStr">
+      <c r="D580" t="inlineStr">
         <is>
           <t>elsevier</t>
         </is>
       </c>
-      <c r="E522" t="inlineStr">
+      <c r="E580" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="F522" t="inlineStr">
+      <c r="F580" t="inlineStr">
         <is>
           <t>10.1016/j.future.2017.10.019</t>
         </is>
       </c>
-      <c r="I522" t="inlineStr">
+      <c r="I580" t="inlineStr">
         <is>
           <t>W2765140999</t>
         </is>
       </c>
-      <c r="K522" t="n">
+      <c r="K580" t="n">
         <v>17</v>
       </c>
-      <c r="N522" t="n">
+      <c r="N580" t="n">
         <v>1.6771</v>
       </c>
-      <c r="O522" t="n">
+      <c r="O580" t="n">
         <v>17</v>
       </c>
-      <c r="P522" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="523">
-      <c r="A523" t="inlineStr">
+      <c r="P580" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
         <is>
           <t>Analysis of Research on Nurses’ Job Stress Using Network Analysis</t>
         </is>
       </c>
-      <c r="B523" t="inlineStr">
+      <c r="B581" t="inlineStr">
         <is>
           <t>Kim, Young-Su, and Soo-Kyoung Lee</t>
         </is>
       </c>
-      <c r="C523" t="inlineStr">
+      <c r="C581" t="inlineStr">
         <is>
           <t>Western journal of nursing research</t>
         </is>
       </c>
-      <c r="D523" t="inlineStr">
+      <c r="D581" t="inlineStr">
         <is>
           <t>sage</t>
         </is>
       </c>
-      <c r="E523" t="inlineStr">
+      <c r="E581" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="F523" t="inlineStr">
+      <c r="F581" t="inlineStr">
         <is>
           <t>10.1177/0193945918781310</t>
         </is>
       </c>
-      <c r="H523" t="inlineStr">
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>포함</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
         <is>
           <t>This study established a network related to nurses’ job stress by conducting 
 a social network analysis of titles, keywords, and abstracts, and it identified 
@@ -30208,58 +33547,58 @@
 Gu, Daegu 42601, South Korea.</t>
         </is>
       </c>
-      <c r="I523" t="inlineStr">
+      <c r="I581" t="inlineStr">
         <is>
           <t>W2808378704</t>
         </is>
       </c>
-      <c r="K523" t="n">
+      <c r="K581" t="n">
         <v>10</v>
       </c>
-      <c r="N523" t="n">
+      <c r="N581" t="n">
         <v>6.0624</v>
       </c>
-      <c r="O523" t="n">
+      <c r="O581" t="n">
         <v>10</v>
       </c>
-      <c r="P523" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="524">
-      <c r="A524" t="inlineStr">
+      <c r="P581" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
         <is>
           <t>Text Network Analysis of Newspaper Articles on Life-sustaining Treatments</t>
         </is>
       </c>
-      <c r="B524" t="inlineStr">
+      <c r="B582" t="inlineStr">
         <is>
           <t>박은준</t>
         </is>
       </c>
-      <c r="C524" t="inlineStr">
+      <c r="C582" t="inlineStr">
         <is>
           <t>Journal of Korean Academy of Community Health Nursing</t>
         </is>
       </c>
-      <c r="D524" t="inlineStr">
+      <c r="D582" t="inlineStr">
         <is>
           <t>Korean Academy of Community Health Nursing</t>
         </is>
       </c>
-      <c r="E524" t="inlineStr">
+      <c r="E582" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="F524" t="inlineStr">
+      <c r="F582" t="inlineStr">
         <is>
           <t>10.12799/jkachn.2018.29.2.244</t>
         </is>
       </c>
-      <c r="H524" t="inlineStr">
+      <c r="H582" t="inlineStr">
         <is>
           <t>PURPOSE
 This study tried to understand discourses of life-sustaining treatments in general daily and healthcare newspapers.
@@ -30271,58 +33610,58 @@
 The discourse that withdrawal of futile LST should be allowed according to the patient's will was consistent in the newspapers. Given that newspaper articles influence knowledge and attitudes of the public, RNs are recommended to participate actively in public communication on LST.</t>
         </is>
       </c>
-      <c r="I524" t="inlineStr">
+      <c r="I582" t="inlineStr">
         <is>
           <t>W2871237788</t>
         </is>
       </c>
-      <c r="K524" t="n">
+      <c r="K582" t="n">
         <v>5</v>
       </c>
-      <c r="N524" t="n">
+      <c r="N582" t="n">
         <v>7.1655</v>
       </c>
-      <c r="O524" t="n">
+      <c r="O582" t="n">
         <v>5</v>
       </c>
-      <c r="P524" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="525">
-      <c r="A525" t="inlineStr">
+      <c r="P582" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
         <is>
           <t>소셜 네트워크 분석(SNA)을 이용한 실과(기술·가정)교육 분야 연구 동향 분석</t>
         </is>
       </c>
-      <c r="B525" t="inlineStr">
+      <c r="B583" t="inlineStr">
         <is>
           <t>김은정, 이윤정, 김지선</t>
         </is>
       </c>
-      <c r="C525" t="inlineStr">
+      <c r="C583" t="inlineStr">
         <is>
           <t>Journal of Korean Practical Arts Education (JKPAE)</t>
         </is>
       </c>
-      <c r="D525" t="inlineStr">
+      <c r="D583" t="inlineStr">
         <is>
           <t>Korean Home Economics Association</t>
         </is>
       </c>
-      <c r="E525" t="inlineStr">
+      <c r="E583" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="F525" t="inlineStr">
+      <c r="F583" t="inlineStr">
         <is>
           <t>10.6115/fer.2018.043</t>
         </is>
       </c>
-      <c r="H525" t="inlineStr">
+      <c r="H583" t="inlineStr">
         <is>
           <t>This study analyzed research trends in the field of Practical Arts (Technology &amp; Home Economics) education. From 
 958 articles published between 2010 and 2018 in the Journal of Korean Practical Arts Education (JKPAE), Journal of 
@@ -30344,216 +33683,216 @@
 Research</t>
         </is>
       </c>
-      <c r="I525" t="inlineStr">
+      <c r="I583" t="inlineStr">
         <is>
           <t>W2904166034</t>
         </is>
       </c>
-      <c r="K525" t="n">
+      <c r="K583" t="n">
         <v>3</v>
       </c>
-      <c r="N525" t="n">
+      <c r="N583" t="n">
         <v>0.2169</v>
       </c>
-      <c r="O525" t="n">
+      <c r="O583" t="n">
         <v>3</v>
       </c>
-      <c r="P525" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="526">
-      <c r="A526" t="inlineStr">
+      <c r="P583" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
         <is>
           <t>암 진단 고지 관련 국내외 연구주제의 텍스트 네트워크 분석</t>
         </is>
       </c>
-      <c r="B526" t="inlineStr">
+      <c r="B584" t="inlineStr">
         <is>
           <t>윤진희</t>
         </is>
       </c>
-      <c r="C526" t="inlineStr">
+      <c r="C584" t="inlineStr">
         <is>
           <t>Korean Oncology Nursing Society</t>
         </is>
       </c>
-      <c r="D526" t="inlineStr">
+      <c r="D584" t="inlineStr">
         <is>
           <t>Korean Oncology Nursing Society</t>
         </is>
       </c>
-      <c r="E526" t="inlineStr">
+      <c r="E584" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="F526" t="inlineStr">
+      <c r="F584" t="inlineStr">
         <is>
           <t>10.5388/aon.2018.18.3.154</t>
         </is>
       </c>
-      <c r="H526" t="inlineStr">
+      <c r="H584" t="inlineStr">
         <is>
           <t>Purpose: This study aimed to identify and compare research topics related to disclosure of cancer diagnosis among Korea and other countries using text network analysis. Methods: Abstracts from 119 studies for the period of 2000~2015 were analyzed. An integrative literature review and text network analysis were applied to examine the research. The keywords from each article’s abstracts were extracted by using a program, KrKwic, and analyzed using network-related measures including degree centrality, and clustering using the NetMiner program. Results: The most important core keywords; ‘patient’, ‘cancer’, ‘diagnosis’, ‘disclosure’, ‘truth’, ‘physician’, ‘family’, ‘telling’, ‘information’, ‘preference’, ‘member’, ‘age’, and ‘tell’ ranked highly. Asian countries as Korea, Japan, and China showed a similar high centrality of degree of connection in family, which appeared as a factor that influences cancer diagnosis disclosure. Conclusion: These findings showed knowledge structure of disclosure of cancer diagnosis and its research trends. The 11 topics identified in this comparative study can provide further starting points for research of communication with cancer patients and their family.</t>
         </is>
       </c>
-      <c r="I526" t="inlineStr">
+      <c r="I584" t="inlineStr">
         <is>
           <t>W2896114795</t>
         </is>
       </c>
-      <c r="K526" t="n">
+      <c r="K584" t="n">
         <v>2</v>
       </c>
-      <c r="N526" t="n">
-        <v>0</v>
-      </c>
-      <c r="O526" t="n">
+      <c r="N584" t="n">
+        <v>0</v>
+      </c>
+      <c r="O584" t="n">
         <v>2</v>
       </c>
-      <c r="P526" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="527">
-      <c r="A527" t="inlineStr">
+      <c r="P584" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
         <is>
           <t>복합문화공간에 대한 시민의 기대와 성과 인식 분석 : 국립아시아문화전당을 중심으로</t>
         </is>
       </c>
-      <c r="B527" t="inlineStr">
+      <c r="B585" t="inlineStr">
         <is>
           <t>강신겸, 김소연, 정성문</t>
         </is>
       </c>
-      <c r="C527" t="inlineStr">
+      <c r="C585" t="inlineStr">
         <is>
           <t>Journal of Region &amp; Culture</t>
         </is>
       </c>
-      <c r="E527" t="inlineStr">
+      <c r="E585" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="F527" t="inlineStr">
+      <c r="F585" t="inlineStr">
         <is>
           <t>10.26654/iagc.2018.5.4.001</t>
         </is>
       </c>
-      <c r="H527" t="inlineStr">
+      <c r="H585" t="inlineStr">
         <is>
           <t>본 연구는 아시아문화중심도시의 핵심 시설인 국립아시아문화전당에 대하여 광주시민들이 개관 전 가지고 있던 기대와 개관 이후 현재까지 인식하는 성과를 통해 문화전당이지역사회의 기대를 충족시키기 위한 방안을 제안하고자 중요도 · 실행도(IPA) 분석을 이용하여 실증 분석하였다. 분석결과 기대와 성과가 모두 높은 부문은 문화행사 및 문화시설증가, 문화행사의 시민참여 기회 증가. 문화도시로서 위상 증대, 지역 문화예술발전에 기여, 주변 상권 활성화, 도시환경정비 · 개선 등이었으며, 당초 기대는 낮았으나 성과가 높게나타난 것은 주변개발 활성화와 지가상승으로 나타났다. 기대와 성과 모두 낮은 영역은 광주전체 지역경제 활성화효과 확산, 아시아국가들과 문화교류 증가, 관광객 증가 등 장기적으로 효과가 나타나는 영역이다. 기대는 높았으나 여전히 성과가 낮은 영역은 문화전문인력 양성, 문화관련 일자리 증가, 문화콘텐츠 산업 · 기업 증가 항목으로 나타났다. 전반적으로 시민들은 문화전당 개관이후 문화적인 면에서는 높은 성과를 나타냈다고 인식하는 반면 경제적인 성과는 전반적으로 낮게 평가했다. 따라서 이러한 결과는 향후 경제영역에서 성과가 가시화될 수 있도록 전략을 마련할 필요가 있음을 시사한다.</t>
         </is>
       </c>
-      <c r="I527" t="inlineStr">
+      <c r="I585" t="inlineStr">
         <is>
           <t>W2922318795</t>
         </is>
       </c>
-      <c r="K527" t="n">
+      <c r="K585" t="n">
         <v>1</v>
       </c>
-      <c r="N527" t="n">
+      <c r="N585" t="n">
         <v>0.617</v>
       </c>
-      <c r="O527" t="n">
+      <c r="O585" t="n">
         <v>1</v>
       </c>
-      <c r="P527" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="528">
-      <c r="A528" t="inlineStr">
+      <c r="P585" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
         <is>
           <t>Assessing destination image via social network analysis the case of the Coastal Uncorked Wine and Food Festival</t>
         </is>
       </c>
-      <c r="B528" t="inlineStr">
+      <c r="B586" t="inlineStr">
         <is>
           <t>Bomi Kang; L. Taylor Damonte; Young‐Jae Kim; Eun-Joo Cha</t>
         </is>
       </c>
-      <c r="C528" t="inlineStr">
+      <c r="C586" t="inlineStr">
         <is>
           <t>Journal of Global Scholars of Marketing Science</t>
         </is>
       </c>
-      <c r="D528" t="inlineStr">
+      <c r="D586" t="inlineStr">
         <is>
           <t>Taylor &amp; Francis</t>
         </is>
       </c>
-      <c r="E528" t="inlineStr">
+      <c r="E586" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="F528" t="inlineStr">
+      <c r="F586" t="inlineStr">
         <is>
           <t>10.1080/21639159.2018.1511379</t>
         </is>
       </c>
-      <c r="H528" t="inlineStr">
+      <c r="H586" t="inlineStr">
         <is>
           <t>Using social network analysis (SNA), this case study examines the image of a unique festival in a well-established tourist destination on the East coast of the United State of America, the Myrtle Beach area of South Carolina. SNA emphasizes the importance of constructing interconnectedness among concepts and knowledge networks in respondents’ minds. The technique visualizes complicated perception of tourists in a most simple but scientific way. Using concept maps and degree centralities derived from SNA, as well as dendrograms, this study provides insights on wine and food festival in Myrtle Beach Area. Together with cluster analysis, the SNA suggests unique contributions to the understanding of tourist behaviour in tourism destination research.</t>
         </is>
       </c>
-      <c r="I528" t="inlineStr">
+      <c r="I586" t="inlineStr">
         <is>
           <t>W2892315243</t>
         </is>
       </c>
-      <c r="K528" t="n">
+      <c r="K586" t="n">
         <v>1</v>
       </c>
-      <c r="N528" t="n">
+      <c r="N586" t="n">
         <v>0.3962</v>
       </c>
-      <c r="O528" t="n">
+      <c r="O586" t="n">
         <v>1</v>
       </c>
-      <c r="P528" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="529">
-      <c r="A529" t="inlineStr">
+      <c r="P586" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
         <is>
           <t>A Method of Biomedical Knowledge Discovery by Literature Mining Based on SPO Predications: A Case Study of Induced Pluripotent Stem Cells</t>
         </is>
       </c>
-      <c r="B529" t="inlineStr">
+      <c r="B587" t="inlineStr">
         <is>
           <t>Zheng-Yin Hu</t>
         </is>
       </c>
-      <c r="C529" t="inlineStr">
+      <c r="C587" t="inlineStr">
         <is>
           <t>Machine Learning and Data Mining</t>
         </is>
       </c>
-      <c r="E529" t="inlineStr">
+      <c r="E587" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="F529" t="inlineStr">
+      <c r="F587" t="inlineStr">
         <is>
           <t>10.1007/978-3-319-96133-0_29</t>
         </is>
       </c>
-      <c r="H529" t="inlineStr">
+      <c r="H587" t="inlineStr">
         <is>
           <t>A large amount of valuable knowledge is hidden in the vast
 biomedical literatures, publications, and online contents. In order to iden
@@ -30567,37 +33906,40 @@
 lights on the ways to further improvements.</t>
         </is>
       </c>
-      <c r="P529" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="530">
-      <c r="A530" t="inlineStr">
+      <c r="O587" t="n">
+        <v>0</v>
+      </c>
+      <c r="P587" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
         <is>
           <t>IT R&amp;D Outcomes and Technology Knowledge Flows in Korea</t>
         </is>
       </c>
-      <c r="B530" t="inlineStr">
+      <c r="B588" t="inlineStr">
         <is>
           <t>정우진, 이상용</t>
         </is>
       </c>
-      <c r="C530" t="inlineStr">
+      <c r="C588" t="inlineStr">
         <is>
           <t>IEEE Technology and Engineering Management Conference</t>
         </is>
       </c>
-      <c r="E530" t="n">
+      <c r="E588" t="n">
         <v>2018</v>
       </c>
-      <c r="F530" t="inlineStr">
+      <c r="F588" t="inlineStr">
         <is>
           <t xml:space="preserve">10.1109/TEMSCON.2018.8488432 </t>
         </is>
       </c>
-      <c r="H530" t="inlineStr">
+      <c r="H588" t="inlineStr">
         <is>
           <t xml:space="preserve">We measured the R&amp;D outcomes of Korea’s 
 firms by analyzing the change and the pattern of technology 
@@ -30614,285 +33956,291 @@
 compared to non-IT segments.  </t>
         </is>
       </c>
-      <c r="P530" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="531">
-      <c r="A531" t="inlineStr">
+      <c r="O588" t="n">
+        <v>0</v>
+      </c>
+      <c r="P588" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
         <is>
           <t>Keyword-based networked knowledge map expressing content relevance between knowledge</t>
         </is>
       </c>
-      <c r="B531" t="inlineStr">
+      <c r="B589" t="inlineStr">
         <is>
           <t>Yoo, Keedong</t>
         </is>
       </c>
-      <c r="C531" t="inlineStr">
+      <c r="C589" t="inlineStr">
         <is>
           <t>this research’s networked knowledge map</t>
         </is>
       </c>
-      <c r="E531" t="inlineStr">
+      <c r="E589" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="F531" t="inlineStr">
+      <c r="F589" t="inlineStr">
         <is>
           <t>10.13088/jiis.2018.24.3.119</t>
         </is>
       </c>
-      <c r="H531" t="inlineStr">
+      <c r="H589" t="inlineStr">
         <is>
           <t>A knowledge map as the taxonomy used in a knowledge repository should be structured to support and supplement knowledge activities of users who sequentially inquire and select knowledge for problem solving. The conventional knowledge map with a hierarchical structure has the advantage of systematically sorting out types and status of the knowledge to be managed, however it is not only irrelevant to knowledge user’s process of cognition and utilization, but also incapable of supporting user's activity of querying and extracting knowledge. This study suggests a methodology for constructing a networked knowledge map that can support and reinforce the referential navigation, searching and selecting related and chained knowledge in term of contents, between knowledge. Regarding a keyword as the semantic information between knowledge, this research’s networked knowledge map can be constructed by aggregating each set of knowledge links in an automated manner. Since a keyword has the meaning of representing contents of a document, documents with common keywords have a similarity in content, and therefore the keyword-based document networks plays the role of a map expressing interactions between related knowledge. In order to examine the feasibility of the proposed methodology, 50 research papers were randomly selected, and an exemplified networked knowledge map between them with content relevance was implemented using common keywords.</t>
         </is>
       </c>
-      <c r="P531" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="532">
-      <c r="A532" t="inlineStr">
+      <c r="O589" t="n">
+        <v>0</v>
+      </c>
+      <c r="P589" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
         <is>
           <t>Analysis of International Journal of Clinical Preventive Dentistry Research Trends Using Word Network Analysis</t>
         </is>
       </c>
-      <c r="B532" t="inlineStr">
+      <c r="B590" t="inlineStr">
         <is>
           <t>Moon. kyung-hui, Sun-Joo Yoon and Hyesook Kwon</t>
         </is>
       </c>
-      <c r="C532" t="inlineStr">
+      <c r="C590" t="inlineStr">
         <is>
           <t>International Journal of Clinical Preventive Dentistry</t>
         </is>
       </c>
-      <c r="D532" t="inlineStr">
+      <c r="D590" t="inlineStr">
         <is>
           <t>대한예방치과학회</t>
         </is>
       </c>
-      <c r="E532" t="inlineStr">
+      <c r="E590" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="F532" t="inlineStr">
+      <c r="F590" t="inlineStr">
         <is>
           <t>10.15236/ijcpd.2018.14.3.184</t>
         </is>
       </c>
-      <c r="I532" t="inlineStr">
+      <c r="I590" t="inlineStr">
         <is>
           <t>W2896778633</t>
         </is>
       </c>
-      <c r="K532" t="n">
-        <v>0</v>
-      </c>
-      <c r="N532" t="n">
-        <v>0</v>
-      </c>
-      <c r="O532" t="n">
-        <v>0</v>
-      </c>
-      <c r="P532" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="533">
-      <c r="A533" t="inlineStr">
+      <c r="K590" t="n">
+        <v>0</v>
+      </c>
+      <c r="N590" t="n">
+        <v>0</v>
+      </c>
+      <c r="O590" t="n">
+        <v>0</v>
+      </c>
+      <c r="P590" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
         <is>
           <t>소셜네트워크 분석 방법론을 활용한 1인 주거 공간 디자인</t>
         </is>
       </c>
-      <c r="B533" t="inlineStr">
+      <c r="B591" t="inlineStr">
         <is>
           <t>Eun Soo Park; Ji Eun Kim</t>
         </is>
       </c>
-      <c r="C533" t="inlineStr">
+      <c r="C591" t="inlineStr">
         <is>
           <t>KOREA SCIENCE &amp; ART FORUM</t>
         </is>
       </c>
-      <c r="D533" t="inlineStr">
+      <c r="D591" t="inlineStr">
         <is>
           <t>Institute of Science Culture Exhibition and Design</t>
         </is>
       </c>
-      <c r="E533" t="inlineStr">
+      <c r="E591" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="F533" t="inlineStr">
+      <c r="F591" t="inlineStr">
         <is>
           <t>10.17548/ksaf.2018.06.30.133</t>
         </is>
       </c>
-      <c r="H533" t="inlineStr">
+      <c r="H591" t="inlineStr">
         <is>
           <t>우리나라의 가구구조는 앞으로 1인 가구가 가장 보편적인 가구 유형이 될 것으로 예측되고 있다. 이에 본 연구는 급격히 늘어난 1인 가구 주거자의 삶을 총체적으로 고려한 1인 주거 공간을 디자인하기 위한 콘텐츠를 도출하기 위해, 1인 가구 주거를 형성하는 사회·경제·문화적 영향요인 등을 빅데이터 분석을 통해 객관적으로 도출하고, 콘텐츠 간의 상관관계를 소셜 네트워크 분석 방법론을 활용하여 다각적으로 분석하였다.BR 빅 데이터 분석 방법론을 적용해 1인 주거공간과 관련된 총 60개의 핵심 콘텐츠를 도출하였으며, 소셜네트워크 분석을 통해 가장 영향력이 큰 콘텐츠는 공간의 편집, 공간 구성 카테고리로 도출되었다. 이는 주거공간은 사용자의 삶의 변화에 따라 탄력적으로 대응할 수 있는 디자인 아이디어가 중요한 부분을 차지한다고 볼 수 있다. 앞으로 더욱 구체화된 1인 주거공간의 컨셉 및 디자인방법론에 대한 연구를 진행하고자 한다.</t>
         </is>
       </c>
-      <c r="I533" t="inlineStr">
+      <c r="I591" t="inlineStr">
         <is>
           <t>W2911344165</t>
         </is>
       </c>
-      <c r="K533" t="n">
-        <v>0</v>
-      </c>
-      <c r="N533" t="n">
-        <v>0</v>
-      </c>
-      <c r="O533" t="n">
-        <v>0</v>
-      </c>
-      <c r="P533" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="534">
-      <c r="A534" t="inlineStr">
+      <c r="K591" t="n">
+        <v>0</v>
+      </c>
+      <c r="N591" t="n">
+        <v>0</v>
+      </c>
+      <c r="O591" t="n">
+        <v>0</v>
+      </c>
+      <c r="P591" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
         <is>
           <t>역대 정권별 보건복지부 장관의 취임사를 통한 보건행정 및 정책 비교분석</t>
         </is>
       </c>
-      <c r="B534" t="inlineStr">
+      <c r="B592" t="inlineStr">
         <is>
           <t>김유호</t>
         </is>
       </c>
-      <c r="C534" t="inlineStr">
+      <c r="C592" t="inlineStr">
         <is>
           <t>Journal of Health Informatics and Statistics</t>
         </is>
       </c>
-      <c r="E534" t="inlineStr">
+      <c r="E592" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="F534" t="inlineStr">
+      <c r="F592" t="inlineStr">
         <is>
           <t>10.21032/jhis.2018.43.4.274</t>
         </is>
       </c>
-      <c r="H534" t="inlineStr">
+      <c r="H592" t="inlineStr">
         <is>
           <t>The purpose of this study is to comprehensively compare the trends of health administration and health policy in the field of health care using the semantic network analysis in the inaugural address of the Ministry of Health and Welfare of each regime in Korea. Methods: This study used a language network analysis method that uses Korean Key Words In Context (KrKwic) program and NetMiner program in sequence. The analysis was conducted by Minister Hwa-joong Kim during the Moo-hyun Roh government, Minister Jae-hee Jeon during the Myung-bak Lee government, Minister Young Jin of Geun-hye Park government and Government Jae-in Moon's inaugural address of Neung-Hoo Park Minister, respectively. Results: The key words differentiated by each regime are that the Moo-hyun Roh Government's Minister Hwa-joong Kim had high connection centrality values in the words 'balanced development' , 'comprehensive' and 'reform' . Minister Jae-Hee Jeon of Myung-bak Lee Government had high connection centrality values in the words 'poverty' and 'return' . In the case of Minister Young Jin of Geun-hye Park Government had high connection centrality values in the words 'demand' , 'Customized' and 'Life cycle' . In the case of Minister Neung-Hoo Park of Jae In Moon Government had high connection centrality values in the words 'Welfare state' , 'Embracing' and 'Soundness' . Conclusions: If the role of health administration in the health care field and the health care policies are constantly changed according to the policies of each regime, it is inconsistent and it is difficult to approach from the long term perspective for public health promotion. In the future, health policy should be developed and implemented with a long-term perspective and consistency based on the consensus and participation of the people with less influence on the change and direction of each government's policies.</t>
         </is>
       </c>
-      <c r="I534" t="inlineStr">
+      <c r="I592" t="inlineStr">
         <is>
           <t>W2905016484</t>
         </is>
       </c>
-      <c r="K534" t="n">
-        <v>0</v>
-      </c>
-      <c r="N534" t="n">
-        <v>0</v>
-      </c>
-      <c r="O534" t="n">
-        <v>0</v>
-      </c>
-      <c r="P534" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="535">
-      <c r="A535" t="inlineStr">
+      <c r="K592" t="n">
+        <v>0</v>
+      </c>
+      <c r="N592" t="n">
+        <v>0</v>
+      </c>
+      <c r="O592" t="n">
+        <v>0</v>
+      </c>
+      <c r="P592" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
         <is>
           <t>아토바스타틴의 새로운 약물 적응증 탐색을 위한 비정형 데이터 분석</t>
         </is>
       </c>
-      <c r="B535" t="inlineStr">
+      <c r="B593" t="inlineStr">
         <is>
           <t>Hwee-Soo Jeong; Gilwon Kang; Woong Choi; Jong-Hyock Park; Kwangsoo Shin; Young-Sung Suh</t>
         </is>
       </c>
-      <c r="C535" t="inlineStr">
+      <c r="C593" t="inlineStr">
         <is>
           <t>Journal of Health Informatics and Statistics</t>
         </is>
       </c>
-      <c r="E535" t="inlineStr">
+      <c r="E593" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="F535" t="inlineStr">
+      <c r="F593" t="inlineStr">
         <is>
           <t>10.21032/jhis.2018.43.4.329</t>
         </is>
       </c>
-      <c r="H535" t="inlineStr">
+      <c r="H593" t="inlineStr">
         <is>
           <t>Objectives: In recent years, there has been an increased need for a way to extract desired information from multiple medical literatures at once. This study was conducted to confirm the usefulness of unstructured data analysis using previously published medical literatures to search for new indications. Methods: The new indications were searched through text mining, network analysis, and topic modeling analysis using 5,057 articles of atorvastatin, a treatment for hyperlipidemia, from 1990 to 2017. Results: The extracted keywords was 273. In the frequency of text mining and network analysis, the existing indications of atorvastatin were extracted in top level. The novel indications by Term Frequency-Inverse Document Frequency (TF-IDF) were atrial fibrillation, heart failure, breast cancer, rheumatoid arthritis, combined hyperlipidemia, arrhythmias, multiple sclerosis, non-alcoholic fatty liver disease, contrast-induced acute kidney injury and prostate cancer. Conclusions: Unstructured data analysis for discovering new indications from massive medical literature is expected to be used in drug repositioning industries.</t>
         </is>
       </c>
-      <c r="I535" t="inlineStr">
+      <c r="I593" t="inlineStr">
         <is>
           <t>W2903774254</t>
         </is>
       </c>
-      <c r="K535" t="n">
-        <v>0</v>
-      </c>
-      <c r="N535" t="n">
-        <v>0</v>
-      </c>
-      <c r="O535" t="n">
-        <v>0</v>
-      </c>
-      <c r="P535" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="536">
-      <c r="A536" t="inlineStr">
+      <c r="K593" t="n">
+        <v>0</v>
+      </c>
+      <c r="N593" t="n">
+        <v>0</v>
+      </c>
+      <c r="O593" t="n">
+        <v>0</v>
+      </c>
+      <c r="P593" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
         <is>
           <t>네트워크 분석을 통한 국내 창의 연구동향 분석</t>
         </is>
       </c>
-      <c r="B536" t="inlineStr">
+      <c r="B594" t="inlineStr">
         <is>
           <t>권정언, 임정연</t>
         </is>
       </c>
-      <c r="C536" t="inlineStr">
+      <c r="C594" t="inlineStr">
         <is>
           <t>Journal of Multimedia Services Convergent with Art</t>
         </is>
       </c>
-      <c r="E536" t="inlineStr">
+      <c r="E594" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="F536" t="inlineStr">
+      <c r="F594" t="inlineStr">
         <is>
           <t>10.21742/AJMAHS.2018.09.65</t>
         </is>
       </c>
-      <c r="H536" t="inlineStr">
+      <c r="H594" t="inlineStr">
         <is>
           <t>The purpose of this study was to analyze the trends of 2003 to 2017 revised ‘creativity research’ 
 through text network analysis using NetMiner4.0 program. Data analysis was conducted by using keyword 
@@ -30909,527 +34257,560 @@
 1)(Professor) Joongbu University, 305, Dongheon-ro, Deogyang-gu, Goyang-si, Gyeonggi-do, Republic of Korea</t>
         </is>
       </c>
-      <c r="P536" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="537">
-      <c r="A537" t="inlineStr">
+      <c r="O594" t="n">
+        <v>0</v>
+      </c>
+      <c r="P594" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
         <is>
           <t>텍스트 분석 기법을 활용한 DMZ 연구 동향 분석</t>
         </is>
       </c>
-      <c r="B537" t="inlineStr">
+      <c r="B595" t="inlineStr">
         <is>
           <t>박선일, 배선학</t>
         </is>
       </c>
-      <c r="C537" t="inlineStr">
+      <c r="C595" t="inlineStr">
         <is>
           <t>Journal of The Korean Association of Regional Geographers 24(3)</t>
         </is>
       </c>
-      <c r="E537" t="inlineStr">
+      <c r="E595" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="F537" t="inlineStr">
+      <c r="F595" t="inlineStr">
         <is>
           <t>10.26863/JKARG.2018.08.24.3.406</t>
         </is>
       </c>
-      <c r="H537" t="inlineStr">
+      <c r="H595" t="inlineStr">
         <is>
           <t>한국의 DMZ에 대한 인식은 2000년대 들어서 전쟁과 대립의 공간에서 평화와 협력의 공간으로 변화하고 있으며, 이와 함께 DMZ와 관련된 연구도 매년 빠르게 증가하고 있다. 이러한 변화 속에서 DMZ의 의미와 가치를 확인하기 위하여 지난 15년 간 DMZ와 관련된 연구 동향을 빈도 분석, 언어 네트워크 분석, 토픽 분석 등 텍스트 마이닝 방법을 적용하여 살펴보았다. 한국학술지인용색인으로부터 274편의 논문 초록을 추출하여 관리･활용, 생태･환경, 정치･제도의 세 연구 분야로 구분하여 분석을 수행하였다. 전체 논문의 키워드를 대상으로 한 빈도 분석에서는 DMZ, 비무장, 평화, 접경, 통일. 지역, 공원, 남북등이 핵심 단어로 추출되었다. 언어 네트워크 분석 결과 DMZ라는 단어를 제외하면 관리･활용 분야에서는 ‘관광’, 생태･환경분야에서는 ‘분류’, 정치･제도 분야에서는 ‘북한’이 가장 중요한 단어로 분석되었다. 토픽 분석 결과 관리･활용 분야에서는 교육, 교류, DMZ 의미, 관광 등이 토픽으로 도출되었고, 생태･환경 분야에서는 식생, 조류, 복원, 변화 등이 도출되었다. 정치･제도 분야에서는 신뢰, 제도, 대립, 공간 등이 도출되었다. 이러한 연구 결과는 동일한 연구 대상인 DMZ를 바라보는 관점이 연구 분야에 따라서 공통점을 갖기도 하지만 서로 차별화되어 나타나기도 함을 의미한다. 본 연구에서 수행한 DMZ 연구 동향분석 결과는 향후 DMZ와 관련된 특정 문제 해결을 위한 의사 결정 자료와 교육자료 등으로 활용될 수 있을 것이다.</t>
         </is>
       </c>
-      <c r="P537" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="538">
-      <c r="A538" t="inlineStr">
+      <c r="O595" t="n">
+        <v>0</v>
+      </c>
+      <c r="P595" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
         <is>
           <t>2018 귀농⋅귀촌박람회의 온라인 뉴스와 SNS 토픽 연구</t>
         </is>
       </c>
-      <c r="B538" t="inlineStr">
+      <c r="B596" t="inlineStr">
         <is>
           <t>하지영</t>
         </is>
       </c>
-      <c r="C538" t="inlineStr">
+      <c r="C596" t="inlineStr">
         <is>
           <t>식품유통연구</t>
         </is>
       </c>
-      <c r="E538" t="inlineStr">
+      <c r="E596" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="H538" t="inlineStr">
+      <c r="H596" t="inlineStr">
         <is>
           <t>This study attempts to collect and analyze online reviews of audience visiting ‘Urban rural migration &amp; Urban rural migration for farming’ exposition to verify the outcomes, and collect and analyze online news articles as well about the hosting performance of ‘Urban rural migration &amp; Urban rural migration for farming’ expositions to comparatively analyze the responses of media and visitors. For this, LDA－based topic analysis was conducted for ‘2018 Korea Urban rural migration &amp; Urban rural migration for farming Exposition’. In the results of analysis, with regard to the same issue, ‘2018 Korea Urban rural migration &amp; Urban rural migration for farming</t>
         </is>
       </c>
-      <c r="P538" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="539">
-      <c r="A539" t="inlineStr">
+      <c r="O596" t="n">
+        <v>0</v>
+      </c>
+      <c r="P596" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
         <is>
           <t>텍스트 네트워크분석을 활용한 국방분야 연구논문 지식구조 분석</t>
         </is>
       </c>
-      <c r="B539" t="inlineStr">
+      <c r="B597" t="inlineStr">
         <is>
           <t>이용규, 윤성웅, 이상훈</t>
         </is>
       </c>
-      <c r="C539" t="inlineStr">
+      <c r="C597" t="inlineStr">
         <is>
           <t>한국컴퓨터정보학회</t>
         </is>
       </c>
-      <c r="E539" t="inlineStr">
+      <c r="E597" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="H539" t="inlineStr">
+      <c r="H597" t="inlineStr">
         <is>
           <t>본 연구에서는 텍스트 네트워크분석을 활용하여 국방분야 연구의 핵심 주제어와 연구주제를 분석하고 이를 통해 전체 지식구조를 파악하고자 하였다. 이를 위해 2010년부터 2017년까지의 국방대학교 학위과정 논문을 대상으로 국방분야 연구현황을 진단하고 지식구조를 구성하였다. 8년간 누적된 논문 710건의 초록을 분석하여 총 6,883개의 단어를 추출한 후, 단어의 논문 등장 빈도수와 단어간 링크수를 파레토 법칙에 따라 상위 20%의 기준으로 총 270개의 단어로 추출하였고, 컴포넌트 분석을 통해 최종 170개의 핵심 주제어를 도출하였다. 이 핵심 주제어를 통해 중심성 분석과 응집구조를 분석하여, 국방분야에 대한 총 6개의 지식구조 그룹을 도출하였다</t>
         </is>
       </c>
-      <c r="P539" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="540">
-      <c r="A540" t="inlineStr">
+      <c r="O597" t="n">
+        <v>0</v>
+      </c>
+      <c r="P597" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
         <is>
           <t>Social media mining for product planning: A product opportunity mining approach based on topic modeling and sentiment analysis</t>
         </is>
       </c>
-      <c r="B540" t="inlineStr">
+      <c r="B598" t="inlineStr">
         <is>
           <t>Byeongki Jeong; Janghyeok Yoon; Jae-Min Lee</t>
         </is>
       </c>
-      <c r="C540" t="inlineStr">
+      <c r="C598" t="inlineStr">
         <is>
           <t>Journal of Information Management</t>
         </is>
       </c>
-      <c r="D540" t="inlineStr">
+      <c r="D598" t="inlineStr">
         <is>
           <t>elsevier</t>
         </is>
       </c>
-      <c r="E540" t="n">
+      <c r="E598" t="n">
         <v>2017</v>
       </c>
-      <c r="F540" t="inlineStr">
+      <c r="F598" t="inlineStr">
         <is>
           <t>10.1016/j.ijinfomgt.2017.09.009</t>
         </is>
       </c>
-      <c r="H540" t="inlineStr">
+      <c r="H598" t="inlineStr">
         <is>
           <t>Social media data have recently attracted considerable attention as an emerging voice of the customer as it has rapidly become a channel for exchanging and storing customer-generated, large-scale, and unregulated voices about products. Although product planning studies using social media data have used systematic methods for product planning, their methods have limitations, such as the difficulty of identifying latent product features due to the use of only term-level analysis and insufficient consideration of opportunity potential analysis of the identified features. Therefore, an opportunity mining approach is proposed in this study to identify product opportunities based on topic modeling and sentiment analysis of social media data. For a multifunctional product, this approach can identify latent product topics discussed by product customers in social media using topic modeling, thereby quantifying the importance of each product topic. Next, the satisfaction level of each product topic is evaluated using sentiment analysis. Finally, the opportunity value and improvement direction of each product topic from a customer-centered view are identified by an opportunity algorithm based on product topics’ importance and satisfaction. We expect that our approach for product planning will contribute to the systematic identification of product opportunities from large-scale customer-generated social media data and will be used as a real-time monitoring tool for changing customer needs analysis in rapidly evolving product environments.</t>
         </is>
       </c>
-      <c r="I540" t="inlineStr">
+      <c r="I598" t="inlineStr">
         <is>
           <t>W2761561877</t>
         </is>
       </c>
-      <c r="K540" t="n">
+      <c r="K598" t="n">
         <v>332</v>
       </c>
-      <c r="N540" t="n">
+      <c r="N598" t="n">
         <v>38.8214</v>
       </c>
-      <c r="O540" t="n">
+      <c r="O598" t="n">
         <v>332</v>
       </c>
-      <c r="P540" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="541">
-      <c r="A541" t="inlineStr">
+      <c r="P598" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
         <is>
           <t>The Role of Mobile Technology in Tourism: Patents, Articles, News, and Mobile Tour App Reviews</t>
         </is>
       </c>
-      <c r="B541" t="inlineStr">
+      <c r="B599" t="inlineStr">
         <is>
           <t>Kim, D; Kim, S</t>
         </is>
       </c>
-      <c r="C541" t="inlineStr">
+      <c r="C599" t="inlineStr">
         <is>
           <t>SUSTAINABILITY</t>
         </is>
       </c>
-      <c r="E541" t="n">
+      <c r="E599" t="n">
         <v>2017</v>
       </c>
-      <c r="F541" t="inlineStr">
+      <c r="F599" t="inlineStr">
         <is>
           <t>10.3390/su9112082</t>
         </is>
       </c>
-      <c r="H541" t="inlineStr">
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>포함</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
         <is>
           <t>The purpose of this research is to identify the status and role of mobile technology in achieving sustainable and smart tourism, and to suggest future research and strategy directions for academia and managers in practice. This research utilized multiple sources, such as patents, academic articles, and news, and selected methodologies optimized for the purpose of each study. Study 1 used Netminer, a social network analysis program, to analyze the relationships between patent's International Patent Classification (IPC) codes. Study 2 used the T-LAB program for content analysis to analyze the texts of patents, journal articles, and news. Study 3 used the Leximancer program, which utilizes relative frequency to analyze mobile app consumer reviews. In study 1, we identified various forms of data related technologies and mobile technologies for smart city systems and maps. In study 2, we found the environment, sustainability, business, and market themes to be related to mobile technology. In study 3, we explored consumers' attitudes and preferences for mobile travel app using their reviews. Advances in mobile technology are expected to create innovative experiences for consumers, foster a sustainable competitive advantage for tourism destinations and tourism-related suppliers, and create sustainable competencies for smart tourism.</t>
         </is>
       </c>
-      <c r="J541" t="inlineStr">
+      <c r="J599" t="inlineStr">
         <is>
           <t>WOS:000416793400161</t>
         </is>
       </c>
-      <c r="K541" t="n">
+      <c r="K599" t="n">
         <v>103</v>
       </c>
-      <c r="O541" t="n">
+      <c r="O599" t="n">
         <v>103</v>
       </c>
-      <c r="P541" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="542">
-      <c r="A542" t="inlineStr">
+      <c r="P599" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
         <is>
           <t>Who should take the responsibility? Stakeholders' power over social responsibility issues in construction projects</t>
         </is>
       </c>
-      <c r="B542" t="inlineStr">
+      <c r="B600" t="inlineStr">
         <is>
           <t>Lin, X; Ho, CMF; Shen, GQP</t>
         </is>
       </c>
-      <c r="C542" t="inlineStr">
+      <c r="C600" t="inlineStr">
         <is>
           <t>JOURNAL OF CLEANER PRODUCTION</t>
         </is>
       </c>
-      <c r="E542" t="n">
+      <c r="E600" t="n">
         <v>2017</v>
       </c>
-      <c r="F542" t="inlineStr">
+      <c r="F600" t="inlineStr">
         <is>
           <t>10.1016/j.jclepro.2017.04.007</t>
         </is>
       </c>
-      <c r="H542" t="inlineStr">
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>포함</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
         <is>
           <t>Construction projects involve multiple stakeholders with different abilities that enable them to deal with the social problems that arise during the project lifecycle. This research aims to study the dynamic stakeholder power in implementing social responsibility issues in construction projects. Empirical research among Hong Kong construction industry practitioners was conducted to investigate the powers of seven stakeholders over thirty-five social responsibility issues. The data was analyzed using two-mode social network analysis methods and processed by Netminer 4. It was found from the results that internal and external stakeholders have control in different domains pertaining to social responsibility issues, but it does not mean either group has superior power. Ranked by the power status on social responsibility issues, the seven stakeholders are classified into five hierarchies: 1) governments, developers, and main contractors; 2) district councils, 3) consultants; 4) non-government organizations; 5) end users. The dynamic nature of stakeholders' powers has been elucidated by describing the power changes in different project stages, as well as in different social responsibility dimensions. (C) 2017 Elsevier Ltd. All rights reserved.</t>
         </is>
       </c>
-      <c r="J542" t="inlineStr">
+      <c r="J600" t="inlineStr">
         <is>
           <t>WOS:000401201900031</t>
         </is>
       </c>
-      <c r="K542" t="n">
+      <c r="K600" t="n">
         <v>82</v>
       </c>
-      <c r="O542" t="n">
+      <c r="O600" t="n">
         <v>82</v>
       </c>
-      <c r="P542" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="543">
-      <c r="A543" t="inlineStr">
+      <c r="P600" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
         <is>
           <t>A Comparison of Hospice Care Research Topics between Korea and Other Countries Using Text Network Analysis</t>
         </is>
       </c>
-      <c r="B543" t="inlineStr">
+      <c r="B601" t="inlineStr">
         <is>
           <t>Eun‐Jun Park; Youngji Kim; Chan Sook Park</t>
         </is>
       </c>
-      <c r="C543" t="inlineStr">
+      <c r="C601" t="inlineStr">
         <is>
           <t>Journal of Korean Academy of Nursing</t>
         </is>
       </c>
-      <c r="D543" t="inlineStr">
+      <c r="D601" t="inlineStr">
         <is>
           <t>Korean Society of Nursing Science</t>
         </is>
       </c>
-      <c r="E543" t="inlineStr">
+      <c r="E601" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="F543" t="inlineStr">
+      <c r="F601" t="inlineStr">
         <is>
           <t>10.4040/jkan.2017.47.5.600</t>
         </is>
       </c>
-      <c r="H543" t="inlineStr">
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>포함</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
         <is>
           <t>PURPOSE: This study aimed to identify and compare hospice care research topics between Korean and international nursing studies using text network analysis. METHODS: The study was conducted in four steps: 1) collecting abstracts of relevant journal articles, 2) extracting and cleaning keywords (semantic morphemes) from the abstracts, 3) developing co-occurrence matrices and text-networks of keywords, and 4) analyzing network-related measures including degree centrality, closeness centrality, betweenness centrality, and clustering using the NetMiner program. Abstracts from 347 Korean and 1,926 international studies for the period of 1998-2016 were analyzed. RESULTS: Between Korean and international studies, six of the most important core keywords-"hospice," "patient," "death," "RNs," "care," and "family"-were common, whereas "cancer" from Korean studies and "palliative care" from international studies ranked more highly. Keywords such as "attitude," "spirituality," "life," "effect," and "meaning" for Korean studies and "communication," "treatment," "USA," and "doctor" for international studies uniquely emerged as core keywords in recent studies (2011~2016). Five subtopic groups each were identified from Korean and international studies. Two common subtopics were "hospice palliative care and volunteers" and "cancer patients." CONCLUSION: For a better quality of hospice care in Korea, it is recommended that nursing researchers focus on study topics of patients with non-cancer disease, children and family, communication, and pain and symptom management.</t>
         </is>
       </c>
-      <c r="I543" t="inlineStr">
+      <c r="I601" t="inlineStr">
         <is>
           <t>W2770863989</t>
         </is>
       </c>
-      <c r="K543" t="n">
+      <c r="K601" t="n">
         <v>33</v>
       </c>
-      <c r="N543" t="n">
+      <c r="N601" t="n">
         <v>3.1147</v>
       </c>
-      <c r="O543" t="n">
+      <c r="O601" t="n">
         <v>33</v>
       </c>
-      <c r="P543" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="544">
-      <c r="A544" t="inlineStr">
+      <c r="P601" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
         <is>
           <t>Feature network-driven quadrant mapping for summarizing customer reviews</t>
         </is>
       </c>
-      <c r="B544" t="inlineStr">
+      <c r="B602" t="inlineStr">
         <is>
           <t>Su Gon Cho &amp; Seoung Bum Kim</t>
         </is>
       </c>
-      <c r="C544" t="inlineStr">
+      <c r="C602" t="inlineStr">
         <is>
           <t>Journal of Systems Science and Systems Engineering</t>
         </is>
       </c>
-      <c r="D544" t="inlineStr">
+      <c r="D602" t="inlineStr">
         <is>
           <t>plos</t>
         </is>
       </c>
-      <c r="E544" t="inlineStr">
+      <c r="E602" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="F544" t="inlineStr">
+      <c r="F602" t="inlineStr">
         <is>
           <t>10.1007/s11518-017-5329-5</t>
         </is>
       </c>
-      <c r="H544" t="inlineStr">
+      <c r="H602" t="inlineStr">
         <is>
           <t>With the rapid growth of e-commerce, customers increasingly write online reviews of the product they purchase. These customer reviews are one of the most valuable sources of information affecting selection of products or services. Summarizing these customer reviews is becoming an interesting area of research, inspiring researchers to develop a more condensed, concise summarization for users. However, most of the current efforts at summarization are based on general product features without feature’s relationship. As a result, these summaries either ignore feedback from customers or do a poor job of reflecting the opinions expressed in customer reviews. To remedy this summarization shortcoming, we propose a feature network-driven quadrant mapping that captures and incorporates opinions from customer reviews. Our focus is on construction of a feature network, which is based on co-occurrence and sematic similarities, and a quadrant display showing the opinions polarity of feature groups. Moreover, the proposed approach involves clustering similar product features, and thus, it is different from standard text summarization based on abstraction and extraction. The summarized results can help customers better understand the overall opinions about a product.</t>
         </is>
       </c>
-      <c r="I544" t="inlineStr">
+      <c r="I602" t="inlineStr">
         <is>
           <t>W2577565335</t>
         </is>
       </c>
-      <c r="K544" t="n">
+      <c r="K602" t="n">
         <v>4</v>
       </c>
-      <c r="N544" t="n">
+      <c r="N602" t="n">
         <v>0.7361</v>
       </c>
-      <c r="O544" t="n">
+      <c r="O602" t="n">
         <v>4</v>
       </c>
-      <c r="P544" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="545">
-      <c r="A545" t="inlineStr">
+      <c r="P602" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
         <is>
           <t>사회연결망 분석을 적용한 치매 지식지도 구축</t>
         </is>
       </c>
-      <c r="B545" t="inlineStr">
+      <c r="B603" t="inlineStr">
         <is>
           <t>한정희, 염영희.</t>
         </is>
       </c>
-      <c r="C545" t="inlineStr">
+      <c r="C603" t="inlineStr">
         <is>
           <t>노인간호학회지</t>
         </is>
       </c>
-      <c r="E545" t="n">
+      <c r="E603" t="n">
         <v>2017</v>
       </c>
-      <c r="F545" t="inlineStr">
+      <c r="F603" t="inlineStr">
         <is>
           <t>10.17079/jkgn.2017.19.2.69</t>
         </is>
       </c>
-      <c r="H545" t="inlineStr">
+      <c r="H603" t="inlineStr">
         <is>
           <t>Purpose: The purpose of this descriptive study was to develop a knowledge map through a social network analysis of dementia-related articles. Methods: For 276,548 keywords from 52,225 studies on dementia, co-occurrence keywords were used to analyze the node centrality in terms of degree, closeness, betweenness, and cohesion through social network analysis. Co-occurrence words were presented using word clouds. Results: The keywords Parkinson disease, amyloid, Mild Cognition Impairment (MCI), Apolipoprotein E (ApoE), depression, tau, aged, neuropsychology, memory, and neurodegeneration demonstrated high degree centrality with regard to dementia and Alzheimer disease. When central keywords such as dementia and Alzheimer disease were excluded, aged, depression, tau, memory, cognition, MCI, Frontotemporal Dementia (FTD), cognition impairment, Parkinson disease, and diagnosis showed high degree centrality. Conclusion: The findings from this study help identify research trends and topics. They also provide information regarding various fields of research by analyzing cohesion between keywords that enable research exchange or convergence, and keywords that promote or control interaction with other keywords. This analysis can help establish research topics at the initial stages and guide researchers when identifying and selecting important nursing science topics related to dementia.</t>
         </is>
       </c>
-      <c r="L545" t="n">
+      <c r="L603" t="n">
         <v>4</v>
       </c>
-      <c r="N545" t="n">
+      <c r="N603" t="n">
         <v>0.44</v>
       </c>
-      <c r="P545" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="546">
-      <c r="A546" t="inlineStr">
+      <c r="O603" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="P603" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
         <is>
           <t>Digital Literacy Integration in Educational Practice Creating a Learning Community</t>
         </is>
       </c>
-      <c r="B546" t="inlineStr">
+      <c r="B604" t="inlineStr">
         <is>
           <t>Exarchou, E., Klonari, A., Lambrinos, N., &amp; Vaitis, M</t>
         </is>
       </c>
-      <c r="C546" t="inlineStr">
+      <c r="C604" t="inlineStr">
         <is>
           <t>Review of International Geographical Education Online</t>
         </is>
       </c>
-      <c r="D546" t="inlineStr">
+      <c r="D604" t="inlineStr">
         <is>
           <t>Through a Geographic Project in Mytilene Senior High School, Greece.</t>
         </is>
       </c>
-      <c r="E546" t="inlineStr">
+      <c r="E604" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="H546" t="inlineStr">
+      <c r="H604" t="inlineStr">
         <is>
           <t>This study focused on the analysis of Grade-12 (Senior) students' sociocultural constructivist interactions using Web 2.0 applications during a geographical research process. In the study methodology context, a transdisciplinary case study (TdCS) with ethnographic and research action data was designed, implemented and analyzed in real teaching conditions for this study. The goal of the research process was students to integrate into authentic activities that that relate to their experiences and create a learning community, developing cognitive geographic knowledge. The study reveals a need to: a) design and implement transdisciplinary actions to create more learning incentives, exchange ideas and collaborate, for the geographical science issues study, b) shape new ways of interacting and</t>
         </is>
       </c>
-      <c r="P546" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="547">
-      <c r="A547" t="inlineStr">
+      <c r="O604" t="n">
+        <v>0</v>
+      </c>
+      <c r="P604" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
         <is>
           <t>A Corpus-Based Analysis of the Near-Synonyms Safety and Security in Maritime English</t>
         </is>
       </c>
-      <c r="B547" t="inlineStr">
+      <c r="B605" t="inlineStr">
         <is>
           <t>Wenyu Lu; Se-Eun Jhang</t>
         </is>
       </c>
-      <c r="C547" t="inlineStr">
+      <c r="C605" t="inlineStr">
         <is>
           <t>Journal of Linguistic Science 83‖Dec</t>
         </is>
       </c>
-      <c r="E547" t="inlineStr">
+      <c r="E605" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="F547" t="inlineStr">
+      <c r="F605" t="inlineStr">
         <is>
           <t>10.21296/jls.2017.12.83.89</t>
         </is>
       </c>
-      <c r="H547" t="inlineStr">
+      <c r="H605" t="inlineStr">
         <is>
           <t>This study examines collocates of the near-synonyms safety and security in maritime English, drawing data from two general corpora (BNC Written and COCA Written) and one self-built specialized corpus (IMO Corpus) through Wordsmith 6.0 as well as tagging semantic domains in Wmatrix 3.0 and conducting network analysis using NetMiner 4.0. Three main discoveries were made in this study. First, the distinction of two near-synonyms used in industrial and information fields cannot be applied to maritime English, in which safety and security have clear collocational preference. Second, a brokerage analysis of some interesting shared collocates such as maritime and ship suggests that safety and security play different roles when collocating with the same collocates. Third, a semantic domain network analysis is displayed to explain how near-synonyms are both different and similar based on their common and exclusive semantic domains, thereby providing a cognitive understanding of the two near-synonyms.</t>
         </is>
       </c>
-      <c r="I547" t="inlineStr">
+      <c r="I605" t="inlineStr">
         <is>
           <t>W2790840236</t>
         </is>
       </c>
-      <c r="K547" t="n">
-        <v>0</v>
-      </c>
-      <c r="N547" t="n">
-        <v>0</v>
-      </c>
-      <c r="O547" t="n">
-        <v>0</v>
-      </c>
-      <c r="P547" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="548">
-      <c r="A548" t="inlineStr">
+      <c r="K605" t="n">
+        <v>0</v>
+      </c>
+      <c r="N605" t="n">
+        <v>0</v>
+      </c>
+      <c r="O605" t="n">
+        <v>0</v>
+      </c>
+      <c r="P605" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
         <is>
           <t>Analyzing Community Care Research Trends Using Text Mining</t>
         </is>
       </c>
-      <c r="B548" t="inlineStr">
+      <c r="B606" t="inlineStr">
         <is>
           <t>Yoonseo Park, Sewon Park, Munjea Lee</t>
         </is>
       </c>
-      <c r="C548" t="inlineStr">
+      <c r="C606" t="inlineStr">
         <is>
           <t>Journal of Multidisciplinary Healthcare 2022:15 1493–1510</t>
         </is>
       </c>
-      <c r="E548" t="inlineStr">
+      <c r="E606" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="F548" t="inlineStr">
+      <c r="F606" t="inlineStr">
         <is>
           <t>10.2147/JMDH.S366726</t>
         </is>
       </c>
-      <c r="H548" t="inlineStr">
+      <c r="H606" t="inlineStr">
         <is>
           <t>Purpose: This study utilized text mining to analyze research trends around community care, which focuses on improving patients’ 
 quality of life by lessening the financial burden on caregivers and relieving patient discomfort.
@@ -31445,690 +34826,729 @@
 medical care systems should be restructured and regional delivery systems established to make them more accessible.</t>
         </is>
       </c>
-      <c r="P548" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="549">
-      <c r="A549" t="inlineStr">
+      <c r="O606" t="n">
+        <v>0</v>
+      </c>
+      <c r="P606" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
         <is>
           <t>ICRA 2017 논문을 통한 로봇 분야 연구동향 분석</t>
         </is>
       </c>
-      <c r="B549" t="inlineStr">
+      <c r="B607" t="inlineStr">
         <is>
           <t>이석, 공경철, 정병규</t>
         </is>
       </c>
-      <c r="C549" t="inlineStr">
+      <c r="C607" t="inlineStr">
         <is>
           <t>한국정밀공학회지</t>
         </is>
       </c>
-      <c r="E549" t="inlineStr">
+      <c r="E607" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="F549" t="inlineStr">
+      <c r="F607" t="inlineStr">
         <is>
           <t>10.7736/JKSPE.020.120</t>
         </is>
       </c>
-      <c r="H549" t="inlineStr">
+      <c r="H607" t="inlineStr">
         <is>
           <t>논문 키워드 네트워크 분석, 연구자, 기관-키워드 네트워크 분석</t>
         </is>
       </c>
-      <c r="P549" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="550">
-      <c r="A550" t="inlineStr">
+      <c r="O607" t="n">
+        <v>0</v>
+      </c>
+      <c r="P607" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
         <is>
           <t>텍스트 네트워크 분석을 활용한 과학영재교육 언론동향 분석</t>
         </is>
       </c>
-      <c r="B550" t="inlineStr">
+      <c r="B608" t="inlineStr">
         <is>
           <t>박경진, 류춘렬, 최진수, 김희목</t>
         </is>
       </c>
-      <c r="C550" t="inlineStr">
+      <c r="C608" t="inlineStr">
         <is>
           <t>Journal of Gifted/Talented Education</t>
         </is>
       </c>
-      <c r="D550" t="inlineStr">
+      <c r="D608" t="inlineStr">
         <is>
           <t>한국영재학회</t>
         </is>
       </c>
-      <c r="E550" t="inlineStr">
+      <c r="E608" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="F550" t="inlineStr">
+      <c r="F608" t="inlineStr">
         <is>
           <t>10.9722/JGTE.2017.27.3.387</t>
         </is>
       </c>
-      <c r="H550" t="inlineStr">
+      <c r="H608" t="inlineStr">
         <is>
           <t>뉴스 기사와 같은 언론보도는 특정 사건과 이슈에 대한 일반 대중들의 사회적 시선을 알아볼 수 있는 주요 통로가 된다. 이런 측면에서 이 연구는 과학영재교육에 대한 사회적 시선이 어떻게 변화해 왔는지를 알아보는 것을 목적으로 한다. 이를 위하여 지난 20년간(`98~`17년)의 과학영재교육 관련 뉴스 기사 총 620개를 수집한 후 지지 및 비판 정도를 분류하였으며, 텍스트 네트워크 분석 방법을 활용하여 과학영재교육 지지 기사와 비판 기사에 사용된 핵심 키워드는 어떤 차이가 있는지 알아보았다. 분석 결과 전체적으로 과학영재교육 관련 지지 기사가 차지하는 비율(57.6%) 이 비판 기사(42.4%)보다 다소 높게 나타났다. 그러나 시간의 흐름에 따라 살펴보면 과학영재교육 관련 지지 기사의 비율은 점차 감소하는 반면, 비판 기사는 증가하는 경향을 보였다. 둘째, 과학영재교육 관련 지지 기사에서 상대적 빈도가 높은 키워드는 ‘기술’, ‘연구’, ‘국가’, ‘소프트웨어’ 등이었으며, 비판 기사에서는 ‘사교육’, ‘특목고’, ‘서울’, ‘선행학습’등이 높게 나타났다. 이와 같은 결과로 볼 때 과학영재교육 관련 지지 기사들은 기술 개발 및 연구 활동을 통해 국가발전을 위한 핵심인재 양성의 필요성을 강조한 반면, 비판 기사들은 영재교육 확대로 선행학습 등을 통한 사교육 유발을 가장 크게 우려하는 것으로 나타났다.</t>
         </is>
       </c>
-      <c r="P550" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="551">
-      <c r="A551" t="inlineStr">
+      <c r="O608" t="n">
+        <v>0</v>
+      </c>
+      <c r="P608" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
         <is>
           <t>키워드 네트워크 분석을 통한 원자력 관련 사회과학 연구경향 분석</t>
         </is>
       </c>
-      <c r="B551" t="inlineStr">
+      <c r="B609" t="inlineStr">
         <is>
           <t>김영준, 왕영민</t>
         </is>
       </c>
-      <c r="C551" t="inlineStr">
+      <c r="C609" t="inlineStr">
         <is>
           <t>기술혁신학회지</t>
         </is>
       </c>
-      <c r="D551" t="inlineStr">
+      <c r="D609" t="inlineStr">
         <is>
           <t>한국기술혁신학회</t>
         </is>
       </c>
-      <c r="E551" t="inlineStr">
+      <c r="E609" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="H551" t="inlineStr">
+      <c r="H609" t="inlineStr">
         <is>
           <t>본 연구는 사회연결망 분석이론을 통해 원자력 과학기술에 대한 사회과학 연구의 경향적 특징을 파악하고, 동 분야의 주요 연구주제와 하부 연구분야를 도출하기 위해 수행되었다. 연구대상은 1957년부터 2016년까지 국내 학술지에 게재된 원자력 관련 사회과학 분야 연구논문 605건으로, 저자가 제시한 키워드 간 관계망 형성을 통해 네트워크 분석을 수행하였다. 분석결과, 첫째 국내에서 수행된 원자력 관련 사회과학 연구의 기술통계적 특징을 확인하였다. 원자력 사회과학 연구는 1957년부터 시작되어 꾸준히 수행되어졌는데, 2011년을 기점으로 논문발표가 급격히 증가했다. 주로 법학, 행정학, 정책학, 정치학의 연구가 대학 내 연구자를 중심으로 수행되어 왔다. 원자력 관련 기술개발이 주로 정부 출연연구기관에서 수행된다는 점을 고려 했을 때, 향후 사회과학 분야에 있어 대학과 출연기관 간의 역할분담이 필요하다. 둘째, 후쿠시마 원전사고가 발생한 2011년을 기점으로 사회과학의 원자력에 관한 연구가 양적, 질적으로 본격적으로 활성화 되었다. 원자력 관련 사회과학 지식 네트워크는 2011년 이전에 비해 규모면에서 큰 차이를 보였다. 또한, 네트워크 중심성 분석결과, 후쿠시마 사고 이전 사회과학 연구자들의 연구경향은 핵비확산, 과학기술 정책, 사회수용성이었다면, 후쿠시마 이후에는 원전해체, 손해배상, 에너지믹스, 탈핵운동 등과 같은 다양한 원자력 현안으로 확대되었다. 셋째, 하부 연구분야 도출을 통해 특정 연구주제별 쏠림현상을 확인했다. 하부 네트워크 분석 결과, 제시된 9개의 하부 연구분야는 네트워크 속성 값에서 차이를 보였다. 특히, 법학 관련 연구주제가 가장 높은 밀도를 갖는 반면 지속가능 발전과 에너지 믹스 관련 연구주제의 밀도가 가장 낮게 나타났다. 본 연구는 원자력에 관련된 학자의 인식을 연구경향 분석을 통해 파악한다는 점에서 의의가 있으며, 이는 추후 원자력 관련 정책연구자 혹은 정책결정자에게 유용한 기초자료를 제공할 것이라 기대된다.</t>
         </is>
       </c>
-      <c r="P551" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="552">
-      <c r="A552" t="inlineStr">
+      <c r="O609" t="n">
+        <v>0</v>
+      </c>
+      <c r="P609" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
         <is>
           <t>텍스트 네트워크 분석을 활용한 해상테러의 연구동향 및 시사점</t>
         </is>
       </c>
-      <c r="B552" t="inlineStr">
+      <c r="B610" t="inlineStr">
         <is>
           <t>윤병훈, 공태명</t>
         </is>
       </c>
-      <c r="C552" t="inlineStr">
+      <c r="C610" t="inlineStr">
         <is>
           <t>한국민간경비학회보</t>
         </is>
       </c>
-      <c r="E552" t="inlineStr">
+      <c r="E610" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="H552" t="inlineStr">
+      <c r="H610" t="inlineStr">
         <is>
           <t>우리나라는 지정학적 위치뿐만 아니라 남북 분단의 현실에서 국가안보적 측면에서는 물론 국민의 안전이라는 측면에서도 테러의 위험이 존재한다. 이 연구에서는 테러의 유형 중에서도 특히 해상테러에 중점을 두고 기존의 해상테러에 대한 연구동향을 텍스트 네트워크 분석 방법을 통해 살펴보았다. 해상테러의 연구동향을 확인하기 위해 한국교육학술정보원(KERIS)을 이용하여 검색된 60편의 학술논문을 이연구의 분석자료로 활용하였다. KwKwic, NetMiner 4.0 프로그램을 활용하여 해상테러 관련 연구들의 키워드를 파악하고 각각의 키워드들 간의 밀도, 연결선의 수, 중앙성 지표 등을 구하고 최종적으로 연결망 그래프 등을 통해 해상테러의 연구동향을 시각화 하였다. 분석결과 "해적", "해상테러", "테러리즘", "유엔해양법협약", "해상무장강도", "해상운송", "국제해사기구", "대량살상무기" 등의 순으로 빈도를 확인할 수 있었고, 해상테러 관련 연구동향에 있어 "해적"이라는 단어가 국내 해상테러 관련 연구에 있어 가장 핵심 단어로 도출되었다. 텍스트 네트워크 분석을 활용하여 해상테러의 연구 동향을 확인한 결과, 국내의 해상테러에 대한 연구동향은 주로 해적을 중심으로 해적행위에 대한 안전이나 보안적 측면을 강조한 정책적 연구와 더불어 유엔해양법협약이나 SUA 협약 등 국제조약에 비춰 국내 해상테러의 대응책에 대한 연구가 주를 이루고 있는 것으로 확인하였다. 이러한 연구 결과를 바탕으로 두 가지 시사점을 도출하였다. 첫째, 체계적인 해상테러 예방 및 대응을 위하여 해상테러 대비 교육훈련 및 대응지침 등에 대한 연구가 필요하다는 것이다. 둘째, 우리나라의 해상테러 연구 동향을 살펴본 결과 대부분 법 해석이나 문헌연구에 그치고 있어 해상테러에 대한 데이터베이스의 구축마련이 필요하다는 점이다.</t>
         </is>
       </c>
-      <c r="P552" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="553">
-      <c r="A553" t="inlineStr">
+      <c r="O610" t="n">
+        <v>0</v>
+      </c>
+      <c r="P610" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
         <is>
           <t>사회네트워크 분석법을 활용한 중등교사들의 융합 및 융합교육에 대한 인식 탐색</t>
         </is>
       </c>
-      <c r="B553" t="inlineStr">
+      <c r="B611" t="inlineStr">
         <is>
           <t>신세인,이준기</t>
         </is>
       </c>
-      <c r="C553" t="inlineStr">
+      <c r="C611" t="inlineStr">
         <is>
           <t>융합교육연구</t>
         </is>
       </c>
-      <c r="E553" t="n">
+      <c r="E611" t="n">
         <v>2017</v>
       </c>
-      <c r="H553" t="inlineStr">
+      <c r="H611" t="inlineStr">
         <is>
           <t>이 연구는 중등교사들이 생각하는 융합 및 융합교육에 대한 인식을 파악하는데 그목적이 있다. 연구목적 달성을 위하여 한국교원대학교 융합교육연구소에서 실시하는 융합교육 연수에 참여한 총 254명이 참여하였다. 이 연구에서는 교사들의 융합 및 융합 교육 프로그램에 대한 인식 자료를 수집하였다. 이를 위해 첫째, 융합의 의미, 둘째, 융합 프로그램의 목적, 셋째, 융합 프로그램의 장점, 넷째, 융합 프로그램의 단점에 대하여 묻는 4개의 서술형 문항을 온라인 설문조사를 통해 수집하였다. 수집된 비정형 언어 자료들은 사회네트워크분석법을 통하여 분석하였다. 연구결과, 첫째, 융합의 의미에 대해서는 특정 주제와 관련된 학습 요소들이나 다양한 교과 및 분야의 지식을 통합하고 연계하는 것으로 인식하였고, 둘째, 융합 프로그램의 목적에 대해서는 사회에서 요구하는 인재양성을 위해 학생들의 다양하고 창의적인 사고력과 문제해결력을 함양시키는것으로 인식하였고, 셋째, 융합 프로그램의 장점에 대해서는 수업의 다양성을 통해 학생들의 수업에 대한 흥미를 유발할 수 있다는 점과 교과 간의 협력을 바탕으로 지식의 통합적 접근을 시도해 학생들의 창의적 사고와 문제해결력, 사고력을 확장시킨다는 점으로 인식하였으며, 넷째, 융합 프로그램의 단점으로는 교사의 입장에서 교과의 운영과재구성에 대한 문제, 교과의 기초적인 지식 함양이 어려워 전문성이 부족해질 수 있다는 점, 실질적 수업 진행의 어려움, 수업 준비에 많은 노력이 필요하다는 점, 융합프로 그램의 개발과 관련된 어려움, 다양한 교사 간 협력과 협동의 어려움, 학생 수준과 관련된 어려움으로 인식하고 있었다.</t>
         </is>
       </c>
-      <c r="P553" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="554">
-      <c r="A554" t="inlineStr">
+      <c r="O611" t="n">
+        <v>0</v>
+      </c>
+      <c r="P611" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
         <is>
           <t>Identifying product opportunities using collaborative filtering-based patent analysis</t>
         </is>
       </c>
-      <c r="B554" t="inlineStr">
+      <c r="B612" t="inlineStr">
         <is>
           <t>Janghyeok Yoon; Wonchul Seo; Byoung‐Youl Coh; Inseok Song; Jae-Min Lee</t>
         </is>
       </c>
-      <c r="C554" t="inlineStr">
+      <c r="C612" t="inlineStr">
         <is>
           <t>Computers &amp; Industrial Engineering</t>
         </is>
       </c>
-      <c r="D554" t="inlineStr">
+      <c r="D612" t="inlineStr">
         <is>
           <t>Elsevier</t>
         </is>
       </c>
-      <c r="E554" t="inlineStr">
+      <c r="E612" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="F554" t="inlineStr">
+      <c r="F612" t="inlineStr">
         <is>
           <t>10.1016/j.cie.2016.04.009</t>
         </is>
       </c>
-      <c r="I554" t="inlineStr">
+      <c r="I612" t="inlineStr">
         <is>
           <t>W2341522766</t>
         </is>
       </c>
-      <c r="K554" t="n">
+      <c r="K612" t="n">
         <v>80</v>
       </c>
-      <c r="N554" t="n">
+      <c r="N612" t="n">
         <v>13.7236</v>
       </c>
-      <c r="O554" t="n">
+      <c r="O612" t="n">
         <v>80</v>
       </c>
-      <c r="P554" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="555">
-      <c r="A555" t="inlineStr">
+      <c r="P612" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
         <is>
           <t>Collective Action that Influences Tourism Social Structural Approach To Community Involvement</t>
         </is>
       </c>
-      <c r="B555" t="inlineStr">
+      <c r="B613" t="inlineStr">
         <is>
           <t>Doohyun Hwang; Sang-Hyun Chi; Byeongcheol Lee</t>
         </is>
       </c>
-      <c r="C555" t="inlineStr">
+      <c r="C613" t="inlineStr">
         <is>
           <t>Journal of Hospitality &amp; Tourism Research</t>
         </is>
       </c>
-      <c r="D555" t="inlineStr">
+      <c r="D613" t="inlineStr">
         <is>
           <t>Sage</t>
         </is>
       </c>
-      <c r="E555" t="inlineStr">
+      <c r="E613" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="F555" t="inlineStr">
+      <c r="F613" t="inlineStr">
         <is>
           <t>10.1177/1096348013503999</t>
         </is>
       </c>
-      <c r="H555" t="inlineStr">
+      <c r="H613" t="inlineStr">
         <is>
           <t>The purpose of this study is to explore the influence of the relational structure of a community on tourism-related community collective action. Employing social network analysis and interviews, the network structure and community collective actions were examined at two communities on Jeju Island, South Korea. The research results demonstrate positive associations between successful collective action involvement and features from the relational network structure in communities, such as network density and social pressure related to social roles. The findings can be used to identify specific types of community network structure that facilitates an individual’s tourism related collective action involvement.</t>
         </is>
       </c>
-      <c r="I555" t="inlineStr">
+      <c r="I613" t="inlineStr">
         <is>
           <t>W2041278174</t>
         </is>
       </c>
-      <c r="K555" t="n">
+      <c r="K613" t="n">
         <v>22</v>
       </c>
-      <c r="N555" t="n">
+      <c r="N613" t="n">
         <v>0.9577</v>
       </c>
-      <c r="O555" t="n">
+      <c r="O613" t="n">
         <v>22</v>
       </c>
-      <c r="P555" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="556">
-      <c r="A556" t="inlineStr">
+      <c r="P613" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
         <is>
           <t>2016 Year-in-Review of Clinical and Consumer Informatics: Analysis and Visualization of Keywords and Topics</t>
         </is>
       </c>
-      <c r="B556" t="inlineStr">
+      <c r="B614" t="inlineStr">
         <is>
           <t>Hyeoun‐Ae Park; Joo Yun Lee; Jeongah On; Ji Hyun Lee; Hyesil Jung; Seul Ki Park</t>
         </is>
       </c>
-      <c r="C556" t="inlineStr">
+      <c r="C614" t="inlineStr">
         <is>
           <t>journal of the Korean Society of Medical Informatics</t>
         </is>
       </c>
-      <c r="D556" t="inlineStr">
+      <c r="D614" t="inlineStr">
         <is>
           <t>the Korean Society of</t>
         </is>
       </c>
-      <c r="E556" t="inlineStr">
+      <c r="E614" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="F556" t="inlineStr">
+      <c r="F614" t="inlineStr">
         <is>
           <t>10.4258/hir.2017.23.2.77</t>
         </is>
       </c>
-      <c r="H556" t="inlineStr">
+      <c r="H614" t="inlineStr">
         <is>
           <t>OBJECTIVES: , an official journal of the Korean Society of Medical Informatics. METHODS: A six-person team conducted an extensive review of the literature on clinical and consumer informatics. The literature was searched using keywords employed in the American Medical Informatics Association year-in-review process and organized into 14 topics used in that process. Data were analyzed using word clouds, social network analysis, and association rules. RESULTS: , followed by 'telecommunications' (4.5%). Telemedicine (47.1%) was the most frequently studied topic area, followed by EHR (14.7%). CONCLUSIONS: The study findings reflect the Korean government's efforts to introduce telemedicine into the Korean healthcare system and reactions to this from the stakeholders associated with telemedicine.</t>
         </is>
       </c>
-      <c r="I556" t="inlineStr">
+      <c r="I614" t="inlineStr">
         <is>
           <t>W2614233833</t>
         </is>
       </c>
-      <c r="K556" t="n">
+      <c r="K614" t="n">
         <v>9</v>
       </c>
-      <c r="N556" t="n">
+      <c r="N614" t="n">
         <v>0.7188</v>
       </c>
-      <c r="O556" t="n">
+      <c r="O614" t="n">
         <v>9</v>
       </c>
-      <c r="P556" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="557">
-      <c r="A557" t="inlineStr">
+      <c r="P614" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
         <is>
           <t>Information Technology in Education Some Reasons for Optimism</t>
         </is>
       </c>
-      <c r="B557" t="inlineStr">
+      <c r="B615" t="inlineStr">
         <is>
           <t>Cleborne D. Maddux; D. LaMont Johnson</t>
         </is>
       </c>
-      <c r="C557" t="inlineStr">
+      <c r="C615" t="inlineStr">
         <is>
           <t>Computers in the Schools</t>
         </is>
       </c>
-      <c r="D557" t="inlineStr">
+      <c r="D615" t="inlineStr">
         <is>
           <t>Taylor &amp; Francis</t>
         </is>
       </c>
-      <c r="E557" t="inlineStr">
+      <c r="E615" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="F557" t="inlineStr">
+      <c r="F615" t="inlineStr">
         <is>
           <t>10.1080/07380560902906179</t>
         </is>
       </c>
-      <c r="H557" t="inlineStr">
+      <c r="H615" t="inlineStr">
         <is>
           <t>Abstract This article identifies three innovations with great promise for improving the use of information technology in education. The Semantic Web, discourse analysis, and social network analysis are briefly described, and their potential contributions to education are highlighted. Two articles in this issue are identified as highly meritorious in promoting the integration of information technology in education.</t>
         </is>
       </c>
-      <c r="I557" t="inlineStr">
+      <c r="I615" t="inlineStr">
         <is>
           <t>W1987658525</t>
         </is>
       </c>
-      <c r="K557" t="n">
+      <c r="K615" t="n">
         <v>5</v>
       </c>
-      <c r="N557" t="n">
+      <c r="N615" t="n">
         <v>2.246</v>
       </c>
-      <c r="O557" t="n">
+      <c r="O615" t="n">
         <v>5</v>
       </c>
-      <c r="P557" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="558">
-      <c r="A558" t="inlineStr">
+      <c r="P615" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
         <is>
           <t>Fundamentals of Big Data Network Analysis for Research and Industry</t>
         </is>
       </c>
-      <c r="B558" t="inlineStr">
+      <c r="B616" t="inlineStr">
         <is>
           <t>Hyunjoung Lee, Il Sohn</t>
         </is>
       </c>
-      <c r="D558" t="inlineStr">
+      <c r="D616" t="inlineStr">
         <is>
           <t>John Wiley &amp; Sons, 2015</t>
         </is>
       </c>
-      <c r="E558" t="n">
+      <c r="E616" t="n">
         <v>2016</v>
       </c>
-      <c r="P558" t="inlineStr">
+      <c r="O616" t="n">
+        <v>0</v>
+      </c>
+      <c r="P616" t="inlineStr">
         <is>
           <t>소개</t>
         </is>
       </c>
     </row>
-    <row r="559">
-      <c r="A559" t="inlineStr">
+    <row r="617">
+      <c r="A617" t="inlineStr">
         <is>
           <t>한국무용전공 대학생의 교우관계 네트워크 특성: 사회 연결망분석</t>
         </is>
       </c>
-      <c r="B559" t="inlineStr">
+      <c r="B617" t="inlineStr">
         <is>
           <t>차은주(EunJooCha), 김영재(YoungJaeKim)</t>
         </is>
       </c>
-      <c r="C559" t="inlineStr">
+      <c r="C617" t="inlineStr">
         <is>
           <t>한국체육학회</t>
         </is>
       </c>
-      <c r="E559" t="n">
+      <c r="E617" t="n">
         <v>2016</v>
       </c>
-      <c r="H559" t="inlineStr">
+      <c r="H617" t="inlineStr">
         <is>
           <t>이 연구의 목적은 한국무용전공 대학생들의 전공 내 교우관계 네트워크의 특성을 사회 연결망 분석(social networkanalysis)방법을 이용하여 파악하는 것이다. 이를 위해 서울에 위치한 A대학교 한국무용전공생 22명을 대상으로 설문을 실시하여 자료를 수집하였다. 수집된 자료의 분석을 위해 NetMiner 4 프로그램을 이용하여 중앙성 분석, 매개중앙성 분석, 근접중앙성 분석, 컴포넌트 분석, 파당분석을 실시하였다. 그 결과 첫째, 한국무용전공 대학생의 교우관계 네트워크는 특정학생에게 집중되는 마당발은 없었으며 외톨이도 없는 것으로 나타났다. 또한 연결망의 유기적인관계성이 없는 것으로 나타났으며 한 집단이 두 집단과 연결성이 전혀 없는 것으로 나타났고 나머지 두 집단 간의연결정도는 매우 약했다. 둘째, 한국무용전공 대학생의 집단의 구조를 살펴보면 연결망에는 2개의 그룹이 존재하는것으로 나타났으며 직접적인 연결성을 가진 그룹은 7개로 나타났고 각 그룹 간의 결속력이 높았다. 이러한 결과를 토대로 한국무용전공 대학생의 교우관계는 상호 연계적이지 못하고 경쟁관계를 맺고 있는 것으로 파악되었으며 교우관계 개선을 위한 지도자의 노력과 필요성이 논의되었다.</t>
         </is>
       </c>
-      <c r="P559" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="560">
-      <c r="A560" t="inlineStr">
+      <c r="O617" t="n">
+        <v>0</v>
+      </c>
+      <c r="P617" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
         <is>
           <t>Schedule risks in prefabrication housing production in Hong Kong a social network analysis</t>
         </is>
       </c>
-      <c r="B560" t="inlineStr">
+      <c r="B618" t="inlineStr">
         <is>
           <t>Clyde Zhengdao Li, Jingke Hong, Fan Xue, Geoffrey Qiping Shen, Xiaoxiao Xu, Margaret Kayan Mok</t>
         </is>
       </c>
-      <c r="C560" t="inlineStr">
+      <c r="C618" t="inlineStr">
         <is>
           <t>Journal of Cleaner Production</t>
         </is>
       </c>
-      <c r="D560" t="inlineStr">
+      <c r="D618" t="inlineStr">
         <is>
           <t>Elsevier</t>
         </is>
       </c>
-      <c r="E560" t="inlineStr">
+      <c r="E618" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="F560" t="inlineStr">
+      <c r="F618" t="inlineStr">
         <is>
           <t>10.1016/j.jclepro.2016.02.123</t>
         </is>
       </c>
-      <c r="H560" t="inlineStr">
+      <c r="H618" t="inlineStr">
         <is>
           <t>Various schedule risks beset prefabrication housing production (PHP) in Hong Kong throughout the prefabrication supply chain, from design, manufacturing, logistics, to on-site assembly. Previous research on the risks in prefabrication construction projects has mainly focused on the construction stage and has been confined to issues of completeness and accuracy without consideration of stakeholder-related risks and their cause-and-effect relationships. However, in reality, the supply chain is inseparable as precast components should be manufactured and transported to sites to fit in with the schedule of on-site assembly in seamless connection manner, and most risks are interrelated and associated with various stakeholders. This study applies social network analysis (SNA) to recognize and investigate the underlying network of stakeholder-associated risk factors in prefabrication housing construction projects. Critical risks and relationships that have important roles in structuring the entire network of PHP are identified and analyzed. BIM (Building Information Modeling)-centered strategies are proposed to facilitate stakeholder communication and mitigate critical schedule risks and interactions underlying the risk network. This study not only provides an effective method to analyze stakeholder-associated risk factors and to evaluate the effect of these risk factors from a network perspective, but also offers a new visual perspective in the promotion of the use of the Internet of things (IoT) and helps identify housing construction problems in Hong Kong.</t>
         </is>
       </c>
-      <c r="P560" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="561">
-      <c r="A561" t="inlineStr">
+      <c r="O618" t="n">
+        <v>0</v>
+      </c>
+      <c r="P618" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
         <is>
           <t>한국 문화사회학 연구의 구조와 흐름: 2006-2015 문화와 사회 게재 논문들의 저자 분석과 키워드 네트워크 분석을 중심으로</t>
         </is>
       </c>
-      <c r="B561" t="inlineStr">
+      <c r="B619" t="inlineStr">
         <is>
           <t>박근영</t>
         </is>
       </c>
-      <c r="C561" t="inlineStr">
+      <c r="C619" t="inlineStr">
         <is>
           <t>Korean Journal of Cultural Sociology</t>
         </is>
       </c>
-      <c r="E561" t="inlineStr">
+      <c r="E619" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="F561" t="inlineStr">
+      <c r="F619" t="inlineStr">
         <is>
           <t>10.17328/kjcs.2016.20..003</t>
         </is>
       </c>
-      <c r="H561" t="inlineStr">
+      <c r="H619" t="inlineStr">
         <is>
           <t>본 연구는 지난 10년간 한국문화사회학의 논문 생산의 주체는 누구였으며 그들의 주요 관심사는 무엇이었는지 파악하는 것을 목적으로 한다. 2006년부터 2015년까지 발행된 한국문화사회학회의 공식 학술지 『문화와 사회』 게재 논문의 저자와 키워드를 대상으로 일반 기술통계 및 네트워크 분석을 수행하였으며, 이를 바탕으로 문화사회학의 논문 생산 주체와 그들의 관심사 변화를 추적하였다. 분석 결과 다음과 같은 경향을 발견할 수 있었다. 첫째, 초기『문화와 사회』는 소수 저자들에 대한 의존도가 높았지만 최근 들어 저자 및 그들 소속 기관의 다양화가 이루어졌다. 둘째, 초기 『문화와 사회』의 주요 관심사는 문화사회학의 정체성을 정립하려는 몇몇 특정 주제에 상당히 편중된 모습을 보였지만, 최근 들어 주제의 집중도는 떨어지는 대신 보다 포괄적인 영역으로 관심사를 확대하는 보습을 보이고 있다. 이러한 결과를 근거로 본 논문은 『문화와 사회』가 학문적인 중심과 정체성을 성공적으로 확립하였으며, 전형적인 학술지 설립 초기의 어려움을 극복하고 안정화의 단계로 진입하고 있다고 평가한다.</t>
         </is>
       </c>
-      <c r="P561" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="562">
-      <c r="A562" t="inlineStr">
+      <c r="O619" t="n">
+        <v>0</v>
+      </c>
+      <c r="P619" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
         <is>
           <t>The review of social networks analysis tools</t>
         </is>
       </c>
-      <c r="B562" t="inlineStr">
+      <c r="B620" t="inlineStr">
         <is>
           <t>Safashahr Branch; Islamic Azad</t>
         </is>
       </c>
-      <c r="C562" t="inlineStr">
+      <c r="C620" t="inlineStr">
         <is>
           <t>Royale des Sciences de Liège</t>
         </is>
       </c>
-      <c r="E562" t="inlineStr">
+      <c r="E620" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="F562" t="inlineStr">
+      <c r="F620" t="inlineStr">
         <is>
           <t>10.25518/0037-9565.5380</t>
         </is>
       </c>
-      <c r="H562" t="inlineStr">
+      <c r="H620" t="inlineStr">
         <is>
           <t>Social networks can include anything ranging from family, friends, classes, objects and other similar cases, important and effective members, members of exception, the formation of such networks can be discovered by using the relationships between the members of the network which are important to business and research works, to achieve these cases , social networks should be analyzed using special tools. Social network analysis tools generally includes two packaged based on graphical user interfaces (GUIs) and packages made for programming / scripting. These tools are powerful and extensible and are able to analyze big data networks and visualize networks, isolated or central data and other important data can be simply discovered by data visualization. In this paper, some of the most important tools of social network analysis are presented and compared according to some their capabilities.</t>
         </is>
       </c>
-      <c r="P562" t="inlineStr">
+      <c r="O620" t="n">
+        <v>0</v>
+      </c>
+      <c r="P620" t="inlineStr">
         <is>
           <t>소개</t>
         </is>
       </c>
     </row>
-    <row r="563">
-      <c r="A563" t="inlineStr">
+    <row r="621">
+      <c r="A621" t="inlineStr">
         <is>
           <t>사회연결망분석을 통한 샐러드 구매자 유형 및 구매행태 분석</t>
         </is>
       </c>
-      <c r="B563" t="inlineStr">
+      <c r="B621" t="inlineStr">
         <is>
           <t>Ji Young Ha; Se Hwa Lim</t>
         </is>
       </c>
-      <c r="C563" t="inlineStr">
+      <c r="C621" t="inlineStr">
         <is>
           <t>Journal of the Korean society for quality management</t>
         </is>
       </c>
-      <c r="E563" t="inlineStr">
+      <c r="E621" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="F563" t="inlineStr">
+      <c r="F621" t="inlineStr">
         <is>
           <t>10.7469/JKSQM.2022.50.2.287</t>
         </is>
       </c>
-      <c r="H563" t="inlineStr">
+      <c r="H621" t="inlineStr">
         <is>
           <t>Purpose: The size of the salad consumption market has expanded since Covid‐19, and continuous growth is predicted. Therefore, by extracting influential core purchasers in the salad consumption market and analyzing their purchasing behaviors and consumer types, this study intended to provide basic data for establishing a marketing strategy.Methods: The analysis data is the purchasing data of 576 people who have purchased salads between 2016 and 2020 (panel data of the Rural Development Administration), and in the social network analysis, the centrality structure was analyzed.Results: First, in the results of analyzing the causes of the rapid increase in salad consumption in 2020, it was found that the increase in consumption of new purchasers (n=102) had little effect. The existing consumer type (n = 474), which has been the majority of the salad consumption market so far, were consumers with stable income. However, the results of study indicated that the type of consumers has expanded since low-income class as well as high-income class increased consumption of purchasing salad. Second, in the results of analyzing the types of key purchasers with great influence in the salad consumption market, there was a difference from the results of frequency analysis in age, number of family members, existence/absence of children, and income decile. This suggests that there should be a difference between the type of customers according to the apparent quantitative figure and the actual influential purchasers. Third, in the results of analyzing the salad purchasing behaviors of core purchasers, the purchasing site for existing purchasers was large‐scale marts and for new purchasers it was corporate‐type supermarkets. Purchases were concentrated on Saturdays for both existing and new purchasers. As for the purchased products, existing purchasers had a high preference for products made of chicken, and new purchasers had a high preference for vegetable/fruit salad. In particular, in the results of purchased products by age group, in the case of 50s and 60s, it was an interesting result that there was a difference between the products purchased by the existing and new purchasers even though they were the same age.Conclusion: When establishing a marketing strategy in the salad consumption market, it is necessary to pay attention to the purchasing behavior of key buyers.</t>
         </is>
       </c>
-      <c r="I563" t="inlineStr">
+      <c r="I621" t="inlineStr">
         <is>
           <t>W7135081421</t>
         </is>
       </c>
-      <c r="K563" t="n">
-        <v>0</v>
-      </c>
-      <c r="N563" t="n">
-        <v>0</v>
-      </c>
-      <c r="O563" t="n">
-        <v>0</v>
-      </c>
-      <c r="P563" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="564">
-      <c r="A564" t="inlineStr">
+      <c r="K621" t="n">
+        <v>0</v>
+      </c>
+      <c r="N621" t="n">
+        <v>0</v>
+      </c>
+      <c r="O621" t="n">
+        <v>0</v>
+      </c>
+      <c r="P621" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
         <is>
           <t>2016년 상반기 IP TREND MAP 분석보고서</t>
         </is>
       </c>
-      <c r="B564" t="inlineStr">
+      <c r="B622" t="inlineStr">
         <is>
           <t>한국지식재산연구원 정책연구팀</t>
         </is>
       </c>
-      <c r="C564" t="inlineStr">
+      <c r="C622" t="inlineStr">
         <is>
           <t>한국지식재산연구원</t>
         </is>
       </c>
-      <c r="E564" t="inlineStr">
+      <c r="E622" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="H564" t="inlineStr">
+      <c r="H622" t="inlineStr">
         <is>
           <t>키워드 네트워크</t>
         </is>
       </c>
-      <c r="P564" t="inlineStr">
-        <is>
-          <t>활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="565">
-      <c r="A565" t="inlineStr">
+      <c r="O622" t="n">
+        <v>0</v>
+      </c>
+      <c r="P622" t="inlineStr">
+        <is>
+          <t>활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
         <is>
           <t>R&amp;D 기획 기반 조성을 위한 로봇분야 기술‧시장‧정책 동향 분석</t>
         </is>
       </c>
-      <c r="B565" t="inlineStr">
+      <c r="B623" t="inlineStr">
         <is>
           <t>기술정책연구실</t>
         </is>
       </c>
-      <c r="C565" t="inlineStr">
+      <c r="C623" t="inlineStr">
         <is>
           <t>ETRI</t>
         </is>
       </c>
-      <c r="E565" t="inlineStr">
+      <c r="E623" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="H565" t="inlineStr">
+      <c r="H623" t="inlineStr">
         <is>
           <t>연구 동향: 기술 네트워크</t>
         </is>
       </c>
-      <c r="P565" t="inlineStr">
+      <c r="O623" t="n">
+        <v>0</v>
+      </c>
+      <c r="P623" t="inlineStr">
         <is>
           <t>활용</t>
         </is>
